--- a/data/historial/2026-06-29.xlsx
+++ b/data/historial/2026-06-29.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C2209C-4B48-4D64-B086-EFFC7758B20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46301E67-CF20-40EA-9E6F-8156488F32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="231">
   <si>
     <t>GOMEZ MARTÍN</t>
   </si>
@@ -755,6 +755,12 @@
   </si>
   <si>
     <t>GONZALO</t>
+  </si>
+  <si>
+    <t>26 - PUJOL ERNESTO</t>
+  </si>
+  <si>
+    <t>30 - GOMEZ MARTÍN</t>
   </si>
 </sst>
 </file>
@@ -1831,7 +1837,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1973,9 +1979,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="18" fillId="34" borderId="25" xfId="47" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2002,6 +2005,10 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="34" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="138">
@@ -2474,7 +2481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
@@ -2488,990 +2495,1094 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="97" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="87" t="s">
+      <c r="C1" s="97" t="s">
         <v>148</v>
       </c>
-      <c r="D1" s="87" t="s">
+      <c r="D1" s="97" t="s">
         <v>149</v>
       </c>
-      <c r="E1" s="87" t="s">
+      <c r="E1" s="97" t="s">
         <v>150</v>
       </c>
-      <c r="F1" s="87" t="s">
+      <c r="F1" s="97" t="s">
         <v>151</v>
       </c>
-      <c r="G1" s="87" t="s">
+      <c r="G1" s="97" t="s">
         <v>152</v>
       </c>
-      <c r="H1" s="87" t="s">
+      <c r="H1" s="97" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="96" t="s">
         <v>154</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>2833.8917890185999</v>
-      </c>
-      <c r="D2">
-        <v>17845.0831506539</v>
-      </c>
-      <c r="E2">
-        <v>64466959.741401754</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>72294.260573036299</v>
-      </c>
-      <c r="H2">
-        <v>72294.23</v>
+      <c r="B2" s="96">
+        <v>0</v>
+      </c>
+      <c r="C2" s="96">
+        <v>6558.7795207961999</v>
+      </c>
+      <c r="D2" s="96">
+        <v>33249.429086679302</v>
+      </c>
+      <c r="E2" s="96">
+        <v>131472225.13729897</v>
+      </c>
+      <c r="F2" s="96">
+        <v>0</v>
+      </c>
+      <c r="G2" s="96">
+        <v>110010.710440881</v>
+      </c>
+      <c r="H2" s="96">
+        <v>110010.71</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="96" t="s">
         <v>81</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="96">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>69.3782903436</v>
-      </c>
-      <c r="D3">
-        <v>127.8257233814</v>
-      </c>
-      <c r="E3">
-        <v>2409808.6857678718</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>72294.260573036299</v>
-      </c>
-      <c r="H3">
-        <v>72294.23</v>
+      <c r="C3" s="96">
+        <v>116.7140046289</v>
+      </c>
+      <c r="D3" s="96">
+        <v>405.59822338279997</v>
+      </c>
+      <c r="E3" s="96">
+        <v>3667023.6813626946</v>
+      </c>
+      <c r="F3" s="96">
+        <v>0</v>
+      </c>
+      <c r="G3" s="96">
+        <v>110010.710440881</v>
+      </c>
+      <c r="H3" s="96">
+        <v>110010.71</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="96" t="s">
         <v>82</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="96">
         <v>1</v>
       </c>
-      <c r="C4">
-        <v>10.483333332999999</v>
-      </c>
-      <c r="D4">
-        <v>57.009999999599998</v>
-      </c>
-      <c r="E4">
-        <v>910195.66733517474</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
+      <c r="C4" s="96">
+        <v>41.587301587100001</v>
+      </c>
+      <c r="D4" s="96">
+        <v>105.26750000059999</v>
+      </c>
+      <c r="E4" s="96">
+        <v>1647814.3144255385</v>
+      </c>
+      <c r="F4" s="96">
+        <v>0</v>
+      </c>
+      <c r="G4" s="96">
+        <v>0</v>
+      </c>
+      <c r="H4" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="96" t="s">
         <v>83</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="96">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>27.2044642856</v>
-      </c>
-      <c r="D5">
-        <v>28.252499999800001</v>
-      </c>
-      <c r="E5">
-        <v>501148.95527489512</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="C5" s="96">
+        <v>58.938888888800001</v>
+      </c>
+      <c r="D5" s="96">
+        <v>198.29750000160001</v>
+      </c>
+      <c r="E5" s="96">
+        <v>1318807.9914469167</v>
+      </c>
+      <c r="F5" s="96">
+        <v>0</v>
+      </c>
+      <c r="G5" s="96">
+        <v>0</v>
+      </c>
+      <c r="H5" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="96" t="s">
         <v>84</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="96">
         <v>1</v>
       </c>
-      <c r="C6">
-        <v>150.14464285720001</v>
-      </c>
-      <c r="D6">
-        <v>414.1002500029</v>
-      </c>
-      <c r="E6">
-        <v>2772298.6238154541</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
+      <c r="C6" s="96">
+        <v>280.46388888860002</v>
+      </c>
+      <c r="D6" s="96">
+        <v>845.98667857580006</v>
+      </c>
+      <c r="E6" s="96">
+        <v>4892925.4103550436</v>
+      </c>
+      <c r="F6" s="96">
+        <v>0</v>
+      </c>
+      <c r="G6" s="96">
+        <v>0</v>
+      </c>
+      <c r="H6" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="96" t="s">
         <v>85</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="96">
         <v>1</v>
       </c>
-      <c r="C7">
-        <v>60.1561309521</v>
-      </c>
-      <c r="D7">
-        <v>287.27250000409998</v>
-      </c>
-      <c r="E7">
-        <v>1318036.6824969184</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="C7" s="96">
+        <v>111.15117063460001</v>
+      </c>
+      <c r="D7" s="96">
+        <v>444.78250000499997</v>
+      </c>
+      <c r="E7" s="96">
+        <v>2332273.4502824824</v>
+      </c>
+      <c r="F7" s="96">
+        <v>0</v>
+      </c>
+      <c r="G7" s="96">
+        <v>0</v>
+      </c>
+      <c r="H7" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="96" t="s">
         <v>111</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="96">
         <v>1</v>
       </c>
-      <c r="C8">
-        <v>-6.6666666599999994E-2</v>
-      </c>
-      <c r="D8">
-        <v>-1.4759999986000001</v>
-      </c>
-      <c r="E8">
-        <v>-41520.785791812603</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+      <c r="C8" s="96">
+        <v>-63.0666666666</v>
+      </c>
+      <c r="D8" s="96">
+        <v>-561.47599999859995</v>
+      </c>
+      <c r="E8" s="96">
+        <v>-974804.98299181263</v>
+      </c>
+      <c r="F8" s="96">
+        <v>0</v>
+      </c>
+      <c r="G8" s="96">
+        <v>0</v>
+      </c>
+      <c r="H8" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="96">
         <v>1</v>
       </c>
-      <c r="C9">
-        <v>27.2205357144</v>
-      </c>
-      <c r="D9">
-        <v>123.7474999998</v>
-      </c>
-      <c r="E9">
-        <v>488198.71039685211</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="C9" s="96">
+        <v>57.559821428699998</v>
+      </c>
+      <c r="D9" s="96">
+        <v>356.74749999900001</v>
+      </c>
+      <c r="E9" s="96">
+        <v>1244100.7657470268</v>
+      </c>
+      <c r="F9" s="96">
+        <v>0</v>
+      </c>
+      <c r="G9" s="96">
+        <v>0</v>
+      </c>
+      <c r="H9" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="96" t="s">
         <v>87</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="96">
         <v>1</v>
       </c>
-      <c r="C10">
-        <v>11.9626984129</v>
-      </c>
-      <c r="D10">
-        <v>24.005833333000002</v>
-      </c>
-      <c r="E10">
-        <v>560866.8378297271</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="C10" s="96">
+        <v>139.331597222</v>
+      </c>
+      <c r="D10" s="96">
+        <v>164.92640624699999</v>
+      </c>
+      <c r="E10" s="96">
+        <v>3336344.5485263281</v>
+      </c>
+      <c r="F10" s="96">
+        <v>0</v>
+      </c>
+      <c r="G10" s="96">
+        <v>0</v>
+      </c>
+      <c r="H10" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="96" t="s">
         <v>213</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="96">
         <v>1</v>
       </c>
-      <c r="C11">
-        <v>14.2825396825</v>
-      </c>
-      <c r="D11">
-        <v>69.213928571500006</v>
-      </c>
-      <c r="E11">
-        <v>235546.28047396851</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
+      <c r="C11" s="96">
+        <v>48.933888888600002</v>
+      </c>
+      <c r="D11" s="96">
+        <v>166.67042857070001</v>
+      </c>
+      <c r="E11" s="96">
+        <v>772280.47046408884</v>
+      </c>
+      <c r="F11" s="96">
+        <v>0</v>
+      </c>
+      <c r="G11" s="96">
+        <v>0</v>
+      </c>
+      <c r="H11" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="96" t="s">
         <v>212</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="96">
         <v>1</v>
       </c>
-      <c r="C12">
-        <v>24.419047619000001</v>
-      </c>
-      <c r="D12">
-        <v>85.116666668400001</v>
-      </c>
-      <c r="E12">
-        <v>673949.31322047231</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
+      <c r="C12" s="96">
+        <v>73.503174603100007</v>
+      </c>
+      <c r="D12" s="96">
+        <v>254.69845238280001</v>
+      </c>
+      <c r="E12" s="96">
+        <v>1763034.9919922091</v>
+      </c>
+      <c r="F12" s="96">
+        <v>0</v>
+      </c>
+      <c r="G12" s="96">
+        <v>0</v>
+      </c>
+      <c r="H12" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="96" t="s">
         <v>90</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="96">
         <v>1</v>
       </c>
-      <c r="C13">
-        <v>143.6990079361</v>
-      </c>
-      <c r="D13">
-        <v>557.15250000100002</v>
-      </c>
-      <c r="E13">
-        <v>2694955.1972862789</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
+      <c r="C13" s="96">
+        <v>187.14523809479999</v>
+      </c>
+      <c r="D13" s="96">
+        <v>683.18651190790001</v>
+      </c>
+      <c r="E13" s="96">
+        <v>3752668.2666791501</v>
+      </c>
+      <c r="F13" s="96">
+        <v>0</v>
+      </c>
+      <c r="G13" s="96">
+        <v>0</v>
+      </c>
+      <c r="H13" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="96" t="s">
         <v>91</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="96">
         <v>1</v>
       </c>
-      <c r="C14">
-        <v>807.71805555599997</v>
-      </c>
-      <c r="D14">
-        <v>9180.8625000041993</v>
-      </c>
-      <c r="E14">
-        <v>22103798.373994444</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
+      <c r="C14" s="96">
+        <v>927.30138888939996</v>
+      </c>
+      <c r="D14" s="96">
+        <v>9490.8625000041993</v>
+      </c>
+      <c r="E14" s="96">
+        <v>27711765.916719597</v>
+      </c>
+      <c r="F14" s="96">
+        <v>0</v>
+      </c>
+      <c r="G14" s="96">
+        <v>0</v>
+      </c>
+      <c r="H14" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="96" t="s">
         <v>92</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="96">
         <v>1</v>
       </c>
-      <c r="C15">
-        <v>72.143551587399998</v>
-      </c>
-      <c r="D15">
-        <v>253.01999999860001</v>
-      </c>
-      <c r="E15">
-        <v>1183899.192504474</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
+      <c r="C15" s="96">
+        <v>132.38382936490001</v>
+      </c>
+      <c r="D15" s="96">
+        <v>597.52499999860004</v>
+      </c>
+      <c r="E15" s="96">
+        <v>2224929.6365325735</v>
+      </c>
+      <c r="F15" s="96">
+        <v>0</v>
+      </c>
+      <c r="G15" s="96">
+        <v>0</v>
+      </c>
+      <c r="H15" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="96" t="s">
         <v>93</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="96">
         <v>1</v>
       </c>
-      <c r="C16">
-        <v>47.845436507700001</v>
-      </c>
-      <c r="D16">
-        <v>217.25249999819999</v>
-      </c>
-      <c r="E16">
-        <v>1123309.4293535382</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
+      <c r="C16" s="96">
+        <v>80.620000000100006</v>
+      </c>
+      <c r="D16" s="96">
+        <v>422.70208333869999</v>
+      </c>
+      <c r="E16" s="96">
+        <v>1974051.5620993127</v>
+      </c>
+      <c r="F16" s="96">
+        <v>0</v>
+      </c>
+      <c r="G16" s="96">
+        <v>0</v>
+      </c>
+      <c r="H16" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="96">
         <v>1</v>
       </c>
-      <c r="C17">
-        <v>44.1025793648</v>
-      </c>
-      <c r="D17">
-        <v>162.5050000034</v>
-      </c>
-      <c r="E17">
-        <v>1210391.5076398768</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
+      <c r="C17" s="96">
+        <v>112.3860119039</v>
+      </c>
+      <c r="D17" s="96">
+        <v>405.94000000680001</v>
+      </c>
+      <c r="E17" s="96">
+        <v>2774896.9225576972</v>
+      </c>
+      <c r="F17" s="96">
+        <v>0</v>
+      </c>
+      <c r="G17" s="96">
+        <v>0</v>
+      </c>
+      <c r="H17" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="96" t="s">
         <v>95</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="96">
         <v>1</v>
       </c>
-      <c r="C18">
-        <v>91.236706349200006</v>
-      </c>
-      <c r="D18">
-        <v>171.89416666540001</v>
-      </c>
-      <c r="E18">
-        <v>1379496.2566107768</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
+      <c r="C18" s="96">
+        <v>269.62529761849999</v>
+      </c>
+      <c r="D18" s="96">
+        <v>1970.7039166622999</v>
+      </c>
+      <c r="E18" s="96">
+        <v>4682028.2206923608</v>
+      </c>
+      <c r="F18" s="96">
+        <v>0</v>
+      </c>
+      <c r="G18" s="96">
+        <v>0</v>
+      </c>
+      <c r="H18" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="96" t="s">
         <v>96</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="96">
         <v>1</v>
       </c>
-      <c r="C19">
-        <v>56.020634920299997</v>
-      </c>
-      <c r="D19">
-        <v>107.7189285721</v>
-      </c>
-      <c r="E19">
-        <v>1545484.3455725485</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
+      <c r="C19" s="96">
+        <v>172.05783730120001</v>
+      </c>
+      <c r="D19" s="96">
+        <v>473.31017857680001</v>
+      </c>
+      <c r="E19" s="96">
+        <v>3804498.4929125779</v>
+      </c>
+      <c r="F19" s="96">
+        <v>0</v>
+      </c>
+      <c r="G19" s="96">
+        <v>0</v>
+      </c>
+      <c r="H19" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="96" t="s">
         <v>97</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="96">
         <v>1</v>
       </c>
-      <c r="C20">
-        <v>55.678472222300002</v>
-      </c>
-      <c r="D20">
-        <v>241.7050000033</v>
-      </c>
-      <c r="E20">
-        <v>1279296.2102717794</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
+      <c r="C20" s="96">
+        <v>407.06958333329999</v>
+      </c>
+      <c r="D20" s="96">
+        <v>1164.4874999997</v>
+      </c>
+      <c r="E20" s="96">
+        <v>7023074.0484903501</v>
+      </c>
+      <c r="F20" s="96">
+        <v>0</v>
+      </c>
+      <c r="G20" s="96">
+        <v>0</v>
+      </c>
+      <c r="H20" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="96" t="s">
         <v>98</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="96">
         <v>1</v>
       </c>
-      <c r="C21">
-        <v>56.560218254299997</v>
-      </c>
-      <c r="D21">
-        <v>230.9696071473</v>
-      </c>
-      <c r="E21">
-        <v>1299165.9114931743</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
+      <c r="C21" s="96">
+        <v>111.473115079</v>
+      </c>
+      <c r="D21" s="96">
+        <v>409.77460714760002</v>
+      </c>
+      <c r="E21" s="96">
+        <v>2482567.9113498144</v>
+      </c>
+      <c r="F21" s="96">
+        <v>0</v>
+      </c>
+      <c r="G21" s="96">
+        <v>0</v>
+      </c>
+      <c r="H21" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="96" t="s">
         <v>207</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="96">
         <v>1</v>
       </c>
-      <c r="C22">
-        <v>56.883630952300003</v>
-      </c>
-      <c r="D22">
-        <v>127.0099999944</v>
-      </c>
-      <c r="E22">
-        <v>1074255.4229483344</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
+      <c r="C22" s="96">
+        <v>77.0229166668</v>
+      </c>
+      <c r="D22" s="96">
+        <v>175.00999999839999</v>
+      </c>
+      <c r="E22" s="96">
+        <v>1231155.9948169386</v>
+      </c>
+      <c r="F22" s="96">
+        <v>0</v>
+      </c>
+      <c r="G22" s="96">
+        <v>0</v>
+      </c>
+      <c r="H22" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="96" t="s">
         <v>155</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="96">
         <v>1</v>
       </c>
-      <c r="C23">
-        <v>122.10228174549999</v>
-      </c>
-      <c r="D23">
-        <v>255.25166666370001</v>
-      </c>
-      <c r="E23">
-        <v>1915368.1820728134</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
+      <c r="C23" s="96">
+        <v>128.10228174549999</v>
+      </c>
+      <c r="D23" s="96">
+        <v>339.25166666370001</v>
+      </c>
+      <c r="E23" s="96">
+        <v>1999132.6820728134</v>
+      </c>
+      <c r="F23" s="96">
+        <v>0</v>
+      </c>
+      <c r="G23" s="96">
+        <v>0</v>
+      </c>
+      <c r="H23" s="96">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="96" t="s">
+        <v>229</v>
+      </c>
+      <c r="B24" s="96">
+        <v>1</v>
+      </c>
+      <c r="C24" s="96">
+        <v>748.66458333349999</v>
+      </c>
+      <c r="D24" s="96">
+        <v>4813.7219583328997</v>
+      </c>
+      <c r="E24" s="96">
+        <v>13993499.751331689</v>
+      </c>
+      <c r="F24" s="96">
+        <v>0</v>
+      </c>
+      <c r="G24" s="96">
+        <v>0</v>
+      </c>
+      <c r="H24" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="96" t="s">
         <v>99</v>
       </c>
-      <c r="B24">
+      <c r="B25" s="96">
         <v>1</v>
       </c>
-      <c r="C24">
-        <v>38.5916666667</v>
-      </c>
-      <c r="D24">
-        <v>121.515</v>
-      </c>
-      <c r="E24">
-        <v>967034.52092210797</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="C25" s="96">
+        <v>108.580952381</v>
+      </c>
+      <c r="D25" s="96">
+        <v>331.05000000159998</v>
+      </c>
+      <c r="E25" s="96">
+        <v>2185400.7533588032</v>
+      </c>
+      <c r="F25" s="96">
+        <v>0</v>
+      </c>
+      <c r="G25" s="96">
+        <v>0</v>
+      </c>
+      <c r="H25" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="96" t="s">
         <v>100</v>
       </c>
-      <c r="B25">
+      <c r="B26" s="96">
         <v>1</v>
       </c>
-      <c r="C25">
-        <v>13.939484127</v>
-      </c>
-      <c r="D25">
-        <v>138.0000000014</v>
-      </c>
-      <c r="E25">
-        <v>370995.20136279258</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="C26" s="96">
+        <v>50.997817460199997</v>
+      </c>
+      <c r="D26" s="96">
+        <v>218.0000000018</v>
+      </c>
+      <c r="E26" s="96">
+        <v>1312962.2237802313</v>
+      </c>
+      <c r="F26" s="96">
+        <v>0</v>
+      </c>
+      <c r="G26" s="96">
+        <v>0</v>
+      </c>
+      <c r="H26" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="96" t="s">
+        <v>230</v>
+      </c>
+      <c r="B27" s="96">
+        <v>1</v>
+      </c>
+      <c r="C27" s="96">
+        <v>835</v>
+      </c>
+      <c r="D27" s="96">
+        <v>2100</v>
+      </c>
+      <c r="E27" s="96">
+        <v>7231266.6113499999</v>
+      </c>
+      <c r="F27" s="96">
+        <v>0</v>
+      </c>
+      <c r="G27" s="96">
+        <v>0</v>
+      </c>
+      <c r="H27" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="96" t="s">
         <v>101</v>
       </c>
-      <c r="B26">
+      <c r="B28" s="96">
         <v>1</v>
       </c>
-      <c r="C26">
-        <v>88.634642857100005</v>
-      </c>
-      <c r="D26">
-        <v>627.48958333509995</v>
-      </c>
-      <c r="E26">
-        <v>1904211.5763949119</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="C28" s="96">
+        <v>172.9596428566</v>
+      </c>
+      <c r="D28" s="96">
+        <v>899.49958333749998</v>
+      </c>
+      <c r="E28" s="96">
+        <v>3717567.9331198842</v>
+      </c>
+      <c r="F28" s="96">
+        <v>0</v>
+      </c>
+      <c r="G28" s="96">
+        <v>0</v>
+      </c>
+      <c r="H28" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="96" t="s">
         <v>214</v>
       </c>
-      <c r="B27">
+      <c r="B29" s="96">
         <v>1</v>
       </c>
-      <c r="C27">
-        <v>103.7097222222</v>
-      </c>
-      <c r="D27">
-        <v>470.41000000029999</v>
-      </c>
-      <c r="E27">
-        <v>2145545.2733516009</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="C29" s="96">
+        <v>281.40083333320001</v>
+      </c>
+      <c r="D29" s="96">
+        <v>1083.4799999999</v>
+      </c>
+      <c r="E29" s="96">
+        <v>5151540.6591492426</v>
+      </c>
+      <c r="F29" s="96">
+        <v>0</v>
+      </c>
+      <c r="G29" s="96">
+        <v>0</v>
+      </c>
+      <c r="H29" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="96" t="s">
         <v>139</v>
       </c>
-      <c r="B28">
+      <c r="B30" s="96">
         <v>1</v>
       </c>
-      <c r="C28">
-        <v>34.320634920400003</v>
-      </c>
-      <c r="D28">
-        <v>162.7625000024</v>
-      </c>
-      <c r="E28">
-        <v>602361.45632991486</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="C30" s="96">
+        <v>55.934623015699998</v>
+      </c>
+      <c r="D30" s="96">
+        <v>202.7625000024</v>
+      </c>
+      <c r="E30" s="96">
+        <v>1012363.4850253685</v>
+      </c>
+      <c r="F30" s="96">
+        <v>0</v>
+      </c>
+      <c r="G30" s="96">
+        <v>0</v>
+      </c>
+      <c r="H30" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="96" t="s">
         <v>216</v>
       </c>
-      <c r="B29">
+      <c r="B31" s="96">
         <v>1</v>
       </c>
-      <c r="C29">
-        <v>36.426587300999998</v>
-      </c>
-      <c r="D29">
-        <v>131.58500000000001</v>
-      </c>
-      <c r="E29">
-        <v>682680.93729586795</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="C31" s="96">
+        <v>55.3718253961</v>
+      </c>
+      <c r="D31" s="96">
+        <v>212.5949999984</v>
+      </c>
+      <c r="E31" s="96">
+        <v>1127867.2813395613</v>
+      </c>
+      <c r="F31" s="96">
+        <v>0</v>
+      </c>
+      <c r="G31" s="96">
+        <v>0</v>
+      </c>
+      <c r="H31" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="96" t="s">
         <v>104</v>
       </c>
-      <c r="B30">
+      <c r="B32" s="96">
         <v>1</v>
       </c>
-      <c r="C30">
-        <v>7.8875000002000002</v>
-      </c>
-      <c r="D30">
-        <v>78</v>
-      </c>
-      <c r="E30">
-        <v>269184.13865821779</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="C32" s="96">
+        <v>15.0083333333</v>
+      </c>
+      <c r="D32" s="96">
+        <v>122.9999999992</v>
+      </c>
+      <c r="E32" s="96">
+        <v>474208.7541035653</v>
+      </c>
+      <c r="F32" s="96">
+        <v>0</v>
+      </c>
+      <c r="G32" s="96">
+        <v>0</v>
+      </c>
+      <c r="H32" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="96" t="s">
         <v>215</v>
       </c>
-      <c r="B31">
+      <c r="B33" s="96">
         <v>1</v>
       </c>
-      <c r="C31">
-        <v>47.335416666699999</v>
-      </c>
-      <c r="D31">
-        <v>372.99999999879998</v>
-      </c>
-      <c r="E31">
-        <v>1241096.8257165046</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="C33" s="96">
+        <v>57.744861111200002</v>
+      </c>
+      <c r="D33" s="96">
+        <v>409.99999999919999</v>
+      </c>
+      <c r="E33" s="96">
+        <v>1465987.5738126547</v>
+      </c>
+      <c r="F33" s="96">
+        <v>0</v>
+      </c>
+      <c r="G33" s="96">
+        <v>0</v>
+      </c>
+      <c r="H33" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="96" t="s">
         <v>206</v>
       </c>
-      <c r="B32">
+      <c r="B34" s="96">
         <v>1</v>
       </c>
-      <c r="C32">
+      <c r="C34" s="96">
         <v>-25</v>
       </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32">
+      <c r="D34" s="96">
+        <v>0</v>
+      </c>
+      <c r="E34" s="96">
         <v>-233849</v>
       </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="F34" s="96">
+        <v>0</v>
+      </c>
+      <c r="G34" s="96">
+        <v>0</v>
+      </c>
+      <c r="H34" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="96" t="s">
         <v>162</v>
       </c>
-      <c r="B33">
+      <c r="B35" s="96">
         <v>1</v>
       </c>
-      <c r="C33">
-        <v>40.482440475899999</v>
-      </c>
-      <c r="D33">
-        <v>119.000000005</v>
-      </c>
-      <c r="E33">
-        <v>831624.25115675328</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="C35" s="96">
+        <v>96.820039681799997</v>
+      </c>
+      <c r="D35" s="96">
+        <v>526.00500000149998</v>
+      </c>
+      <c r="E35" s="96">
+        <v>2007902.2622231084</v>
+      </c>
+      <c r="F35" s="96">
+        <v>0</v>
+      </c>
+      <c r="G35" s="96">
+        <v>0</v>
+      </c>
+      <c r="H35" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="96" t="s">
         <v>107</v>
       </c>
-      <c r="B34">
+      <c r="B36" s="96">
         <v>1</v>
       </c>
-      <c r="C34">
-        <v>419.9150396828</v>
-      </c>
-      <c r="D34">
+      <c r="C36" s="96">
+        <v>419.7483730161</v>
+      </c>
+      <c r="D36" s="96">
         <v>2354.8888214259</v>
       </c>
-      <c r="E34">
-        <v>7398671.9615932852</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="E36" s="96">
+        <v>7395442.6965926401</v>
+      </c>
+      <c r="F36" s="96">
+        <v>0</v>
+      </c>
+      <c r="G36" s="96">
+        <v>0</v>
+      </c>
+      <c r="H36" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="96" t="s">
         <v>112</v>
       </c>
-      <c r="B35">
+      <c r="B37" s="96">
         <v>1</v>
       </c>
-      <c r="C35">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="D35">
-        <v>345.63</v>
-      </c>
-      <c r="E35">
-        <v>483655.59259999997</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="C37" s="96">
+        <v>53.475757575700001</v>
+      </c>
+      <c r="D37" s="96">
+        <v>472.43</v>
+      </c>
+      <c r="E37" s="96">
+        <v>968840.97419863928</v>
+      </c>
+      <c r="F37" s="96">
+        <v>0</v>
+      </c>
+      <c r="G37" s="96">
+        <v>0</v>
+      </c>
+      <c r="H37" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="96" t="s">
         <v>108</v>
       </c>
-      <c r="B36">
+      <c r="B38" s="96">
         <v>1</v>
       </c>
-      <c r="C36">
-        <v>4.5</v>
-      </c>
-      <c r="D36">
-        <v>-24.56</v>
-      </c>
-      <c r="E36">
-        <v>-6760.5810000000001</v>
-      </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="C38" s="96">
+        <v>84.666666666699996</v>
+      </c>
+      <c r="D38" s="96">
+        <v>682.28</v>
+      </c>
+      <c r="E38" s="96">
+        <v>1445131.6450023698</v>
+      </c>
+      <c r="F38" s="96">
+        <v>0</v>
+      </c>
+      <c r="G38" s="96">
+        <v>0</v>
+      </c>
+      <c r="H38" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="B37">
+      <c r="B39" s="96">
         <v>1</v>
       </c>
-      <c r="C37">
-        <v>39.323062168900002</v>
-      </c>
-      <c r="D37">
-        <v>188.95147487009999</v>
-      </c>
-      <c r="E37">
-        <v>855590.57458566967</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="C39" s="96">
+        <v>110.56512566089999</v>
+      </c>
+      <c r="D39" s="96">
+        <v>374.96807010729998</v>
+      </c>
+      <c r="E39" s="96">
+        <v>2373341.2642009868</v>
+      </c>
+      <c r="F39" s="96">
+        <v>0</v>
+      </c>
+      <c r="G39" s="96">
+        <v>0</v>
+      </c>
+      <c r="H39" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="96" t="s">
+        <v>140</v>
+      </c>
+      <c r="B40" s="96">
+        <v>1</v>
+      </c>
+      <c r="C40" s="96">
+        <v>-188</v>
+      </c>
+      <c r="D40" s="96">
+        <v>-1860</v>
+      </c>
+      <c r="E40" s="96">
+        <v>-2433547.0814999999</v>
+      </c>
+      <c r="F40" s="96">
+        <v>0</v>
+      </c>
+      <c r="G40" s="96">
+        <v>0</v>
+      </c>
+      <c r="H40" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="96" t="s">
+        <v>146</v>
+      </c>
+      <c r="B41" s="96">
+        <v>1</v>
+      </c>
+      <c r="C41" s="96">
+        <v>-3.2222222223000001</v>
+      </c>
+      <c r="D41" s="96">
+        <v>-20.505000001599999</v>
+      </c>
+      <c r="E41" s="96">
+        <v>-388379.73864699452</v>
+      </c>
+      <c r="F41" s="96">
+        <v>0</v>
+      </c>
+      <c r="G41" s="96">
+        <v>0</v>
+      </c>
+      <c r="H41" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="96" t="s">
         <v>156</v>
       </c>
-      <c r="B38">
+      <c r="B42" s="96">
         <v>1</v>
       </c>
-      <c r="C38">
-        <v>16.250000000099998</v>
-      </c>
-      <c r="D38">
-        <v>38.000000001399997</v>
-      </c>
-      <c r="E38">
-        <v>316968.01186656969</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
+      <c r="C42" s="96">
+        <v>157.7577380953</v>
+      </c>
+      <c r="D42" s="96">
+        <v>1811.0000000018999</v>
+      </c>
+      <c r="E42" s="96">
+        <v>3004106.7923235167</v>
+      </c>
+      <c r="F42" s="96">
+        <v>0</v>
+      </c>
+      <c r="G42" s="96">
+        <v>0</v>
+      </c>
+      <c r="H42" s="96">
         <v>0</v>
       </c>
     </row>
@@ -3491,8 +3602,8 @@
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" style="2" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="2" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="17.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
@@ -3541,7 +3652,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="87" t="s">
         <v>209</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -3552,46 +3663,48 @@
       </c>
       <c r="D2" s="59">
         <f>IFERROR(+VLOOKUP(B2,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4682028.2206923608</v>
+      </c>
+      <c r="E2" s="59">
         <v>1379496.2566107768</v>
       </c>
-      <c r="E2" s="59"/>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>1379496.2566107768</v>
+        <v>3302531.964081584</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G41" si="1">+D2/C2</f>
-        <v>4.2736546403439303E-2</v>
+        <v>0.14504839382995705</v>
       </c>
       <c r="H2" s="59">
         <f>+D2/$N$3*$N$4</f>
-        <v>33107910.158658642</v>
+        <v>56184338.648308329</v>
       </c>
       <c r="I2" s="60">
         <f t="shared" ref="I2:I41" si="2">+H2/C2</f>
-        <v>1.0256771136825431</v>
+        <v>1.7405807259594843</v>
       </c>
       <c r="J2" s="59">
         <f>+D2/$N$3</f>
-        <v>1379496.2566107768</v>
+        <v>2341014.1103461804</v>
       </c>
       <c r="K2" s="59">
         <f t="shared" ref="K2:K41" si="3">+(C2-D2)/$N$2</f>
-        <v>1343460.0165930425</v>
+        <v>1254411.2917071998</v>
       </c>
       <c r="L2" s="61" cm="1">
         <f t="array" ref="L2">+_xlfn.IFS(I2&gt;114%,H2*0.02,I2&gt;109%,H2*0.015,I2&gt;104%,H2*0.0125,I2&gt;99%,H2*0.01,I2&lt;99%,H2*0)</f>
-        <v>331079.10158658645</v>
+        <v>1123686.7729661667</v>
       </c>
       <c r="M2" s="53" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="89"/>
+      <c r="A3" s="88"/>
       <c r="B3" s="36" t="s">
         <v>94</v>
       </c>
@@ -3600,47 +3713,49 @@
       </c>
       <c r="D3" s="4">
         <f>IFERROR(+VLOOKUP(B3,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2774896.9225576972</v>
+      </c>
+      <c r="E3" s="4">
         <v>1210391.5076398768</v>
       </c>
-      <c r="E3" s="4"/>
       <c r="F3" s="4">
         <f t="shared" si="0"/>
-        <v>1210391.5076398768</v>
+        <v>1564505.4149178204</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
-        <v>3.906665354488819E-2</v>
+        <v>8.956270430855634E-2</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H41" si="4">+D3/$N$3*$N$4</f>
-        <v>29049396.183357045</v>
+        <v>33298763.070692368</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="2"/>
-        <v>0.93759968507731672</v>
+        <v>1.0747524517026761</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J41" si="5">+D3/$N$3</f>
-        <v>1210391.5076398768</v>
+        <v>1387448.4612788486</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="3"/>
-        <v>1294449.4204888425</v>
+        <v>1282174.1480147981</v>
       </c>
       <c r="L3" s="63" cm="1">
         <f t="array" ref="L3">+_xlfn.IFS(I3&gt;114%,H3*0.02,I3&gt;109%,H3*0.015,I3&gt;104%,H3*0.0125,I3&gt;99%,H3*0.01,I3&lt;99%,H3*0)</f>
-        <v>0</v>
+        <v>416234.53838365461</v>
       </c>
       <c r="M3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="N3">
         <f>N4-N2</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="89"/>
+      <c r="A4" s="88"/>
       <c r="B4" s="36" t="s">
         <v>92</v>
       </c>
@@ -3649,36 +3764,38 @@
       </c>
       <c r="D4" s="4">
         <f>IFERROR(+VLOOKUP(B4,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2224929.6365325735</v>
+      </c>
+      <c r="E4" s="4">
         <v>1183899.192504474</v>
       </c>
-      <c r="E4" s="4"/>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>1183899.192504474</v>
+        <v>1041030.4440280995</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>4.1701228915740601E-2</v>
+        <v>7.8370101679167886E-2</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="4"/>
-        <v>28413580.620107375</v>
+        <v>26699155.638390884</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>1.0008294939777744</v>
+        <v>0.94044122015001475</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="5"/>
-        <v>1183899.192504474</v>
+        <v>1112464.8182662867</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>1182875.30728886</v>
+        <v>1189322.8010734399</v>
       </c>
       <c r="L4" s="63" cm="1">
         <f t="array" ref="L4">+_xlfn.IFS(I4&gt;114%,H4*0.02,I4&gt;109%,H4*0.015,I4&gt;104%,H4*0.0125,I4&gt;99%,H4*0.01,I4&lt;99%,H4*0)</f>
-        <v>284135.80620107375</v>
+        <v>0</v>
       </c>
       <c r="M4" s="53" t="s">
         <v>47</v>
@@ -3688,7 +3805,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="89"/>
+      <c r="A5" s="88"/>
       <c r="B5" s="36" t="s">
         <v>90</v>
       </c>
@@ -3697,40 +3814,42 @@
       </c>
       <c r="D5" s="4">
         <f>IFERROR(+VLOOKUP(B5,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3752668.2666791501</v>
+      </c>
+      <c r="E5" s="4">
         <v>2694955.1972862789</v>
       </c>
-      <c r="E5" s="4"/>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>2694955.1972862789</v>
+        <v>1057713.0693928711</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>9.4926108836986392E-2</v>
+        <v>0.13218260424907871</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="4"/>
-        <v>64678924.734870695</v>
+        <v>45032019.200149804</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>2.2782266120876735</v>
+        <v>1.5861912509889446</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="5"/>
-        <v>2694955.1972862789</v>
+        <v>1876334.133339575</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>1117177.2201244337</v>
+        <v>1119880.1360667774</v>
       </c>
       <c r="L5" s="63" cm="1">
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
-        <v>1293578.4946974139</v>
+        <v>900640.38400299614</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="89"/>
+      <c r="A6" s="88"/>
       <c r="B6" s="36" t="s">
         <v>212</v>
       </c>
@@ -3739,32 +3858,34 @@
       </c>
       <c r="D6" s="4">
         <f>IFERROR(+VLOOKUP(B6,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1763034.9919922091</v>
+      </c>
+      <c r="E6" s="4">
         <v>673949.31322047231</v>
       </c>
-      <c r="E6" s="4"/>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>673949.31322047231</v>
+        <v>1089085.6787717368</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>2.8643682412353367E-2</v>
+        <v>7.4931175686161061E-2</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="4"/>
-        <v>16174783.517291335</v>
+        <v>21156419.903906509</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>0.68744837789648083</v>
+        <v>0.89917410823393273</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="5"/>
-        <v>673949.31322047231</v>
+        <v>881517.49599610455</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>993685.8793173763</v>
+        <v>989349.5247967235</v>
       </c>
       <c r="L6" s="63" cm="1">
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
@@ -3772,7 +3893,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="89"/>
+      <c r="A7" s="88"/>
       <c r="B7" s="36" t="s">
         <v>86</v>
       </c>
@@ -3781,32 +3902,34 @@
       </c>
       <c r="D7" s="4">
         <f>IFERROR(+VLOOKUP(B7,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1244100.7657470268</v>
+      </c>
+      <c r="E7" s="4">
         <v>488198.71039685211</v>
       </c>
-      <c r="E7" s="4"/>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F8" si="6">+D7-E7</f>
-        <v>488198.71039685211</v>
+        <v>755902.05535017466</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>1.7597910257440248E-2</v>
+        <v>4.4845619540927889E-2</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="4"/>
-        <v>11716769.049524451</v>
+        <v>14929209.188964322</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>0.42234984617856591</v>
+        <v>0.53814743449113478</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="5"/>
-        <v>488198.71039685211</v>
+        <v>622050.38287351339</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>1184941.666089898</v>
+        <v>1204443.4665780673</v>
       </c>
       <c r="L7" s="63" cm="1">
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
@@ -3814,7 +3937,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="89"/>
+      <c r="A8" s="88"/>
       <c r="B8" s="36" t="s">
         <v>85</v>
       </c>
@@ -3823,32 +3946,34 @@
       </c>
       <c r="D8" s="4">
         <f>IFERROR(+VLOOKUP(B8,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2332273.4502824824</v>
+      </c>
+      <c r="E8" s="4">
         <v>1318036.6824969184</v>
       </c>
-      <c r="E8" s="4"/>
       <c r="F8" s="4">
         <f t="shared" si="6"/>
-        <v>1318036.6824969184</v>
+        <v>1014236.7677855641</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>3.6784741018785302E-2</v>
+        <v>6.5090809681490447E-2</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="4"/>
-        <v>31632880.379926041</v>
+        <v>27987281.403389789</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>0.88283378445084737</v>
+        <v>0.78108971617788536</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="5"/>
-        <v>1318036.6824969184</v>
+        <v>1166136.7251412412</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="3"/>
-        <v>1500566.7275835124</v>
+        <v>1522672.6348470554</v>
       </c>
       <c r="L8" s="63" cm="1">
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
@@ -3856,7 +3981,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="89"/>
+      <c r="A9" s="88"/>
       <c r="B9" s="36" t="s">
         <v>84</v>
       </c>
@@ -3865,77 +3990,81 @@
       </c>
       <c r="D9" s="4">
         <f>IFERROR(+VLOOKUP(B9,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4892925.4103550436</v>
+      </c>
+      <c r="E9" s="4">
         <v>2772298.6238154541</v>
       </c>
-      <c r="E9" s="4"/>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>2772298.6238154541</v>
+        <v>2120626.7865395895</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>7.7371357154185139E-2</v>
+        <v>0.13655537545675622</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="4"/>
-        <v>66535166.971570894</v>
+        <v>58715104.924260527</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>1.8569125717004431</v>
+        <v>1.6386645054810749</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="5"/>
-        <v>2772298.6238154541</v>
+        <v>2446462.7051775218</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>1437337.9475261848</v>
+        <v>1406279.3639346664</v>
       </c>
       <c r="L9" s="63" cm="1">
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
-        <v>1330703.3394314179</v>
+        <v>1174302.0984852107</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="90"/>
+      <c r="A10" s="89"/>
       <c r="B10" s="3"/>
       <c r="C10" s="64">
         <v>242974591.73925051</v>
       </c>
       <c r="D10" s="64">
         <f>+SUM(D2:D9)</f>
+        <v>23666857.664838541</v>
+      </c>
+      <c r="E10" s="65">
         <v>11721225.483971104</v>
       </c>
-      <c r="E10" s="65"/>
       <c r="F10" s="64">
         <f>+SUM(F2:F9)</f>
-        <v>11721225.483971104</v>
+        <v>11945632.180867441</v>
       </c>
       <c r="G10" s="66">
         <f t="shared" si="1"/>
-        <v>4.8240539885544081E-2</v>
+        <v>9.7404660690763742E-2</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="4"/>
-        <v>281309411.6153065</v>
+        <v>284002291.97806251</v>
       </c>
       <c r="I10" s="66">
         <f t="shared" si="2"/>
-        <v>1.157772957253058</v>
+        <v>1.1688559282891648</v>
       </c>
       <c r="J10" s="64">
         <f t="shared" si="5"/>
-        <v>11721225.483971104</v>
+        <v>11833428.832419271</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
-        <v>10054494.185012149</v>
+        <v>9968533.3670187257</v>
       </c>
       <c r="L10" s="68"/>
     </row>
     <row r="11" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="88" t="s">
+      <c r="A11" s="87" t="s">
         <v>210</v>
       </c>
       <c r="B11" s="57" t="s">
@@ -3946,32 +4075,34 @@
       </c>
       <c r="D11" s="59">
         <f>IFERROR(+VLOOKUP(B11,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7023074.0484903501</v>
+      </c>
+      <c r="E11" s="59">
         <v>1279296.2102717794</v>
       </c>
-      <c r="E11" s="59"/>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F16" si="7">+D11-E11</f>
-        <v>1279296.2102717794</v>
+        <v>5743777.8382185707</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
-        <v>1.319243585719858E-2</v>
+        <v>7.242376953917623E-2</v>
       </c>
       <c r="H11" s="59">
         <f t="shared" si="4"/>
-        <v>30703109.046522707</v>
+        <v>84276888.581884205</v>
       </c>
       <c r="I11" s="60">
         <f t="shared" si="2"/>
-        <v>0.31661846057276594</v>
+        <v>0.86908523447011488</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="5"/>
-        <v>1279296.2102717794</v>
+        <v>3511537.0242451751</v>
       </c>
       <c r="K11" s="59">
         <f t="shared" si="3"/>
-        <v>4160550.0986898146</v>
+        <v>4088585.2014385075</v>
       </c>
       <c r="L11" s="61" cm="1">
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
@@ -3979,7 +4110,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="89"/>
+      <c r="A12" s="88"/>
       <c r="B12" s="36" t="s">
         <v>107</v>
       </c>
@@ -3988,41 +4119,43 @@
       </c>
       <c r="D12" s="4">
         <f>IFERROR(+VLOOKUP(B12,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7395442.6965926401</v>
+      </c>
+      <c r="E12" s="4">
         <v>7398671.9615932852</v>
       </c>
-      <c r="E12" s="4"/>
       <c r="F12" s="4">
         <f t="shared" si="7"/>
-        <v>7398671.9615932852</v>
+        <v>-3229.2650006450713</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.23390644585560125</v>
+        <v>0.23380435376354097</v>
       </c>
       <c r="H12" s="4">
         <f t="shared" si="4"/>
-        <v>177568127.07823884</v>
+        <v>88745312.359111682</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>5.6137547005344297</v>
+        <v>2.8056522451624919</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="5"/>
-        <v>7398671.9615932852</v>
+        <v>3697721.3482963201</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>1053575.2368249444</v>
+        <v>1101611.8050897438</v>
       </c>
       <c r="L12" s="63" cm="1">
         <f t="array" ref="L12">+_xlfn.IFS(I12&gt;114%,H12*0.02,I12&gt;109%,H12*0.015,I12&gt;104%,H12*0.0125,I12&gt;99%,H12*0.01,I12&lt;99%,H12*0)</f>
-        <v>3551362.541564777</v>
+        <v>1774906.2471822337</v>
       </c>
       <c r="M12" s="27"/>
     </row>
     <row r="13" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="89"/>
+      <c r="A13" s="88"/>
       <c r="B13" s="36" t="s">
         <v>91</v>
       </c>
@@ -4031,36 +4164,38 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>27711765.916719597</v>
+      </c>
+      <c r="E13" s="4">
         <v>22103798.373994444</v>
       </c>
-      <c r="E13" s="4"/>
       <c r="F13" s="4">
         <f t="shared" si="7"/>
-        <v>22103798.373994444</v>
+        <v>5607967.5427251533</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>0.17219635431770633</v>
+        <v>0.2158843915342161</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>530491160.97586668</v>
+        <v>332541191.00063515</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>4.1327125036249521</v>
+        <v>2.5906126984105931</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>22103798.373994444</v>
+        <v>13855882.958359798</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>4620005.1174187195</v>
+        <v>4575097.7344502443</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;114%,H13*0.0125,I13&gt;109%,H13*0.01,I13&gt;104%,H13*0.0075,I13&gt;99%,H13*0.005,I13&lt;99%,H13*0)</f>
-        <v>6631139.5121983336</v>
+        <v>4156764.8875079397</v>
       </c>
       <c r="M13" s="53" t="s">
         <v>61</v>
@@ -4070,7 +4205,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="89"/>
+      <c r="A14" s="88"/>
       <c r="B14" s="36" t="s">
         <v>112</v>
       </c>
@@ -4079,32 +4214,34 @@
       </c>
       <c r="D14" s="4">
         <f>IFERROR(+VLOOKUP(B14,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>968840.97419863928</v>
+      </c>
+      <c r="E14" s="4">
         <v>483655.59259999997</v>
       </c>
-      <c r="E14" s="4"/>
       <c r="F14" s="4">
         <f t="shared" si="7"/>
-        <v>483655.59259999997</v>
+        <v>485185.3815986393</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>1.1393788750118483E-2</v>
+        <v>2.2823615732709485E-2</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="4"/>
-        <v>11607734.222399998</v>
+        <v>11626091.690383671</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0.2734509300028436</v>
+        <v>0.27388338879251378</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="5"/>
-        <v>483655.59259999997</v>
+        <v>484420.48709931964</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>1824582.6870597824</v>
+        <v>1885464.3827625618</v>
       </c>
       <c r="L14" s="63" cm="1">
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
@@ -4113,7 +4250,7 @@
       <c r="N14" s="28"/>
     </row>
     <row r="15" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="89"/>
+      <c r="A15" s="88"/>
       <c r="B15" s="36" t="s">
         <v>108</v>
       </c>
@@ -4122,32 +4259,34 @@
       </c>
       <c r="D15" s="4">
         <f>IFERROR(+VLOOKUP(B15,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1445131.6450023698</v>
+      </c>
+      <c r="E15" s="4">
         <v>-6760.5810000000001</v>
       </c>
-      <c r="E15" s="4"/>
       <c r="F15" s="4">
         <f t="shared" si="7"/>
-        <v>-6760.5810000000001</v>
+        <v>1451892.2260023698</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>-1.5926339511134347E-4</v>
+        <v>3.4043904239283308E-2</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="4"/>
-        <v>-162253.94400000002</v>
+        <v>17341579.740028437</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>-3.8223214826722438E-3</v>
+        <v>0.40852685087139967</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="5"/>
-        <v>-6760.5810000000001</v>
+        <v>722565.82250118488</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>1845905.1293902174</v>
+        <v>1863814.8068169376</v>
       </c>
       <c r="L15" s="63" cm="1">
         <f t="array" ref="L15">+_xlfn.IFS(I15&gt;109%,H15*0.015,I15&gt;104%,H15*0.0125,I15&gt;99%,H15*0.01,I15&lt;99%,H15*0)</f>
@@ -4155,44 +4294,46 @@
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="90"/>
+      <c r="A16" s="89"/>
       <c r="B16" s="3"/>
       <c r="C16" s="64">
         <v>341864881.75327951</v>
       </c>
       <c r="D16" s="64">
         <f>+SUM(D11:D15)</f>
+        <v>44544255.281003602</v>
+      </c>
+      <c r="E16" s="65">
         <v>31258661.557459507</v>
       </c>
-      <c r="E16" s="65"/>
       <c r="F16" s="64">
         <f t="shared" si="7"/>
-        <v>31258661.557459507</v>
+        <v>13285593.723544095</v>
       </c>
       <c r="G16" s="66">
         <f t="shared" si="1"/>
-        <v>9.1435719858521683E-2</v>
+        <v>0.13029783887878471</v>
       </c>
       <c r="H16" s="64">
         <f t="shared" si="4"/>
-        <v>750207877.3790282</v>
+        <v>534531063.37204325</v>
       </c>
       <c r="I16" s="66">
         <f t="shared" si="2"/>
-        <v>2.1944572766045205</v>
+        <v>1.5635740665454168</v>
       </c>
       <c r="J16" s="64">
         <f t="shared" si="5"/>
-        <v>31258661.557459507</v>
+        <v>22272127.640501801</v>
       </c>
       <c r="K16" s="67">
         <f t="shared" si="3"/>
-        <v>13504618.269383477</v>
+        <v>13514573.930557996</v>
       </c>
       <c r="L16" s="68"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="91" t="s">
+      <c r="A17" s="90" t="s">
         <v>211</v>
       </c>
       <c r="B17" s="69" t="s">
@@ -4203,32 +4344,34 @@
       </c>
       <c r="D17" s="59">
         <f>IFERROR(+VLOOKUP(B17,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1647814.3144255385</v>
+      </c>
+      <c r="E17" s="59">
         <v>910195.66733517474</v>
       </c>
-      <c r="E17" s="59"/>
       <c r="F17" s="59">
         <f t="shared" ref="F17:F40" si="8">+D17-E17</f>
-        <v>910195.66733517474</v>
+        <v>737618.64709036378</v>
       </c>
       <c r="G17" s="60">
         <f t="shared" si="1"/>
-        <v>3.1024442865378157E-2</v>
+        <v>5.616651768989557E-2</v>
       </c>
       <c r="H17" s="59">
         <f t="shared" si="4"/>
-        <v>21844696.016044192</v>
+        <v>19773771.773106463</v>
       </c>
       <c r="I17" s="60">
         <f t="shared" si="2"/>
-        <v>0.74458662876907566</v>
+        <v>0.6739982122787469</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" si="5"/>
-        <v>910195.66733517474</v>
+        <v>823907.15721276926</v>
       </c>
       <c r="K17" s="59">
         <f t="shared" si="3"/>
-        <v>1235992.2810941229</v>
+        <v>1258645.6280942939</v>
       </c>
       <c r="L17" s="61" cm="1">
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
@@ -4236,7 +4379,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="92"/>
+      <c r="A18" s="91"/>
       <c r="B18" s="19" t="s">
         <v>83</v>
       </c>
@@ -4245,32 +4388,34 @@
       </c>
       <c r="D18" s="4">
         <f>IFERROR(+VLOOKUP(B18,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1318807.9914469167</v>
+      </c>
+      <c r="E18" s="4">
         <v>501148.95527489512</v>
       </c>
-      <c r="E18" s="4"/>
       <c r="F18" s="4">
         <f t="shared" si="8"/>
-        <v>501148.95527489512</v>
+        <v>817659.03617202165</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>2.0078480611064303E-2</v>
+        <v>5.2837904593572765E-2</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="4"/>
-        <v>12027574.926597483</v>
+        <v>15825695.897363</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0.48188353466554329</v>
+        <v>0.63405485512287318</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="5"/>
-        <v>501148.95527489512</v>
+        <v>659403.99572345836</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>1063406.8236837003</v>
+        <v>1074577.1776615039</v>
       </c>
       <c r="L18" s="63" cm="1">
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
@@ -4278,7 +4423,7 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="92"/>
+      <c r="A19" s="91"/>
       <c r="B19" s="19" t="s">
         <v>93</v>
       </c>
@@ -4287,40 +4432,42 @@
       </c>
       <c r="D19" s="4">
         <f>IFERROR(+VLOOKUP(B19,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1974051.5620993127</v>
+      </c>
+      <c r="E19" s="4">
         <v>1123309.4293535382</v>
       </c>
-      <c r="E19" s="4"/>
       <c r="F19" s="4">
         <f t="shared" si="8"/>
-        <v>1123309.4293535382</v>
+        <v>850742.13274577446</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>4.3443733900702539E-2</v>
+        <v>7.6345990275772435E-2</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="4"/>
-        <v>26959426.304484919</v>
+        <v>23688618.745191753</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>1.042649613616861</v>
+        <v>0.91615188330926922</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="5"/>
-        <v>1123309.4293535382</v>
+        <v>987025.78104965633</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
-        <v>1075362.6407020201</v>
+        <v>1085572.6637909403</v>
       </c>
       <c r="L19" s="63" cm="1">
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
-        <v>336992.82880606153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="92"/>
+      <c r="A20" s="91"/>
       <c r="B20" s="19" t="s">
         <v>96</v>
       </c>
@@ -4329,40 +4476,42 @@
       </c>
       <c r="D20" s="4">
         <f>IFERROR(+VLOOKUP(B20,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3804498.4929125779</v>
+      </c>
+      <c r="E20" s="4">
         <v>1545484.3455725485</v>
       </c>
-      <c r="E20" s="4"/>
       <c r="F20" s="4">
         <f t="shared" si="8"/>
-        <v>1545484.3455725485</v>
+        <v>2259014.1473400295</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>4.6067674877036321E-2</v>
+        <v>0.113404189530462</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="4"/>
-        <v>37091624.293741167</v>
+        <v>45653981.914950937</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>1.1056241970488718</v>
+        <v>1.360850274365544</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="5"/>
-        <v>1545484.3455725485</v>
+        <v>1902249.246456289</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>1391419.3762794544</v>
+        <v>1351983.2503221554</v>
       </c>
       <c r="L20" s="63" cm="1">
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
-        <v>556374.36440611747</v>
+        <v>913079.63829901873</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="92"/>
+      <c r="A21" s="91"/>
       <c r="B21" s="19" t="s">
         <v>98</v>
       </c>
@@ -4371,40 +4520,42 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2482567.9113498144</v>
+      </c>
+      <c r="E21" s="4">
         <v>1299165.9114931743</v>
       </c>
-      <c r="E21" s="4"/>
       <c r="F21" s="4">
         <f t="shared" ref="F21:F23" si="9">+D21-E21</f>
-        <v>1299165.9114931743</v>
+        <v>1183401.9998566401</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>5.103071277514569E-2</v>
+        <v>9.7514265813270856E-2</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>31179981.875836182</v>
+        <v>29790814.936197773</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>1.2247371066034964</v>
+        <v>1.1701711897592504</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>1299165.9114931743</v>
+        <v>1241283.9556749072</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1050406.2647176881</v>
+        <v>1044361.0040295538</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
-        <v>623599.63751672371</v>
+        <v>595816.29872395552</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="92"/>
+      <c r="A22" s="91"/>
       <c r="B22" s="19" t="s">
         <v>101</v>
       </c>
@@ -4413,40 +4564,42 @@
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3717567.9331198842</v>
+      </c>
+      <c r="E22" s="4">
         <v>1904211.5763949119</v>
       </c>
-      <c r="E22" s="4"/>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>1904211.5763949119</v>
+        <v>1813356.3567249724</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>5.9988601050414488E-2</v>
+        <v>0.1171149794393922</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>45701077.833477885</v>
+        <v>44610815.197438613</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>1.4397264252099478</v>
+        <v>1.4053797532727064</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>1904211.5763949119</v>
+        <v>1858783.9665599421</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>1297333.8532002214</v>
+        <v>1273878.2848581872</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
-        <v>914021.5566695577</v>
+        <v>892216.30394877226</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="92"/>
+      <c r="A23" s="91"/>
       <c r="B23" s="19" t="s">
         <v>162</v>
       </c>
@@ -4455,32 +4608,34 @@
       </c>
       <c r="D23" s="4">
         <f>IFERROR(+VLOOKUP(B23,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2007902.2622231084</v>
+      </c>
+      <c r="E23" s="4">
         <v>831624.25115675328</v>
       </c>
-      <c r="E23" s="4"/>
       <c r="F23" s="4">
         <f t="shared" si="9"/>
-        <v>831624.25115675328</v>
+        <v>1176278.0110663553</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>3.0311484218007712E-2</v>
+        <v>7.3185092483799785E-2</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>19958982.027762078</v>
+        <v>24094827.1466773</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>0.72747562123218501</v>
+        <v>0.87822110980559742</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="5"/>
-        <v>831624.25115675328</v>
+        <v>1003951.1311115542</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>1156709.6512540544</v>
+        <v>1155820.1803534953</v>
       </c>
       <c r="L23" s="63" cm="1">
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
@@ -4488,7 +4643,7 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="92"/>
+      <c r="A24" s="91"/>
       <c r="B24" s="19" t="s">
         <v>109</v>
       </c>
@@ -4497,32 +4652,34 @@
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2373341.2642009868</v>
+      </c>
+      <c r="E24" s="4">
         <v>855590.57458566967</v>
       </c>
-      <c r="E24" s="4"/>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>855590.57458566967</v>
+        <v>1517750.6896153172</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>2.5544550356344422E-2</v>
+        <v>7.0858582641038448E-2</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>20534173.790056072</v>
+        <v>28480095.17041184</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>0.6130692085522661</v>
+        <v>0.85030299169246126</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>855590.57458566967</v>
+        <v>1186670.6321004934</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>1419063.6706701883</v>
+        <v>1414577.8970817735</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
@@ -4530,7 +4687,7 @@
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="92"/>
+      <c r="A25" s="91"/>
       <c r="B25" s="19" t="s">
         <v>140</v>
       </c>
@@ -4539,32 +4696,34 @@
       </c>
       <c r="D25" s="4">
         <f>IFERROR(+VLOOKUP(B25,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="4"/>
+        <v>-2433547.0814999999</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
       <c r="F25" s="4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-2433547.0814999999</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-4.5011545419757569E-2</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-29202564.978</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.5401385450370908</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-1216773.5407499999</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>2350650.1245652176</v>
+        <v>2568113.6339318189</v>
       </c>
       <c r="L25" s="63" cm="1">
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;109%,H25*0.015,I25&gt;104%,H25*0.0125,I25&gt;99%,H25*0.01,I25&lt;99%,H25*0)</f>
@@ -4572,44 +4731,46 @@
       </c>
     </row>
     <row r="26" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="93"/>
+      <c r="A26" s="92"/>
       <c r="B26" s="72"/>
       <c r="C26" s="67">
         <v>285898658.49300003</v>
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
+        <v>16893004.650278136</v>
+      </c>
+      <c r="E26" s="65">
         <v>8970730.711166665</v>
       </c>
-      <c r="E26" s="65"/>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>8970730.711166665</v>
+        <v>7922273.9391114712</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>3.1377309562948874E-2</v>
+        <v>5.9087386905985591E-2</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>215297537.06799996</v>
+        <v>202716055.80333763</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>0.75305542951077309</v>
+        <v>0.70904864287182712</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>8970730.711166665</v>
+        <v>8446502.3251390681</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>12040344.686166668</v>
+        <v>12227529.720123721</v>
       </c>
       <c r="L26" s="68"/>
     </row>
     <row r="27" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="88" t="s">
+      <c r="A27" s="87" t="s">
         <v>228</v>
       </c>
       <c r="B27" s="57" t="s">
@@ -4620,32 +4781,34 @@
       </c>
       <c r="D27" s="59">
         <f>IFERROR(+VLOOKUP(B27,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5151540.6591492426</v>
+      </c>
+      <c r="E27" s="59">
         <v>2145545.2733516009</v>
       </c>
-      <c r="E27" s="59"/>
       <c r="F27" s="59">
         <f t="shared" si="8"/>
-        <v>2145545.2733516009</v>
+        <v>3005995.3857976417</v>
       </c>
       <c r="G27" s="60">
         <f t="shared" si="1"/>
-        <v>2.6172303850334918E-2</v>
+        <v>6.2840756195273142E-2</v>
       </c>
       <c r="H27" s="59">
         <f t="shared" si="4"/>
-        <v>51493086.560438424</v>
+        <v>61818487.909790911</v>
       </c>
       <c r="I27" s="60">
         <f t="shared" si="2"/>
-        <v>0.62813529240803812</v>
+        <v>0.75408907434327765</v>
       </c>
       <c r="J27" s="59">
         <f t="shared" si="5"/>
-        <v>2145545.2733516009</v>
+        <v>2575770.3295746213</v>
       </c>
       <c r="K27" s="59">
         <f t="shared" si="3"/>
-        <v>3470963.2489847131</v>
+        <v>3492098.1518568527</v>
       </c>
       <c r="L27" s="61" cm="1">
         <f t="array" ref="L27">+_xlfn.IFS(I27&gt;114%,H27*0.0125,I27&gt;109%,H27*0.01,I27&gt;104%,H27*0.0075,I27&gt;99%,H27*0.005,I27&lt;99%,H27*0)</f>
@@ -4653,7 +4816,7 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="89"/>
+      <c r="A28" s="88"/>
       <c r="B28" s="36" t="s">
         <v>216</v>
       </c>
@@ -4662,32 +4825,34 @@
       </c>
       <c r="D28" s="4">
         <f>IFERROR(+VLOOKUP(B28,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1127867.2813395613</v>
+      </c>
+      <c r="E28" s="4">
         <v>682680.93729586795</v>
       </c>
-      <c r="E28" s="4"/>
       <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>682680.93729586795</v>
+        <v>445186.34404369339</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>3.2508616061707997E-2</v>
+        <v>5.3707965778074351E-2</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
-        <v>16384342.49510083</v>
+        <v>13534407.376074735</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>0.78020678548099187</v>
+        <v>0.64449558933689211</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="5"/>
-        <v>682680.93729586795</v>
+        <v>563933.64066978067</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>883361.69837844046</v>
+        <v>903278.75993911095</v>
       </c>
       <c r="L28" s="63" cm="1">
         <f t="array" ref="L28">+_xlfn.IFS(I28&gt;114%,H28*0.02,I28&gt;109%,H28*0.015,I28&gt;104%,H28*0.0125,I28&gt;99%,H28*0.01,I28&lt;99%,H28*0)</f>
@@ -4695,7 +4860,7 @@
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="89"/>
+      <c r="A29" s="88"/>
       <c r="B29" s="36" t="s">
         <v>87</v>
       </c>
@@ -4704,41 +4869,43 @@
       </c>
       <c r="D29" s="4">
         <f>IFERROR(+VLOOKUP(B29,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3336344.5485263281</v>
+      </c>
+      <c r="E29" s="4">
         <v>560866.8378297271</v>
       </c>
-      <c r="E29" s="4"/>
       <c r="F29" s="4">
         <f t="shared" si="8"/>
-        <v>560866.8378297271</v>
+        <v>2775477.7106966008</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>2.1789952401532538E-2</v>
+        <v>0.12961862603396029</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
-        <v>13460804.107913449</v>
+        <v>40036134.582315937</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>0.52295885763678085</v>
+        <v>1.5554235124075237</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="5"/>
-        <v>560866.8378297271</v>
+        <v>1668172.274263164</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>1094731.8766160987</v>
+        <v>1018334.3387033488</v>
       </c>
       <c r="L29" s="63" cm="1">
         <f t="array" ref="L29">+_xlfn.IFS(I29&gt;114%,H29*0.02,I29&gt;109%,H29*0.015,I29&gt;104%,H29*0.0125,I29&gt;99%,H29*0.01,I29&lt;99%,H29*0)</f>
-        <v>0</v>
+        <v>800722.69164631877</v>
       </c>
       <c r="M29" s="27"/>
     </row>
     <row r="30" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="89"/>
+      <c r="A30" s="88"/>
       <c r="B30" s="36" t="s">
         <v>215</v>
       </c>
@@ -4747,32 +4914,34 @@
       </c>
       <c r="D30" s="4">
         <f>IFERROR(+VLOOKUP(B30,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1465987.5738126547</v>
+      </c>
+      <c r="E30" s="4">
         <v>1241096.8257165046</v>
       </c>
-      <c r="E30" s="4"/>
       <c r="F30" s="4">
         <f t="shared" si="8"/>
-        <v>1241096.8257165046</v>
+        <v>224890.74809615011</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>3.2461228978234169E-2</v>
+        <v>3.8343308375883879E-2</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="4"/>
-        <v>29786323.817196108</v>
+        <v>17591850.885751858</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>0.77906949547761994</v>
+        <v>0.46011970051060663</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="5"/>
-        <v>1241096.8257165046</v>
+        <v>732993.78690632735</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>1608352.534191703</v>
+        <v>1671237.1608324097</v>
       </c>
       <c r="L30" s="63" cm="1">
         <f t="array" ref="L30">+_xlfn.IFS(I30&gt;114%,H30*0.02,I30&gt;109%,H30*0.015,I30&gt;104%,H30*0.0125,I30&gt;99%,H30*0.01,I30&lt;99%,H30*0)</f>
@@ -4781,7 +4950,7 @@
       <c r="M30" s="26"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="89"/>
+      <c r="A31" s="88"/>
       <c r="B31" s="36" t="s">
         <v>99</v>
       </c>
@@ -4790,41 +4959,43 @@
       </c>
       <c r="D31" s="4">
         <f>IFERROR(+VLOOKUP(B31,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2185400.7533588032</v>
+      </c>
+      <c r="E31" s="4">
         <v>967034.52092210797</v>
       </c>
-      <c r="E31" s="4"/>
       <c r="F31" s="4">
         <f t="shared" si="8"/>
-        <v>967034.52092210797</v>
+        <v>1218366.2324366951</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>3.8049380624707918E-2</v>
+        <v>8.5987773221148853E-2</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="4"/>
-        <v>23208828.50213059</v>
+        <v>26224809.040305637</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>0.91318513499299003</v>
+        <v>1.0318532786537862</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="5"/>
-        <v>967034.52092210797</v>
+        <v>1092700.3766794016</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>1062965.8903946909</v>
+        <v>1055902.2384836907</v>
       </c>
       <c r="L31" s="63" cm="1">
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
-        <v>0</v>
+        <v>262248.09040305635</v>
       </c>
       <c r="M31" s="27"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="89"/>
+      <c r="A32" s="88"/>
       <c r="B32" s="36" t="s">
         <v>213</v>
       </c>
@@ -4833,32 +5004,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>772280.47046408884</v>
+      </c>
+      <c r="E32" s="4">
         <v>235546.28047396851</v>
       </c>
-      <c r="E32" s="4"/>
       <c r="F32" s="4">
         <f t="shared" si="8"/>
-        <v>235546.28047396851</v>
+        <v>536734.18999012036</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>9.347074621982877E-3</v>
+        <v>3.064605041524162E-2</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>5653110.7313752444</v>
+        <v>9267365.6455690656</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.22432979092758906</v>
+        <v>0.36775260498289941</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>235546.28047396851</v>
+        <v>386140.23523204442</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1085411.0312837404</v>
+        <v>1110350.8877061778</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -4867,7 +5040,7 @@
       <c r="M32" s="26"/>
     </row>
     <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="89"/>
+      <c r="A33" s="88"/>
       <c r="B33" s="36" t="s">
         <v>100</v>
       </c>
@@ -4876,32 +5049,34 @@
       </c>
       <c r="D33" s="4">
         <f>IFERROR(+VLOOKUP(B33,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1312962.2237802313</v>
+      </c>
+      <c r="E33" s="4">
         <v>370995.20136279258</v>
       </c>
-      <c r="E33" s="4"/>
       <c r="F33" s="4">
         <f t="shared" si="8"/>
-        <v>370995.20136279258</v>
+        <v>941967.02241743868</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>1.4001536088870996E-2</v>
+        <v>4.9551821403765794E-2</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="4"/>
-        <v>8903884.8327070214</v>
+        <v>15755546.685362775</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>0.3360368661329039</v>
+        <v>0.59462185684518953</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="5"/>
-        <v>370995.20136279258</v>
+        <v>656481.11189011566</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>1135902.3825494437</v>
+        <v>1144717.6261918077</v>
       </c>
       <c r="L33" s="63" cm="1">
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
@@ -4909,7 +5084,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="89"/>
+      <c r="A34" s="88"/>
       <c r="B34" s="36" t="s">
         <v>139</v>
       </c>
@@ -4918,32 +5093,34 @@
       </c>
       <c r="D34" s="4">
         <f>IFERROR(+VLOOKUP(B34,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1012363.4850253685</v>
+      </c>
+      <c r="E34" s="4">
         <v>602361.45632991486</v>
       </c>
-      <c r="E34" s="4"/>
       <c r="F34" s="4">
         <f t="shared" si="8"/>
-        <v>602361.45632991486</v>
+        <v>410002.02869545366</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>2.8683878872853088E-2</v>
+        <v>4.8207785001208023E-2</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="4"/>
-        <v>14456674.951917958</v>
+        <v>12148361.820304422</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>0.68841309294847419</v>
+        <v>0.57849342001449622</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="5"/>
-        <v>602361.45632991486</v>
+        <v>506181.74251268426</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>886853.84972478624</v>
+        <v>908528.9324988469</v>
       </c>
       <c r="L34" s="63" cm="1">
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
@@ -4951,7 +5128,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="89"/>
+      <c r="A35" s="88"/>
       <c r="B35" s="19" t="s">
         <v>104</v>
       </c>
@@ -4960,32 +5137,34 @@
       </c>
       <c r="D35" s="4">
         <f>IFERROR(+VLOOKUP(B35,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>474208.7541035653</v>
+      </c>
+      <c r="E35" s="4">
         <v>269184.13865821779</v>
       </c>
-      <c r="E35" s="4"/>
       <c r="F35" s="4">
         <f t="shared" si="8"/>
-        <v>269184.13865821779</v>
+        <v>205024.6154453475</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>1.0916617541354106E-2</v>
+        <v>1.9231280227411787E-2</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="4"/>
-        <v>6460419.3277972266</v>
+        <v>5690505.0492427833</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>0.26199882099249849</v>
+        <v>0.23077536272894142</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="5"/>
-        <v>269184.13865821779</v>
+        <v>237104.37705178265</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>1060391.9939713818</v>
+        <v>1099272.3293589288</v>
       </c>
       <c r="L35" s="63" cm="1">
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.02,I35&gt;109%,H35*0.015,I35&gt;104%,H35*0.0125,I35&gt;99%,H35*0.01,I35&lt;99%,H35*0)</f>
@@ -4993,7 +5172,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="89"/>
+      <c r="A36" s="88"/>
       <c r="B36" s="36" t="s">
         <v>207</v>
       </c>
@@ -5002,40 +5181,42 @@
       </c>
       <c r="D36" s="4">
         <f>IFERROR(+VLOOKUP(B36,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1231155.9948169386</v>
+      </c>
+      <c r="E36" s="4">
         <v>1074255.4229483344</v>
       </c>
-      <c r="E36" s="4"/>
       <c r="F36" s="4">
         <f t="shared" si="8"/>
-        <v>1074255.4229483344</v>
+        <v>156900.57186860428</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>4.2570058369262309E-2</v>
+        <v>4.8787636014144584E-2</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="4"/>
-        <v>25782130.150760025</v>
+        <v>14773871.937803265</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>1.0216814008622954</v>
+        <v>0.58545163216973506</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="5"/>
-        <v>1074255.4229483344</v>
+        <v>615577.99740846932</v>
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>1050467.1555239854</v>
+        <v>1091083.8184174118</v>
       </c>
       <c r="L36" s="63" cm="1">
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;114%,H36*0.02,I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
-        <v>257821.30150760026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="89"/>
+      <c r="A37" s="88"/>
       <c r="B37" s="36" t="s">
         <v>111</v>
       </c>
@@ -5044,32 +5225,34 @@
       </c>
       <c r="D37" s="4">
         <f>IFERROR(+VLOOKUP(B37,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>-974804.98299181263</v>
+      </c>
+      <c r="E37" s="4">
         <v>-41520.785791812603</v>
       </c>
-      <c r="E37" s="4"/>
       <c r="F37" s="4">
         <f t="shared" si="8"/>
-        <v>-41520.785791812603</v>
+        <v>-933284.19720000005</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
-        <v>-3.4030153482605242E-4</v>
+        <v>-7.9894353043195639E-3</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="4"/>
-        <v>-996498.85900350241</v>
+        <v>-11697659.795901751</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>-8.1672368358252576E-3</v>
+        <v>-9.5873223651834774E-2</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="5"/>
-        <v>-41520.785791812603</v>
+        <v>-487402.49149590632</v>
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>5306663.9472083393</v>
+        <v>5590297.9537723549</v>
       </c>
       <c r="L37" s="63" cm="1">
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.0125,I37&gt;109%,H37*0.01,I37&gt;104%,H37*0.0075,I37&gt;99%,H37*0.005,I37&lt;99%,H37*0)</f>
@@ -5077,7 +5260,7 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="89"/>
+      <c r="A38" s="88"/>
       <c r="B38" s="36" t="s">
         <v>217</v>
       </c>
@@ -5088,7 +5271,9 @@
         <f>IFERROR(+VLOOKUP(B38,COMISIONES!A:E,5,FALSE),"0")*1</f>
         <v>0</v>
       </c>
-      <c r="E38" s="4"/>
+      <c r="E38" s="4">
+        <v>0</v>
+      </c>
       <c r="F38" s="4">
         <f t="shared" ref="F38" si="10">+D38-E38</f>
         <v>0</v>
@@ -5111,7 +5296,7 @@
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>1552173.9130434783</v>
+        <v>1622727.2727272727</v>
       </c>
       <c r="L38" s="63" cm="1">
         <f t="array" ref="L38">+_xlfn.IFS(I38&gt;109%,H38*0.015,I38&gt;104%,H38*0.0125,I38&gt;99%,H38*0.01,I38&lt;99%,H38*0)</f>
@@ -5119,7 +5304,7 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="89"/>
+      <c r="A39" s="88"/>
       <c r="B39" s="36" t="s">
         <v>81</v>
       </c>
@@ -5128,72 +5313,76 @@
       </c>
       <c r="D39" s="4">
         <f>IFERROR(+VLOOKUP(B39,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3667023.6813626946</v>
+      </c>
+      <c r="E39" s="4">
         <v>2409808.6857678718</v>
       </c>
-      <c r="E39" s="4"/>
       <c r="F39" s="4">
         <f t="shared" si="8"/>
-        <v>2409808.6857678718</v>
+        <v>1257214.9955948228</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>6.6273764139992641E-2</v>
+        <v>0.10084927653788393</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="4"/>
-        <v>57835408.458428919</v>
+        <v>44004284.176352337</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>1.5905703393598232</v>
+        <v>1.2101913184546071</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="5"/>
-        <v>2409808.6857678718</v>
+        <v>1833511.8406813473</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>1476157.3501405271</v>
+        <v>1486109.2753471502</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
-        <v>1156708.1691685785</v>
+        <v>880085.68352704681</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="90"/>
+      <c r="A40" s="89"/>
       <c r="B40" s="3"/>
       <c r="C40" s="75">
         <v>509028982.85112572</v>
       </c>
       <c r="D40" s="67">
         <f>+SUM(D27:D39)</f>
+        <v>20762330.442747667</v>
+      </c>
+      <c r="E40" s="65">
         <v>10517854.794865096</v>
       </c>
-      <c r="E40" s="65"/>
       <c r="F40" s="67">
         <f t="shared" si="8"/>
-        <v>10517854.794865096</v>
+        <v>10244475.647882571</v>
       </c>
       <c r="G40" s="66">
         <f t="shared" si="1"/>
-        <v>2.0662585332476488E-2</v>
+        <v>4.0788110583518521E-2</v>
       </c>
       <c r="H40" s="64">
         <f t="shared" si="4"/>
-        <v>252428515.07676232</v>
+        <v>249147965.31297201</v>
       </c>
       <c r="I40" s="66">
         <f t="shared" si="2"/>
-        <v>0.49590204797943577</v>
+        <v>0.48945732700222222</v>
       </c>
       <c r="J40" s="64">
         <f t="shared" si="5"/>
-        <v>10517854.794865096</v>
+        <v>10381165.221373834</v>
       </c>
       <c r="K40" s="67">
         <f t="shared" si="3"/>
-        <v>21674396.872011334</v>
+        <v>22193938.745835368</v>
       </c>
       <c r="L40" s="68"/>
     </row>
@@ -5207,32 +5396,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
+        <v>105866448.03886795</v>
+      </c>
+      <c r="E41" s="82">
         <v>62468472.547462374</v>
       </c>
-      <c r="E41" s="82"/>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>62468472.547462374</v>
+        <v>43397975.491405576</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>4.5274648464467077E-2</v>
+        <v>7.6727764001270155E-2</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1499243341.139097</v>
+        <v>1270397376.4664154</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>1.0865915631472098</v>
+        <v>0.92073316801524185</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>62468472.547462374</v>
+        <v>52933224.019433975</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>57273855.415029287</v>
+        <v>57904577.229739457</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -5283,11 +5474,11 @@
         <v>0</v>
       </c>
       <c r="E43" s="4">
-        <v>22657877.380181327</v>
+        <v>0</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" ref="F43" si="11">+D43-E43</f>
-        <v>-22657877.380181327</v>
+        <v>0</v>
       </c>
       <c r="G43" s="5">
         <f>+D43/C43</f>
@@ -5307,7 +5498,7 @@
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>1739130.4347826086</v>
+        <v>1818181.8181818181</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
@@ -5323,34 +5514,34 @@
       </c>
       <c r="D44" s="4">
         <f>IFERROR(+VLOOKUP(B44,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>-388379.73864699452</v>
       </c>
       <c r="E44" s="4">
-        <v>16555407.699089281</v>
+        <v>0</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" ref="F44" si="14">+D44-E44</f>
-        <v>-16555407.699089281</v>
+        <v>-388379.73864699452</v>
       </c>
       <c r="G44" s="5">
         <f>+D44/C44</f>
-        <v>0</v>
+        <v>-1.2945991288233151E-2</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>0</v>
+        <v>-4660556.863763934</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>0</v>
+        <v>-0.1553518954587978</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>0</v>
+        <v>-194189.86932349726</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>1304347.8260869565</v>
+        <v>1381289.9881203179</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
@@ -5480,7 +5671,7 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="93" t="s">
         <v>37</v>
       </c>
       <c r="B2">
@@ -5492,14 +5683,14 @@
       </c>
       <c r="D2" s="22">
         <f>H2/G2</f>
-        <v>0.79166666666666663</v>
+        <v>6.9444444444444448E-2</v>
       </c>
       <c r="E2" s="13">
         <v>33</v>
       </c>
       <c r="F2" s="12">
         <f>+H2-E2</f>
-        <v>24</v>
+        <v>-28</v>
       </c>
       <c r="G2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5507,11 +5698,11 @@
       </c>
       <c r="H2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="I2" s="17">
         <f>(+G2*$M$2)-H2</f>
-        <v>4.1999999999999957</v>
+        <v>56.199999999999996</v>
       </c>
       <c r="J2" t="s">
         <v>55</v>
@@ -5547,7 +5738,7 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="94"/>
+      <c r="A3" s="93"/>
       <c r="B3">
         <v>49</v>
       </c>
@@ -5557,14 +5748,14 @@
       </c>
       <c r="D3" s="22">
         <f t="shared" ref="D3:D38" si="0">H3/G3</f>
-        <v>0.42259414225941422</v>
+        <v>0.23012552301255229</v>
       </c>
       <c r="E3" s="13">
         <v>1</v>
       </c>
       <c r="F3" s="12">
         <f t="shared" ref="F3:F38" si="1">+H3-E3</f>
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="G3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5572,11 +5763,11 @@
       </c>
       <c r="H3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="I3" s="17">
         <f t="shared" ref="I3:I38" si="2">(+G3*$M$2)-H3</f>
-        <v>102.15</v>
+        <v>148.15</v>
       </c>
       <c r="J3" t="s">
         <v>56</v>
@@ -5595,18 +5786,18 @@
         <v>148 - ALMACEN</v>
       </c>
       <c r="S3" s="12">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="T3" s="12">
         <v>213</v>
       </c>
       <c r="U3" s="41">
         <f>+S3/T3</f>
-        <v>0.30985915492957744</v>
+        <v>5.1643192488262914E-2</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="94"/>
+      <c r="A4" s="93"/>
       <c r="B4">
         <v>20</v>
       </c>
@@ -5616,14 +5807,14 @@
       </c>
       <c r="D4" s="22">
         <f t="shared" si="0"/>
-        <v>0.92920353982300885</v>
+        <v>0.11504424778761062</v>
       </c>
       <c r="E4" s="13">
         <v>126</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" si="1"/>
-        <v>84</v>
+        <v>-100</v>
       </c>
       <c r="G4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5631,11 +5822,11 @@
       </c>
       <c r="H4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>210</v>
+        <v>26</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>-17.900000000000006</v>
+        <v>166.1</v>
       </c>
       <c r="J4" t="s">
         <v>57</v>
@@ -5653,18 +5844,18 @@
         <v>148 - Articulos Sin Asociar Agrupacion</v>
       </c>
       <c r="S4" s="13">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="T4" s="13">
         <v>213</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U11" si="3">+S4/T4</f>
-        <v>0.27230046948356806</v>
+        <v>1.4084507042253521E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="94"/>
+      <c r="A5" s="93"/>
       <c r="B5">
         <v>15</v>
       </c>
@@ -5674,14 +5865,14 @@
       </c>
       <c r="D5" s="22">
         <f t="shared" si="0"/>
-        <v>0.81538461538461537</v>
+        <v>0.12307692307692308</v>
       </c>
       <c r="E5" s="13">
         <v>21</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>-13</v>
       </c>
       <c r="G5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5689,11 +5880,11 @@
       </c>
       <c r="H5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>2.25</v>
+        <v>47.25</v>
       </c>
       <c r="K5" t="s">
         <v>64</v>
@@ -5708,18 +5899,18 @@
         <v>148 - BEBIDAS</v>
       </c>
       <c r="S5" s="13">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="T5" s="13">
         <v>213</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="3"/>
-        <v>0.42253521126760563</v>
+        <v>2.8169014084507043E-2</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="94"/>
+      <c r="A6" s="93"/>
       <c r="B6">
         <v>19</v>
       </c>
@@ -5729,14 +5920,14 @@
       </c>
       <c r="D6" s="22">
         <f t="shared" si="0"/>
-        <v>0.88405797101449279</v>
+        <v>0.15458937198067632</v>
       </c>
       <c r="E6" s="13">
         <v>100</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" si="1"/>
-        <v>83</v>
+        <v>-68</v>
       </c>
       <c r="G6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5744,11 +5935,11 @@
       </c>
       <c r="H6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>183</v>
+        <v>32</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>-7.0500000000000114</v>
+        <v>143.94999999999999</v>
       </c>
       <c r="J6" t="s">
         <v>58</v>
@@ -5766,18 +5957,18 @@
         <v>148 - CHOCOLATE</v>
       </c>
       <c r="S6" s="13">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="T6" s="13">
         <v>213</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="3"/>
-        <v>0.23943661971830985</v>
+        <v>2.3474178403755867E-2</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="94"/>
+      <c r="A7" s="93"/>
       <c r="B7">
         <v>16</v>
       </c>
@@ -5787,14 +5978,14 @@
       </c>
       <c r="D7" s="22">
         <f t="shared" si="0"/>
-        <v>0.85858585858585856</v>
+        <v>0.11616161616161616</v>
       </c>
       <c r="E7" s="13">
         <v>81</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>89</v>
+        <v>-58</v>
       </c>
       <c r="G7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5802,11 +5993,11 @@
       </c>
       <c r="H7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>170</v>
+        <v>23</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>-1.7000000000000171</v>
+        <v>145.29999999999998</v>
       </c>
       <c r="J7" t="s">
         <v>58</v>
@@ -5824,18 +6015,18 @@
         <v>148 - GALLETITAS</v>
       </c>
       <c r="S7" s="13">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="T7" s="13">
         <v>213</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="3"/>
-        <v>0.50234741784037562</v>
+        <v>6.5727699530516437E-2</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="94"/>
+      <c r="A8" s="93"/>
       <c r="B8">
         <v>12</v>
       </c>
@@ -5845,14 +6036,14 @@
       </c>
       <c r="D8" s="22">
         <f t="shared" si="0"/>
-        <v>0.85915492957746475</v>
+        <v>0.12676056338028169</v>
       </c>
       <c r="E8" s="13">
         <v>89</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>94</v>
+        <v>-62</v>
       </c>
       <c r="G8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5860,11 +6051,11 @@
       </c>
       <c r="H8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>183</v>
+        <v>27</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>-1.9500000000000171</v>
+        <v>154.04999999999998</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
@@ -5883,18 +6074,18 @@
         <v>148 - GOLOSINAS</v>
       </c>
       <c r="S8" s="13">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="T8" s="13">
         <v>213</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="3"/>
-        <v>0.38967136150234744</v>
+        <v>5.6338028169014086E-2</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="94"/>
+      <c r="A9" s="93"/>
       <c r="B9">
         <v>11</v>
       </c>
@@ -5904,26 +6095,26 @@
       </c>
       <c r="D9" s="22">
         <f>H9/G9</f>
-        <v>0.7407407407407407</v>
+        <v>0.10303030303030303</v>
       </c>
       <c r="E9" s="13">
         <v>92</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>-75</v>
       </c>
       <c r="G9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>17.699999999999989</v>
+        <v>123.25</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
@@ -5941,18 +6132,18 @@
         <v>148 - MASCOTAS</v>
       </c>
       <c r="S9" s="13">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="T9" s="13">
         <v>213</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="3"/>
-        <v>0.10328638497652583</v>
+        <v>1.8779342723004695E-2</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="94"/>
+      <c r="A10" s="93"/>
       <c r="B10">
         <v>8</v>
       </c>
@@ -5962,14 +6153,14 @@
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
-        <v>0.865979381443299</v>
+        <v>8.7628865979381437E-2</v>
       </c>
       <c r="E10" s="13">
         <v>64</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>104</v>
+        <v>-47</v>
       </c>
       <c r="G10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5977,11 +6168,11 @@
       </c>
       <c r="H10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>168</v>
+        <v>17</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>-3.0999999999999943</v>
+        <v>147.9</v>
       </c>
       <c r="J10" t="s">
         <v>58</v>
@@ -5999,18 +6190,18 @@
         <v>148 - NO PERECEDEROS</v>
       </c>
       <c r="S10" s="13">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="T10" s="13">
         <v>213</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
-        <v>0.215962441314554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="94"/>
+      <c r="A11" s="93"/>
       <c r="B11">
         <v>52</v>
       </c>
@@ -6020,14 +6211,14 @@
       </c>
       <c r="D11" s="32">
         <f t="shared" si="0"/>
-        <v>0.57425742574257421</v>
+        <v>2.9702970297029702E-2</v>
       </c>
       <c r="E11" s="31">
         <v>19</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
-        <v>39</v>
+        <v>-16</v>
       </c>
       <c r="G11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6035,11 +6226,11 @@
       </c>
       <c r="H11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="I11" s="34">
         <f t="shared" si="2"/>
-        <v>27.849999999999994</v>
+        <v>82.85</v>
       </c>
       <c r="J11" t="s">
         <v>59</v>
@@ -6054,18 +6245,18 @@
         <v>148 - PILAS</v>
       </c>
       <c r="S11" s="13">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="T11" s="13">
         <v>213</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="3"/>
-        <v>0.23943661971830985</v>
+        <v>4.6948356807511738E-3</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="94"/>
+      <c r="A12" s="93"/>
       <c r="B12">
         <v>53</v>
       </c>
@@ -6075,14 +6266,14 @@
       </c>
       <c r="D12" s="32">
         <f t="shared" si="0"/>
-        <v>0.64761904761904765</v>
+        <v>2.8571428571428571E-2</v>
       </c>
       <c r="E12" s="31">
         <v>24</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>-21</v>
       </c>
       <c r="G12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6090,18 +6281,18 @@
       </c>
       <c r="H12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="I12" s="34">
         <f t="shared" si="2"/>
-        <v>21.25</v>
+        <v>86.25</v>
       </c>
       <c r="J12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="94"/>
+      <c r="A13" s="93"/>
       <c r="B13">
         <v>5</v>
       </c>
@@ -6111,14 +6302,14 @@
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
-        <v>0.90384615384615385</v>
+        <v>0.10384615384615385</v>
       </c>
       <c r="E13" s="13">
         <v>144</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" si="1"/>
-        <v>91</v>
+        <v>-117</v>
       </c>
       <c r="G13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6126,11 +6317,11 @@
       </c>
       <c r="H13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>235</v>
+        <v>27</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>-14</v>
+        <v>194</v>
       </c>
       <c r="J13" t="s">
         <v>57</v>
@@ -6140,7 +6331,7 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="94"/>
+      <c r="A14" s="93"/>
       <c r="B14">
         <v>4</v>
       </c>
@@ -6150,14 +6341,14 @@
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
-        <v>0.87912087912087911</v>
+        <v>0.11538461538461539</v>
       </c>
       <c r="E14" s="13">
         <v>85</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" si="1"/>
-        <v>75</v>
+        <v>-64</v>
       </c>
       <c r="G14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6165,11 +6356,11 @@
       </c>
       <c r="H14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="2"/>
-        <v>-5.3000000000000114</v>
+        <v>133.69999999999999</v>
       </c>
       <c r="J14" t="s">
         <v>55</v>
@@ -6179,26 +6370,26 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="95"/>
+      <c r="A15" s="94"/>
       <c r="C15" s="9"/>
       <c r="D15" s="23"/>
       <c r="E15" s="14"/>
       <c r="F15" s="16">
         <f>+SUM(F2:F14)</f>
-        <v>887</v>
+        <v>-615</v>
       </c>
       <c r="G15" s="8">
         <f>+SUM(G2:G14)</f>
-        <v>2224</v>
+        <v>2227</v>
       </c>
       <c r="H15" s="8">
         <f>+SUM(H2:H14)</f>
-        <v>1766</v>
+        <v>264</v>
       </c>
       <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="96" t="s">
+      <c r="A16" s="95" t="s">
         <v>38</v>
       </c>
       <c r="B16">
@@ -6210,14 +6401,14 @@
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
-        <v>0.87577639751552794</v>
+        <v>0.14906832298136646</v>
       </c>
       <c r="E16" s="13">
         <v>90</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" si="1"/>
-        <v>51</v>
+        <v>-66</v>
       </c>
       <c r="G16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6225,11 +6416,11 @@
       </c>
       <c r="H16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="2"/>
-        <v>-4.1500000000000057</v>
+        <v>112.85</v>
       </c>
       <c r="J16" t="s">
         <v>55</v>
@@ -6239,7 +6430,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="94"/>
+      <c r="A17" s="93"/>
       <c r="B17">
         <v>54</v>
       </c>
@@ -6249,14 +6440,14 @@
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
-        <v>0.74752475247524752</v>
+        <v>7.9207920792079209E-2</v>
       </c>
       <c r="E17" s="13">
         <v>92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="1"/>
-        <v>59</v>
+        <v>-76</v>
       </c>
       <c r="G17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6264,11 +6455,11 @@
       </c>
       <c r="H17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>151</v>
+        <v>16</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>20.699999999999989</v>
+        <v>155.69999999999999</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -6278,7 +6469,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="94"/>
+      <c r="A18" s="93"/>
       <c r="B18">
         <v>21</v>
       </c>
@@ -6288,26 +6479,26 @@
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
-        <v>0.88165680473372776</v>
+        <v>0.12352941176470589</v>
       </c>
       <c r="E18" s="13">
         <v>88</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="1"/>
-        <v>61</v>
+        <v>-67</v>
       </c>
       <c r="G18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>-5.3499999999999943</v>
+        <v>123.5</v>
       </c>
       <c r="J18" t="s">
         <v>58</v>
@@ -6317,7 +6508,7 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="94"/>
+      <c r="A19" s="93"/>
       <c r="B19">
         <v>23</v>
       </c>
@@ -6327,14 +6518,14 @@
       </c>
       <c r="D19" s="22">
         <f t="shared" si="0"/>
-        <v>0.86875000000000002</v>
+        <v>0.15</v>
       </c>
       <c r="E19" s="13">
         <v>95</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>-71</v>
       </c>
       <c r="G19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6342,11 +6533,11 @@
       </c>
       <c r="H19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="2"/>
-        <v>-3</v>
+        <v>112</v>
       </c>
       <c r="J19" t="s">
         <v>58</v>
@@ -6356,7 +6547,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="94"/>
+      <c r="A20" s="93"/>
       <c r="B20">
         <v>18</v>
       </c>
@@ -6366,26 +6557,26 @@
       </c>
       <c r="D20" s="22">
         <f t="shared" si="0"/>
-        <v>0.90340909090909094</v>
+        <v>0.11864406779661017</v>
       </c>
       <c r="E20" s="13">
         <v>83</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="1"/>
-        <v>76</v>
+        <v>-62</v>
       </c>
       <c r="G20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>-9.4000000000000057</v>
+        <v>129.44999999999999</v>
       </c>
       <c r="J20" t="s">
         <v>55</v>
@@ -6395,7 +6586,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="94"/>
+      <c r="A21" s="93"/>
       <c r="B21">
         <v>44</v>
       </c>
@@ -6405,14 +6596,14 @@
       </c>
       <c r="D21" s="22">
         <f t="shared" si="0"/>
-        <v>0.85798816568047342</v>
+        <v>0.15384615384615385</v>
       </c>
       <c r="E21" s="13">
         <v>64</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" si="1"/>
-        <v>81</v>
+        <v>-38</v>
       </c>
       <c r="G21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6420,11 +6611,11 @@
       </c>
       <c r="H21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>145</v>
+        <v>26</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="2"/>
-        <v>-1.3499999999999943</v>
+        <v>117.65</v>
       </c>
       <c r="J21" t="s">
         <v>58</v>
@@ -6434,7 +6625,7 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="94"/>
+      <c r="A22" s="93"/>
       <c r="B22">
         <v>56</v>
       </c>
@@ -6444,14 +6635,14 @@
       </c>
       <c r="D22" s="22">
         <f t="shared" si="0"/>
-        <v>0.51515151515151514</v>
+        <v>0</v>
       </c>
       <c r="E22" s="13">
         <v>66</v>
       </c>
       <c r="F22" s="12">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>-66</v>
       </c>
       <c r="G22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6459,11 +6650,11 @@
       </c>
       <c r="H22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="I22" s="17">
         <f t="shared" si="2"/>
-        <v>66.299999999999983</v>
+        <v>168.29999999999998</v>
       </c>
       <c r="J22" t="s">
         <v>58</v>
@@ -6473,7 +6664,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="94"/>
+      <c r="A23" s="93"/>
       <c r="B23">
         <v>2</v>
       </c>
@@ -6483,14 +6674,14 @@
       </c>
       <c r="D23" s="22">
         <f t="shared" si="0"/>
-        <v>0.88405797101449279</v>
+        <v>9.420289855072464E-2</v>
       </c>
       <c r="E23" s="13">
         <v>70</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" si="1"/>
-        <v>52</v>
+        <v>-57</v>
       </c>
       <c r="G23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6498,11 +6689,11 @@
       </c>
       <c r="H23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="I23" s="17">
         <f t="shared" si="2"/>
-        <v>-4.7000000000000028</v>
+        <v>104.3</v>
       </c>
       <c r="J23" t="s">
         <v>58</v>
@@ -6512,7 +6703,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="94"/>
+      <c r="A24" s="93"/>
       <c r="B24">
         <v>3</v>
       </c>
@@ -6522,14 +6713,14 @@
       </c>
       <c r="D24" s="22">
         <f t="shared" si="0"/>
-        <v>0.91176470588235292</v>
+        <v>0.1</v>
       </c>
       <c r="E24" s="13">
         <v>79</v>
       </c>
       <c r="F24" s="12">
         <f t="shared" si="1"/>
-        <v>76</v>
+        <v>-62</v>
       </c>
       <c r="G24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6537,11 +6728,11 @@
       </c>
       <c r="H24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="I24" s="17">
         <f t="shared" si="2"/>
-        <v>-10.5</v>
+        <v>127.5</v>
       </c>
       <c r="J24" t="s">
         <v>60</v>
@@ -6551,26 +6742,26 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="95"/>
+      <c r="A25" s="94"/>
       <c r="C25" s="9"/>
       <c r="D25" s="23"/>
       <c r="E25" s="14"/>
       <c r="F25" s="16">
         <f>+SUM(F16:F24)</f>
-        <v>536</v>
+        <v>-565</v>
       </c>
       <c r="G25" s="8">
         <f>+SUM(G16:G24)</f>
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="H25" s="8">
         <f>+SUM(H16:H24)</f>
-        <v>1263</v>
+        <v>162</v>
       </c>
       <c r="I25" s="8"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="96" t="s">
+      <c r="A26" s="95" t="s">
         <v>227</v>
       </c>
       <c r="B26">
@@ -6582,14 +6773,14 @@
       </c>
       <c r="D26" s="22">
         <f t="shared" si="0"/>
-        <v>0.8928571428571429</v>
+        <v>7.1428571428571425E-2</v>
       </c>
       <c r="E26" s="13">
         <v>20</v>
       </c>
       <c r="F26" s="12">
         <f>+H26-E26</f>
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="G26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6597,11 +6788,11 @@
       </c>
       <c r="H26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="I26" s="17">
         <f t="shared" si="2"/>
-        <v>-2.3999999999999986</v>
+        <v>43.6</v>
       </c>
       <c r="J26" t="s">
         <v>55</v>
@@ -6611,7 +6802,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="94"/>
+      <c r="A27" s="93"/>
       <c r="B27">
         <v>36</v>
       </c>
@@ -6621,14 +6812,14 @@
       </c>
       <c r="D27" s="22">
         <f t="shared" si="0"/>
-        <v>0.60897435897435892</v>
+        <v>0.11538461538461539</v>
       </c>
       <c r="E27" s="13">
         <v>68</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" si="1"/>
-        <v>27</v>
+        <v>-50</v>
       </c>
       <c r="G27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6636,11 +6827,11 @@
       </c>
       <c r="H27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" si="2"/>
-        <v>37.599999999999994</v>
+        <v>114.6</v>
       </c>
       <c r="J27" t="s">
         <v>58</v>
@@ -6650,7 +6841,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="94"/>
+      <c r="A28" s="93"/>
       <c r="B28">
         <v>9</v>
       </c>
@@ -6660,14 +6851,14 @@
       </c>
       <c r="D28" s="22">
         <f t="shared" si="0"/>
-        <v>0.86335403726708071</v>
+        <v>7.4534161490683232E-2</v>
       </c>
       <c r="E28" s="13">
         <v>80</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" si="1"/>
-        <v>59</v>
+        <v>-68</v>
       </c>
       <c r="G28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6675,11 +6866,11 @@
       </c>
       <c r="H28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="I28" s="17">
         <f t="shared" si="2"/>
-        <v>-2.1500000000000057</v>
+        <v>124.85</v>
       </c>
       <c r="J28" t="s">
         <v>58</v>
@@ -6689,7 +6880,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="94"/>
+      <c r="A29" s="93"/>
       <c r="B29">
         <v>40</v>
       </c>
@@ -6699,14 +6890,14 @@
       </c>
       <c r="D29" s="22">
         <f t="shared" si="0"/>
-        <v>0.50602409638554213</v>
+        <v>6.8273092369477914E-2</v>
       </c>
       <c r="E29" s="13">
         <v>68</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>-51</v>
       </c>
       <c r="G29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6714,11 +6905,11 @@
       </c>
       <c r="H29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" si="2"/>
-        <v>85.65</v>
+        <v>194.65</v>
       </c>
       <c r="J29" t="s">
         <v>58</v>
@@ -6728,7 +6919,7 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="94"/>
+      <c r="A30" s="93"/>
       <c r="B30">
         <v>27</v>
       </c>
@@ -6738,14 +6929,14 @@
       </c>
       <c r="D30" s="22">
         <f t="shared" si="0"/>
-        <v>0.8928571428571429</v>
+        <v>0.12857142857142856</v>
       </c>
       <c r="E30" s="13">
         <v>73</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" si="1"/>
-        <v>52</v>
+        <v>-55</v>
       </c>
       <c r="G30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6753,11 +6944,11 @@
       </c>
       <c r="H30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="2"/>
-        <v>-6</v>
+        <v>101</v>
       </c>
       <c r="J30" t="s">
         <v>55</v>
@@ -6767,7 +6958,7 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="94"/>
+      <c r="A31" s="93"/>
       <c r="B31">
         <v>10</v>
       </c>
@@ -6777,14 +6968,14 @@
       </c>
       <c r="D31" s="22">
         <f t="shared" si="0"/>
-        <v>0.72928176795580113</v>
+        <v>6.6298342541436461E-2</v>
       </c>
       <c r="E31" s="13">
         <v>40</v>
       </c>
       <c r="F31" s="12">
         <f t="shared" si="1"/>
-        <v>92</v>
+        <v>-28</v>
       </c>
       <c r="G31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6792,11 +6983,11 @@
       </c>
       <c r="H31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>132</v>
+        <v>12</v>
       </c>
       <c r="I31" s="17">
         <f t="shared" si="2"/>
-        <v>21.849999999999994</v>
+        <v>141.85</v>
       </c>
       <c r="J31" t="s">
         <v>58</v>
@@ -6806,7 +6997,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="94"/>
+      <c r="A32" s="93"/>
       <c r="B32">
         <v>28</v>
       </c>
@@ -6816,14 +7007,14 @@
       </c>
       <c r="D32" s="22">
         <f t="shared" si="0"/>
-        <v>0.875</v>
+        <v>0.13690476190476192</v>
       </c>
       <c r="E32" s="13">
         <v>67</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>-44</v>
       </c>
       <c r="G32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6831,11 +7022,11 @@
       </c>
       <c r="H32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="2"/>
-        <v>-4.2000000000000171</v>
+        <v>119.79999999999998</v>
       </c>
       <c r="J32" t="s">
         <v>58</v>
@@ -6845,7 +7036,7 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="94"/>
+      <c r="A33" s="93"/>
       <c r="B33">
         <v>33</v>
       </c>
@@ -6855,14 +7046,14 @@
       </c>
       <c r="D33" s="22">
         <f t="shared" si="0"/>
-        <v>0.79069767441860461</v>
+        <v>0.10465116279069768</v>
       </c>
       <c r="E33" s="13">
         <v>66</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>-48</v>
       </c>
       <c r="G33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6870,11 +7061,11 @@
       </c>
       <c r="H33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="I33" s="17">
         <f t="shared" si="2"/>
-        <v>10.199999999999989</v>
+        <v>128.19999999999999</v>
       </c>
       <c r="J33" t="s">
         <v>58</v>
@@ -6884,7 +7075,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="94"/>
+      <c r="A34" s="93"/>
       <c r="B34">
         <v>37</v>
       </c>
@@ -6894,14 +7085,14 @@
       </c>
       <c r="D34" s="22">
         <f t="shared" si="0"/>
-        <v>0.72340425531914898</v>
+        <v>3.5460992907801421E-2</v>
       </c>
       <c r="E34" s="13">
         <v>82</v>
       </c>
       <c r="F34" s="12">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>-77</v>
       </c>
       <c r="G34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6909,11 +7100,11 @@
       </c>
       <c r="H34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="I34" s="17">
         <f t="shared" si="2"/>
-        <v>17.849999999999994</v>
+        <v>114.85</v>
       </c>
       <c r="J34" t="s">
         <v>55</v>
@@ -6923,7 +7114,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="94"/>
+      <c r="A35" s="93"/>
       <c r="B35">
         <v>24</v>
       </c>
@@ -6933,14 +7124,14 @@
       </c>
       <c r="D35" s="22">
         <f t="shared" si="0"/>
-        <v>0.7247191011235955</v>
+        <v>7.8651685393258425E-2</v>
       </c>
       <c r="E35" s="13">
         <v>81</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" si="1"/>
-        <v>48</v>
+        <v>-67</v>
       </c>
       <c r="G35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6948,11 +7139,11 @@
       </c>
       <c r="H35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="I35" s="17">
         <f t="shared" si="2"/>
-        <v>22.299999999999983</v>
+        <v>137.29999999999998</v>
       </c>
       <c r="J35" t="s">
         <v>58</v>
@@ -6962,7 +7153,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="94"/>
+      <c r="A36" s="93"/>
       <c r="B36">
         <v>7</v>
       </c>
@@ -6972,14 +7163,14 @@
       </c>
       <c r="D36" s="22">
         <f t="shared" si="0"/>
-        <v>0.25663716814159293</v>
+        <v>0</v>
       </c>
       <c r="E36" s="13">
         <v>0</v>
       </c>
       <c r="F36" s="12">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6987,18 +7178,18 @@
       </c>
       <c r="H36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I36" s="17">
         <f t="shared" si="2"/>
-        <v>67.05</v>
+        <v>96.05</v>
       </c>
       <c r="J36" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="94"/>
+      <c r="A37" s="93"/>
       <c r="B37">
         <v>57</v>
       </c>
@@ -7008,14 +7199,14 @@
       </c>
       <c r="D37" s="22">
         <f t="shared" si="0"/>
-        <v>0.22330097087378642</v>
+        <v>0</v>
       </c>
       <c r="E37" s="13">
         <v>17</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>-17</v>
       </c>
       <c r="G37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7023,18 +7214,18 @@
       </c>
       <c r="H37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I37" s="17">
         <f t="shared" si="2"/>
-        <v>64.55</v>
+        <v>87.55</v>
       </c>
       <c r="J37" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="94"/>
+      <c r="A38" s="93"/>
       <c r="B38">
         <v>1</v>
       </c>
@@ -7044,14 +7235,14 @@
       </c>
       <c r="D38" s="22">
         <f t="shared" si="0"/>
-        <v>0.88976377952755903</v>
+        <v>0.14960629921259844</v>
       </c>
       <c r="E38" s="13">
         <v>60</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="1"/>
-        <v>53</v>
+        <v>-41</v>
       </c>
       <c r="G38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7059,11 +7250,11 @@
       </c>
       <c r="H38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="I38" s="17">
         <f t="shared" si="2"/>
-        <v>-5.0499999999999972</v>
+        <v>88.95</v>
       </c>
       <c r="J38" t="s">
         <v>55</v>
@@ -7073,13 +7264,13 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="95"/>
+      <c r="A39" s="94"/>
       <c r="C39" s="9"/>
       <c r="D39" s="23"/>
       <c r="E39" s="14"/>
       <c r="F39" s="8">
         <f>+SUM(F26:F38)</f>
-        <v>624</v>
+        <v>-562</v>
       </c>
       <c r="G39" s="8">
         <f>+SUM(G26:G38)</f>
@@ -7087,7 +7278,7 @@
       </c>
       <c r="H39" s="8">
         <f>+SUM(H26:H38)</f>
-        <v>1346</v>
+        <v>160</v>
       </c>
       <c r="I39" s="8"/>
       <c r="L39" t="s">
@@ -7103,20 +7294,20 @@
       <c r="E40" s="6"/>
       <c r="F40" s="8">
         <f>+SUM(F39+F25+F15)</f>
-        <v>2047</v>
+        <v>-1742</v>
       </c>
       <c r="G40" s="8">
         <f>+G15+G25+G39</f>
-        <v>5712</v>
+        <v>5717</v>
       </c>
       <c r="H40" s="8">
         <f>+H15+H25+H39</f>
-        <v>4375</v>
+        <v>586</v>
       </c>
       <c r="I40" s="8"/>
       <c r="L40" s="1">
         <f>+H40/G40</f>
-        <v>0.76593137254901966</v>
+        <v>0.10250131187685849</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -7129,14 +7320,14 @@
       </c>
       <c r="D41" s="22">
         <f t="shared" ref="D41:D42" si="4">H41/G41</f>
-        <v>0.31932773109243695</v>
+        <v>0</v>
       </c>
       <c r="E41" s="13">
         <v>60</v>
       </c>
       <c r="F41" s="12">
         <f t="shared" ref="F41:F42" si="5">+H41-E41</f>
-        <v>-22</v>
+        <v>-60</v>
       </c>
       <c r="G41" s="13">
         <f>VLOOKUP(B41,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7144,11 +7335,11 @@
       </c>
       <c r="H41" s="13">
         <f>VLOOKUP(B41,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I41" s="17">
         <f t="shared" ref="I41:I42" si="6">(+G41*$M$2)-H41</f>
-        <v>63.149999999999991</v>
+        <v>101.14999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -7161,14 +7352,14 @@
       </c>
       <c r="D42" s="22">
         <f t="shared" si="4"/>
-        <v>0.55462184873949583</v>
+        <v>0</v>
       </c>
       <c r="E42" s="13">
         <v>60</v>
       </c>
       <c r="F42" s="12">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>-60</v>
       </c>
       <c r="G42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7176,11 +7367,11 @@
       </c>
       <c r="H42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I42" s="17">
         <f t="shared" si="6"/>
-        <v>35.149999999999991</v>
+        <v>101.14999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -7754,7 +7945,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" s="51">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C3" s="51">
         <v>3408</v>
@@ -7762,9 +7953,7 @@
       <c r="G3" t="s">
         <v>218</v>
       </c>
-      <c r="H3" s="51">
-        <v>3</v>
-      </c>
+      <c r="H3" s="51"/>
       <c r="I3" s="51">
         <v>3408</v>
       </c>
@@ -7774,16 +7963,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="51">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="C4" s="51">
         <v>127</v>
       </c>
       <c r="G4" t="s">
         <v>219</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
       </c>
       <c r="I4" s="51">
         <v>3408</v>
@@ -7794,7 +7980,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="51">
-        <v>132</v>
+        <v>12</v>
       </c>
       <c r="C5" s="51">
         <v>181</v>
@@ -7802,9 +7988,7 @@
       <c r="G5" t="s">
         <v>220</v>
       </c>
-      <c r="H5" s="51">
-        <v>2</v>
-      </c>
+      <c r="H5" s="51"/>
       <c r="I5" s="51">
         <v>3408</v>
       </c>
@@ -7814,7 +7998,7 @@
         <v>100</v>
       </c>
       <c r="B6" s="51">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="C6" s="51">
         <v>2024</v>
@@ -7822,9 +8006,7 @@
       <c r="G6" t="s">
         <v>221</v>
       </c>
-      <c r="H6" s="51">
-        <v>2</v>
-      </c>
+      <c r="H6" s="51"/>
       <c r="I6" s="51">
         <v>3408</v>
       </c>
@@ -7834,17 +8016,15 @@
         <v>11</v>
       </c>
       <c r="B7" s="51">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="C7" s="51">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G7" t="s">
         <v>222</v>
       </c>
-      <c r="H7" s="51">
-        <v>4</v>
-      </c>
+      <c r="H7" s="51"/>
       <c r="I7" s="51">
         <v>3408</v>
       </c>
@@ -7854,7 +8034,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="51">
-        <v>183</v>
+        <v>27</v>
       </c>
       <c r="C8" s="51">
         <v>213</v>
@@ -7863,7 +8043,7 @@
         <v>223</v>
       </c>
       <c r="H8" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" s="51">
         <v>3408</v>
@@ -7874,7 +8054,7 @@
         <v>123</v>
       </c>
       <c r="B9" s="51">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C9" s="51">
         <v>489</v>
@@ -7882,9 +8062,7 @@
       <c r="G9" t="s">
         <v>224</v>
       </c>
-      <c r="H9" s="51">
-        <v>3</v>
-      </c>
+      <c r="H9" s="51"/>
       <c r="I9" s="51">
         <v>3408</v>
       </c>
@@ -7894,7 +8072,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="51">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="C10" s="51">
         <v>65</v>
@@ -7911,7 +8089,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="51">
-        <v>170</v>
+        <v>23</v>
       </c>
       <c r="C11" s="51">
         <v>198</v>
@@ -7929,10 +8107,10 @@
         <v>18</v>
       </c>
       <c r="B12" s="51">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="C12" s="51">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E12">
         <f>+F12</f>
@@ -7945,7 +8123,7 @@
         <v>218</v>
       </c>
       <c r="H12">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="I12" s="51">
         <v>127</v>
@@ -7956,7 +8134,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="51">
-        <v>183</v>
+        <v>32</v>
       </c>
       <c r="C13" s="51">
         <v>207</v>
@@ -7969,7 +8147,7 @@
         <v>219</v>
       </c>
       <c r="H13" s="51">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="I13" s="51">
         <v>127</v>
@@ -7980,7 +8158,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="51">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="C14" s="51">
         <v>138</v>
@@ -7993,7 +8171,7 @@
         <v>220</v>
       </c>
       <c r="H14" s="51">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="I14" s="51">
         <v>127</v>
@@ -8004,7 +8182,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="51">
-        <v>210</v>
+        <v>26</v>
       </c>
       <c r="C15" s="51">
         <v>226</v>
@@ -8017,7 +8195,7 @@
         <v>221</v>
       </c>
       <c r="H15" s="51">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="I15" s="51">
         <v>127</v>
@@ -8028,10 +8206,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="51">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="C16" s="51">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E16">
         <f t="shared" si="0"/>
@@ -8041,7 +8219,7 @@
         <v>222</v>
       </c>
       <c r="H16" s="51">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="I16" s="51">
         <v>127</v>
@@ -8052,7 +8230,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="51">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="C17" s="51">
         <v>72</v>
@@ -8065,7 +8243,7 @@
         <v>223</v>
       </c>
       <c r="H17" s="51">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="I17" s="51">
         <v>127</v>
@@ -8076,7 +8254,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="51">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="C18" s="51">
         <v>160</v>
@@ -8089,7 +8267,7 @@
         <v>224</v>
       </c>
       <c r="H18" s="51">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="I18" s="51">
         <v>127</v>
@@ -8100,7 +8278,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="51">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="C19" s="51">
         <v>178</v>
@@ -8113,7 +8291,7 @@
         <v>225</v>
       </c>
       <c r="H19" s="51">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="I19" s="51">
         <v>127</v>
@@ -8124,7 +8302,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="51">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="C20" s="51">
         <v>172</v>
@@ -8137,7 +8315,7 @@
         <v>226</v>
       </c>
       <c r="H20">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="I20" s="51">
         <v>127</v>
@@ -8147,9 +8325,7 @@
       <c r="A21">
         <v>26</v>
       </c>
-      <c r="B21" s="51">
-        <v>67</v>
-      </c>
+      <c r="B21" s="51"/>
       <c r="C21" s="51">
         <v>162</v>
       </c>
@@ -8163,9 +8339,7 @@
       <c r="G21" t="s">
         <v>218</v>
       </c>
-      <c r="H21" s="51">
-        <v>32</v>
-      </c>
+      <c r="H21" s="51"/>
       <c r="I21" s="51">
         <v>181</v>
       </c>
@@ -8175,7 +8349,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="51">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="C22" s="51">
         <v>140</v>
@@ -8187,9 +8361,7 @@
       <c r="G22" t="s">
         <v>219</v>
       </c>
-      <c r="H22" s="51">
-        <v>24</v>
-      </c>
+      <c r="H22" s="51"/>
       <c r="I22" s="51">
         <v>181</v>
       </c>
@@ -8199,7 +8371,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="51">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="C23" s="51">
         <v>168</v>
@@ -8212,7 +8384,7 @@
         <v>220</v>
       </c>
       <c r="H23" s="51">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="I23" s="51">
         <v>181</v>
@@ -8223,7 +8395,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="51">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="C24" s="51">
         <v>170</v>
@@ -8236,7 +8408,7 @@
         <v>221</v>
       </c>
       <c r="H24" s="51">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="I24" s="51">
         <v>181</v>
@@ -8246,9 +8418,7 @@
       <c r="A25">
         <v>30</v>
       </c>
-      <c r="B25" s="51">
-        <v>31</v>
-      </c>
+      <c r="B25" s="51"/>
       <c r="C25" s="51">
         <v>138</v>
       </c>
@@ -8260,7 +8430,7 @@
         <v>222</v>
       </c>
       <c r="H25" s="51">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="I25" s="51">
         <v>181</v>
@@ -8271,7 +8441,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="51">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="C26" s="51">
         <v>161</v>
@@ -8284,7 +8454,7 @@
         <v>223</v>
       </c>
       <c r="H26" s="51">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="I26" s="51">
         <v>181</v>
@@ -8295,7 +8465,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="51">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="C27" s="51">
         <v>56</v>
@@ -8307,9 +8477,7 @@
       <c r="G27" t="s">
         <v>224</v>
       </c>
-      <c r="H27" s="51">
-        <v>21</v>
-      </c>
+      <c r="H27" s="51"/>
       <c r="I27" s="51">
         <v>181</v>
       </c>
@@ -8319,7 +8487,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="51">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="C28" s="51">
         <v>172</v>
@@ -8332,7 +8500,7 @@
         <v>225</v>
       </c>
       <c r="H28" s="51">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="I28" s="51">
         <v>181</v>
@@ -8343,7 +8511,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="51">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="C29" s="51">
         <v>156</v>
@@ -8355,9 +8523,7 @@
       <c r="G29" t="s">
         <v>226</v>
       </c>
-      <c r="H29" s="51">
-        <v>27</v>
-      </c>
+      <c r="H29" s="51"/>
       <c r="I29" s="51">
         <v>181</v>
       </c>
@@ -8367,7 +8533,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="51">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="C30" s="51">
         <v>141</v>
@@ -8383,7 +8549,7 @@
         <v>218</v>
       </c>
       <c r="H30" s="51">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="I30" s="51">
         <v>2024</v>
@@ -8394,7 +8560,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="51">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="C31" s="51">
         <v>182</v>
@@ -8407,7 +8573,7 @@
         <v>219</v>
       </c>
       <c r="H31" s="51">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I31" s="51">
         <v>2024</v>
@@ -8418,7 +8584,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="51">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="C32" s="51">
         <v>249</v>
@@ -8431,7 +8597,7 @@
         <v>220</v>
       </c>
       <c r="H32" s="51">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I32" s="51">
         <v>2024</v>
@@ -8441,9 +8607,7 @@
       <c r="A33">
         <v>42</v>
       </c>
-      <c r="B33" s="51">
-        <v>12</v>
-      </c>
+      <c r="B33" s="51"/>
       <c r="C33" s="51">
         <v>52</v>
       </c>
@@ -8455,7 +8619,7 @@
         <v>221</v>
       </c>
       <c r="H33" s="51">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I33" s="51">
         <v>2024</v>
@@ -8465,9 +8629,7 @@
       <c r="A34">
         <v>43</v>
       </c>
-      <c r="B34" s="51">
-        <v>22</v>
-      </c>
+      <c r="B34" s="51"/>
       <c r="C34" s="51">
         <v>93</v>
       </c>
@@ -8479,7 +8641,7 @@
         <v>222</v>
       </c>
       <c r="H34" s="51">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="I34" s="51">
         <v>2024</v>
@@ -8490,7 +8652,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="51">
-        <v>145</v>
+        <v>26</v>
       </c>
       <c r="C35" s="51">
         <v>169</v>
@@ -8503,7 +8665,7 @@
         <v>223</v>
       </c>
       <c r="H35" s="51">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I35" s="51">
         <v>2024</v>
@@ -8514,7 +8676,7 @@
         <v>49</v>
       </c>
       <c r="B36" s="51">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="C36" s="51">
         <v>239</v>
@@ -8527,7 +8689,7 @@
         <v>224</v>
       </c>
       <c r="H36" s="51">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I36" s="51">
         <v>2024</v>
@@ -8538,7 +8700,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="51">
-        <v>235</v>
+        <v>27</v>
       </c>
       <c r="C37" s="51">
         <v>260</v>
@@ -8551,7 +8713,7 @@
         <v>225</v>
       </c>
       <c r="H37" s="51">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I37" s="51">
         <v>2024</v>
@@ -8562,7 +8724,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="51">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C38" s="51">
         <v>101</v>
@@ -8574,9 +8736,7 @@
       <c r="G38" t="s">
         <v>226</v>
       </c>
-      <c r="H38" s="51">
-        <v>6</v>
-      </c>
+      <c r="H38" s="51"/>
       <c r="I38" s="51">
         <v>2024</v>
       </c>
@@ -8586,7 +8746,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="51">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C39" s="51">
         <v>105</v>
@@ -8602,10 +8762,10 @@
         <v>218</v>
       </c>
       <c r="H39" s="51">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="I39" s="51">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -8613,7 +8773,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="51">
-        <v>151</v>
+        <v>16</v>
       </c>
       <c r="C40" s="51">
         <v>202</v>
@@ -8625,20 +8785,15 @@
       <c r="G40" t="s">
         <v>219</v>
       </c>
-      <c r="H40" s="51">
-        <v>22</v>
-      </c>
+      <c r="H40" s="51"/>
       <c r="I40" s="51">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>56</v>
       </c>
-      <c r="B41">
-        <v>102</v>
-      </c>
       <c r="C41" s="51">
         <v>198</v>
       </c>
@@ -8650,19 +8805,17 @@
         <v>220</v>
       </c>
       <c r="H41" s="51">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="I41" s="51">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>57</v>
       </c>
-      <c r="B42" s="51">
-        <v>23</v>
-      </c>
+      <c r="B42" s="51"/>
       <c r="C42" s="51">
         <v>103</v>
       </c>
@@ -8674,19 +8827,17 @@
         <v>221</v>
       </c>
       <c r="H42" s="51">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="I42" s="51">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>58</v>
       </c>
-      <c r="B43" s="51">
-        <v>38</v>
-      </c>
+      <c r="B43" s="51"/>
       <c r="C43" s="51">
         <v>119</v>
       </c>
@@ -8698,19 +8849,17 @@
         <v>222</v>
       </c>
       <c r="H43" s="51">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="I43" s="51">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>59</v>
       </c>
-      <c r="B44" s="51">
-        <v>66</v>
-      </c>
+      <c r="B44" s="51"/>
       <c r="C44" s="51">
         <v>119</v>
       </c>
@@ -8722,19 +8871,17 @@
         <v>223</v>
       </c>
       <c r="H44" s="51">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="I44" s="51">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>7</v>
       </c>
-      <c r="B45" s="51">
-        <v>29</v>
-      </c>
+      <c r="B45" s="51"/>
       <c r="C45" s="51">
         <v>113</v>
       </c>
@@ -8745,11 +8892,9 @@
       <c r="G45" t="s">
         <v>224</v>
       </c>
-      <c r="H45" s="51">
-        <v>16</v>
-      </c>
+      <c r="H45" s="51"/>
       <c r="I45" s="51">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -8757,7 +8902,7 @@
         <v>8</v>
       </c>
       <c r="B46" s="51">
-        <v>168</v>
+        <v>17</v>
       </c>
       <c r="C46" s="51">
         <v>194</v>
@@ -8770,10 +8915,10 @@
         <v>225</v>
       </c>
       <c r="H46" s="51">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="I46" s="51">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -8781,7 +8926,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="51">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="C47" s="51">
         <v>161</v>
@@ -8794,10 +8939,10 @@
         <v>226</v>
       </c>
       <c r="H47" s="51">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I47" s="51">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -8814,7 +8959,7 @@
         <v>218</v>
       </c>
       <c r="H48" s="51">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="I48" s="51">
         <v>213</v>
@@ -8831,7 +8976,7 @@
         <v>219</v>
       </c>
       <c r="H49" s="51">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="I49" s="51">
         <v>213</v>
@@ -8846,7 +8991,7 @@
         <v>220</v>
       </c>
       <c r="H50" s="51">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="I50" s="51">
         <v>213</v>
@@ -8861,7 +9006,7 @@
         <v>221</v>
       </c>
       <c r="H51" s="51">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="I51" s="51">
         <v>213</v>
@@ -8876,7 +9021,7 @@
         <v>222</v>
       </c>
       <c r="H52" s="51">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="I52" s="51">
         <v>213</v>
@@ -8891,7 +9036,7 @@
         <v>223</v>
       </c>
       <c r="H53" s="51">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="I53" s="51">
         <v>213</v>
@@ -8906,7 +9051,7 @@
         <v>224</v>
       </c>
       <c r="H54" s="51">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I54" s="51">
         <v>213</v>
@@ -8920,9 +9065,7 @@
       <c r="G55" t="s">
         <v>225</v>
       </c>
-      <c r="H55" s="51">
-        <v>46</v>
-      </c>
+      <c r="H55" s="51"/>
       <c r="I55" s="51">
         <v>213</v>
       </c>
@@ -8936,7 +9079,7 @@
         <v>226</v>
       </c>
       <c r="H56" s="51">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="I56" s="51">
         <v>213</v>
@@ -8954,7 +9097,7 @@
         <v>218</v>
       </c>
       <c r="H57" s="51">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I57" s="51">
         <v>489</v>
@@ -8969,7 +9112,7 @@
         <v>219</v>
       </c>
       <c r="H58" s="51">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I58" s="51">
         <v>489</v>
@@ -8984,7 +9127,7 @@
         <v>220</v>
       </c>
       <c r="H59" s="51">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I59" s="51">
         <v>489</v>
@@ -8998,9 +9141,7 @@
       <c r="G60" t="s">
         <v>221</v>
       </c>
-      <c r="H60" s="51">
-        <v>9</v>
-      </c>
+      <c r="H60" s="51"/>
       <c r="I60" s="51">
         <v>489</v>
       </c>
@@ -9014,7 +9155,7 @@
         <v>222</v>
       </c>
       <c r="H61" s="51">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I61" s="51">
         <v>489</v>
@@ -9028,9 +9169,7 @@
       <c r="G62" t="s">
         <v>223</v>
       </c>
-      <c r="H62" s="51">
-        <v>16</v>
-      </c>
+      <c r="H62" s="51"/>
       <c r="I62" s="51">
         <v>489</v>
       </c>
@@ -9044,7 +9183,7 @@
         <v>224</v>
       </c>
       <c r="H63" s="51">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I63" s="51">
         <v>489</v>
@@ -9058,9 +9197,7 @@
       <c r="G64" t="s">
         <v>225</v>
       </c>
-      <c r="H64" s="51">
-        <v>10</v>
-      </c>
+      <c r="H64" s="51"/>
       <c r="I64" s="51">
         <v>489</v>
       </c>
@@ -9073,9 +9210,7 @@
       <c r="G65" t="s">
         <v>226</v>
       </c>
-      <c r="H65" s="51">
-        <v>4</v>
-      </c>
+      <c r="H65" s="51"/>
       <c r="I65" s="51">
         <v>489</v>
       </c>
@@ -9092,7 +9227,7 @@
         <v>218</v>
       </c>
       <c r="H66" s="51">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I66" s="51">
         <v>65</v>
@@ -9107,7 +9242,7 @@
         <v>219</v>
       </c>
       <c r="H67" s="51">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I67" s="51">
         <v>65</v>
@@ -9122,7 +9257,7 @@
         <v>220</v>
       </c>
       <c r="H68" s="51">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="I68" s="51">
         <v>65</v>
@@ -9137,7 +9272,7 @@
         <v>221</v>
       </c>
       <c r="H69" s="51">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I69" s="51">
         <v>65</v>
@@ -9152,7 +9287,7 @@
         <v>222</v>
       </c>
       <c r="H70" s="51">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="I70" s="51">
         <v>65</v>
@@ -9167,7 +9302,7 @@
         <v>223</v>
       </c>
       <c r="H71" s="51">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I71" s="51">
         <v>65</v>
@@ -9182,7 +9317,7 @@
         <v>224</v>
       </c>
       <c r="H72" s="51">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="I72" s="51">
         <v>65</v>
@@ -9197,7 +9332,7 @@
         <v>225</v>
       </c>
       <c r="H73" s="51">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I73" s="51">
         <v>65</v>
@@ -9212,7 +9347,7 @@
         <v>226</v>
       </c>
       <c r="H74" s="51">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I74" s="51">
         <v>65</v>
@@ -9230,7 +9365,7 @@
         <v>218</v>
       </c>
       <c r="H75" s="51">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="I75" s="51">
         <v>198</v>
@@ -9245,7 +9380,7 @@
         <v>219</v>
       </c>
       <c r="H76">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="I76" s="51">
         <v>198</v>
@@ -9260,7 +9395,7 @@
         <v>220</v>
       </c>
       <c r="H77" s="51">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="I77" s="51">
         <v>198</v>
@@ -9275,7 +9410,7 @@
         <v>221</v>
       </c>
       <c r="H78" s="51">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="I78" s="51">
         <v>198</v>
@@ -9290,7 +9425,7 @@
         <v>222</v>
       </c>
       <c r="H79" s="51">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="I79" s="51">
         <v>198</v>
@@ -9305,7 +9440,7 @@
         <v>223</v>
       </c>
       <c r="H80" s="51">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="I80" s="51">
         <v>198</v>
@@ -9320,7 +9455,7 @@
         <v>224</v>
       </c>
       <c r="H81" s="51">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I81" s="51">
         <v>198</v>
@@ -9335,7 +9470,7 @@
         <v>225</v>
       </c>
       <c r="H82" s="51">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="I82" s="51">
         <v>198</v>
@@ -9350,7 +9485,7 @@
         <v>226</v>
       </c>
       <c r="H83" s="51">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="I83" s="51">
         <v>198</v>
@@ -9368,10 +9503,10 @@
         <v>218</v>
       </c>
       <c r="H84" s="51">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="I84" s="51">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="5:9" x14ac:dyDescent="0.25">
@@ -9383,10 +9518,10 @@
         <v>219</v>
       </c>
       <c r="H85" s="51">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="I85" s="51">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="86" spans="5:9" x14ac:dyDescent="0.25">
@@ -9398,10 +9533,10 @@
         <v>220</v>
       </c>
       <c r="H86" s="51">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="I86" s="51">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="87" spans="5:9" x14ac:dyDescent="0.25">
@@ -9413,10 +9548,10 @@
         <v>221</v>
       </c>
       <c r="H87" s="51">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="I87" s="51">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="88" spans="5:9" x14ac:dyDescent="0.25">
@@ -9428,10 +9563,10 @@
         <v>222</v>
       </c>
       <c r="H88" s="51">
-        <v>124</v>
+        <v>12</v>
       </c>
       <c r="I88" s="51">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="89" spans="5:9" x14ac:dyDescent="0.25">
@@ -9443,10 +9578,10 @@
         <v>223</v>
       </c>
       <c r="H89" s="51">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="I89" s="51">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="90" spans="5:9" x14ac:dyDescent="0.25">
@@ -9458,10 +9593,10 @@
         <v>224</v>
       </c>
       <c r="H90" s="51">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="I90" s="51">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="91" spans="5:9" x14ac:dyDescent="0.25">
@@ -9473,10 +9608,10 @@
         <v>225</v>
       </c>
       <c r="H91" s="51">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I91" s="51">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="92" spans="5:9" x14ac:dyDescent="0.25">
@@ -9488,10 +9623,10 @@
         <v>226</v>
       </c>
       <c r="H92" s="51">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="I92" s="51">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="93" spans="5:9" x14ac:dyDescent="0.25">
@@ -9506,7 +9641,7 @@
         <v>218</v>
       </c>
       <c r="H93" s="51">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="I93" s="51">
         <v>207</v>
@@ -9521,7 +9656,7 @@
         <v>219</v>
       </c>
       <c r="H94" s="51">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I94" s="51">
         <v>207</v>
@@ -9536,7 +9671,7 @@
         <v>220</v>
       </c>
       <c r="H95" s="51">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="I95" s="51">
         <v>207</v>
@@ -9551,7 +9686,7 @@
         <v>221</v>
       </c>
       <c r="H96" s="51">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="I96" s="51">
         <v>207</v>
@@ -9566,7 +9701,7 @@
         <v>222</v>
       </c>
       <c r="H97" s="51">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="I97" s="51">
         <v>207</v>
@@ -9581,7 +9716,7 @@
         <v>223</v>
       </c>
       <c r="H98" s="51">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="I98" s="51">
         <v>207</v>
@@ -9595,9 +9730,7 @@
       <c r="G99" t="s">
         <v>224</v>
       </c>
-      <c r="H99" s="51">
-        <v>18</v>
-      </c>
+      <c r="H99" s="51"/>
       <c r="I99" s="51">
         <v>207</v>
       </c>
@@ -9611,7 +9744,7 @@
         <v>225</v>
       </c>
       <c r="H100" s="51">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="I100" s="51">
         <v>207</v>
@@ -9626,7 +9759,7 @@
         <v>226</v>
       </c>
       <c r="H101" s="51">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="I101" s="51">
         <v>207</v>
@@ -9643,9 +9776,7 @@
       <c r="G102" t="s">
         <v>218</v>
       </c>
-      <c r="H102" s="51">
-        <v>36</v>
-      </c>
+      <c r="H102" s="51"/>
       <c r="I102" s="51">
         <v>138</v>
       </c>
@@ -9659,7 +9790,7 @@
         <v>219</v>
       </c>
       <c r="H103" s="51">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="I103" s="51">
         <v>138</v>
@@ -9674,7 +9805,7 @@
         <v>220</v>
       </c>
       <c r="H104" s="51">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="I104" s="51">
         <v>138</v>
@@ -9689,7 +9820,7 @@
         <v>221</v>
       </c>
       <c r="H105" s="51">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="I105" s="51">
         <v>138</v>
@@ -9704,7 +9835,7 @@
         <v>222</v>
       </c>
       <c r="H106" s="51">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="I106" s="51">
         <v>138</v>
@@ -9719,7 +9850,7 @@
         <v>223</v>
       </c>
       <c r="H107" s="51">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="I107" s="51">
         <v>138</v>
@@ -9734,7 +9865,7 @@
         <v>224</v>
       </c>
       <c r="H108" s="51">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I108" s="51">
         <v>138</v>
@@ -9749,7 +9880,7 @@
         <v>225</v>
       </c>
       <c r="H109" s="51">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="I109" s="51">
         <v>138</v>
@@ -9764,7 +9895,7 @@
         <v>226</v>
       </c>
       <c r="H110" s="51">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="I110" s="51">
         <v>138</v>
@@ -9782,7 +9913,7 @@
         <v>218</v>
       </c>
       <c r="H111" s="51">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="I111" s="51">
         <v>226</v>
@@ -9797,7 +9928,7 @@
         <v>219</v>
       </c>
       <c r="H112" s="51">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="I112" s="51">
         <v>226</v>
@@ -9812,7 +9943,7 @@
         <v>220</v>
       </c>
       <c r="H113" s="51">
-        <v>112</v>
+        <v>7</v>
       </c>
       <c r="I113" s="51">
         <v>226</v>
@@ -9827,7 +9958,7 @@
         <v>221</v>
       </c>
       <c r="H114" s="51">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="I114" s="51">
         <v>226</v>
@@ -9842,7 +9973,7 @@
         <v>222</v>
       </c>
       <c r="H115" s="51">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="I115" s="51">
         <v>226</v>
@@ -9857,7 +9988,7 @@
         <v>223</v>
       </c>
       <c r="H116">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="I116" s="51">
         <v>226</v>
@@ -9872,7 +10003,7 @@
         <v>224</v>
       </c>
       <c r="H117" s="51">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I117" s="51">
         <v>226</v>
@@ -9887,7 +10018,7 @@
         <v>225</v>
       </c>
       <c r="H118" s="51">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="I118" s="51">
         <v>226</v>
@@ -9902,7 +10033,7 @@
         <v>226</v>
       </c>
       <c r="H119" s="51">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="I119" s="51">
         <v>226</v>
@@ -9920,10 +10051,10 @@
         <v>218</v>
       </c>
       <c r="H120" s="51">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="I120" s="51">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="121" spans="5:9" x14ac:dyDescent="0.25">
@@ -9935,10 +10066,10 @@
         <v>219</v>
       </c>
       <c r="H121" s="51">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="I121" s="51">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="122" spans="5:9" x14ac:dyDescent="0.25">
@@ -9950,10 +10081,10 @@
         <v>220</v>
       </c>
       <c r="H122" s="51">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="I122" s="51">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="123" spans="5:9" x14ac:dyDescent="0.25">
@@ -9965,10 +10096,10 @@
         <v>221</v>
       </c>
       <c r="H123" s="51">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="I123" s="51">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="124" spans="5:9" x14ac:dyDescent="0.25">
@@ -9980,10 +10111,10 @@
         <v>222</v>
       </c>
       <c r="H124">
-        <v>132</v>
+        <v>16</v>
       </c>
       <c r="I124" s="51">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="125" spans="5:9" x14ac:dyDescent="0.25">
@@ -9995,10 +10126,10 @@
         <v>223</v>
       </c>
       <c r="H125" s="51">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="I125" s="51">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="126" spans="5:9" x14ac:dyDescent="0.25">
@@ -10010,10 +10141,10 @@
         <v>224</v>
       </c>
       <c r="H126" s="51">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="I126" s="51">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="127" spans="5:9" x14ac:dyDescent="0.25">
@@ -10025,10 +10156,10 @@
         <v>225</v>
       </c>
       <c r="H127" s="51">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="I127" s="51">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="128" spans="5:9" x14ac:dyDescent="0.25">
@@ -10039,11 +10170,9 @@
       <c r="G128" t="s">
         <v>226</v>
       </c>
-      <c r="H128" s="51">
-        <v>31</v>
-      </c>
+      <c r="H128" s="51"/>
       <c r="I128" s="51">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="129" spans="5:9" x14ac:dyDescent="0.25">
@@ -10058,7 +10187,7 @@
         <v>218</v>
       </c>
       <c r="H129" s="51">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="I129" s="51">
         <v>72</v>
@@ -10073,7 +10202,7 @@
         <v>219</v>
       </c>
       <c r="H130" s="51">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="I130" s="51">
         <v>72</v>
@@ -10088,7 +10217,7 @@
         <v>220</v>
       </c>
       <c r="H131" s="51">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="I131" s="51">
         <v>72</v>
@@ -10103,7 +10232,7 @@
         <v>221</v>
       </c>
       <c r="H132" s="51">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="I132" s="51">
         <v>72</v>
@@ -10118,7 +10247,7 @@
         <v>222</v>
       </c>
       <c r="H133" s="51">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="I133" s="51">
         <v>72</v>
@@ -10133,7 +10262,7 @@
         <v>223</v>
       </c>
       <c r="H134" s="51">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="I134" s="51">
         <v>72</v>
@@ -10148,7 +10277,7 @@
         <v>224</v>
       </c>
       <c r="H135" s="51">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="I135" s="51">
         <v>72</v>
@@ -10163,7 +10292,7 @@
         <v>225</v>
       </c>
       <c r="H136" s="51">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="I136" s="51">
         <v>72</v>
@@ -10178,7 +10307,7 @@
         <v>226</v>
       </c>
       <c r="H137" s="51">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="I137" s="51">
         <v>72</v>
@@ -10196,7 +10325,7 @@
         <v>218</v>
       </c>
       <c r="H138" s="51">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="I138" s="51">
         <v>160</v>
@@ -10211,7 +10340,7 @@
         <v>219</v>
       </c>
       <c r="H139" s="51">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="I139" s="51">
         <v>160</v>
@@ -10226,7 +10355,7 @@
         <v>220</v>
       </c>
       <c r="H140">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="I140" s="51">
         <v>160</v>
@@ -10241,7 +10370,7 @@
         <v>221</v>
       </c>
       <c r="H141" s="51">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="I141" s="51">
         <v>160</v>
@@ -10256,7 +10385,7 @@
         <v>222</v>
       </c>
       <c r="H142" s="51">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="I142" s="51">
         <v>160</v>
@@ -10271,7 +10400,7 @@
         <v>223</v>
       </c>
       <c r="H143" s="51">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="I143" s="51">
         <v>160</v>
@@ -10286,7 +10415,7 @@
         <v>224</v>
       </c>
       <c r="H144" s="51">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I144" s="51">
         <v>160</v>
@@ -10301,7 +10430,7 @@
         <v>225</v>
       </c>
       <c r="H145" s="51">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="I145" s="51">
         <v>160</v>
@@ -10316,7 +10445,7 @@
         <v>226</v>
       </c>
       <c r="H146" s="51">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="I146" s="51">
         <v>160</v>
@@ -10334,7 +10463,7 @@
         <v>218</v>
       </c>
       <c r="H147" s="51">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="I147" s="51">
         <v>178</v>
@@ -10349,7 +10478,7 @@
         <v>219</v>
       </c>
       <c r="H148">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="I148" s="51">
         <v>178</v>
@@ -10364,7 +10493,7 @@
         <v>220</v>
       </c>
       <c r="H149" s="51">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="I149" s="51">
         <v>178</v>
@@ -10379,7 +10508,7 @@
         <v>221</v>
       </c>
       <c r="H150" s="51">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="I150" s="51">
         <v>178</v>
@@ -10394,7 +10523,7 @@
         <v>222</v>
       </c>
       <c r="H151" s="51">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="I151" s="51">
         <v>178</v>
@@ -10409,7 +10538,7 @@
         <v>223</v>
       </c>
       <c r="H152" s="51">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="I152" s="51">
         <v>178</v>
@@ -10424,7 +10553,7 @@
         <v>224</v>
       </c>
       <c r="H153" s="51">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I153" s="51">
         <v>178</v>
@@ -10438,9 +10567,7 @@
       <c r="G154" t="s">
         <v>225</v>
       </c>
-      <c r="H154" s="51">
-        <v>33</v>
-      </c>
+      <c r="H154" s="51"/>
       <c r="I154" s="51">
         <v>178</v>
       </c>
@@ -10454,7 +10581,7 @@
         <v>226</v>
       </c>
       <c r="H155" s="51">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="I155" s="51">
         <v>178</v>
@@ -10472,7 +10599,7 @@
         <v>218</v>
       </c>
       <c r="H156" s="51">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="I156" s="51">
         <v>172</v>
@@ -10487,7 +10614,7 @@
         <v>219</v>
       </c>
       <c r="H157" s="51">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I157" s="51">
         <v>172</v>
@@ -10502,7 +10629,7 @@
         <v>220</v>
       </c>
       <c r="H158" s="51">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="I158" s="51">
         <v>172</v>
@@ -10517,7 +10644,7 @@
         <v>221</v>
       </c>
       <c r="H159" s="51">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="I159" s="51">
         <v>172</v>
@@ -10532,7 +10659,7 @@
         <v>222</v>
       </c>
       <c r="H160" s="51">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="I160" s="51">
         <v>172</v>
@@ -10547,7 +10674,7 @@
         <v>223</v>
       </c>
       <c r="H161" s="51">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="I161" s="51">
         <v>172</v>
@@ -10562,7 +10689,7 @@
         <v>224</v>
       </c>
       <c r="H162" s="51">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="I162" s="51">
         <v>172</v>
@@ -10577,7 +10704,7 @@
         <v>225</v>
       </c>
       <c r="H163" s="51">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="I163" s="51">
         <v>172</v>
@@ -10592,7 +10719,7 @@
         <v>226</v>
       </c>
       <c r="H164">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="I164" s="51">
         <v>172</v>
@@ -10609,9 +10736,7 @@
       <c r="G165" t="s">
         <v>218</v>
       </c>
-      <c r="H165" s="51">
-        <v>26</v>
-      </c>
+      <c r="H165" s="51"/>
       <c r="I165" s="51">
         <v>162</v>
       </c>
@@ -10624,9 +10749,7 @@
       <c r="G166" t="s">
         <v>219</v>
       </c>
-      <c r="H166" s="51">
-        <v>11</v>
-      </c>
+      <c r="H166" s="51"/>
       <c r="I166" s="51">
         <v>162</v>
       </c>
@@ -10639,9 +10762,7 @@
       <c r="G167" t="s">
         <v>220</v>
       </c>
-      <c r="H167" s="51">
-        <v>15</v>
-      </c>
+      <c r="H167" s="51"/>
       <c r="I167" s="51">
         <v>162</v>
       </c>
@@ -10654,9 +10775,7 @@
       <c r="G168" t="s">
         <v>221</v>
       </c>
-      <c r="H168" s="51">
-        <v>25</v>
-      </c>
+      <c r="H168" s="51"/>
       <c r="I168" s="51">
         <v>162</v>
       </c>
@@ -10669,9 +10788,7 @@
       <c r="G169" t="s">
         <v>222</v>
       </c>
-      <c r="H169" s="51">
-        <v>32</v>
-      </c>
+      <c r="H169" s="51"/>
       <c r="I169" s="51">
         <v>162</v>
       </c>
@@ -10684,9 +10801,7 @@
       <c r="G170" t="s">
         <v>223</v>
       </c>
-      <c r="H170" s="51">
-        <v>17</v>
-      </c>
+      <c r="H170" s="51"/>
       <c r="I170" s="51">
         <v>162</v>
       </c>
@@ -10699,9 +10814,7 @@
       <c r="G171" t="s">
         <v>224</v>
       </c>
-      <c r="H171" s="51">
-        <v>38</v>
-      </c>
+      <c r="H171" s="51"/>
       <c r="I171" s="51">
         <v>162</v>
       </c>
@@ -10714,9 +10827,7 @@
       <c r="G172" t="s">
         <v>225</v>
       </c>
-      <c r="H172" s="51">
-        <v>22</v>
-      </c>
+      <c r="H172" s="51"/>
       <c r="I172" s="51">
         <v>162</v>
       </c>
@@ -10729,9 +10840,7 @@
       <c r="G173" t="s">
         <v>226</v>
       </c>
-      <c r="H173" s="51">
-        <v>24</v>
-      </c>
+      <c r="H173" s="51"/>
       <c r="I173" s="51">
         <v>162</v>
       </c>
@@ -10748,7 +10857,7 @@
         <v>218</v>
       </c>
       <c r="H174" s="51">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="I174" s="51">
         <v>140</v>
@@ -10763,7 +10872,7 @@
         <v>219</v>
       </c>
       <c r="H175" s="51">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="I175" s="51">
         <v>140</v>
@@ -10778,7 +10887,7 @@
         <v>220</v>
       </c>
       <c r="H176" s="51">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="I176" s="51">
         <v>140</v>
@@ -10793,7 +10902,7 @@
         <v>221</v>
       </c>
       <c r="H177" s="51">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="I177" s="51">
         <v>140</v>
@@ -10808,7 +10917,7 @@
         <v>222</v>
       </c>
       <c r="H178" s="51">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="I178" s="51">
         <v>140</v>
@@ -10823,7 +10932,7 @@
         <v>223</v>
       </c>
       <c r="H179" s="51">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="I179" s="51">
         <v>140</v>
@@ -10838,7 +10947,7 @@
         <v>224</v>
       </c>
       <c r="H180">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="I180" s="51">
         <v>140</v>
@@ -10853,7 +10962,7 @@
         <v>225</v>
       </c>
       <c r="H181" s="51">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="I181" s="51">
         <v>140</v>
@@ -10868,7 +10977,7 @@
         <v>226</v>
       </c>
       <c r="H182" s="51">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="I182" s="51">
         <v>140</v>
@@ -10886,7 +10995,7 @@
         <v>218</v>
       </c>
       <c r="H183" s="51">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="I183" s="51">
         <v>168</v>
@@ -10901,7 +11010,7 @@
         <v>219</v>
       </c>
       <c r="H184" s="51">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="I184" s="51">
         <v>168</v>
@@ -10916,7 +11025,7 @@
         <v>220</v>
       </c>
       <c r="H185" s="51">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="I185" s="51">
         <v>168</v>
@@ -10931,7 +11040,7 @@
         <v>221</v>
       </c>
       <c r="H186">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="I186" s="51">
         <v>168</v>
@@ -10946,7 +11055,7 @@
         <v>222</v>
       </c>
       <c r="H187" s="51">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="I187" s="51">
         <v>168</v>
@@ -10961,7 +11070,7 @@
         <v>223</v>
       </c>
       <c r="H188" s="51">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="I188" s="51">
         <v>168</v>
@@ -10976,7 +11085,7 @@
         <v>224</v>
       </c>
       <c r="H189" s="51">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I189" s="51">
         <v>168</v>
@@ -10991,7 +11100,7 @@
         <v>225</v>
       </c>
       <c r="H190" s="51">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I190" s="51">
         <v>168</v>
@@ -11005,9 +11114,7 @@
       <c r="G191" t="s">
         <v>226</v>
       </c>
-      <c r="H191" s="51">
-        <v>40</v>
-      </c>
+      <c r="H191" s="51"/>
       <c r="I191" s="51">
         <v>168</v>
       </c>
@@ -11024,7 +11131,7 @@
         <v>218</v>
       </c>
       <c r="H192" s="51">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="I192" s="51">
         <v>170</v>
@@ -11039,7 +11146,7 @@
         <v>219</v>
       </c>
       <c r="H193" s="51">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="I193" s="51">
         <v>170</v>
@@ -11054,7 +11161,7 @@
         <v>220</v>
       </c>
       <c r="H194" s="51">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="I194" s="51">
         <v>170</v>
@@ -11069,7 +11176,7 @@
         <v>221</v>
       </c>
       <c r="H195" s="51">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I195" s="51">
         <v>170</v>
@@ -11084,7 +11191,7 @@
         <v>222</v>
       </c>
       <c r="H196">
-        <v>104</v>
+        <v>7</v>
       </c>
       <c r="I196" s="51">
         <v>170</v>
@@ -11099,7 +11206,7 @@
         <v>223</v>
       </c>
       <c r="H197" s="51">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="I197" s="51">
         <v>170</v>
@@ -11113,9 +11220,7 @@
       <c r="G198" t="s">
         <v>224</v>
       </c>
-      <c r="H198" s="51">
-        <v>21</v>
-      </c>
+      <c r="H198" s="51"/>
       <c r="I198" s="51">
         <v>170</v>
       </c>
@@ -11129,7 +11234,7 @@
         <v>225</v>
       </c>
       <c r="H199" s="51">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="I199" s="51">
         <v>170</v>
@@ -11144,7 +11249,7 @@
         <v>226</v>
       </c>
       <c r="H200" s="51">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="I200" s="51">
         <v>170</v>
@@ -11161,9 +11266,7 @@
       <c r="G201" t="s">
         <v>218</v>
       </c>
-      <c r="H201" s="51">
-        <v>7</v>
-      </c>
+      <c r="H201" s="51"/>
       <c r="I201" s="51">
         <v>138</v>
       </c>
@@ -11176,9 +11279,7 @@
       <c r="G202" t="s">
         <v>219</v>
       </c>
-      <c r="H202" s="51">
-        <v>1</v>
-      </c>
+      <c r="H202" s="51"/>
       <c r="I202" s="51">
         <v>138</v>
       </c>
@@ -11191,9 +11292,7 @@
       <c r="G203" t="s">
         <v>220</v>
       </c>
-      <c r="H203" s="51">
-        <v>18</v>
-      </c>
+      <c r="H203" s="51"/>
       <c r="I203" s="51">
         <v>138</v>
       </c>
@@ -11206,9 +11305,7 @@
       <c r="G204" t="s">
         <v>221</v>
       </c>
-      <c r="H204" s="51">
-        <v>6</v>
-      </c>
+      <c r="H204" s="51"/>
       <c r="I204" s="51">
         <v>138</v>
       </c>
@@ -11221,9 +11318,7 @@
       <c r="G205" t="s">
         <v>222</v>
       </c>
-      <c r="H205" s="51">
-        <v>9</v>
-      </c>
+      <c r="H205" s="51"/>
       <c r="I205" s="51">
         <v>138</v>
       </c>
@@ -11236,9 +11331,7 @@
       <c r="G206" t="s">
         <v>223</v>
       </c>
-      <c r="H206" s="51">
-        <v>2</v>
-      </c>
+      <c r="H206" s="51"/>
       <c r="I206" s="51">
         <v>138</v>
       </c>
@@ -11251,9 +11344,7 @@
       <c r="G207" t="s">
         <v>224</v>
       </c>
-      <c r="H207" s="51">
-        <v>14</v>
-      </c>
+      <c r="H207" s="51"/>
       <c r="I207" s="51">
         <v>138</v>
       </c>
@@ -11266,9 +11357,7 @@
       <c r="G208" t="s">
         <v>225</v>
       </c>
-      <c r="H208" s="51">
-        <v>1</v>
-      </c>
+      <c r="H208" s="51"/>
       <c r="I208" s="51">
         <v>138</v>
       </c>
@@ -11281,9 +11370,7 @@
       <c r="G209" t="s">
         <v>226</v>
       </c>
-      <c r="H209" s="51">
-        <v>2</v>
-      </c>
+      <c r="H209" s="51"/>
       <c r="I209" s="51">
         <v>138</v>
       </c>
@@ -11300,7 +11387,7 @@
         <v>218</v>
       </c>
       <c r="H210" s="51">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="I210" s="51">
         <v>161</v>
@@ -11315,7 +11402,7 @@
         <v>219</v>
       </c>
       <c r="H211" s="51">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="I211" s="51">
         <v>161</v>
@@ -11330,7 +11417,7 @@
         <v>220</v>
       </c>
       <c r="H212">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="I212" s="51">
         <v>161</v>
@@ -11345,7 +11432,7 @@
         <v>221</v>
       </c>
       <c r="H213" s="51">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="I213" s="51">
         <v>161</v>
@@ -11360,7 +11447,7 @@
         <v>222</v>
       </c>
       <c r="H214" s="51">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="I214" s="51">
         <v>161</v>
@@ -11375,7 +11462,7 @@
         <v>223</v>
       </c>
       <c r="H215" s="51">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="I215" s="51">
         <v>161</v>
@@ -11390,7 +11477,7 @@
         <v>224</v>
       </c>
       <c r="H216" s="51">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="I216" s="51">
         <v>161</v>
@@ -11405,7 +11492,7 @@
         <v>225</v>
       </c>
       <c r="H217" s="51">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="I217" s="51">
         <v>161</v>
@@ -11420,7 +11507,7 @@
         <v>226</v>
       </c>
       <c r="H218" s="51">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="I218" s="51">
         <v>161</v>
@@ -11438,7 +11525,7 @@
         <v>218</v>
       </c>
       <c r="H219" s="51">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="I219" s="51">
         <v>56</v>
@@ -11452,9 +11539,7 @@
       <c r="G220" t="s">
         <v>219</v>
       </c>
-      <c r="H220" s="51">
-        <v>11</v>
-      </c>
+      <c r="H220" s="51"/>
       <c r="I220" s="51">
         <v>56</v>
       </c>
@@ -11468,7 +11553,7 @@
         <v>220</v>
       </c>
       <c r="H221" s="51">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="I221" s="51">
         <v>56</v>
@@ -11483,7 +11568,7 @@
         <v>221</v>
       </c>
       <c r="H222" s="51">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="I222" s="51">
         <v>56</v>
@@ -11498,7 +11583,7 @@
         <v>222</v>
       </c>
       <c r="H223" s="51">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="I223" s="51">
         <v>56</v>
@@ -11513,7 +11598,7 @@
         <v>223</v>
       </c>
       <c r="H224" s="51">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="I224" s="51">
         <v>56</v>
@@ -11528,7 +11613,7 @@
         <v>224</v>
       </c>
       <c r="H225" s="51">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="I225" s="51">
         <v>56</v>
@@ -11543,7 +11628,7 @@
         <v>225</v>
       </c>
       <c r="H226" s="51">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="I226" s="51">
         <v>56</v>
@@ -11558,7 +11643,7 @@
         <v>226</v>
       </c>
       <c r="H227" s="51">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="I227" s="51">
         <v>56</v>
@@ -11576,7 +11661,7 @@
         <v>218</v>
       </c>
       <c r="H228" s="51">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="I228" s="51">
         <v>172</v>
@@ -11591,7 +11676,7 @@
         <v>219</v>
       </c>
       <c r="H229" s="51">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I229" s="51">
         <v>172</v>
@@ -11606,7 +11691,7 @@
         <v>220</v>
       </c>
       <c r="H230" s="51">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="I230" s="51">
         <v>172</v>
@@ -11621,7 +11706,7 @@
         <v>221</v>
       </c>
       <c r="H231" s="51">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="I231" s="51">
         <v>172</v>
@@ -11636,7 +11721,7 @@
         <v>222</v>
       </c>
       <c r="H232" s="51">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="I232" s="51">
         <v>172</v>
@@ -11651,7 +11736,7 @@
         <v>223</v>
       </c>
       <c r="H233" s="51">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="I233" s="51">
         <v>172</v>
@@ -11666,7 +11751,7 @@
         <v>224</v>
       </c>
       <c r="H234" s="51">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I234" s="51">
         <v>172</v>
@@ -11681,7 +11766,7 @@
         <v>225</v>
       </c>
       <c r="H235" s="51">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I235" s="51">
         <v>172</v>
@@ -11695,9 +11780,6 @@
       <c r="G236" t="s">
         <v>226</v>
       </c>
-      <c r="H236">
-        <v>24</v>
-      </c>
       <c r="I236" s="51">
         <v>172</v>
       </c>
@@ -11714,7 +11796,7 @@
         <v>218</v>
       </c>
       <c r="H237" s="51">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I237" s="51">
         <v>156</v>
@@ -11729,7 +11811,7 @@
         <v>219</v>
       </c>
       <c r="H238" s="51">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I238" s="51">
         <v>156</v>
@@ -11744,7 +11826,7 @@
         <v>220</v>
       </c>
       <c r="H239" s="51">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I239" s="51">
         <v>156</v>
@@ -11759,7 +11841,7 @@
         <v>221</v>
       </c>
       <c r="H240" s="51">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="I240" s="51">
         <v>156</v>
@@ -11774,7 +11856,7 @@
         <v>222</v>
       </c>
       <c r="H241" s="51">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="I241" s="51">
         <v>156</v>
@@ -11789,7 +11871,7 @@
         <v>223</v>
       </c>
       <c r="H242" s="51">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I242" s="51">
         <v>156</v>
@@ -11804,7 +11886,7 @@
         <v>224</v>
       </c>
       <c r="H243" s="51">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I243" s="51">
         <v>156</v>
@@ -11819,7 +11901,7 @@
         <v>225</v>
       </c>
       <c r="H244">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I244" s="51">
         <v>156</v>
@@ -11833,9 +11915,7 @@
       <c r="G245" t="s">
         <v>226</v>
       </c>
-      <c r="H245" s="51">
-        <v>11</v>
-      </c>
+      <c r="H245" s="51"/>
       <c r="I245" s="51">
         <v>156</v>
       </c>
@@ -11852,7 +11932,7 @@
         <v>218</v>
       </c>
       <c r="H246" s="51">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I246" s="51">
         <v>141</v>
@@ -11866,9 +11946,7 @@
       <c r="G247" t="s">
         <v>219</v>
       </c>
-      <c r="H247" s="51">
-        <v>32</v>
-      </c>
+      <c r="H247" s="51"/>
       <c r="I247" s="51">
         <v>141</v>
       </c>
@@ -11881,9 +11959,7 @@
       <c r="G248" t="s">
         <v>220</v>
       </c>
-      <c r="H248" s="51">
-        <v>47</v>
-      </c>
+      <c r="H248" s="51"/>
       <c r="I248" s="51">
         <v>141</v>
       </c>
@@ -11896,9 +11972,7 @@
       <c r="G249" t="s">
         <v>221</v>
       </c>
-      <c r="H249" s="51">
-        <v>38</v>
-      </c>
+      <c r="H249" s="51"/>
       <c r="I249" s="51">
         <v>141</v>
       </c>
@@ -11912,7 +11986,7 @@
         <v>222</v>
       </c>
       <c r="H250" s="51">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="I250" s="51">
         <v>141</v>
@@ -11927,7 +12001,7 @@
         <v>223</v>
       </c>
       <c r="H251" s="51">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="I251" s="51">
         <v>141</v>
@@ -11942,7 +12016,7 @@
         <v>224</v>
       </c>
       <c r="H252">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I252" s="51">
         <v>141</v>
@@ -11957,7 +12031,7 @@
         <v>225</v>
       </c>
       <c r="H253" s="51">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I253" s="51">
         <v>141</v>
@@ -11971,9 +12045,7 @@
       <c r="G254" t="s">
         <v>226</v>
       </c>
-      <c r="H254" s="51">
-        <v>30</v>
-      </c>
+      <c r="H254" s="51"/>
       <c r="I254" s="51">
         <v>141</v>
       </c>
@@ -11990,7 +12062,7 @@
         <v>218</v>
       </c>
       <c r="H255" s="51">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="I255" s="51">
         <v>182</v>
@@ -12005,7 +12077,7 @@
         <v>219</v>
       </c>
       <c r="H256" s="51">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="I256" s="51">
         <v>182</v>
@@ -12020,7 +12092,7 @@
         <v>220</v>
       </c>
       <c r="H257" s="51">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="I257" s="51">
         <v>182</v>
@@ -12035,7 +12107,7 @@
         <v>221</v>
       </c>
       <c r="H258">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="I258" s="51">
         <v>182</v>
@@ -12050,7 +12122,7 @@
         <v>222</v>
       </c>
       <c r="H259" s="51">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="I259" s="51">
         <v>182</v>
@@ -12065,7 +12137,7 @@
         <v>223</v>
       </c>
       <c r="H260">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="I260" s="51">
         <v>182</v>
@@ -12080,7 +12152,7 @@
         <v>224</v>
       </c>
       <c r="H261" s="51">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I261" s="51">
         <v>182</v>
@@ -12095,7 +12167,7 @@
         <v>225</v>
       </c>
       <c r="H262" s="51">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="I262" s="51">
         <v>182</v>
@@ -12110,7 +12182,7 @@
         <v>226</v>
       </c>
       <c r="H263" s="51">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="I263" s="51">
         <v>182</v>
@@ -12128,7 +12200,7 @@
         <v>218</v>
       </c>
       <c r="H264" s="51">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="I264" s="51">
         <v>249</v>
@@ -12143,7 +12215,7 @@
         <v>219</v>
       </c>
       <c r="H265">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I265" s="51">
         <v>249</v>
@@ -12158,7 +12230,7 @@
         <v>220</v>
       </c>
       <c r="H266" s="51">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="I266" s="51">
         <v>249</v>
@@ -12173,7 +12245,7 @@
         <v>221</v>
       </c>
       <c r="H267" s="51">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="I267" s="51">
         <v>249</v>
@@ -12188,7 +12260,7 @@
         <v>222</v>
       </c>
       <c r="H268">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="I268" s="51">
         <v>249</v>
@@ -12203,7 +12275,7 @@
         <v>223</v>
       </c>
       <c r="H269" s="51">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="I269" s="51">
         <v>249</v>
@@ -12218,7 +12290,7 @@
         <v>224</v>
       </c>
       <c r="H270" s="51">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="I270" s="51">
         <v>249</v>
@@ -12233,7 +12305,7 @@
         <v>225</v>
       </c>
       <c r="H271" s="51">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I271" s="51">
         <v>249</v>
@@ -12248,7 +12320,7 @@
         <v>226</v>
       </c>
       <c r="H272" s="51">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="I272" s="51">
         <v>249</v>
@@ -12265,9 +12337,7 @@
       <c r="G273" t="s">
         <v>218</v>
       </c>
-      <c r="H273" s="51">
-        <v>3</v>
-      </c>
+      <c r="H273" s="51"/>
       <c r="I273" s="51">
         <v>52</v>
       </c>
@@ -12280,9 +12350,7 @@
       <c r="G274" t="s">
         <v>219</v>
       </c>
-      <c r="H274" s="51">
-        <v>2</v>
-      </c>
+      <c r="H274" s="51"/>
       <c r="I274" s="51">
         <v>52</v>
       </c>
@@ -12295,9 +12363,7 @@
       <c r="G275" t="s">
         <v>220</v>
       </c>
-      <c r="H275" s="51">
-        <v>2</v>
-      </c>
+      <c r="H275" s="51"/>
       <c r="I275" s="51">
         <v>52</v>
       </c>
@@ -12310,9 +12376,6 @@
       <c r="G276" t="s">
         <v>221</v>
       </c>
-      <c r="H276">
-        <v>3</v>
-      </c>
       <c r="I276" s="51">
         <v>52</v>
       </c>
@@ -12325,9 +12388,7 @@
       <c r="G277" t="s">
         <v>222</v>
       </c>
-      <c r="H277" s="51">
-        <v>4</v>
-      </c>
+      <c r="H277" s="51"/>
       <c r="I277" s="51">
         <v>52</v>
       </c>
@@ -12340,9 +12401,7 @@
       <c r="G278" t="s">
         <v>223</v>
       </c>
-      <c r="H278" s="51">
-        <v>3</v>
-      </c>
+      <c r="H278" s="51"/>
       <c r="I278" s="51">
         <v>52</v>
       </c>
@@ -12355,9 +12414,7 @@
       <c r="G279" t="s">
         <v>224</v>
       </c>
-      <c r="H279" s="51">
-        <v>9</v>
-      </c>
+      <c r="H279" s="51"/>
       <c r="I279" s="51">
         <v>52</v>
       </c>
@@ -12370,9 +12427,7 @@
       <c r="G280" t="s">
         <v>225</v>
       </c>
-      <c r="H280" s="51">
-        <v>5</v>
-      </c>
+      <c r="H280" s="51"/>
       <c r="I280" s="51">
         <v>52</v>
       </c>
@@ -12385,9 +12440,7 @@
       <c r="G281" t="s">
         <v>226</v>
       </c>
-      <c r="H281" s="51">
-        <v>6</v>
-      </c>
+      <c r="H281" s="51"/>
       <c r="I281" s="51">
         <v>52</v>
       </c>
@@ -12403,9 +12456,7 @@
       <c r="G282" t="s">
         <v>218</v>
       </c>
-      <c r="H282" s="51">
-        <v>6</v>
-      </c>
+      <c r="H282" s="51"/>
       <c r="I282" s="51">
         <v>93</v>
       </c>
@@ -12431,9 +12482,6 @@
       <c r="G284" t="s">
         <v>220</v>
       </c>
-      <c r="H284">
-        <v>3</v>
-      </c>
       <c r="I284" s="51">
         <v>93</v>
       </c>
@@ -12446,9 +12494,6 @@
       <c r="G285" t="s">
         <v>221</v>
       </c>
-      <c r="H285">
-        <v>3</v>
-      </c>
       <c r="I285" s="51">
         <v>93</v>
       </c>
@@ -12461,9 +12506,6 @@
       <c r="G286" t="s">
         <v>222</v>
       </c>
-      <c r="H286">
-        <v>2</v>
-      </c>
       <c r="I286" s="51">
         <v>93</v>
       </c>
@@ -12488,9 +12530,6 @@
       <c r="G288" t="s">
         <v>224</v>
       </c>
-      <c r="H288">
-        <v>9</v>
-      </c>
       <c r="I288" s="51">
         <v>93</v>
       </c>
@@ -12503,9 +12542,7 @@
       <c r="G289" t="s">
         <v>225</v>
       </c>
-      <c r="H289" s="51">
-        <v>5</v>
-      </c>
+      <c r="H289" s="51"/>
       <c r="I289" s="51">
         <v>93</v>
       </c>
@@ -12518,9 +12555,6 @@
       <c r="G290" t="s">
         <v>226</v>
       </c>
-      <c r="H290">
-        <v>4</v>
-      </c>
       <c r="I290" s="51">
         <v>93</v>
       </c>
@@ -12537,7 +12571,7 @@
         <v>218</v>
       </c>
       <c r="H291">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="I291" s="51">
         <v>169</v>
@@ -12552,7 +12586,7 @@
         <v>219</v>
       </c>
       <c r="H292">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="I292" s="51">
         <v>169</v>
@@ -12567,7 +12601,7 @@
         <v>220</v>
       </c>
       <c r="H293">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="I293" s="51">
         <v>169</v>
@@ -12582,7 +12616,7 @@
         <v>221</v>
       </c>
       <c r="H294">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="I294" s="51">
         <v>169</v>
@@ -12597,7 +12631,7 @@
         <v>222</v>
       </c>
       <c r="H295">
-        <v>115</v>
+        <v>14</v>
       </c>
       <c r="I295" s="51">
         <v>169</v>
@@ -12612,7 +12646,7 @@
         <v>223</v>
       </c>
       <c r="H296">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="I296" s="51">
         <v>169</v>
@@ -12627,7 +12661,7 @@
         <v>224</v>
       </c>
       <c r="H297" s="51">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I297" s="51">
         <v>169</v>
@@ -12642,7 +12676,7 @@
         <v>225</v>
       </c>
       <c r="H298">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="I298" s="51">
         <v>169</v>
@@ -12657,7 +12691,7 @@
         <v>226</v>
       </c>
       <c r="H299" s="51">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="I299" s="51">
         <v>169</v>
@@ -12675,7 +12709,7 @@
         <v>218</v>
       </c>
       <c r="H300" s="51">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="I300" s="51">
         <v>239</v>
@@ -12690,7 +12724,7 @@
         <v>219</v>
       </c>
       <c r="H301" s="51">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I301" s="51">
         <v>239</v>
@@ -12705,7 +12739,7 @@
         <v>220</v>
       </c>
       <c r="H302" s="51">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="I302" s="51">
         <v>239</v>
@@ -12720,7 +12754,7 @@
         <v>221</v>
       </c>
       <c r="H303" s="51">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I303" s="51">
         <v>239</v>
@@ -12735,7 +12769,7 @@
         <v>222</v>
       </c>
       <c r="H304" s="51">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="I304" s="51">
         <v>239</v>
@@ -12750,7 +12784,7 @@
         <v>223</v>
       </c>
       <c r="H305" s="51">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="I305" s="51">
         <v>239</v>
@@ -12765,7 +12799,7 @@
         <v>224</v>
       </c>
       <c r="H306" s="51">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I306" s="51">
         <v>239</v>
@@ -12780,7 +12814,7 @@
         <v>225</v>
       </c>
       <c r="H307">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I307" s="51">
         <v>239</v>
@@ -12795,7 +12829,7 @@
         <v>226</v>
       </c>
       <c r="H308">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="I308" s="51">
         <v>239</v>
@@ -12813,7 +12847,7 @@
         <v>218</v>
       </c>
       <c r="H309">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="I309" s="51">
         <v>260</v>
@@ -12828,7 +12862,7 @@
         <v>219</v>
       </c>
       <c r="H310">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="I310" s="51">
         <v>260</v>
@@ -12843,7 +12877,7 @@
         <v>220</v>
       </c>
       <c r="H311">
-        <v>129</v>
+        <v>8</v>
       </c>
       <c r="I311" s="51">
         <v>260</v>
@@ -12858,7 +12892,7 @@
         <v>221</v>
       </c>
       <c r="H312">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="I312" s="51">
         <v>260</v>
@@ -12873,7 +12907,7 @@
         <v>222</v>
       </c>
       <c r="H313">
-        <v>161</v>
+        <v>17</v>
       </c>
       <c r="I313" s="51">
         <v>260</v>
@@ -12888,7 +12922,7 @@
         <v>223</v>
       </c>
       <c r="H314">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="I314" s="51">
         <v>260</v>
@@ -12903,7 +12937,7 @@
         <v>224</v>
       </c>
       <c r="H315" s="51">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="I315" s="51">
         <v>260</v>
@@ -12918,7 +12952,7 @@
         <v>225</v>
       </c>
       <c r="H316">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="I316" s="51">
         <v>260</v>
@@ -12933,7 +12967,7 @@
         <v>226</v>
       </c>
       <c r="H317" s="51">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="I317" s="51">
         <v>260</v>
@@ -12950,7 +12984,9 @@
       <c r="G318" t="s">
         <v>218</v>
       </c>
-      <c r="H318" s="51"/>
+      <c r="H318" s="51">
+        <v>1</v>
+      </c>
       <c r="I318" s="51">
         <v>101</v>
       </c>
@@ -12963,9 +12999,7 @@
       <c r="G319" t="s">
         <v>219</v>
       </c>
-      <c r="H319" s="51">
-        <v>5</v>
-      </c>
+      <c r="H319" s="51"/>
       <c r="I319" s="51">
         <v>101</v>
       </c>
@@ -13030,7 +13064,7 @@
         <v>224</v>
       </c>
       <c r="H324" s="51">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="I324" s="51">
         <v>101</v>
@@ -13085,9 +13119,6 @@
       <c r="G328" t="s">
         <v>219</v>
       </c>
-      <c r="H328">
-        <v>15</v>
-      </c>
       <c r="I328" s="51">
         <v>105</v>
       </c>
@@ -13113,9 +13144,6 @@
       <c r="G330" t="s">
         <v>221</v>
       </c>
-      <c r="H330">
-        <v>1</v>
-      </c>
       <c r="I330" s="51">
         <v>105</v>
       </c>
@@ -13128,9 +13156,7 @@
       <c r="G331" t="s">
         <v>222</v>
       </c>
-      <c r="H331" s="51">
-        <v>1</v>
-      </c>
+      <c r="H331" s="51"/>
       <c r="I331" s="51">
         <v>105</v>
       </c>
@@ -13143,9 +13169,6 @@
       <c r="G332" t="s">
         <v>223</v>
       </c>
-      <c r="H332">
-        <v>1</v>
-      </c>
       <c r="I332" s="51">
         <v>105</v>
       </c>
@@ -13159,7 +13182,7 @@
         <v>224</v>
       </c>
       <c r="H333" s="51">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="I333" s="51">
         <v>105</v>
@@ -13203,7 +13226,7 @@
         <v>218</v>
       </c>
       <c r="H336" s="51">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="I336" s="51">
         <v>202</v>
@@ -13218,7 +13241,7 @@
         <v>219</v>
       </c>
       <c r="H337" s="51">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="I337" s="51">
         <v>202</v>
@@ -13233,7 +13256,7 @@
         <v>220</v>
       </c>
       <c r="H338" s="51">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="I338" s="51">
         <v>202</v>
@@ -13248,7 +13271,7 @@
         <v>221</v>
       </c>
       <c r="H339" s="51">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="I339" s="51">
         <v>202</v>
@@ -13263,7 +13286,7 @@
         <v>222</v>
       </c>
       <c r="H340">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="I340" s="51">
         <v>202</v>
@@ -13278,7 +13301,7 @@
         <v>223</v>
       </c>
       <c r="H341" s="51">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="I341" s="51">
         <v>202</v>
@@ -13293,7 +13316,7 @@
         <v>224</v>
       </c>
       <c r="H342" s="51">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I342" s="51">
         <v>202</v>
@@ -13308,7 +13331,7 @@
         <v>225</v>
       </c>
       <c r="H343" s="51">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="I343" s="51">
         <v>202</v>
@@ -13323,7 +13346,7 @@
         <v>226</v>
       </c>
       <c r="H344" s="51">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="I344" s="51">
         <v>202</v>
@@ -13340,9 +13363,6 @@
       <c r="G345" t="s">
         <v>218</v>
       </c>
-      <c r="H345">
-        <v>24</v>
-      </c>
       <c r="I345" s="51">
         <v>198</v>
       </c>
@@ -13355,9 +13375,7 @@
       <c r="G346" t="s">
         <v>219</v>
       </c>
-      <c r="H346" s="51">
-        <v>15</v>
-      </c>
+      <c r="H346" s="51"/>
       <c r="I346" s="51">
         <v>198</v>
       </c>
@@ -13370,9 +13388,7 @@
       <c r="G347" t="s">
         <v>220</v>
       </c>
-      <c r="H347" s="51">
-        <v>63</v>
-      </c>
+      <c r="H347" s="51"/>
       <c r="I347" s="51">
         <v>198</v>
       </c>
@@ -13385,9 +13401,6 @@
       <c r="G348" t="s">
         <v>221</v>
       </c>
-      <c r="H348">
-        <v>25</v>
-      </c>
       <c r="I348" s="51">
         <v>198</v>
       </c>
@@ -13400,9 +13413,7 @@
       <c r="G349" t="s">
         <v>222</v>
       </c>
-      <c r="H349" s="51">
-        <v>48</v>
-      </c>
+      <c r="H349" s="51"/>
       <c r="I349" s="51">
         <v>198</v>
       </c>
@@ -13415,9 +13426,7 @@
       <c r="G350" t="s">
         <v>223</v>
       </c>
-      <c r="H350" s="51">
-        <v>25</v>
-      </c>
+      <c r="H350" s="51"/>
       <c r="I350" s="51">
         <v>198</v>
       </c>
@@ -13430,9 +13439,7 @@
       <c r="G351" t="s">
         <v>224</v>
       </c>
-      <c r="H351" s="51">
-        <v>39</v>
-      </c>
+      <c r="H351" s="51"/>
       <c r="I351" s="51">
         <v>198</v>
       </c>
@@ -13445,9 +13452,6 @@
       <c r="G352" t="s">
         <v>225</v>
       </c>
-      <c r="H352">
-        <v>14</v>
-      </c>
       <c r="I352" s="51">
         <v>198</v>
       </c>
@@ -13460,9 +13464,7 @@
       <c r="G353" t="s">
         <v>226</v>
       </c>
-      <c r="H353" s="51">
-        <v>19</v>
-      </c>
+      <c r="H353" s="51"/>
       <c r="I353" s="51">
         <v>198</v>
       </c>
@@ -13491,9 +13493,7 @@
       <c r="G355" t="s">
         <v>219</v>
       </c>
-      <c r="H355" s="51">
-        <v>3</v>
-      </c>
+      <c r="H355" s="51"/>
       <c r="I355" s="51">
         <v>103</v>
       </c>
@@ -13558,9 +13558,7 @@
       <c r="G360" t="s">
         <v>224</v>
       </c>
-      <c r="H360" s="51">
-        <v>23</v>
-      </c>
+      <c r="H360" s="51"/>
       <c r="I360" s="51">
         <v>103</v>
       </c>
@@ -13602,9 +13600,7 @@
       <c r="G363" t="s">
         <v>218</v>
       </c>
-      <c r="H363" s="51">
-        <v>7</v>
-      </c>
+      <c r="H363" s="51"/>
       <c r="I363" s="51">
         <v>119</v>
       </c>
@@ -13617,9 +13613,7 @@
       <c r="G364" t="s">
         <v>219</v>
       </c>
-      <c r="H364" s="51">
-        <v>21</v>
-      </c>
+      <c r="H364" s="51"/>
       <c r="I364" s="51">
         <v>119</v>
       </c>
@@ -13632,9 +13626,7 @@
       <c r="G365" t="s">
         <v>220</v>
       </c>
-      <c r="H365" s="51">
-        <v>12</v>
-      </c>
+      <c r="H365" s="51"/>
       <c r="I365" s="51">
         <v>119</v>
       </c>
@@ -13647,9 +13639,7 @@
       <c r="G366" t="s">
         <v>221</v>
       </c>
-      <c r="H366" s="51">
-        <v>27</v>
-      </c>
+      <c r="H366" s="51"/>
       <c r="I366" s="51">
         <v>119</v>
       </c>
@@ -13662,9 +13652,7 @@
       <c r="G367" t="s">
         <v>222</v>
       </c>
-      <c r="H367" s="51">
-        <v>24</v>
-      </c>
+      <c r="H367" s="51"/>
       <c r="I367" s="51">
         <v>119</v>
       </c>
@@ -13677,9 +13665,7 @@
       <c r="G368" t="s">
         <v>223</v>
       </c>
-      <c r="H368" s="51">
-        <v>25</v>
-      </c>
+      <c r="H368" s="51"/>
       <c r="I368" s="51">
         <v>119</v>
       </c>
@@ -13692,9 +13678,7 @@
       <c r="G369" t="s">
         <v>224</v>
       </c>
-      <c r="H369" s="51">
-        <v>8</v>
-      </c>
+      <c r="H369" s="51"/>
       <c r="I369" s="51">
         <v>119</v>
       </c>
@@ -13707,9 +13691,7 @@
       <c r="G370" t="s">
         <v>225</v>
       </c>
-      <c r="H370" s="51">
-        <v>7</v>
-      </c>
+      <c r="H370" s="51"/>
       <c r="I370" s="51">
         <v>119</v>
       </c>
@@ -13722,9 +13704,7 @@
       <c r="G371" t="s">
         <v>226</v>
       </c>
-      <c r="H371" s="35">
-        <v>8</v>
-      </c>
+      <c r="H371" s="35"/>
       <c r="I371" s="35">
         <v>119</v>
       </c>
@@ -13740,9 +13720,6 @@
       <c r="G372" t="s">
         <v>218</v>
       </c>
-      <c r="H372">
-        <v>39</v>
-      </c>
       <c r="I372">
         <v>119</v>
       </c>
@@ -13755,9 +13732,6 @@
       <c r="G373" t="s">
         <v>219</v>
       </c>
-      <c r="H373">
-        <v>9</v>
-      </c>
       <c r="I373">
         <v>119</v>
       </c>
@@ -13770,9 +13744,6 @@
       <c r="G374" t="s">
         <v>220</v>
       </c>
-      <c r="H374">
-        <v>20</v>
-      </c>
       <c r="I374">
         <v>119</v>
       </c>
@@ -13785,9 +13756,6 @@
       <c r="G375" t="s">
         <v>221</v>
       </c>
-      <c r="H375">
-        <v>36</v>
-      </c>
       <c r="I375">
         <v>119</v>
       </c>
@@ -13800,9 +13768,6 @@
       <c r="G376" t="s">
         <v>222</v>
       </c>
-      <c r="H376">
-        <v>45</v>
-      </c>
       <c r="I376">
         <v>119</v>
       </c>
@@ -13815,9 +13780,6 @@
       <c r="G377" t="s">
         <v>223</v>
       </c>
-      <c r="H377">
-        <v>39</v>
-      </c>
       <c r="I377">
         <v>119</v>
       </c>
@@ -13830,9 +13792,6 @@
       <c r="G378" t="s">
         <v>224</v>
       </c>
-      <c r="H378">
-        <v>12</v>
-      </c>
       <c r="I378">
         <v>119</v>
       </c>
@@ -13845,9 +13804,6 @@
       <c r="G379" t="s">
         <v>225</v>
       </c>
-      <c r="H379">
-        <v>6</v>
-      </c>
       <c r="I379">
         <v>119</v>
       </c>
@@ -13860,9 +13816,6 @@
       <c r="G380" t="s">
         <v>226</v>
       </c>
-      <c r="H380">
-        <v>5</v>
-      </c>
       <c r="I380">
         <v>119</v>
       </c>
@@ -13878,9 +13831,6 @@
       <c r="G381" t="s">
         <v>218</v>
       </c>
-      <c r="H381">
-        <v>2</v>
-      </c>
       <c r="I381">
         <v>113</v>
       </c>
@@ -13905,9 +13855,6 @@
       <c r="G383" t="s">
         <v>220</v>
       </c>
-      <c r="H383">
-        <v>9</v>
-      </c>
       <c r="I383">
         <v>113</v>
       </c>
@@ -13920,9 +13867,6 @@
       <c r="G384" t="s">
         <v>221</v>
       </c>
-      <c r="H384">
-        <v>1</v>
-      </c>
       <c r="I384">
         <v>113</v>
       </c>
@@ -13935,9 +13879,6 @@
       <c r="G385" t="s">
         <v>222</v>
       </c>
-      <c r="H385">
-        <v>3</v>
-      </c>
       <c r="I385">
         <v>113</v>
       </c>
@@ -13950,9 +13891,6 @@
       <c r="G386" t="s">
         <v>223</v>
       </c>
-      <c r="H386">
-        <v>10</v>
-      </c>
       <c r="I386">
         <v>113</v>
       </c>
@@ -13965,9 +13903,6 @@
       <c r="G387" t="s">
         <v>224</v>
       </c>
-      <c r="H387">
-        <v>15</v>
-      </c>
       <c r="I387">
         <v>113</v>
       </c>
@@ -13980,9 +13915,6 @@
       <c r="G388" t="s">
         <v>225</v>
       </c>
-      <c r="H388">
-        <v>4</v>
-      </c>
       <c r="I388">
         <v>113</v>
       </c>
@@ -13995,9 +13927,6 @@
       <c r="G389" t="s">
         <v>226</v>
       </c>
-      <c r="H389">
-        <v>4</v>
-      </c>
       <c r="I389">
         <v>113</v>
       </c>
@@ -14014,7 +13943,7 @@
         <v>218</v>
       </c>
       <c r="H390">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="I390">
         <v>194</v>
@@ -14028,9 +13957,6 @@
       <c r="G391" t="s">
         <v>219</v>
       </c>
-      <c r="H391">
-        <v>40</v>
-      </c>
       <c r="I391">
         <v>194</v>
       </c>
@@ -14044,7 +13970,7 @@
         <v>220</v>
       </c>
       <c r="H392">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="I392">
         <v>194</v>
@@ -14059,7 +13985,7 @@
         <v>221</v>
       </c>
       <c r="H393">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="I393">
         <v>194</v>
@@ -14074,7 +14000,7 @@
         <v>222</v>
       </c>
       <c r="H394">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="I394">
         <v>194</v>
@@ -14089,7 +14015,7 @@
         <v>223</v>
       </c>
       <c r="H395">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="I395">
         <v>194</v>
@@ -14104,7 +14030,7 @@
         <v>224</v>
       </c>
       <c r="H396">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I396">
         <v>194</v>
@@ -14119,7 +14045,7 @@
         <v>225</v>
       </c>
       <c r="H397">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I397">
         <v>194</v>
@@ -14134,7 +14060,7 @@
         <v>226</v>
       </c>
       <c r="H398">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="I398">
         <v>194</v>
@@ -14152,7 +14078,7 @@
         <v>218</v>
       </c>
       <c r="H399">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="I399">
         <v>161</v>
@@ -14167,7 +14093,7 @@
         <v>219</v>
       </c>
       <c r="H400">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="I400">
         <v>161</v>
@@ -14182,7 +14108,7 @@
         <v>220</v>
       </c>
       <c r="H401">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="I401">
         <v>161</v>
@@ -14197,7 +14123,7 @@
         <v>221</v>
       </c>
       <c r="H402">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="I402">
         <v>161</v>
@@ -14212,7 +14138,7 @@
         <v>222</v>
       </c>
       <c r="H403">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="I403">
         <v>161</v>
@@ -14227,7 +14153,7 @@
         <v>223</v>
       </c>
       <c r="H404">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="I404">
         <v>161</v>
@@ -14242,7 +14168,7 @@
         <v>224</v>
       </c>
       <c r="H405">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I405">
         <v>161</v>
@@ -14257,7 +14183,7 @@
         <v>225</v>
       </c>
       <c r="H406">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="I406">
         <v>161</v>
@@ -14272,7 +14198,7 @@
         <v>226</v>
       </c>
       <c r="H407">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="I407">
         <v>161</v>

--- a/data/historial/2026-06-29.xlsx
+++ b/data/historial/2026-06-29.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46301E67-CF20-40EA-9E6F-8156488F32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE1BB90A-BFEB-48EE-87C3-D034647CF518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="231">
   <si>
     <t>GOMEZ MARTÍN</t>
   </si>
@@ -724,33 +724,6 @@
     <t>57 - ROUBINEAU SEBASTIAN</t>
   </si>
   <si>
-    <t>148 - ALMACEN</t>
-  </si>
-  <si>
-    <t>148 - Articulos Sin Asociar Agrupacion</t>
-  </si>
-  <si>
-    <t>148 - BEBIDAS</t>
-  </si>
-  <si>
-    <t>148 - CHOCOLATE</t>
-  </si>
-  <si>
-    <t>148 - GALLETITAS</t>
-  </si>
-  <si>
-    <t>148 - GOLOSINAS</t>
-  </si>
-  <si>
-    <t>148 - MASCOTAS</t>
-  </si>
-  <si>
-    <t>148 - NO PERECEDEROS</t>
-  </si>
-  <si>
-    <t>148 - PILAS</t>
-  </si>
-  <si>
     <t>GONZALO (SUPERVISOR)</t>
   </si>
   <si>
@@ -761,6 +734,33 @@
   </si>
   <si>
     <t>30 - GOMEZ MARTÍN</t>
+  </si>
+  <si>
+    <t>145 - ALMACEN</t>
+  </si>
+  <si>
+    <t>145 - Articulos Sin Asociar Agrupacion</t>
+  </si>
+  <si>
+    <t>145 - BEBIDAS</t>
+  </si>
+  <si>
+    <t>145 - CHOCOLATE</t>
+  </si>
+  <si>
+    <t>145 - GALLETITAS</t>
+  </si>
+  <si>
+    <t>145 - GOLOSINAS</t>
+  </si>
+  <si>
+    <t>145 - MASCOTAS</t>
+  </si>
+  <si>
+    <t>145 - NO PERECEDEROS</t>
+  </si>
+  <si>
+    <t>145 - PILAS</t>
   </si>
 </sst>
 </file>
@@ -944,6 +944,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="41">
@@ -2481,7 +2482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
@@ -2528,22 +2529,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="96">
-        <v>6558.7795207961999</v>
+        <v>12759.648138517299</v>
       </c>
       <c r="D2" s="96">
-        <v>33249.429086679302</v>
+        <v>61262.625914064098</v>
       </c>
       <c r="E2" s="96">
-        <v>131472225.13729897</v>
+        <v>223094212.44056469</v>
       </c>
       <c r="F2" s="96">
         <v>0</v>
       </c>
       <c r="G2" s="96">
-        <v>110010.710440881</v>
+        <v>141404.35170655229</v>
       </c>
       <c r="H2" s="96">
-        <v>110010.71</v>
+        <v>141404.38</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2554,22 +2555,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="96">
-        <v>116.7140046289</v>
+        <v>168.2765046287</v>
       </c>
       <c r="D3" s="96">
-        <v>405.59822338279997</v>
+        <v>491.7907233853</v>
       </c>
       <c r="E3" s="96">
-        <v>3667023.6813626946</v>
+        <v>4713478.3902184051</v>
       </c>
       <c r="F3" s="96">
         <v>0</v>
       </c>
       <c r="G3" s="96">
-        <v>110010.710440881</v>
+        <v>141404.35170655229</v>
       </c>
       <c r="H3" s="96">
-        <v>110010.71</v>
+        <v>141404.38</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2580,13 +2581,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="96">
-        <v>41.587301587100001</v>
+        <v>89.716765872799996</v>
       </c>
       <c r="D4" s="96">
-        <v>105.26750000059999</v>
+        <v>228.65250000060001</v>
       </c>
       <c r="E4" s="96">
-        <v>1647814.3144255385</v>
+        <v>3490474.4748070529</v>
       </c>
       <c r="F4" s="96">
         <v>0</v>
@@ -2606,13 +2607,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="96">
-        <v>58.938888888800001</v>
+        <v>113.08222222160001</v>
       </c>
       <c r="D5" s="96">
-        <v>198.29750000160001</v>
+        <v>487.77000000160001</v>
       </c>
       <c r="E5" s="96">
-        <v>1318807.9914469167</v>
+        <v>2539362.2668490014</v>
       </c>
       <c r="F5" s="96">
         <v>0</v>
@@ -2632,13 +2633,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="96">
-        <v>280.46388888860002</v>
+        <v>319.23392857089999</v>
       </c>
       <c r="D6" s="96">
-        <v>845.98667857580006</v>
+        <v>1011.7841785766</v>
       </c>
       <c r="E6" s="96">
-        <v>4892925.4103550436</v>
+        <v>5960130.3637676956</v>
       </c>
       <c r="F6" s="96">
         <v>0</v>
@@ -2658,13 +2659,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="96">
-        <v>111.15117063460001</v>
+        <v>219.94720238030001</v>
       </c>
       <c r="D7" s="96">
-        <v>444.78250000499997</v>
+        <v>984.96450000130005</v>
       </c>
       <c r="E7" s="96">
-        <v>2332273.4502824824</v>
+        <v>4232380.5042614806</v>
       </c>
       <c r="F7" s="96">
         <v>0</v>
@@ -2684,13 +2685,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="96">
-        <v>-63.0666666666</v>
+        <v>1614.9333333334</v>
       </c>
       <c r="D8" s="96">
-        <v>-561.47599999859995</v>
+        <v>1507.4840000014001</v>
       </c>
       <c r="E8" s="96">
-        <v>-974804.98299181263</v>
+        <v>16463801.298558187</v>
       </c>
       <c r="F8" s="96">
         <v>0</v>
@@ -2710,13 +2711,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="96">
-        <v>57.559821428699998</v>
+        <v>113.1691071427</v>
       </c>
       <c r="D9" s="96">
-        <v>356.74749999900001</v>
+        <v>643.5574999982</v>
       </c>
       <c r="E9" s="96">
-        <v>1244100.7657470268</v>
+        <v>2229458.8498637299</v>
       </c>
       <c r="F9" s="96">
         <v>0</v>
@@ -2736,13 +2737,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="96">
-        <v>139.331597222</v>
+        <v>67.089751984100005</v>
       </c>
       <c r="D10" s="96">
-        <v>164.92640624699999</v>
+        <v>200.80203124760001</v>
       </c>
       <c r="E10" s="96">
-        <v>3336344.5485263281</v>
+        <v>2237337.654012111</v>
       </c>
       <c r="F10" s="96">
         <v>0</v>
@@ -2762,13 +2763,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="96">
-        <v>48.933888888600002</v>
+        <v>69.604761904499995</v>
       </c>
       <c r="D11" s="96">
-        <v>166.67042857070001</v>
+        <v>303.04959523730003</v>
       </c>
       <c r="E11" s="96">
-        <v>772280.47046408884</v>
+        <v>1556471.8667402903</v>
       </c>
       <c r="F11" s="96">
         <v>0</v>
@@ -2788,13 +2789,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="96">
-        <v>73.503174603100007</v>
+        <v>178.19682539589999</v>
       </c>
       <c r="D12" s="96">
-        <v>254.69845238280001</v>
+        <v>527.69845237909999</v>
       </c>
       <c r="E12" s="96">
-        <v>1763034.9919922091</v>
+        <v>3454829.7358999122</v>
       </c>
       <c r="F12" s="96">
         <v>0</v>
@@ -2814,13 +2815,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="96">
-        <v>187.14523809479999</v>
+        <v>225.7950396821</v>
       </c>
       <c r="D13" s="96">
-        <v>683.18651190790001</v>
+        <v>829.79151190790003</v>
       </c>
       <c r="E13" s="96">
-        <v>3752668.2666791501</v>
+        <v>4650179.1579327742</v>
       </c>
       <c r="F13" s="96">
         <v>0</v>
@@ -2840,13 +2841,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="96">
-        <v>927.30138888939996</v>
+        <v>1444.0819444447</v>
       </c>
       <c r="D14" s="96">
-        <v>9490.8625000041993</v>
+        <v>13580.7225000012</v>
       </c>
       <c r="E14" s="96">
-        <v>27711765.916719597</v>
+        <v>35677866.984969728</v>
       </c>
       <c r="F14" s="96">
         <v>0</v>
@@ -2866,13 +2867,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="96">
-        <v>132.38382936490001</v>
+        <v>203.11855158700001</v>
       </c>
       <c r="D15" s="96">
-        <v>597.52499999860004</v>
+        <v>755.52499999940005</v>
       </c>
       <c r="E15" s="96">
-        <v>2224929.6365325735</v>
+        <v>3799689.1529486589</v>
       </c>
       <c r="F15" s="96">
         <v>0</v>
@@ -2892,13 +2893,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="96">
-        <v>80.620000000100006</v>
+        <v>128.3049206343</v>
       </c>
       <c r="D16" s="96">
-        <v>422.70208333869999</v>
+        <v>693.45458333670001</v>
       </c>
       <c r="E16" s="96">
-        <v>1974051.5620993127</v>
+        <v>3126324.9965506792</v>
       </c>
       <c r="F16" s="96">
         <v>0</v>
@@ -2918,13 +2919,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="96">
-        <v>112.3860119039</v>
+        <v>214.7180555544</v>
       </c>
       <c r="D17" s="96">
-        <v>405.94000000680001</v>
+        <v>616.00885714909998</v>
       </c>
       <c r="E17" s="96">
-        <v>2774896.9225576972</v>
+        <v>5092283.3348378455</v>
       </c>
       <c r="F17" s="96">
         <v>0</v>
@@ -2944,13 +2945,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="96">
-        <v>269.62529761849999</v>
+        <v>339.81365079310001</v>
       </c>
       <c r="D18" s="96">
-        <v>1970.7039166622999</v>
+        <v>2209.1249285679</v>
       </c>
       <c r="E18" s="96">
-        <v>4682028.2206923608</v>
+        <v>6538018.3834050605</v>
       </c>
       <c r="F18" s="96">
         <v>0</v>
@@ -2970,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="96">
-        <v>172.05783730120001</v>
+        <v>242.1867394173</v>
       </c>
       <c r="D19" s="96">
-        <v>473.31017857680001</v>
+        <v>821.9142142938</v>
       </c>
       <c r="E19" s="96">
-        <v>3804498.4929125779</v>
+        <v>5313079.7996425815</v>
       </c>
       <c r="F19" s="96">
         <v>0</v>
@@ -2996,13 +2997,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="96">
-        <v>407.06958333329999</v>
+        <v>1331.513234127</v>
       </c>
       <c r="D20" s="96">
-        <v>1164.4874999997</v>
+        <v>7081.0849999985003</v>
       </c>
       <c r="E20" s="96">
-        <v>7023074.0484903501</v>
+        <v>18543635.055367131</v>
       </c>
       <c r="F20" s="96">
         <v>0</v>
@@ -3022,13 +3023,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="96">
-        <v>111.473115079</v>
+        <v>174.00490079319999</v>
       </c>
       <c r="D21" s="96">
-        <v>409.77460714760002</v>
+        <v>605.7746071478</v>
       </c>
       <c r="E21" s="96">
-        <v>2482567.9113498144</v>
+        <v>3621062.6775038806</v>
       </c>
       <c r="F21" s="96">
         <v>0</v>
@@ -3048,13 +3049,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="96">
-        <v>77.0229166668</v>
+        <v>123.90625</v>
       </c>
       <c r="D22" s="96">
-        <v>175.00999999839999</v>
+        <v>291.22892856869998</v>
       </c>
       <c r="E22" s="96">
-        <v>1231155.9948169386</v>
+        <v>1931060.2247250369</v>
       </c>
       <c r="F22" s="96">
         <v>0</v>
@@ -3094,7 +3095,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="96" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="B24" s="96">
         <v>1</v>
@@ -3126,13 +3127,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="96">
-        <v>108.580952381</v>
+        <v>151.11507936480001</v>
       </c>
       <c r="D25" s="96">
-        <v>331.05000000159998</v>
+        <v>563.25500000219995</v>
       </c>
       <c r="E25" s="96">
-        <v>2185400.7533588032</v>
+        <v>3265458.2459612871</v>
       </c>
       <c r="F25" s="96">
         <v>0</v>
@@ -3152,13 +3153,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="96">
-        <v>50.997817460199997</v>
+        <v>78.740436507300004</v>
       </c>
       <c r="D26" s="96">
-        <v>218.0000000018</v>
+        <v>282.00000000040001</v>
       </c>
       <c r="E26" s="96">
-        <v>1312962.2237802313</v>
+        <v>1905347.2963424551</v>
       </c>
       <c r="F26" s="96">
         <v>0</v>
@@ -3172,19 +3173,19 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="96" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B27" s="96">
         <v>1</v>
       </c>
       <c r="C27" s="96">
-        <v>835</v>
+        <v>1334.5</v>
       </c>
       <c r="D27" s="96">
-        <v>2100</v>
+        <v>2577.1799999999998</v>
       </c>
       <c r="E27" s="96">
-        <v>7231266.6113499999</v>
+        <v>13136953.343350001</v>
       </c>
       <c r="F27" s="96">
         <v>0</v>
@@ -3204,13 +3205,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="96">
-        <v>172.9596428566</v>
+        <v>224.8947354492</v>
       </c>
       <c r="D28" s="96">
-        <v>899.49958333749998</v>
+        <v>1004.4995833371</v>
       </c>
       <c r="E28" s="96">
-        <v>3717567.9331198842</v>
+        <v>4525419.7648018571</v>
       </c>
       <c r="F28" s="96">
         <v>0</v>
@@ -3230,13 +3231,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="96">
-        <v>281.40083333320001</v>
+        <v>386.73</v>
       </c>
       <c r="D29" s="96">
-        <v>1083.4799999999</v>
+        <v>1523.5400000018999</v>
       </c>
       <c r="E29" s="96">
-        <v>5151540.6591492426</v>
+        <v>7197381.3632933144</v>
       </c>
       <c r="F29" s="96">
         <v>0</v>
@@ -3256,13 +3257,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="96">
-        <v>55.934623015699998</v>
+        <v>73.557242063700002</v>
       </c>
       <c r="D30" s="96">
-        <v>202.7625000024</v>
+        <v>290.52000000279997</v>
       </c>
       <c r="E30" s="96">
-        <v>1012363.4850253685</v>
+        <v>1342266.2312651528</v>
       </c>
       <c r="F30" s="96">
         <v>0</v>
@@ -3282,13 +3283,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="96">
-        <v>55.3718253961</v>
+        <v>90.458531745100004</v>
       </c>
       <c r="D31" s="96">
-        <v>212.5949999984</v>
+        <v>283.59499999920001</v>
       </c>
       <c r="E31" s="96">
-        <v>1127867.2813395613</v>
+        <v>1662817.6962441357</v>
       </c>
       <c r="F31" s="96">
         <v>0</v>
@@ -3308,13 +3309,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="96">
-        <v>15.0083333333</v>
+        <v>28.535912698600001</v>
       </c>
       <c r="D32" s="96">
-        <v>122.9999999992</v>
+        <v>178.64666666860001</v>
       </c>
       <c r="E32" s="96">
-        <v>474208.7541035653</v>
+        <v>920475.59202497394</v>
       </c>
       <c r="F32" s="96">
         <v>0</v>
@@ -3334,13 +3335,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="96">
-        <v>57.744861111200002</v>
+        <v>215.69446428559999</v>
       </c>
       <c r="D33" s="96">
-        <v>409.99999999919999</v>
+        <v>439.00999999959998</v>
       </c>
       <c r="E33" s="96">
-        <v>1465987.5738126547</v>
+        <v>2806120.8392654946</v>
       </c>
       <c r="F33" s="96">
         <v>0</v>
@@ -3386,13 +3387,13 @@
         <v>1</v>
       </c>
       <c r="C35" s="96">
-        <v>96.820039681799997</v>
+        <v>186.83611111089999</v>
       </c>
       <c r="D35" s="96">
-        <v>526.00500000149998</v>
+        <v>804.41601190910001</v>
       </c>
       <c r="E35" s="96">
-        <v>2007902.2622231084</v>
+        <v>3880349.2779353959</v>
       </c>
       <c r="F35" s="96">
         <v>0</v>
@@ -3412,13 +3413,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="96">
-        <v>419.7483730161</v>
+        <v>414.39123015899997</v>
       </c>
       <c r="D36" s="96">
-        <v>2354.8888214259</v>
+        <v>2342.8888214259</v>
       </c>
       <c r="E36" s="96">
-        <v>7395442.6965926401</v>
+        <v>7342359.2744361712</v>
       </c>
       <c r="F36" s="96">
         <v>0</v>
@@ -3438,13 +3439,13 @@
         <v>1</v>
       </c>
       <c r="C37" s="96">
-        <v>53.475757575700001</v>
+        <v>197.30909090899999</v>
       </c>
       <c r="D37" s="96">
-        <v>472.43</v>
+        <v>2277.9899999992999</v>
       </c>
       <c r="E37" s="96">
-        <v>968840.97419863928</v>
+        <v>4699575.8856638623</v>
       </c>
       <c r="F37" s="96">
         <v>0</v>
@@ -3464,13 +3465,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="96">
-        <v>84.666666666699996</v>
+        <v>283.9166666667</v>
       </c>
       <c r="D38" s="96">
-        <v>682.28</v>
+        <v>3082.25</v>
       </c>
       <c r="E38" s="96">
-        <v>1445131.6450023698</v>
+        <v>5825319.4707523696</v>
       </c>
       <c r="F38" s="96">
         <v>0</v>
@@ -3490,13 +3491,13 @@
         <v>1</v>
       </c>
       <c r="C39" s="96">
-        <v>110.56512566089999</v>
+        <v>131.14181216910001</v>
       </c>
       <c r="D39" s="96">
-        <v>374.96807010729998</v>
+        <v>471.4394986822</v>
       </c>
       <c r="E39" s="96">
-        <v>2373341.2642009868</v>
+        <v>3150944.560423614</v>
       </c>
       <c r="F39" s="96">
         <v>0</v>
@@ -3516,13 +3517,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="96">
-        <v>-188</v>
+        <v>548.43968253950004</v>
       </c>
       <c r="D40" s="96">
-        <v>-1860</v>
+        <v>4046.0241666669999</v>
       </c>
       <c r="E40" s="96">
-        <v>-2433547.0814999999</v>
+        <v>7402539.5016198214</v>
       </c>
       <c r="F40" s="96">
         <v>0</v>
@@ -3536,19 +3537,19 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="96" t="s">
-        <v>146</v>
+        <v>217</v>
       </c>
       <c r="B41" s="96">
         <v>1</v>
       </c>
       <c r="C41" s="96">
-        <v>-3.2222222223000001</v>
+        <v>6</v>
       </c>
       <c r="D41" s="96">
-        <v>-20.505000001599999</v>
+        <v>81</v>
       </c>
       <c r="E41" s="96">
-        <v>-388379.73864699452</v>
+        <v>149294.68419999999</v>
       </c>
       <c r="F41" s="96">
         <v>0</v>
@@ -3562,19 +3563,19 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="96" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B42" s="96">
         <v>1</v>
       </c>
       <c r="C42" s="96">
-        <v>157.7577380953</v>
+        <v>-6.2142857142999999</v>
       </c>
       <c r="D42" s="96">
-        <v>1811.0000000018999</v>
+        <v>-6.2810714286999998</v>
       </c>
       <c r="E42" s="96">
-        <v>3004106.7923235167</v>
+        <v>-275260.76904147147</v>
       </c>
       <c r="F42" s="96">
         <v>0</v>
@@ -3583,6 +3584,58 @@
         <v>0</v>
       </c>
       <c r="H42" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="96" t="s">
+        <v>146</v>
+      </c>
+      <c r="B43" s="96">
+        <v>1</v>
+      </c>
+      <c r="C43" s="96">
+        <v>-3.2847222223000001</v>
+      </c>
+      <c r="D43" s="96">
+        <v>-20.505000001599999</v>
+      </c>
+      <c r="E43" s="96">
+        <v>-402349.89063324447</v>
+      </c>
+      <c r="F43" s="96">
+        <v>0</v>
+      </c>
+      <c r="G43" s="96">
+        <v>0</v>
+      </c>
+      <c r="H43" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="96" t="s">
+        <v>156</v>
+      </c>
+      <c r="B44" s="96">
+        <v>1</v>
+      </c>
+      <c r="C44" s="96">
+        <v>184.42559523840001</v>
+      </c>
+      <c r="D44" s="96">
+        <v>2016.0000000025</v>
+      </c>
+      <c r="E44" s="96">
+        <v>3629491.4663937623</v>
+      </c>
+      <c r="F44" s="96">
+        <v>0</v>
+      </c>
+      <c r="G44" s="96">
+        <v>0</v>
+      </c>
+      <c r="H44" s="96">
         <v>0</v>
       </c>
     </row>
@@ -3663,44 +3716,44 @@
       </c>
       <c r="D2" s="59">
         <f>IFERROR(+VLOOKUP(B2,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6538018.3834050605</v>
+      </c>
+      <c r="E2" s="59">
         <v>4682028.2206923608</v>
-      </c>
-      <c r="E2" s="59">
-        <v>1379496.2566107768</v>
       </c>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>3302531.964081584</v>
+        <v>1855990.1627126997</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G41" si="1">+D2/C2</f>
-        <v>0.14504839382995705</v>
+        <v>0.20254663591143432</v>
       </c>
       <c r="H2" s="59">
         <f>+D2/$N$3*$N$4</f>
-        <v>56184338.648308329</v>
+        <v>52304147.067240477</v>
       </c>
       <c r="I2" s="60">
         <f t="shared" ref="I2:I41" si="2">+H2/C2</f>
-        <v>1.7405807259594843</v>
+        <v>1.6203730872914743</v>
       </c>
       <c r="J2" s="59">
         <f>+D2/$N$3</f>
-        <v>2341014.1103461804</v>
+        <v>2179339.46113502</v>
       </c>
       <c r="K2" s="59">
         <f t="shared" ref="K2:K41" si="3">+(C2-D2)/$N$2</f>
-        <v>1254411.2917071998</v>
+        <v>1225764.6788021759</v>
       </c>
       <c r="L2" s="61" cm="1">
         <f t="array" ref="L2">+_xlfn.IFS(I2&gt;114%,H2*0.02,I2&gt;109%,H2*0.015,I2&gt;104%,H2*0.0125,I2&gt;99%,H2*0.01,I2&lt;99%,H2*0)</f>
-        <v>1123686.7729661667</v>
+        <v>1046082.9413448096</v>
       </c>
       <c r="M2" s="53" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3713,45 +3766,45 @@
       </c>
       <c r="D3" s="4">
         <f>IFERROR(+VLOOKUP(B3,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5092283.3348378455</v>
+      </c>
+      <c r="E3" s="4">
         <v>2774896.9225576972</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1210391.5076398768</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="0"/>
-        <v>1564505.4149178204</v>
+        <v>2317386.4122801484</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
-        <v>8.956270430855634E-2</v>
+        <v>0.16435877774987445</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H41" si="4">+D3/$N$3*$N$4</f>
-        <v>33298763.070692368</v>
+        <v>40738266.678702764</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="2"/>
-        <v>1.0747524517026761</v>
+        <v>1.3148702219989956</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J41" si="5">+D3/$N$3</f>
-        <v>1387448.4612788486</v>
+        <v>1697427.7782792819</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="3"/>
-        <v>1282174.1480147981</v>
+        <v>1232878.3259069242</v>
       </c>
       <c r="L3" s="63" cm="1">
         <f t="array" ref="L3">+_xlfn.IFS(I3&gt;114%,H3*0.02,I3&gt;109%,H3*0.015,I3&gt;104%,H3*0.0125,I3&gt;99%,H3*0.01,I3&lt;99%,H3*0)</f>
-        <v>416234.53838365461</v>
+        <v>814765.33357405534</v>
       </c>
       <c r="M3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="N3">
         <f>N4-N2</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3764,38 +3817,38 @@
       </c>
       <c r="D4" s="4">
         <f>IFERROR(+VLOOKUP(B4,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3799689.1529486589</v>
+      </c>
+      <c r="E4" s="4">
         <v>2224929.6365325735</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1183899.192504474</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>1041030.4440280995</v>
+        <v>1574759.5164160854</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>7.8370101679167886E-2</v>
+        <v>0.13383885062086462</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="4"/>
-        <v>26699155.638390884</v>
+        <v>30397513.223589271</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>0.94044122015001475</v>
+        <v>1.070710804966917</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="5"/>
-        <v>1112464.8182662867</v>
+        <v>1266563.0509828862</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>1189322.8010734399</v>
+        <v>1170968.6717714092</v>
       </c>
       <c r="L4" s="63" cm="1">
         <f t="array" ref="L4">+_xlfn.IFS(I4&gt;114%,H4*0.02,I4&gt;109%,H4*0.015,I4&gt;104%,H4*0.0125,I4&gt;99%,H4*0.01,I4&lt;99%,H4*0)</f>
-        <v>0</v>
+        <v>379968.9152948659</v>
       </c>
       <c r="M4" s="53" t="s">
         <v>47</v>
@@ -3814,38 +3867,38 @@
       </c>
       <c r="D5" s="4">
         <f>IFERROR(+VLOOKUP(B5,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4650179.1579327742</v>
+      </c>
+      <c r="E5" s="4">
         <v>3752668.2666791501</v>
-      </c>
-      <c r="E5" s="4">
-        <v>2694955.1972862789</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>1057713.0693928711</v>
+        <v>897510.89125362411</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>0.13218260424907871</v>
+        <v>0.16379619716940358</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="4"/>
-        <v>45032019.200149804</v>
+        <v>37201433.263462193</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>1.5861912509889446</v>
+        <v>1.3103695773552286</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="5"/>
-        <v>1876334.133339575</v>
+        <v>1550059.7193109246</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>1119880.1360667774</v>
+        <v>1130469.1477245467</v>
       </c>
       <c r="L5" s="63" cm="1">
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
-        <v>900640.38400299614</v>
+        <v>744028.66526924388</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3858,38 +3911,38 @@
       </c>
       <c r="D6" s="4">
         <f>IFERROR(+VLOOKUP(B6,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3454829.7358999122</v>
+      </c>
+      <c r="E6" s="4">
         <v>1763034.9919922091</v>
-      </c>
-      <c r="E6" s="4">
-        <v>673949.31322047231</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>1089085.6787717368</v>
+        <v>1691794.7439077031</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>7.4931175686161061E-2</v>
+        <v>0.14683455239533538</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="4"/>
-        <v>21156419.903906509</v>
+        <v>27638637.887199298</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>0.89917410823393273</v>
+        <v>1.1746764191626831</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="5"/>
-        <v>881517.49599610455</v>
+        <v>1151609.9119666375</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>989349.5247967235</v>
+        <v>955899.75245810545</v>
       </c>
       <c r="L6" s="63" cm="1">
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
-        <v>0</v>
+        <v>552772.75774398597</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3902,34 +3955,34 @@
       </c>
       <c r="D7" s="4">
         <f>IFERROR(+VLOOKUP(B7,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2229458.8498637299</v>
+      </c>
+      <c r="E7" s="4">
         <v>1244100.7657470268</v>
-      </c>
-      <c r="E7" s="4">
-        <v>488198.71039685211</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F8" si="6">+D7-E7</f>
-        <v>755902.05535017466</v>
+        <v>985358.08411670313</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>4.4845619540927889E-2</v>
+        <v>8.0364441623913901E-2</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="4"/>
-        <v>14929209.188964322</v>
+        <v>17835670.798909839</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>0.53814743449113478</v>
+        <v>0.64291553299131121</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="5"/>
-        <v>622050.38287351339</v>
+        <v>743152.94995457667</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>1204443.4665780673</v>
+        <v>1214876.103838132</v>
       </c>
       <c r="L7" s="63" cm="1">
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
@@ -3946,34 +3999,34 @@
       </c>
       <c r="D8" s="4">
         <f>IFERROR(+VLOOKUP(B8,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4232380.5042614806</v>
+      </c>
+      <c r="E8" s="4">
         <v>2332273.4502824824</v>
-      </c>
-      <c r="E8" s="4">
-        <v>1318036.6824969184</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="6"/>
-        <v>1014236.7677855641</v>
+        <v>1900107.0539789982</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>6.5090809681490447E-2</v>
+        <v>0.11812040044839839</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="4"/>
-        <v>27987281.403389789</v>
+        <v>33859044.034091845</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>0.78108971617788536</v>
+        <v>0.94496320358718711</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="5"/>
-        <v>1166136.7251412412</v>
+        <v>1410793.5014204935</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="3"/>
-        <v>1522672.6348470554</v>
+        <v>1504699.5672693441</v>
       </c>
       <c r="L8" s="63" cm="1">
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
@@ -3990,38 +4043,38 @@
       </c>
       <c r="D9" s="4">
         <f>IFERROR(+VLOOKUP(B9,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5960130.3637676956</v>
+      </c>
+      <c r="E9" s="4">
         <v>4892925.4103550436</v>
-      </c>
-      <c r="E9" s="4">
-        <v>2772298.6238154541</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>2120626.7865395895</v>
+        <v>1067204.953412652</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>0.13655537545675622</v>
+        <v>0.16633971935747391</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="4"/>
-        <v>58715104.924260527</v>
+        <v>47681042.910141565</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>1.6386645054810749</v>
+        <v>1.3307177548597913</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="5"/>
-        <v>2446462.7051775218</v>
+        <v>1986710.1212558986</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>1406279.3639346664</v>
+        <v>1422425.7644357148</v>
       </c>
       <c r="L9" s="63" cm="1">
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
-        <v>1174302.0984852107</v>
+        <v>953620.85820283135</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4032,34 +4085,34 @@
       </c>
       <c r="D10" s="64">
         <f>+SUM(D2:D9)</f>
+        <v>35956969.48291716</v>
+      </c>
+      <c r="E10" s="65">
         <v>23666857.664838541</v>
-      </c>
-      <c r="E10" s="65">
-        <v>11721225.483971104</v>
       </c>
       <c r="F10" s="64">
         <f>+SUM(F2:F9)</f>
-        <v>11945632.180867441</v>
+        <v>12290111.818078615</v>
       </c>
       <c r="G10" s="66">
         <f t="shared" si="1"/>
-        <v>9.7404660690763742E-2</v>
+        <v>0.14798654141378115</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="4"/>
-        <v>284002291.97806251</v>
+        <v>287655755.86333728</v>
       </c>
       <c r="I10" s="66">
         <f t="shared" si="2"/>
-        <v>1.1688559282891648</v>
+        <v>1.1838923313102492</v>
       </c>
       <c r="J10" s="64">
         <f t="shared" si="5"/>
-        <v>11833428.832419271</v>
+        <v>11985656.494305721</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
-        <v>9968533.3670187257</v>
+        <v>9857982.0122063495</v>
       </c>
       <c r="L10" s="68"/>
     </row>
@@ -4075,38 +4128,38 @@
       </c>
       <c r="D11" s="59">
         <f>IFERROR(+VLOOKUP(B11,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>18543635.055367131</v>
+      </c>
+      <c r="E11" s="59">
         <v>7023074.0484903501</v>
-      </c>
-      <c r="E11" s="59">
-        <v>1279296.2102717794</v>
       </c>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F16" si="7">+D11-E11</f>
-        <v>5743777.8382185707</v>
+        <v>11520561.006876782</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
-        <v>7.242376953917623E-2</v>
+        <v>0.19122679647058316</v>
       </c>
       <c r="H11" s="59">
         <f t="shared" si="4"/>
-        <v>84276888.581884205</v>
+        <v>148349080.44293705</v>
       </c>
       <c r="I11" s="60">
         <f t="shared" si="2"/>
-        <v>0.86908523447011488</v>
+        <v>1.5298143717646653</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="5"/>
-        <v>3511537.0242451751</v>
+        <v>6181211.6851223772</v>
       </c>
       <c r="K11" s="59">
         <f t="shared" si="3"/>
-        <v>4088585.2014385075</v>
+        <v>3734681.5916557326</v>
       </c>
       <c r="L11" s="61" cm="1">
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
-        <v>0</v>
+        <v>1854363.5055367132</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4119,38 +4172,38 @@
       </c>
       <c r="D12" s="4">
         <f>IFERROR(+VLOOKUP(B12,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7342359.2744361712</v>
+      </c>
+      <c r="E12" s="4">
         <v>7395442.6965926401</v>
-      </c>
-      <c r="E12" s="4">
-        <v>7398671.9615932852</v>
       </c>
       <c r="F12" s="4">
         <f t="shared" si="7"/>
-        <v>-3229.2650006450713</v>
+        <v>-53083.422156468965</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.23380435376354097</v>
+        <v>0.23212613979826088</v>
       </c>
       <c r="H12" s="4">
         <f t="shared" si="4"/>
-        <v>88745312.359111682</v>
+        <v>58738874.195489362</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>2.8056522451624919</v>
+        <v>1.8570091183860868</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="5"/>
-        <v>3697721.3482963201</v>
+        <v>2447453.0914787236</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>1101611.8050897438</v>
+        <v>1156597.2921014682</v>
       </c>
       <c r="L12" s="63" cm="1">
         <f t="array" ref="L12">+_xlfn.IFS(I12&gt;114%,H12*0.02,I12&gt;109%,H12*0.015,I12&gt;104%,H12*0.0125,I12&gt;99%,H12*0.01,I12&lt;99%,H12*0)</f>
-        <v>1774906.2471822337</v>
+        <v>1174777.4839097874</v>
       </c>
       <c r="M12" s="27"/>
     </row>
@@ -4164,38 +4217,38 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>35677866.984969728</v>
+      </c>
+      <c r="E13" s="4">
         <v>27711765.916719597</v>
-      </c>
-      <c r="E13" s="4">
-        <v>22103798.373994444</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="7"/>
-        <v>5607967.5427251533</v>
+        <v>7966101.0682501309</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>0.2158843915342161</v>
+        <v>0.27794311731832977</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>332541191.00063515</v>
+        <v>285422935.87975782</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>2.5906126984105931</v>
+        <v>2.2235449385466382</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>13855882.958359798</v>
+        <v>11892622.328323243</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>4575097.7344502443</v>
+        <v>4413621.3852216788</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;114%,H13*0.0125,I13&gt;109%,H13*0.01,I13&gt;104%,H13*0.0075,I13&gt;99%,H13*0.005,I13&lt;99%,H13*0)</f>
-        <v>4156764.8875079397</v>
+        <v>3567786.6984969731</v>
       </c>
       <c r="M13" s="53" t="s">
         <v>61</v>
@@ -4214,34 +4267,34 @@
       </c>
       <c r="D14" s="4">
         <f>IFERROR(+VLOOKUP(B14,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4699575.8856638623</v>
+      </c>
+      <c r="E14" s="4">
         <v>968840.97419863928</v>
-      </c>
-      <c r="E14" s="4">
-        <v>483655.59259999997</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="7"/>
-        <v>485185.3815986393</v>
+        <v>3730734.9114652229</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>2.2823615732709485E-2</v>
+        <v>0.11071095977316531</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="4"/>
-        <v>11626091.690383671</v>
+        <v>37596607.085310899</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0.27388338879251378</v>
+        <v>0.88568767818532246</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="5"/>
-        <v>484420.48709931964</v>
+        <v>1566525.2952212875</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>1885464.3827625618</v>
+        <v>1797594.3575862448</v>
       </c>
       <c r="L14" s="63" cm="1">
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
@@ -4259,38 +4312,38 @@
       </c>
       <c r="D15" s="4">
         <f>IFERROR(+VLOOKUP(B15,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5825319.4707523696</v>
+      </c>
+      <c r="E15" s="4">
         <v>1445131.6450023698</v>
-      </c>
-      <c r="E15" s="4">
-        <v>-6760.5810000000001</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="7"/>
-        <v>1451892.2260023698</v>
+        <v>4380187.8257499998</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>3.4043904239283308E-2</v>
+        <v>0.13723083216076207</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="4"/>
-        <v>17341579.740028437</v>
+        <v>46602555.766018957</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>0.40852685087139967</v>
+        <v>1.0978466572860965</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="5"/>
-        <v>722565.82250118488</v>
+        <v>1941773.1569174565</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>1863814.8068169376</v>
+        <v>1743987.5202010777</v>
       </c>
       <c r="L15" s="63" cm="1">
         <f t="array" ref="L15">+_xlfn.IFS(I15&gt;109%,H15*0.015,I15&gt;104%,H15*0.0125,I15&gt;99%,H15*0.01,I15&lt;99%,H15*0)</f>
-        <v>0</v>
+        <v>699038.3364902843</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4301,34 +4354,34 @@
       </c>
       <c r="D16" s="64">
         <f>+SUM(D11:D15)</f>
+        <v>72088756.671189263</v>
+      </c>
+      <c r="E16" s="65">
         <v>44544255.281003602</v>
-      </c>
-      <c r="E16" s="65">
-        <v>31258661.557459507</v>
       </c>
       <c r="F16" s="64">
         <f t="shared" si="7"/>
-        <v>13285593.723544095</v>
+        <v>27544501.390185662</v>
       </c>
       <c r="G16" s="66">
         <f t="shared" si="1"/>
-        <v>0.13029783887878471</v>
+        <v>0.21086914894994976</v>
       </c>
       <c r="H16" s="64">
         <f t="shared" si="4"/>
-        <v>534531063.37204325</v>
+        <v>576710053.36951411</v>
       </c>
       <c r="I16" s="66">
         <f t="shared" si="2"/>
-        <v>1.5635740665454168</v>
+        <v>1.6869531915995981</v>
       </c>
       <c r="J16" s="64">
         <f t="shared" si="5"/>
-        <v>22272127.640501801</v>
+        <v>24029585.557063088</v>
       </c>
       <c r="K16" s="67">
         <f t="shared" si="3"/>
-        <v>13514573.930557996</v>
+        <v>12846482.146766203</v>
       </c>
       <c r="L16" s="68"/>
     </row>
@@ -4344,34 +4397,34 @@
       </c>
       <c r="D17" s="59">
         <f>IFERROR(+VLOOKUP(B17,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3490474.4748070529</v>
+      </c>
+      <c r="E17" s="59">
         <v>1647814.3144255385</v>
-      </c>
-      <c r="E17" s="59">
-        <v>910195.66733517474</v>
       </c>
       <c r="F17" s="59">
         <f t="shared" ref="F17:F40" si="8">+D17-E17</f>
-        <v>737618.64709036378</v>
+        <v>1842660.1603815143</v>
       </c>
       <c r="G17" s="60">
         <f t="shared" si="1"/>
-        <v>5.616651768989557E-2</v>
+        <v>0.11897444670744077</v>
       </c>
       <c r="H17" s="59">
         <f t="shared" si="4"/>
-        <v>19773771.773106463</v>
+        <v>27923795.798456423</v>
       </c>
       <c r="I17" s="60">
         <f t="shared" si="2"/>
-        <v>0.6739982122787469</v>
+        <v>0.95179557365952616</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" si="5"/>
-        <v>823907.15721276926</v>
+        <v>1163491.491602351</v>
       </c>
       <c r="K17" s="59">
         <f t="shared" si="3"/>
-        <v>1258645.6280942939</v>
+        <v>1230835.4122710929</v>
       </c>
       <c r="L17" s="61" cm="1">
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
@@ -4388,34 +4441,34 @@
       </c>
       <c r="D18" s="4">
         <f>IFERROR(+VLOOKUP(B18,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2539362.2668490014</v>
+      </c>
+      <c r="E18" s="4">
         <v>1318807.9914469167</v>
-      </c>
-      <c r="E18" s="4">
-        <v>501148.95527489512</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="8"/>
-        <v>817659.03617202165</v>
+        <v>1220554.2754020847</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>5.2837904593572765E-2</v>
+        <v>0.10173928430406153</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="4"/>
-        <v>15825695.897363</v>
+        <v>20314898.134792011</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0.63405485512287318</v>
+        <v>0.8139142744324922</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="5"/>
-        <v>659403.99572345836</v>
+        <v>846454.08894966717</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>1074577.1776615039</v>
+        <v>1067625.8872929048</v>
       </c>
       <c r="L18" s="63" cm="1">
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
@@ -4432,34 +4485,34 @@
       </c>
       <c r="D19" s="4">
         <f>IFERROR(+VLOOKUP(B19,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3126324.9965506792</v>
+      </c>
+      <c r="E19" s="4">
         <v>1974051.5620993127</v>
-      </c>
-      <c r="E19" s="4">
-        <v>1123309.4293535382</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="8"/>
-        <v>850742.13274577446</v>
+        <v>1152273.4344513665</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>7.6345990275772435E-2</v>
+        <v>0.12090990041401692</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="4"/>
-        <v>23688618.745191753</v>
+        <v>25010599.972405434</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>0.91615188330926922</v>
+        <v>0.96727920331213535</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="5"/>
-        <v>987025.78104965633</v>
+        <v>1042108.3321835598</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
-        <v>1085572.6637909403</v>
+        <v>1082396.4366166343</v>
       </c>
       <c r="L19" s="63" cm="1">
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
@@ -4476,38 +4529,38 @@
       </c>
       <c r="D20" s="4">
         <f>IFERROR(+VLOOKUP(B20,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5313079.7996425815</v>
+      </c>
+      <c r="E20" s="4">
         <v>3804498.4929125779</v>
-      </c>
-      <c r="E20" s="4">
-        <v>1545484.3455725485</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="8"/>
-        <v>2259014.1473400295</v>
+        <v>1508581.3067300036</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.113404189530462</v>
+        <v>0.15837186155063132</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="4"/>
-        <v>45653981.914950937</v>
+        <v>42504638.397140652</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>1.360850274365544</v>
+        <v>1.2669748924050506</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="5"/>
-        <v>1902249.246456289</v>
+        <v>1771026.5998808604</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>1351983.2503221554</v>
+        <v>1344526.2000170199</v>
       </c>
       <c r="L20" s="63" cm="1">
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
-        <v>913079.63829901873</v>
+        <v>850092.76794281311</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4520,38 +4573,38 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3621062.6775038806</v>
+      </c>
+      <c r="E21" s="4">
         <v>2482567.9113498144</v>
-      </c>
-      <c r="E21" s="4">
-        <v>1299165.9114931743</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" ref="F21:F23" si="9">+D21-E21</f>
-        <v>1183401.9998566401</v>
+        <v>1138494.7661540662</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>9.7514265813270856E-2</v>
+        <v>0.14223388083214142</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>29790814.936197773</v>
+        <v>28968501.420031041</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>1.1701711897592504</v>
+        <v>1.1378710466571311</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>1241283.9556749072</v>
+        <v>1207020.8925012934</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1044361.0040295538</v>
+        <v>1039878.4439283867</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
-        <v>595816.29872395552</v>
+        <v>434527.52130046563</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4564,38 +4617,38 @@
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4525419.7648018571</v>
+      </c>
+      <c r="E22" s="4">
         <v>3717567.9331198842</v>
-      </c>
-      <c r="E22" s="4">
-        <v>1904211.5763949119</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>1813356.3567249724</v>
+        <v>807851.83168197284</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.1171149794393922</v>
+        <v>0.14256483062156253</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>44610815.197438613</v>
+        <v>36203358.118414856</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>1.4053797532727064</v>
+        <v>1.1405186449725002</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>1858783.9665599421</v>
+        <v>1508473.2549339524</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>1273878.2848581872</v>
+        <v>1296070.0207237212</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
-        <v>892216.30394877226</v>
+        <v>724067.16236829711</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4608,38 +4661,38 @@
       </c>
       <c r="D23" s="4">
         <f>IFERROR(+VLOOKUP(B23,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3880349.2779353959</v>
+      </c>
+      <c r="E23" s="4">
         <v>2007902.2622231084</v>
-      </c>
-      <c r="E23" s="4">
-        <v>831624.25115675328</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="9"/>
-        <v>1176278.0110663553</v>
+        <v>1872447.0157122875</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>7.3185092483799785E-2</v>
+        <v>0.1414330399034098</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>24094827.1466773</v>
+        <v>31042794.223483168</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>0.87822110980559742</v>
+        <v>1.1314643192272784</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="5"/>
-        <v>1003951.1311115542</v>
+        <v>1293449.7593117987</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>1155820.1803534953</v>
+        <v>1121695.0929554575</v>
       </c>
       <c r="L23" s="63" cm="1">
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
-        <v>0</v>
+        <v>465641.9133522475</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4652,34 +4705,34 @@
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3150944.560423614</v>
+      </c>
+      <c r="E24" s="4">
         <v>2373341.2642009868</v>
-      </c>
-      <c r="E24" s="4">
-        <v>855590.57458566967</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>1517750.6896153172</v>
+        <v>777603.29622262716</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>7.0858582641038448E-2</v>
+        <v>9.407474133614499E-2</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>28480095.17041184</v>
+        <v>25207556.483388916</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>0.85030299169246126</v>
+        <v>0.75259793068916003</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>1186670.6321004934</v>
+        <v>1050314.8534745381</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>1414577.8970817735</v>
+        <v>1444910.020932209</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
@@ -4696,38 +4749,38 @@
       </c>
       <c r="D25" s="4">
         <f>IFERROR(+VLOOKUP(B25,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7402539.5016198214</v>
+      </c>
+      <c r="E25" s="4">
         <v>-2433547.0814999999</v>
-      </c>
-      <c r="E25" s="4">
-        <v>0</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="8"/>
-        <v>-2433547.0814999999</v>
+        <v>9836086.5831198208</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>-4.5011545419757569E-2</v>
+        <v>0.13691937400008347</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>-29202564.978</v>
+        <v>59220316.012958571</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>-0.5401385450370908</v>
+        <v>1.0953549920006678</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="5"/>
-        <v>-1216773.5407499999</v>
+        <v>2467513.1672066073</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>2568113.6339318189</v>
+        <v>2222019.6839704849</v>
       </c>
       <c r="L25" s="63" cm="1">
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;109%,H25*0.015,I25&gt;104%,H25*0.0125,I25&gt;99%,H25*0.01,I25&lt;99%,H25*0)</f>
-        <v>0</v>
+        <v>888304.74019437854</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4738,40 +4791,40 @@
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
+        <v>37049557.32013388</v>
+      </c>
+      <c r="E26" s="65">
         <v>16893004.650278136</v>
-      </c>
-      <c r="E26" s="65">
-        <v>8970730.711166665</v>
       </c>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>7922273.9391114712</v>
+        <v>20156552.669855744</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>5.9087386905985591E-2</v>
+        <v>0.12958982569357178</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>202716055.80333763</v>
+        <v>296396458.56107104</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>0.70904864287182712</v>
+        <v>1.0367186055485742</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>8446502.3251390681</v>
+        <v>12349852.440044627</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>12227529.720123721</v>
+        <v>11849957.198707912</v>
       </c>
       <c r="L26" s="68"/>
     </row>
     <row r="27" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="87" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B27" s="57" t="s">
         <v>214</v>
@@ -4781,34 +4834,34 @@
       </c>
       <c r="D27" s="59">
         <f>IFERROR(+VLOOKUP(B27,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7197381.3632933144</v>
+      </c>
+      <c r="E27" s="59">
         <v>5151540.6591492426</v>
-      </c>
-      <c r="E27" s="59">
-        <v>2145545.2733516009</v>
       </c>
       <c r="F27" s="59">
         <f t="shared" si="8"/>
-        <v>3005995.3857976417</v>
+        <v>2045840.7041440718</v>
       </c>
       <c r="G27" s="60">
         <f t="shared" si="1"/>
-        <v>6.2840756195273142E-2</v>
+        <v>8.7796819907039525E-2</v>
       </c>
       <c r="H27" s="59">
         <f t="shared" si="4"/>
-        <v>61818487.909790911</v>
+        <v>57579050.906346515</v>
       </c>
       <c r="I27" s="60">
         <f t="shared" si="2"/>
-        <v>0.75408907434327765</v>
+        <v>0.7023745592563162</v>
       </c>
       <c r="J27" s="59">
         <f t="shared" si="5"/>
-        <v>2575770.3295746213</v>
+        <v>2399127.1210977715</v>
       </c>
       <c r="K27" s="59">
         <f t="shared" si="3"/>
-        <v>3492098.1518568527</v>
+        <v>3560967.5541288895</v>
       </c>
       <c r="L27" s="61" cm="1">
         <f t="array" ref="L27">+_xlfn.IFS(I27&gt;114%,H27*0.0125,I27&gt;109%,H27*0.01,I27&gt;104%,H27*0.0075,I27&gt;99%,H27*0.005,I27&lt;99%,H27*0)</f>
@@ -4825,34 +4878,34 @@
       </c>
       <c r="D28" s="4">
         <f>IFERROR(+VLOOKUP(B28,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1662817.6962441357</v>
+      </c>
+      <c r="E28" s="4">
         <v>1127867.2813395613</v>
-      </c>
-      <c r="E28" s="4">
-        <v>682680.93729586795</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>445186.34404369339</v>
+        <v>534950.4149045744</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>5.3707965778074351E-2</v>
+        <v>7.9181795059244553E-2</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
-        <v>13534407.376074735</v>
+        <v>13302541.569953088</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>0.64449558933689211</v>
+        <v>0.63345436047395653</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="5"/>
-        <v>563933.64066978067</v>
+        <v>554272.56541471195</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>903278.75993911095</v>
+        <v>920818.2049407555</v>
       </c>
       <c r="L28" s="63" cm="1">
         <f t="array" ref="L28">+_xlfn.IFS(I28&gt;114%,H28*0.02,I28&gt;109%,H28*0.015,I28&gt;104%,H28*0.0125,I28&gt;99%,H28*0.01,I28&lt;99%,H28*0)</f>
@@ -4869,38 +4922,38 @@
       </c>
       <c r="D29" s="4">
         <f>IFERROR(+VLOOKUP(B29,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2237337.654012111</v>
+      </c>
+      <c r="E29" s="4">
         <v>3336344.5485263281</v>
-      </c>
-      <c r="E29" s="4">
-        <v>560866.8378297271</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="8"/>
-        <v>2775477.7106966008</v>
+        <v>-1099006.894514217</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.12961862603396029</v>
+        <v>8.6921667852077181E-2</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
-        <v>40036134.582315937</v>
+        <v>17898701.232096888</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>1.5554235124075237</v>
+        <v>0.69537334281661745</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="5"/>
-        <v>1668172.274263164</v>
+        <v>745779.21800403704</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>1018334.3387033488</v>
+        <v>1119160.1117137091</v>
       </c>
       <c r="L29" s="63" cm="1">
         <f t="array" ref="L29">+_xlfn.IFS(I29&gt;114%,H29*0.02,I29&gt;109%,H29*0.015,I29&gt;104%,H29*0.0125,I29&gt;99%,H29*0.01,I29&lt;99%,H29*0)</f>
-        <v>800722.69164631877</v>
+        <v>0</v>
       </c>
       <c r="M29" s="27"/>
     </row>
@@ -4914,34 +4967,34 @@
       </c>
       <c r="D30" s="4">
         <f>IFERROR(+VLOOKUP(B30,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2806120.8392654946</v>
+      </c>
+      <c r="E30" s="4">
         <v>1465987.5738126547</v>
-      </c>
-      <c r="E30" s="4">
-        <v>1241096.8257165046</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="8"/>
-        <v>224890.74809615011</v>
+        <v>1340133.2654528399</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>3.8343308375883879E-2</v>
+        <v>7.3394862686401677E-2</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="4"/>
-        <v>17591850.885751858</v>
+        <v>22448966.714123957</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>0.46011970051060663</v>
+        <v>0.58715890149121341</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="5"/>
-        <v>732993.78690632735</v>
+        <v>935373.61308849824</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>1671237.1608324097</v>
+        <v>1687004.0129933418</v>
       </c>
       <c r="L30" s="63" cm="1">
         <f t="array" ref="L30">+_xlfn.IFS(I30&gt;114%,H30*0.02,I30&gt;109%,H30*0.015,I30&gt;104%,H30*0.0125,I30&gt;99%,H30*0.01,I30&lt;99%,H30*0)</f>
@@ -4959,38 +5012,38 @@
       </c>
       <c r="D31" s="4">
         <f>IFERROR(+VLOOKUP(B31,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3265458.2459612871</v>
+      </c>
+      <c r="E31" s="4">
         <v>2185400.7533588032</v>
-      </c>
-      <c r="E31" s="4">
-        <v>967034.52092210797</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="8"/>
-        <v>1218366.2324366951</v>
+        <v>1080057.4926024838</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>8.5987773221148853E-2</v>
+        <v>0.12848420715756434</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="4"/>
-        <v>26224809.040305637</v>
+        <v>26123665.967690296</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>1.0318532786537862</v>
+        <v>1.0278736572605147</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="5"/>
-        <v>1092700.3766794016</v>
+        <v>1088486.0819870958</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>1055902.2384836907</v>
+        <v>1054751.9882875578</v>
       </c>
       <c r="L31" s="63" cm="1">
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
-        <v>262248.09040305635</v>
+        <v>261236.65967690296</v>
       </c>
       <c r="M31" s="27"/>
     </row>
@@ -5004,34 +5057,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1556471.8667402903</v>
+      </c>
+      <c r="E32" s="4">
         <v>772280.47046408884</v>
-      </c>
-      <c r="E32" s="4">
-        <v>235546.28047396851</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="8"/>
-        <v>536734.18999012036</v>
+        <v>784191.39627620147</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>3.064605041524162E-2</v>
+        <v>6.1764756616678185E-2</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>9267365.6455690656</v>
+        <v>12451774.933922322</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.36775260498289941</v>
+        <v>0.49411805293342548</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>386140.23523204442</v>
+        <v>518823.95558009675</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1110350.8877061778</v>
+        <v>1125882.2920599862</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -5049,34 +5102,34 @@
       </c>
       <c r="D33" s="4">
         <f>IFERROR(+VLOOKUP(B33,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1905347.2963424551</v>
+      </c>
+      <c r="E33" s="4">
         <v>1312962.2237802313</v>
-      </c>
-      <c r="E33" s="4">
-        <v>370995.20136279258</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="8"/>
-        <v>941967.02241743868</v>
+        <v>592385.07256222377</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>4.9551821403765794E-2</v>
+        <v>7.19087169687775E-2</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="4"/>
-        <v>15755546.685362775</v>
+        <v>15242778.370739641</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>0.59462185684518953</v>
+        <v>0.57526973575022</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="5"/>
-        <v>656481.11189011566</v>
+        <v>635115.76544748503</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>1144717.6261918077</v>
+        <v>1171019.1763646449</v>
       </c>
       <c r="L33" s="63" cm="1">
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
@@ -5093,34 +5146,34 @@
       </c>
       <c r="D34" s="4">
         <f>IFERROR(+VLOOKUP(B34,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1342266.2312651528</v>
+      </c>
+      <c r="E34" s="4">
         <v>1012363.4850253685</v>
-      </c>
-      <c r="E34" s="4">
-        <v>602361.45632991486</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="8"/>
-        <v>410002.02869545366</v>
+        <v>329902.74623978429</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>4.8207785001208023E-2</v>
+        <v>6.3917439584054894E-2</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="4"/>
-        <v>12148361.820304422</v>
+        <v>10738129.850121222</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>0.57849342001449622</v>
+        <v>0.51133951667243915</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="5"/>
-        <v>506181.74251268426</v>
+        <v>447422.07708838425</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>908528.9324988469</v>
+        <v>936082.56041594502</v>
       </c>
       <c r="L34" s="63" cm="1">
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
@@ -5137,34 +5190,34 @@
       </c>
       <c r="D35" s="4">
         <f>IFERROR(+VLOOKUP(B35,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>920475.59202497394</v>
+      </c>
+      <c r="E35" s="4">
         <v>474208.7541035653</v>
-      </c>
-      <c r="E35" s="4">
-        <v>269184.13865821779</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="8"/>
-        <v>205024.6154453475</v>
+        <v>446266.83792140865</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>1.9231280227411787E-2</v>
+        <v>3.7329391116341579E-2</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="4"/>
-        <v>5690505.0492427833</v>
+        <v>7363804.7361997925</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>0.23077536272894142</v>
+        <v>0.29863512893073269</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="5"/>
-        <v>237104.37705178265</v>
+        <v>306825.197341658</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>1099272.3293589288</v>
+        <v>1130367.8289511916</v>
       </c>
       <c r="L35" s="63" cm="1">
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.02,I35&gt;109%,H35*0.015,I35&gt;104%,H35*0.0125,I35&gt;99%,H35*0.01,I35&lt;99%,H35*0)</f>
@@ -5181,34 +5234,34 @@
       </c>
       <c r="D36" s="4">
         <f>IFERROR(+VLOOKUP(B36,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1931060.2247250369</v>
+      </c>
+      <c r="E36" s="4">
         <v>1231155.9948169386</v>
-      </c>
-      <c r="E36" s="4">
-        <v>1074255.4229483344</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="8"/>
-        <v>156900.57186860428</v>
+        <v>699904.22990809823</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>4.8787636014144584E-2</v>
+        <v>7.6523091924907347E-2</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="4"/>
-        <v>14773871.937803265</v>
+        <v>15448481.797800295</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>0.58545163216973506</v>
+        <v>0.61218473539925877</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="5"/>
-        <v>615577.99740846932</v>
+        <v>643686.74157501233</v>
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>1091083.8184174118</v>
+        <v>1109711.4178702363</v>
       </c>
       <c r="L36" s="63" cm="1">
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;114%,H36*0.02,I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
@@ -5225,38 +5278,38 @@
       </c>
       <c r="D37" s="4">
         <f>IFERROR(+VLOOKUP(B37,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>16463801.298558187</v>
+      </c>
+      <c r="E37" s="4">
         <v>-974804.98299181263</v>
-      </c>
-      <c r="E37" s="4">
-        <v>-41520.785791812603</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="8"/>
-        <v>-933284.19720000005</v>
+        <v>17438606.281549998</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
-        <v>-7.9894353043195639E-3</v>
+        <v>0.13493619506775525</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="4"/>
-        <v>-11697659.795901751</v>
+        <v>131710410.38846549</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>-9.5873223651834774E-2</v>
+        <v>1.079489560542042</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="5"/>
-        <v>-487402.49149590632</v>
+        <v>5487933.7661860622</v>
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>5590297.9537723549</v>
+        <v>5026092.7953067524</v>
       </c>
       <c r="L37" s="63" cm="1">
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.0125,I37&gt;109%,H37*0.01,I37&gt;104%,H37*0.0075,I37&gt;99%,H37*0.005,I37&lt;99%,H37*0)</f>
-        <v>0</v>
+        <v>987828.07791349117</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -5269,34 +5322,34 @@
       </c>
       <c r="D38" s="4">
         <f>IFERROR(+VLOOKUP(B38,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>149294.68419999999</v>
       </c>
       <c r="E38" s="4">
         <v>0</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" ref="F38" si="10">+D38-E38</f>
-        <v>0</v>
+        <v>149294.68419999999</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.1819239271708684E-3</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1194357.4735999999</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.3455391417366948E-2</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>49764.894733333327</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>1622727.2727272727</v>
+        <v>1692890.7293238097</v>
       </c>
       <c r="L38" s="63" cm="1">
         <f t="array" ref="L38">+_xlfn.IFS(I38&gt;109%,H38*0.015,I38&gt;104%,H38*0.0125,I38&gt;99%,H38*0.01,I38&lt;99%,H38*0)</f>
@@ -5313,38 +5366,38 @@
       </c>
       <c r="D39" s="4">
         <f>IFERROR(+VLOOKUP(B39,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4713478.3902184051</v>
+      </c>
+      <c r="E39" s="4">
         <v>3667023.6813626946</v>
-      </c>
-      <c r="E39" s="4">
-        <v>2409808.6857678718</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="8"/>
-        <v>1257214.9955948228</v>
+        <v>1046454.7088557105</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>0.10084927653788393</v>
+        <v>0.12962852900198119</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="4"/>
-        <v>44004284.176352337</v>
+        <v>37707827.12174724</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>1.2101913184546071</v>
+        <v>1.0370282320158495</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="5"/>
-        <v>1833511.8406813473</v>
+        <v>1571159.4634061351</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>1486109.2753471502</v>
+        <v>1507045.2070848378</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
-        <v>880085.68352704681</v>
+        <v>377078.27121747239</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5355,34 +5408,34 @@
       </c>
       <c r="D40" s="67">
         <f>+SUM(D27:D39)</f>
+        <v>46151311.382850848</v>
+      </c>
+      <c r="E40" s="65">
         <v>20762330.442747667</v>
-      </c>
-      <c r="E40" s="65">
-        <v>10517854.794865096</v>
       </c>
       <c r="F40" s="67">
         <f t="shared" si="8"/>
-        <v>10244475.647882571</v>
+        <v>25388980.940103181</v>
       </c>
       <c r="G40" s="66">
         <f t="shared" si="1"/>
-        <v>4.0788110583518521E-2</v>
+        <v>9.0665390258040754E-2</v>
       </c>
       <c r="H40" s="64">
         <f t="shared" si="4"/>
-        <v>249147965.31297201</v>
+        <v>369210491.06280679</v>
       </c>
       <c r="I40" s="66">
         <f t="shared" si="2"/>
-        <v>0.48945732700222222</v>
+        <v>0.72532312206432603</v>
       </c>
       <c r="J40" s="64">
         <f t="shared" si="5"/>
-        <v>10381165.221373834</v>
+        <v>15383770.460950283</v>
       </c>
       <c r="K40" s="67">
         <f t="shared" si="3"/>
-        <v>22193938.745835368</v>
+        <v>22041793.87944166</v>
       </c>
       <c r="L40" s="68"/>
     </row>
@@ -5396,34 +5449,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
+        <v>191246594.85709113</v>
+      </c>
+      <c r="E41" s="82">
         <v>105866448.03886795</v>
-      </c>
-      <c r="E41" s="82">
-        <v>62468472.547462374</v>
       </c>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>43397975.491405576</v>
+        <v>85380146.818223178</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>7.6727764001270155E-2</v>
+        <v>0.13860787688705689</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1270397376.4664154</v>
+        <v>1529972758.856729</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>0.92073316801524185</v>
+        <v>1.1088630150964551</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>52933224.019433975</v>
+        <v>63748864.952363707</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>57904577.229739457</v>
+        <v>56596216.773144998</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -5471,34 +5524,34 @@
       </c>
       <c r="D43" s="4">
         <f>IFERROR(+VLOOKUP(B43,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>-275260.76904147147</v>
       </c>
       <c r="E43" s="4">
         <v>0</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" ref="F43" si="11">+D43-E43</f>
-        <v>0</v>
+        <v>-275260.76904147147</v>
       </c>
       <c r="G43" s="5">
         <f>+D43/C43</f>
-        <v>0</v>
+        <v>-6.8815192260367865E-3</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" ref="H43" si="12">+D43/$N$3*$N$4</f>
-        <v>0</v>
+        <v>-2202086.1523317718</v>
       </c>
       <c r="I43" s="5">
         <f>+H43/C43</f>
-        <v>0</v>
+        <v>-5.5052153808294292E-2</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43" si="13">+D43/$N$3</f>
-        <v>0</v>
+        <v>-91753.589680490491</v>
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>1818181.8181818181</v>
+        <v>1917869.5604305463</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
@@ -5514,34 +5567,34 @@
       </c>
       <c r="D44" s="4">
         <f>IFERROR(+VLOOKUP(B44,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>-402349.89063324447</v>
+      </c>
+      <c r="E44" s="4">
         <v>-388379.73864699452</v>
-      </c>
-      <c r="E44" s="4">
-        <v>0</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" ref="F44" si="14">+D44-E44</f>
-        <v>-388379.73864699452</v>
+        <v>-13970.151986249955</v>
       </c>
       <c r="G44" s="5">
         <f>+D44/C44</f>
-        <v>-1.2945991288233151E-2</v>
+        <v>-1.3411663021108149E-2</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>-4660556.863763934</v>
+        <v>-3218799.1250659563</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>-0.1553518954587978</v>
+        <v>-0.10729330416886521</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>-194189.86932349726</v>
+        <v>-134116.6302110815</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>1381289.9881203179</v>
+        <v>1447730.9471730117</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
@@ -5683,14 +5736,14 @@
       </c>
       <c r="D2" s="22">
         <f>H2/G2</f>
-        <v>6.9444444444444448E-2</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="E2" s="13">
         <v>33</v>
       </c>
       <c r="F2" s="12">
         <f>+H2-E2</f>
-        <v>-28</v>
+        <v>-17</v>
       </c>
       <c r="G2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5698,11 +5751,11 @@
       </c>
       <c r="H2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I2" s="17">
         <f>(+G2*$M$2)-H2</f>
-        <v>56.199999999999996</v>
+        <v>45.199999999999996</v>
       </c>
       <c r="J2" t="s">
         <v>55</v>
@@ -5783,17 +5836,17 @@
         <v>12</v>
       </c>
       <c r="R3" s="12" t="str">
-        <v>148 - ALMACEN</v>
+        <v>145 - ALMACEN</v>
       </c>
       <c r="S3" s="12">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T3" s="12">
         <v>213</v>
       </c>
       <c r="U3" s="41">
         <f>+S3/T3</f>
-        <v>5.1643192488262914E-2</v>
+        <v>7.0422535211267609E-2</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -5807,26 +5860,26 @@
       </c>
       <c r="D4" s="22">
         <f t="shared" si="0"/>
-        <v>0.11504424778761062</v>
+        <v>0.25550660792951541</v>
       </c>
       <c r="E4" s="13">
         <v>126</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" si="1"/>
-        <v>-100</v>
+        <v>-68</v>
       </c>
       <c r="G4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>166.1</v>
+        <v>134.94999999999999</v>
       </c>
       <c r="J4" t="s">
         <v>57</v>
@@ -5841,17 +5894,17 @@
         <v>0</v>
       </c>
       <c r="R4" s="13" t="str">
-        <v>148 - Articulos Sin Asociar Agrupacion</v>
+        <v>145 - Articulos Sin Asociar Agrupacion</v>
       </c>
       <c r="S4" s="13">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T4" s="13">
         <v>213</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U11" si="3">+S4/T4</f>
-        <v>1.4084507042253521E-2</v>
+        <v>3.2863849765258218E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -5865,14 +5918,14 @@
       </c>
       <c r="D5" s="22">
         <f t="shared" si="0"/>
-        <v>0.12307692307692308</v>
+        <v>0.18461538461538463</v>
       </c>
       <c r="E5" s="13">
         <v>21</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>-9</v>
       </c>
       <c r="G5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5880,11 +5933,11 @@
       </c>
       <c r="H5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>47.25</v>
+        <v>43.25</v>
       </c>
       <c r="K5" t="s">
         <v>64</v>
@@ -5896,17 +5949,17 @@
         <v>0</v>
       </c>
       <c r="R5" s="13" t="str">
-        <v>148 - BEBIDAS</v>
+        <v>145 - BEBIDAS</v>
       </c>
       <c r="S5" s="13">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T5" s="13">
         <v>213</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="3"/>
-        <v>2.8169014084507043E-2</v>
+        <v>5.1643192488262914E-2</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -5920,14 +5973,14 @@
       </c>
       <c r="D6" s="22">
         <f t="shared" si="0"/>
-        <v>0.15458937198067632</v>
+        <v>0.28502415458937197</v>
       </c>
       <c r="E6" s="13">
         <v>100</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" si="1"/>
-        <v>-68</v>
+        <v>-41</v>
       </c>
       <c r="G6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5935,11 +5988,11 @@
       </c>
       <c r="H6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>143.94999999999999</v>
+        <v>116.94999999999999</v>
       </c>
       <c r="J6" t="s">
         <v>58</v>
@@ -5954,17 +6007,17 @@
         <v>0</v>
       </c>
       <c r="R6" s="13" t="str">
-        <v>148 - CHOCOLATE</v>
+        <v>145 - CHOCOLATE</v>
       </c>
       <c r="S6" s="13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T6" s="13">
         <v>213</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="3"/>
-        <v>2.3474178403755867E-2</v>
+        <v>3.2863849765258218E-2</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -5978,14 +6031,14 @@
       </c>
       <c r="D7" s="22">
         <f t="shared" si="0"/>
-        <v>0.11616161616161616</v>
+        <v>0.20202020202020202</v>
       </c>
       <c r="E7" s="13">
         <v>81</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>-58</v>
+        <v>-41</v>
       </c>
       <c r="G7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5993,11 +6046,11 @@
       </c>
       <c r="H7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>145.29999999999998</v>
+        <v>128.29999999999998</v>
       </c>
       <c r="J7" t="s">
         <v>58</v>
@@ -6012,17 +6065,17 @@
         <v>0</v>
       </c>
       <c r="R7" s="13" t="str">
-        <v>148 - GALLETITAS</v>
+        <v>145 - GALLETITAS</v>
       </c>
       <c r="S7" s="13">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="T7" s="13">
         <v>213</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="3"/>
-        <v>6.5727699530516437E-2</v>
+        <v>8.9201877934272297E-2</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -6036,14 +6089,14 @@
       </c>
       <c r="D8" s="22">
         <f t="shared" si="0"/>
-        <v>0.12676056338028169</v>
+        <v>0.22535211267605634</v>
       </c>
       <c r="E8" s="13">
         <v>89</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>-62</v>
+        <v>-41</v>
       </c>
       <c r="G8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6051,11 +6104,11 @@
       </c>
       <c r="H8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>154.04999999999998</v>
+        <v>133.04999999999998</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
@@ -6071,17 +6124,17 @@
         <v>0</v>
       </c>
       <c r="R8" s="13" t="str">
-        <v>148 - GOLOSINAS</v>
+        <v>145 - GOLOSINAS</v>
       </c>
       <c r="S8" s="13">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T8" s="13">
         <v>213</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="3"/>
-        <v>5.6338028169014086E-2</v>
+        <v>8.4507042253521125E-2</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -6095,14 +6148,14 @@
       </c>
       <c r="D9" s="22">
         <f>H9/G9</f>
-        <v>0.10303030303030303</v>
+        <v>0.21818181818181817</v>
       </c>
       <c r="E9" s="13">
         <v>92</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>-75</v>
+        <v>-56</v>
       </c>
       <c r="G9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6110,11 +6163,11 @@
       </c>
       <c r="H9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>123.25</v>
+        <v>104.25</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
@@ -6129,17 +6182,17 @@
         <v>0</v>
       </c>
       <c r="R9" s="13" t="str">
-        <v>148 - MASCOTAS</v>
+        <v>145 - MASCOTAS</v>
       </c>
       <c r="S9" s="13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T9" s="13">
         <v>213</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="3"/>
-        <v>1.8779342723004695E-2</v>
+        <v>3.2863849765258218E-2</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -6153,14 +6206,14 @@
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
-        <v>8.7628865979381437E-2</v>
+        <v>0.15979381443298968</v>
       </c>
       <c r="E10" s="13">
         <v>64</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>-47</v>
+        <v>-33</v>
       </c>
       <c r="G10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6168,11 +6221,11 @@
       </c>
       <c r="H10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>147.9</v>
+        <v>133.9</v>
       </c>
       <c r="J10" t="s">
         <v>58</v>
@@ -6187,17 +6240,17 @@
         <v>0</v>
       </c>
       <c r="R10" s="13" t="str">
-        <v>148 - NO PERECEDEROS</v>
+        <v>145 - NO PERECEDEROS</v>
       </c>
       <c r="S10" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T10" s="13">
         <v>213</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.3896713615023476E-3</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -6211,14 +6264,14 @@
       </c>
       <c r="D11" s="32">
         <f t="shared" si="0"/>
-        <v>2.9702970297029702E-2</v>
+        <v>7.9207920792079209E-2</v>
       </c>
       <c r="E11" s="31">
         <v>19</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
-        <v>-16</v>
+        <v>-11</v>
       </c>
       <c r="G11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6226,11 +6279,11 @@
       </c>
       <c r="H11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I11" s="34">
         <f t="shared" si="2"/>
-        <v>82.85</v>
+        <v>77.849999999999994</v>
       </c>
       <c r="J11" t="s">
         <v>59</v>
@@ -6242,17 +6295,17 @@
         <v>0</v>
       </c>
       <c r="R11" s="13" t="str">
-        <v>148 - PILAS</v>
+        <v>145 - PILAS</v>
       </c>
       <c r="S11" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T11" s="13">
         <v>213</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="3"/>
-        <v>4.6948356807511738E-3</v>
+        <v>1.4084507042253521E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -6266,14 +6319,14 @@
       </c>
       <c r="D12" s="32">
         <f t="shared" si="0"/>
-        <v>2.8571428571428571E-2</v>
+        <v>7.6190476190476197E-2</v>
       </c>
       <c r="E12" s="31">
         <v>24</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
-        <v>-21</v>
+        <v>-16</v>
       </c>
       <c r="G12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6281,11 +6334,11 @@
       </c>
       <c r="H12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I12" s="34">
         <f t="shared" si="2"/>
-        <v>86.25</v>
+        <v>81.25</v>
       </c>
       <c r="J12" t="s">
         <v>59</v>
@@ -6302,14 +6355,14 @@
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
-        <v>0.10384615384615385</v>
+        <v>0.20384615384615384</v>
       </c>
       <c r="E13" s="13">
         <v>144</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" si="1"/>
-        <v>-117</v>
+        <v>-91</v>
       </c>
       <c r="G13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6317,11 +6370,11 @@
       </c>
       <c r="H13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="J13" t="s">
         <v>57</v>
@@ -6341,14 +6394,14 @@
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
-        <v>0.11538461538461539</v>
+        <v>0.21978021978021978</v>
       </c>
       <c r="E14" s="13">
         <v>85</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" si="1"/>
-        <v>-64</v>
+        <v>-45</v>
       </c>
       <c r="G14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6356,11 +6409,11 @@
       </c>
       <c r="H14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="2"/>
-        <v>133.69999999999999</v>
+        <v>114.69999999999999</v>
       </c>
       <c r="J14" t="s">
         <v>55</v>
@@ -6376,15 +6429,15 @@
       <c r="E15" s="14"/>
       <c r="F15" s="16">
         <f>+SUM(F2:F14)</f>
-        <v>-615</v>
+        <v>-415</v>
       </c>
       <c r="G15" s="8">
         <f>+SUM(G2:G14)</f>
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="H15" s="8">
         <f>+SUM(H2:H14)</f>
-        <v>264</v>
+        <v>464</v>
       </c>
       <c r="I15" s="8"/>
     </row>
@@ -6401,14 +6454,14 @@
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
-        <v>0.14906832298136646</v>
+        <v>0.29813664596273293</v>
       </c>
       <c r="E16" s="13">
         <v>90</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" si="1"/>
-        <v>-66</v>
+        <v>-42</v>
       </c>
       <c r="G16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6416,11 +6469,11 @@
       </c>
       <c r="H16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="2"/>
-        <v>112.85</v>
+        <v>88.85</v>
       </c>
       <c r="J16" t="s">
         <v>55</v>
@@ -6440,14 +6493,14 @@
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
-        <v>7.9207920792079209E-2</v>
+        <v>0.22277227722772278</v>
       </c>
       <c r="E17" s="13">
         <v>92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="1"/>
-        <v>-76</v>
+        <v>-47</v>
       </c>
       <c r="G17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6455,11 +6508,11 @@
       </c>
       <c r="H17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>155.69999999999999</v>
+        <v>126.69999999999999</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -6479,14 +6532,14 @@
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
-        <v>0.12352941176470589</v>
+        <v>0.3</v>
       </c>
       <c r="E18" s="13">
         <v>88</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="1"/>
-        <v>-67</v>
+        <v>-37</v>
       </c>
       <c r="G18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6494,11 +6547,11 @@
       </c>
       <c r="H18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>123.5</v>
+        <v>93.5</v>
       </c>
       <c r="J18" t="s">
         <v>58</v>
@@ -6518,14 +6571,14 @@
       </c>
       <c r="D19" s="22">
         <f t="shared" si="0"/>
-        <v>0.15</v>
+        <v>0.33750000000000002</v>
       </c>
       <c r="E19" s="13">
         <v>95</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="1"/>
-        <v>-71</v>
+        <v>-41</v>
       </c>
       <c r="G19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6533,11 +6586,11 @@
       </c>
       <c r="H19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="2"/>
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="J19" t="s">
         <v>58</v>
@@ -6557,14 +6610,14 @@
       </c>
       <c r="D20" s="22">
         <f t="shared" si="0"/>
-        <v>0.11864406779661017</v>
+        <v>0.2824858757062147</v>
       </c>
       <c r="E20" s="13">
         <v>83</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="1"/>
-        <v>-62</v>
+        <v>-33</v>
       </c>
       <c r="G20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6572,11 +6625,11 @@
       </c>
       <c r="H20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>129.44999999999999</v>
+        <v>100.44999999999999</v>
       </c>
       <c r="J20" t="s">
         <v>55</v>
@@ -6596,14 +6649,14 @@
       </c>
       <c r="D21" s="22">
         <f t="shared" si="0"/>
-        <v>0.15384615384615385</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="E21" s="13">
         <v>64</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" si="1"/>
-        <v>-38</v>
+        <v>-12</v>
       </c>
       <c r="G21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6611,11 +6664,11 @@
       </c>
       <c r="H21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="2"/>
-        <v>117.65</v>
+        <v>91.65</v>
       </c>
       <c r="J21" t="s">
         <v>58</v>
@@ -6674,14 +6727,14 @@
       </c>
       <c r="D23" s="22">
         <f t="shared" si="0"/>
-        <v>9.420289855072464E-2</v>
+        <v>0.20289855072463769</v>
       </c>
       <c r="E23" s="13">
         <v>70</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" si="1"/>
-        <v>-57</v>
+        <v>-42</v>
       </c>
       <c r="G23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6689,11 +6742,11 @@
       </c>
       <c r="H23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="I23" s="17">
         <f t="shared" si="2"/>
-        <v>104.3</v>
+        <v>89.3</v>
       </c>
       <c r="J23" t="s">
         <v>58</v>
@@ -6713,14 +6766,14 @@
       </c>
       <c r="D24" s="22">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.22941176470588234</v>
       </c>
       <c r="E24" s="13">
         <v>79</v>
       </c>
       <c r="F24" s="12">
         <f t="shared" si="1"/>
-        <v>-62</v>
+        <v>-40</v>
       </c>
       <c r="G24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6728,11 +6781,11 @@
       </c>
       <c r="H24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="I24" s="17">
         <f t="shared" si="2"/>
-        <v>127.5</v>
+        <v>105.5</v>
       </c>
       <c r="J24" t="s">
         <v>60</v>
@@ -6748,7 +6801,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="16">
         <f>+SUM(F16:F24)</f>
-        <v>-565</v>
+        <v>-360</v>
       </c>
       <c r="G25" s="8">
         <f>+SUM(G16:G24)</f>
@@ -6756,13 +6809,13 @@
       </c>
       <c r="H25" s="8">
         <f>+SUM(H16:H24)</f>
-        <v>162</v>
+        <v>367</v>
       </c>
       <c r="I25" s="8"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="95" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B26">
         <v>32</v>
@@ -6773,14 +6826,14 @@
       </c>
       <c r="D26" s="22">
         <f t="shared" si="0"/>
-        <v>7.1428571428571425E-2</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="E26" s="13">
         <v>20</v>
       </c>
       <c r="F26" s="12">
         <f>+H26-E26</f>
-        <v>-16</v>
+        <v>-12</v>
       </c>
       <c r="G26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6788,11 +6841,11 @@
       </c>
       <c r="H26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I26" s="17">
         <f t="shared" si="2"/>
-        <v>43.6</v>
+        <v>39.6</v>
       </c>
       <c r="J26" t="s">
         <v>55</v>
@@ -6812,14 +6865,14 @@
       </c>
       <c r="D27" s="22">
         <f t="shared" si="0"/>
-        <v>0.11538461538461539</v>
+        <v>0.21153846153846154</v>
       </c>
       <c r="E27" s="13">
         <v>68</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" si="1"/>
-        <v>-50</v>
+        <v>-35</v>
       </c>
       <c r="G27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6827,11 +6880,11 @@
       </c>
       <c r="H27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" si="2"/>
-        <v>114.6</v>
+        <v>99.6</v>
       </c>
       <c r="J27" t="s">
         <v>58</v>
@@ -6851,14 +6904,14 @@
       </c>
       <c r="D28" s="22">
         <f t="shared" si="0"/>
-        <v>7.4534161490683232E-2</v>
+        <v>0.21739130434782608</v>
       </c>
       <c r="E28" s="13">
         <v>80</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" si="1"/>
-        <v>-68</v>
+        <v>-45</v>
       </c>
       <c r="G28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6866,11 +6919,11 @@
       </c>
       <c r="H28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="I28" s="17">
         <f t="shared" si="2"/>
-        <v>124.85</v>
+        <v>101.85</v>
       </c>
       <c r="J28" t="s">
         <v>58</v>
@@ -6890,14 +6943,14 @@
       </c>
       <c r="D29" s="22">
         <f t="shared" si="0"/>
-        <v>6.8273092369477914E-2</v>
+        <v>0.10441767068273092</v>
       </c>
       <c r="E29" s="13">
         <v>68</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" si="1"/>
-        <v>-51</v>
+        <v>-42</v>
       </c>
       <c r="G29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6905,11 +6958,11 @@
       </c>
       <c r="H29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" si="2"/>
-        <v>194.65</v>
+        <v>185.65</v>
       </c>
       <c r="J29" t="s">
         <v>58</v>
@@ -6929,14 +6982,14 @@
       </c>
       <c r="D30" s="22">
         <f t="shared" si="0"/>
-        <v>0.12857142857142856</v>
+        <v>0.23571428571428571</v>
       </c>
       <c r="E30" s="13">
         <v>73</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" si="1"/>
-        <v>-55</v>
+        <v>-40</v>
       </c>
       <c r="G30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6944,11 +6997,11 @@
       </c>
       <c r="H30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="2"/>
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s">
         <v>55</v>
@@ -6968,14 +7021,14 @@
       </c>
       <c r="D31" s="22">
         <f t="shared" si="0"/>
-        <v>6.6298342541436461E-2</v>
+        <v>0.17679558011049723</v>
       </c>
       <c r="E31" s="13">
         <v>40</v>
       </c>
       <c r="F31" s="12">
         <f t="shared" si="1"/>
-        <v>-28</v>
+        <v>-8</v>
       </c>
       <c r="G31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6983,11 +7036,11 @@
       </c>
       <c r="H31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="I31" s="17">
         <f t="shared" si="2"/>
-        <v>141.85</v>
+        <v>121.85</v>
       </c>
       <c r="J31" t="s">
         <v>58</v>
@@ -7007,14 +7060,14 @@
       </c>
       <c r="D32" s="22">
         <f t="shared" si="0"/>
-        <v>0.13690476190476192</v>
+        <v>0.21428571428571427</v>
       </c>
       <c r="E32" s="13">
         <v>67</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>-44</v>
+        <v>-31</v>
       </c>
       <c r="G32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7022,11 +7075,11 @@
       </c>
       <c r="H32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="2"/>
-        <v>119.79999999999998</v>
+        <v>106.79999999999998</v>
       </c>
       <c r="J32" t="s">
         <v>58</v>
@@ -7046,14 +7099,14 @@
       </c>
       <c r="D33" s="22">
         <f t="shared" si="0"/>
-        <v>0.10465116279069768</v>
+        <v>0.23837209302325582</v>
       </c>
       <c r="E33" s="13">
         <v>66</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>-48</v>
+        <v>-25</v>
       </c>
       <c r="G33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7061,11 +7114,11 @@
       </c>
       <c r="H33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I33" s="17">
         <f t="shared" si="2"/>
-        <v>128.19999999999999</v>
+        <v>105.19999999999999</v>
       </c>
       <c r="J33" t="s">
         <v>58</v>
@@ -7085,14 +7138,14 @@
       </c>
       <c r="D34" s="22">
         <f t="shared" si="0"/>
-        <v>3.5460992907801421E-2</v>
+        <v>9.2198581560283682E-2</v>
       </c>
       <c r="E34" s="13">
         <v>82</v>
       </c>
       <c r="F34" s="12">
         <f t="shared" si="1"/>
-        <v>-77</v>
+        <v>-69</v>
       </c>
       <c r="G34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7100,11 +7153,11 @@
       </c>
       <c r="H34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I34" s="17">
         <f t="shared" si="2"/>
-        <v>114.85</v>
+        <v>106.85</v>
       </c>
       <c r="J34" t="s">
         <v>55</v>
@@ -7124,14 +7177,14 @@
       </c>
       <c r="D35" s="22">
         <f t="shared" si="0"/>
-        <v>7.8651685393258425E-2</v>
+        <v>0.17415730337078653</v>
       </c>
       <c r="E35" s="13">
         <v>81</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" si="1"/>
-        <v>-67</v>
+        <v>-50</v>
       </c>
       <c r="G35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7139,11 +7192,11 @@
       </c>
       <c r="H35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="I35" s="17">
         <f t="shared" si="2"/>
-        <v>137.29999999999998</v>
+        <v>120.29999999999998</v>
       </c>
       <c r="J35" t="s">
         <v>58</v>
@@ -7163,14 +7216,14 @@
       </c>
       <c r="D36" s="22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.8495575221238937E-3</v>
       </c>
       <c r="E36" s="13">
         <v>0</v>
       </c>
       <c r="F36" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7178,11 +7231,11 @@
       </c>
       <c r="H36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="17">
         <f t="shared" si="2"/>
-        <v>96.05</v>
+        <v>95.05</v>
       </c>
       <c r="J36" t="s">
         <v>58</v>
@@ -7199,14 +7252,14 @@
       </c>
       <c r="D37" s="22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.7087378640776691E-3</v>
       </c>
       <c r="E37" s="13">
         <v>17</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" si="1"/>
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="G37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7214,11 +7267,11 @@
       </c>
       <c r="H37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="17">
         <f t="shared" si="2"/>
-        <v>87.55</v>
+        <v>86.55</v>
       </c>
       <c r="J37" t="s">
         <v>59</v>
@@ -7235,14 +7288,14 @@
       </c>
       <c r="D38" s="22">
         <f t="shared" si="0"/>
-        <v>0.14960629921259844</v>
+        <v>0.29133858267716534</v>
       </c>
       <c r="E38" s="13">
         <v>60</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="1"/>
-        <v>-41</v>
+        <v>-23</v>
       </c>
       <c r="G38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7250,11 +7303,11 @@
       </c>
       <c r="H38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I38" s="17">
         <f t="shared" si="2"/>
-        <v>88.95</v>
+        <v>70.95</v>
       </c>
       <c r="J38" t="s">
         <v>55</v>
@@ -7270,7 +7323,7 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8">
         <f>+SUM(F26:F38)</f>
-        <v>-562</v>
+        <v>-395</v>
       </c>
       <c r="G39" s="8">
         <f>+SUM(G26:G38)</f>
@@ -7278,7 +7331,7 @@
       </c>
       <c r="H39" s="8">
         <f>+SUM(H26:H38)</f>
-        <v>160</v>
+        <v>327</v>
       </c>
       <c r="I39" s="8"/>
       <c r="L39" t="s">
@@ -7294,20 +7347,20 @@
       <c r="E40" s="6"/>
       <c r="F40" s="8">
         <f>+SUM(F39+F25+F15)</f>
-        <v>-1742</v>
+        <v>-1170</v>
       </c>
       <c r="G40" s="8">
         <f>+G15+G25+G39</f>
-        <v>5717</v>
+        <v>5718</v>
       </c>
       <c r="H40" s="8">
         <f>+H15+H25+H39</f>
-        <v>586</v>
+        <v>1158</v>
       </c>
       <c r="I40" s="8"/>
       <c r="L40" s="1">
         <f>+H40/G40</f>
-        <v>0.10250131187685849</v>
+        <v>0.20251836306400839</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -7331,7 +7384,7 @@
       </c>
       <c r="G41" s="13">
         <f>VLOOKUP(B41,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H41" s="13">
         <f>VLOOKUP(B41,'Base Cobertura'!$A:$C,2,FALSE)</f>
@@ -7339,7 +7392,7 @@
       </c>
       <c r="I41" s="17">
         <f t="shared" ref="I41:I42" si="6">(+G41*$M$2)-H41</f>
-        <v>101.14999999999999</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -7888,7 +7941,7 @@
     </row>
     <row r="40" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C40" s="44"/>
     </row>
@@ -7951,7 +8004,7 @@
         <v>3408</v>
       </c>
       <c r="G3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H3" s="51"/>
       <c r="I3" s="51">
@@ -7963,13 +8016,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="51">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C4" s="51">
         <v>127</v>
       </c>
       <c r="G4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I4" s="51">
         <v>3408</v>
@@ -7980,13 +8033,13 @@
         <v>10</v>
       </c>
       <c r="B5" s="51">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C5" s="51">
         <v>181</v>
       </c>
       <c r="G5" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H5" s="51"/>
       <c r="I5" s="51">
@@ -7998,13 +8051,13 @@
         <v>100</v>
       </c>
       <c r="B6" s="51">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C6" s="51">
         <v>2024</v>
       </c>
       <c r="G6" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H6" s="51"/>
       <c r="I6" s="51">
@@ -8016,13 +8069,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="51">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C7" s="51">
         <v>165</v>
       </c>
       <c r="G7" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H7" s="51"/>
       <c r="I7" s="51">
@@ -8034,13 +8087,13 @@
         <v>12</v>
       </c>
       <c r="B8" s="51">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C8" s="51">
         <v>213</v>
       </c>
       <c r="G8" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H8" s="51">
         <v>1</v>
@@ -8054,13 +8107,13 @@
         <v>123</v>
       </c>
       <c r="B9" s="51">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C9" s="51">
         <v>489</v>
       </c>
       <c r="G9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H9" s="51"/>
       <c r="I9" s="51">
@@ -8072,13 +8125,13 @@
         <v>15</v>
       </c>
       <c r="B10" s="51">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C10" s="51">
         <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="I10" s="51">
         <v>3408</v>
@@ -8089,13 +8142,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="51">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C11" s="51">
         <v>198</v>
       </c>
       <c r="G11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H11" s="51"/>
       <c r="I11" s="51">
@@ -8107,7 +8160,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="51">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C12" s="51">
         <v>177</v>
@@ -8120,10 +8173,10 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H12">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I12" s="51">
         <v>127</v>
@@ -8134,7 +8187,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="51">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="C13" s="51">
         <v>207</v>
@@ -8144,10 +8197,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H13" s="51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I13" s="51">
         <v>127</v>
@@ -8158,7 +8211,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="51">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C14" s="51">
         <v>138</v>
@@ -8168,10 +8221,10 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H14" s="51">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I14" s="51">
         <v>127</v>
@@ -8182,20 +8235,20 @@
         <v>20</v>
       </c>
       <c r="B15" s="51">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C15" s="51">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H15" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I15" s="51">
         <v>127</v>
@@ -8206,7 +8259,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="51">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C16" s="51">
         <v>170</v>
@@ -8216,10 +8269,10 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H16" s="51">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I16" s="51">
         <v>127</v>
@@ -8230,7 +8283,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="51">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C17" s="51">
         <v>72</v>
@@ -8240,10 +8293,10 @@
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H17" s="51">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I17" s="51">
         <v>127</v>
@@ -8254,7 +8307,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="51">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="C18" s="51">
         <v>160</v>
@@ -8264,10 +8317,10 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H18" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I18" s="51">
         <v>127</v>
@@ -8278,7 +8331,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="51">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C19" s="51">
         <v>178</v>
@@ -8288,10 +8341,10 @@
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H19" s="51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I19" s="51">
         <v>127</v>
@@ -8302,7 +8355,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="51">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="51">
         <v>172</v>
@@ -8312,10 +8365,10 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I20" s="51">
         <v>127</v>
@@ -8325,7 +8378,9 @@
       <c r="A21">
         <v>26</v>
       </c>
-      <c r="B21" s="51"/>
+      <c r="B21" s="51">
+        <v>32</v>
+      </c>
       <c r="C21" s="51">
         <v>162</v>
       </c>
@@ -8337,9 +8392,11 @@
         <v>10</v>
       </c>
       <c r="G21" t="s">
-        <v>218</v>
-      </c>
-      <c r="H21" s="51"/>
+        <v>222</v>
+      </c>
+      <c r="H21" s="51">
+        <v>7</v>
+      </c>
       <c r="I21" s="51">
         <v>181</v>
       </c>
@@ -8349,7 +8406,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="51">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C22" s="51">
         <v>140</v>
@@ -8359,9 +8416,11 @@
         <v>10</v>
       </c>
       <c r="G22" t="s">
-        <v>219</v>
-      </c>
-      <c r="H22" s="51"/>
+        <v>223</v>
+      </c>
+      <c r="H22" s="51">
+        <v>1</v>
+      </c>
       <c r="I22" s="51">
         <v>181</v>
       </c>
@@ -8371,7 +8430,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="51">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C23" s="51">
         <v>168</v>
@@ -8381,10 +8440,10 @@
         <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H23" s="51">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I23" s="51">
         <v>181</v>
@@ -8395,7 +8454,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="51">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C24" s="51">
         <v>170</v>
@@ -8405,10 +8464,10 @@
         <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H24" s="51">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I24" s="51">
         <v>181</v>
@@ -8418,7 +8477,9 @@
       <c r="A25">
         <v>30</v>
       </c>
-      <c r="B25" s="51"/>
+      <c r="B25" s="51">
+        <v>2</v>
+      </c>
       <c r="C25" s="51">
         <v>138</v>
       </c>
@@ -8427,10 +8488,10 @@
         <v>10</v>
       </c>
       <c r="G25" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H25" s="51">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I25" s="51">
         <v>181</v>
@@ -8441,7 +8502,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="51">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C26" s="51">
         <v>161</v>
@@ -8451,10 +8512,10 @@
         <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H26" s="51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I26" s="51">
         <v>181</v>
@@ -8465,7 +8526,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C27" s="51">
         <v>56</v>
@@ -8475,9 +8536,11 @@
         <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>224</v>
-      </c>
-      <c r="H27" s="51"/>
+        <v>228</v>
+      </c>
+      <c r="H27" s="51">
+        <v>1</v>
+      </c>
       <c r="I27" s="51">
         <v>181</v>
       </c>
@@ -8487,7 +8550,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="51">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C28" s="51">
         <v>172</v>
@@ -8497,7 +8560,7 @@
         <v>10</v>
       </c>
       <c r="G28" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H28" s="51">
         <v>1</v>
@@ -8511,7 +8574,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="51">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C29" s="51">
         <v>156</v>
@@ -8521,7 +8584,7 @@
         <v>10</v>
       </c>
       <c r="G29" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H29" s="51"/>
       <c r="I29" s="51">
@@ -8533,7 +8596,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="51">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C30" s="51">
         <v>141</v>
@@ -8546,10 +8609,10 @@
         <v>100</v>
       </c>
       <c r="G30" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H30" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I30" s="51">
         <v>2024</v>
@@ -8560,7 +8623,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="51">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C31" s="51">
         <v>182</v>
@@ -8570,7 +8633,7 @@
         <v>100</v>
       </c>
       <c r="G31" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H31" s="51">
         <v>2</v>
@@ -8584,7 +8647,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="51">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C32" s="51">
         <v>249</v>
@@ -8594,10 +8657,10 @@
         <v>100</v>
       </c>
       <c r="G32" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H32" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" s="51">
         <v>2024</v>
@@ -8616,10 +8679,10 @@
         <v>100</v>
       </c>
       <c r="G33" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H33" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I33" s="51">
         <v>2024</v>
@@ -8638,10 +8701,10 @@
         <v>100</v>
       </c>
       <c r="G34" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H34" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I34" s="51">
         <v>2024</v>
@@ -8652,7 +8715,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="51">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C35" s="51">
         <v>169</v>
@@ -8662,10 +8725,10 @@
         <v>100</v>
       </c>
       <c r="G35" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H35" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I35" s="51">
         <v>2024</v>
@@ -8686,10 +8749,10 @@
         <v>100</v>
       </c>
       <c r="G36" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H36" s="51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I36" s="51">
         <v>2024</v>
@@ -8700,7 +8763,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="51">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C37" s="51">
         <v>260</v>
@@ -8710,7 +8773,7 @@
         <v>100</v>
       </c>
       <c r="G37" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H37" s="51">
         <v>3</v>
@@ -8724,7 +8787,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C38" s="51">
         <v>101</v>
@@ -8734,7 +8797,7 @@
         <v>100</v>
       </c>
       <c r="G38" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H38" s="51"/>
       <c r="I38" s="51">
@@ -8746,7 +8809,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C39" s="51">
         <v>105</v>
@@ -8759,10 +8822,10 @@
         <v>11</v>
       </c>
       <c r="G39" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H39" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I39" s="51">
         <v>165</v>
@@ -8773,7 +8836,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="51">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C40" s="51">
         <v>202</v>
@@ -8783,7 +8846,7 @@
         <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H40" s="51"/>
       <c r="I40" s="51">
@@ -8802,10 +8865,10 @@
         <v>11</v>
       </c>
       <c r="G41" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H41" s="51">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I41" s="51">
         <v>165</v>
@@ -8815,7 +8878,9 @@
       <c r="A42">
         <v>57</v>
       </c>
-      <c r="B42" s="51"/>
+      <c r="B42" s="51">
+        <v>1</v>
+      </c>
       <c r="C42" s="51">
         <v>103</v>
       </c>
@@ -8824,10 +8889,10 @@
         <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H42" s="51">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I42" s="51">
         <v>165</v>
@@ -8839,17 +8904,17 @@
       </c>
       <c r="B43" s="51"/>
       <c r="C43" s="51">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E43">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="G43" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H43" s="51">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I43" s="51">
         <v>165</v>
@@ -8868,10 +8933,10 @@
         <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H44" s="51">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I44" s="51">
         <v>165</v>
@@ -8881,7 +8946,9 @@
       <c r="A45">
         <v>7</v>
       </c>
-      <c r="B45" s="51"/>
+      <c r="B45" s="51">
+        <v>1</v>
+      </c>
       <c r="C45" s="51">
         <v>113</v>
       </c>
@@ -8890,9 +8957,11 @@
         <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>224</v>
-      </c>
-      <c r="H45" s="51"/>
+        <v>228</v>
+      </c>
+      <c r="H45" s="51">
+        <v>1</v>
+      </c>
       <c r="I45" s="51">
         <v>165</v>
       </c>
@@ -8902,7 +8971,7 @@
         <v>8</v>
       </c>
       <c r="B46" s="51">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C46" s="51">
         <v>194</v>
@@ -8912,10 +8981,10 @@
         <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H46" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I46" s="51">
         <v>165</v>
@@ -8926,7 +8995,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="51">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C47" s="51">
         <v>161</v>
@@ -8936,7 +9005,7 @@
         <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H47" s="51">
         <v>4</v>
@@ -8956,10 +9025,10 @@
         <v>12</v>
       </c>
       <c r="G48" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H48" s="51">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I48" s="51">
         <v>213</v>
@@ -8973,10 +9042,10 @@
         <v>12</v>
       </c>
       <c r="G49" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H49" s="51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I49" s="51">
         <v>213</v>
@@ -8988,10 +9057,10 @@
         <v>12</v>
       </c>
       <c r="G50" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H50" s="51">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I50" s="51">
         <v>213</v>
@@ -9003,10 +9072,10 @@
         <v>12</v>
       </c>
       <c r="G51" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H51" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I51" s="51">
         <v>213</v>
@@ -9018,10 +9087,10 @@
         <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H52" s="51">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I52" s="51">
         <v>213</v>
@@ -9033,10 +9102,10 @@
         <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H53" s="51">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I53" s="51">
         <v>213</v>
@@ -9048,10 +9117,10 @@
         <v>12</v>
       </c>
       <c r="G54" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H54" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I54" s="51">
         <v>213</v>
@@ -9063,9 +9132,11 @@
         <v>12</v>
       </c>
       <c r="G55" t="s">
-        <v>225</v>
-      </c>
-      <c r="H55" s="51"/>
+        <v>229</v>
+      </c>
+      <c r="H55" s="51">
+        <v>2</v>
+      </c>
       <c r="I55" s="51">
         <v>213</v>
       </c>
@@ -9076,10 +9147,10 @@
         <v>12</v>
       </c>
       <c r="G56" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H56" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I56" s="51">
         <v>213</v>
@@ -9094,10 +9165,10 @@
         <v>123</v>
       </c>
       <c r="G57" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H57" s="51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I57" s="51">
         <v>489</v>
@@ -9109,10 +9180,10 @@
         <v>123</v>
       </c>
       <c r="G58" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H58" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I58" s="51">
         <v>489</v>
@@ -9124,10 +9195,10 @@
         <v>123</v>
       </c>
       <c r="G59" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H59" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I59" s="51">
         <v>489</v>
@@ -9139,7 +9210,7 @@
         <v>123</v>
       </c>
       <c r="G60" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H60" s="51"/>
       <c r="I60" s="51">
@@ -9152,10 +9223,10 @@
         <v>123</v>
       </c>
       <c r="G61" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H61" s="51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I61" s="51">
         <v>489</v>
@@ -9167,7 +9238,7 @@
         <v>123</v>
       </c>
       <c r="G62" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H62" s="51"/>
       <c r="I62" s="51">
@@ -9180,10 +9251,10 @@
         <v>123</v>
       </c>
       <c r="G63" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H63" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I63" s="51">
         <v>489</v>
@@ -9195,7 +9266,7 @@
         <v>123</v>
       </c>
       <c r="G64" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H64" s="51"/>
       <c r="I64" s="51">
@@ -9208,7 +9279,7 @@
         <v>123</v>
       </c>
       <c r="G65" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H65" s="51"/>
       <c r="I65" s="51">
@@ -9224,10 +9295,10 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H66" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I66" s="51">
         <v>65</v>
@@ -9239,10 +9310,10 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H67" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I67" s="51">
         <v>65</v>
@@ -9254,10 +9325,10 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H68" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I68" s="51">
         <v>65</v>
@@ -9269,7 +9340,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H69" s="51">
         <v>5</v>
@@ -9284,10 +9355,10 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H70" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I70" s="51">
         <v>65</v>
@@ -9299,10 +9370,10 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H71" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I71" s="51">
         <v>65</v>
@@ -9314,10 +9385,10 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H72" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I72" s="51">
         <v>65</v>
@@ -9329,7 +9400,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H73" s="51">
         <v>2</v>
@@ -9344,10 +9415,10 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H74" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I74" s="51">
         <v>65</v>
@@ -9362,10 +9433,10 @@
         <v>16</v>
       </c>
       <c r="G75" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H75" s="51">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I75" s="51">
         <v>198</v>
@@ -9377,7 +9448,7 @@
         <v>16</v>
       </c>
       <c r="G76" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H76">
         <v>2</v>
@@ -9392,10 +9463,10 @@
         <v>16</v>
       </c>
       <c r="G77" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H77" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I77" s="51">
         <v>198</v>
@@ -9407,10 +9478,10 @@
         <v>16</v>
       </c>
       <c r="G78" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H78" s="51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I78" s="51">
         <v>198</v>
@@ -9422,10 +9493,10 @@
         <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H79" s="51">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I79" s="51">
         <v>198</v>
@@ -9437,10 +9508,10 @@
         <v>16</v>
       </c>
       <c r="G80" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H80" s="51">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I80" s="51">
         <v>198</v>
@@ -9452,7 +9523,7 @@
         <v>16</v>
       </c>
       <c r="G81" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H81" s="51">
         <v>1</v>
@@ -9467,10 +9538,10 @@
         <v>16</v>
       </c>
       <c r="G82" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H82" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I82" s="51">
         <v>198</v>
@@ -9482,10 +9553,10 @@
         <v>16</v>
       </c>
       <c r="G83" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H83" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I83" s="51">
         <v>198</v>
@@ -9500,10 +9571,10 @@
         <v>18</v>
       </c>
       <c r="G84" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H84" s="51">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I84" s="51">
         <v>177</v>
@@ -9515,10 +9586,10 @@
         <v>18</v>
       </c>
       <c r="G85" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H85" s="51">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I85" s="51">
         <v>177</v>
@@ -9530,10 +9601,10 @@
         <v>18</v>
       </c>
       <c r="G86" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H86" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I86" s="51">
         <v>177</v>
@@ -9545,10 +9616,10 @@
         <v>18</v>
       </c>
       <c r="G87" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H87" s="51">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I87" s="51">
         <v>177</v>
@@ -9560,10 +9631,10 @@
         <v>18</v>
       </c>
       <c r="G88" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H88" s="51">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I88" s="51">
         <v>177</v>
@@ -9575,10 +9646,10 @@
         <v>18</v>
       </c>
       <c r="G89" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H89" s="51">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I89" s="51">
         <v>177</v>
@@ -9590,10 +9661,10 @@
         <v>18</v>
       </c>
       <c r="G90" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H90" s="51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I90" s="51">
         <v>177</v>
@@ -9605,10 +9676,10 @@
         <v>18</v>
       </c>
       <c r="G91" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H91" s="51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I91" s="51">
         <v>177</v>
@@ -9620,10 +9691,10 @@
         <v>18</v>
       </c>
       <c r="G92" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H92" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I92" s="51">
         <v>177</v>
@@ -9638,10 +9709,10 @@
         <v>19</v>
       </c>
       <c r="G93" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H93" s="51">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I93" s="51">
         <v>207</v>
@@ -9653,10 +9724,10 @@
         <v>19</v>
       </c>
       <c r="G94" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H94" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I94" s="51">
         <v>207</v>
@@ -9668,10 +9739,10 @@
         <v>19</v>
       </c>
       <c r="G95" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H95" s="51">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I95" s="51">
         <v>207</v>
@@ -9683,10 +9754,10 @@
         <v>19</v>
       </c>
       <c r="G96" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H96" s="51">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I96" s="51">
         <v>207</v>
@@ -9698,10 +9769,10 @@
         <v>19</v>
       </c>
       <c r="G97" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H97" s="51">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I97" s="51">
         <v>207</v>
@@ -9713,10 +9784,10 @@
         <v>19</v>
       </c>
       <c r="G98" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H98" s="51">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I98" s="51">
         <v>207</v>
@@ -9728,7 +9799,7 @@
         <v>19</v>
       </c>
       <c r="G99" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H99" s="51"/>
       <c r="I99" s="51">
@@ -9741,10 +9812,10 @@
         <v>19</v>
       </c>
       <c r="G100" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H100" s="51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I100" s="51">
         <v>207</v>
@@ -9756,10 +9827,10 @@
         <v>19</v>
       </c>
       <c r="G101" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H101" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I101" s="51">
         <v>207</v>
@@ -9774,9 +9845,11 @@
         <v>2</v>
       </c>
       <c r="G102" t="s">
-        <v>218</v>
-      </c>
-      <c r="H102" s="51"/>
+        <v>222</v>
+      </c>
+      <c r="H102" s="51">
+        <v>2</v>
+      </c>
       <c r="I102" s="51">
         <v>138</v>
       </c>
@@ -9787,10 +9860,10 @@
         <v>2</v>
       </c>
       <c r="G103" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H103" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I103" s="51">
         <v>138</v>
@@ -9802,10 +9875,10 @@
         <v>2</v>
       </c>
       <c r="G104" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H104" s="51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I104" s="51">
         <v>138</v>
@@ -9817,10 +9890,10 @@
         <v>2</v>
       </c>
       <c r="G105" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H105" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I105" s="51">
         <v>138</v>
@@ -9832,10 +9905,10 @@
         <v>2</v>
       </c>
       <c r="G106" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H106" s="51">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I106" s="51">
         <v>138</v>
@@ -9847,10 +9920,10 @@
         <v>2</v>
       </c>
       <c r="G107" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H107" s="51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I107" s="51">
         <v>138</v>
@@ -9862,10 +9935,10 @@
         <v>2</v>
       </c>
       <c r="G108" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H108" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I108" s="51">
         <v>138</v>
@@ -9877,10 +9950,10 @@
         <v>2</v>
       </c>
       <c r="G109" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H109" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I109" s="51">
         <v>138</v>
@@ -9892,7 +9965,7 @@
         <v>2</v>
       </c>
       <c r="G110" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H110" s="51">
         <v>5</v>
@@ -9910,13 +9983,13 @@
         <v>20</v>
       </c>
       <c r="G111" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H111" s="51">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I111" s="51">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="5:9" x14ac:dyDescent="0.25">
@@ -9925,13 +9998,13 @@
         <v>20</v>
       </c>
       <c r="G112" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H112" s="51">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I112" s="51">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="5:9" x14ac:dyDescent="0.25">
@@ -9940,13 +10013,13 @@
         <v>20</v>
       </c>
       <c r="G113" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H113" s="51">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I113" s="51">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="5:9" x14ac:dyDescent="0.25">
@@ -9955,13 +10028,13 @@
         <v>20</v>
       </c>
       <c r="G114" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H114" s="51">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I114" s="51">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="5:9" x14ac:dyDescent="0.25">
@@ -9970,13 +10043,13 @@
         <v>20</v>
       </c>
       <c r="G115" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H115" s="51">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="I115" s="51">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="5:9" x14ac:dyDescent="0.25">
@@ -9985,13 +10058,13 @@
         <v>20</v>
       </c>
       <c r="G116" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H116">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I116" s="51">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="5:9" x14ac:dyDescent="0.25">
@@ -10000,13 +10073,13 @@
         <v>20</v>
       </c>
       <c r="G117" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H117" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I117" s="51">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="5:9" x14ac:dyDescent="0.25">
@@ -10015,13 +10088,13 @@
         <v>20</v>
       </c>
       <c r="G118" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H118" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I118" s="51">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="5:9" x14ac:dyDescent="0.25">
@@ -10030,13 +10103,13 @@
         <v>20</v>
       </c>
       <c r="G119" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H119" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I119" s="51">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="5:9" x14ac:dyDescent="0.25">
@@ -10048,10 +10121,10 @@
         <v>21</v>
       </c>
       <c r="G120" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H120" s="51">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I120" s="51">
         <v>170</v>
@@ -10063,10 +10136,10 @@
         <v>21</v>
       </c>
       <c r="G121" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H121" s="51">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I121" s="51">
         <v>170</v>
@@ -10078,10 +10151,10 @@
         <v>21</v>
       </c>
       <c r="G122" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H122" s="51">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="I122" s="51">
         <v>170</v>
@@ -10093,10 +10166,10 @@
         <v>21</v>
       </c>
       <c r="G123" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H123" s="51">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I123" s="51">
         <v>170</v>
@@ -10108,10 +10181,10 @@
         <v>21</v>
       </c>
       <c r="G124" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H124">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="I124" s="51">
         <v>170</v>
@@ -10123,10 +10196,10 @@
         <v>21</v>
       </c>
       <c r="G125" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H125" s="51">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I125" s="51">
         <v>170</v>
@@ -10138,10 +10211,10 @@
         <v>21</v>
       </c>
       <c r="G126" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H126" s="51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I126" s="51">
         <v>170</v>
@@ -10153,10 +10226,10 @@
         <v>21</v>
       </c>
       <c r="G127" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H127" s="51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I127" s="51">
         <v>170</v>
@@ -10168,9 +10241,11 @@
         <v>21</v>
       </c>
       <c r="G128" t="s">
-        <v>226</v>
-      </c>
-      <c r="H128" s="51"/>
+        <v>230</v>
+      </c>
+      <c r="H128" s="51">
+        <v>1</v>
+      </c>
       <c r="I128" s="51">
         <v>170</v>
       </c>
@@ -10184,10 +10259,10 @@
         <v>22</v>
       </c>
       <c r="G129" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H129" s="51">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I129" s="51">
         <v>72</v>
@@ -10199,10 +10274,10 @@
         <v>22</v>
       </c>
       <c r="G130" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H130" s="51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I130" s="51">
         <v>72</v>
@@ -10214,10 +10289,10 @@
         <v>22</v>
       </c>
       <c r="G131" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H131" s="51">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I131" s="51">
         <v>72</v>
@@ -10229,10 +10304,10 @@
         <v>22</v>
       </c>
       <c r="G132" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H132" s="51">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I132" s="51">
         <v>72</v>
@@ -10244,10 +10319,10 @@
         <v>22</v>
       </c>
       <c r="G133" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H133" s="51">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I133" s="51">
         <v>72</v>
@@ -10259,10 +10334,10 @@
         <v>22</v>
       </c>
       <c r="G134" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H134" s="51">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I134" s="51">
         <v>72</v>
@@ -10274,10 +10349,10 @@
         <v>22</v>
       </c>
       <c r="G135" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H135" s="51">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I135" s="51">
         <v>72</v>
@@ -10289,10 +10364,10 @@
         <v>22</v>
       </c>
       <c r="G136" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H136" s="51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I136" s="51">
         <v>72</v>
@@ -10304,10 +10379,10 @@
         <v>22</v>
       </c>
       <c r="G137" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H137" s="51">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I137" s="51">
         <v>72</v>
@@ -10322,10 +10397,10 @@
         <v>23</v>
       </c>
       <c r="G138" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H138" s="51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I138" s="51">
         <v>160</v>
@@ -10337,10 +10412,10 @@
         <v>23</v>
       </c>
       <c r="G139" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H139" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I139" s="51">
         <v>160</v>
@@ -10352,10 +10427,10 @@
         <v>23</v>
       </c>
       <c r="G140" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H140">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I140" s="51">
         <v>160</v>
@@ -10367,10 +10442,10 @@
         <v>23</v>
       </c>
       <c r="G141" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H141" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I141" s="51">
         <v>160</v>
@@ -10382,10 +10457,10 @@
         <v>23</v>
       </c>
       <c r="G142" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H142" s="51">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="I142" s="51">
         <v>160</v>
@@ -10397,10 +10472,10 @@
         <v>23</v>
       </c>
       <c r="G143" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H143" s="51">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="I143" s="51">
         <v>160</v>
@@ -10412,10 +10487,10 @@
         <v>23</v>
       </c>
       <c r="G144" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H144" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I144" s="51">
         <v>160</v>
@@ -10427,10 +10502,10 @@
         <v>23</v>
       </c>
       <c r="G145" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H145" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I145" s="51">
         <v>160</v>
@@ -10442,10 +10517,10 @@
         <v>23</v>
       </c>
       <c r="G146" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H146" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I146" s="51">
         <v>160</v>
@@ -10460,10 +10535,10 @@
         <v>24</v>
       </c>
       <c r="G147" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H147" s="51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I147" s="51">
         <v>178</v>
@@ -10475,7 +10550,7 @@
         <v>24</v>
       </c>
       <c r="G148" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H148">
         <v>3</v>
@@ -10490,10 +10565,10 @@
         <v>24</v>
       </c>
       <c r="G149" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H149" s="51">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I149" s="51">
         <v>178</v>
@@ -10505,10 +10580,10 @@
         <v>24</v>
       </c>
       <c r="G150" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H150" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I150" s="51">
         <v>178</v>
@@ -10520,10 +10595,10 @@
         <v>24</v>
       </c>
       <c r="G151" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H151" s="51">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I151" s="51">
         <v>178</v>
@@ -10535,10 +10610,10 @@
         <v>24</v>
       </c>
       <c r="G152" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H152" s="51">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I152" s="51">
         <v>178</v>
@@ -10550,7 +10625,7 @@
         <v>24</v>
       </c>
       <c r="G153" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H153" s="51">
         <v>1</v>
@@ -10565,7 +10640,7 @@
         <v>24</v>
       </c>
       <c r="G154" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H154" s="51"/>
       <c r="I154" s="51">
@@ -10578,7 +10653,7 @@
         <v>24</v>
       </c>
       <c r="G155" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H155" s="51">
         <v>1</v>
@@ -10596,7 +10671,7 @@
         <v>25</v>
       </c>
       <c r="G156" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H156" s="51">
         <v>5</v>
@@ -10611,7 +10686,7 @@
         <v>25</v>
       </c>
       <c r="G157" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H157" s="51">
         <v>4</v>
@@ -10626,7 +10701,7 @@
         <v>25</v>
       </c>
       <c r="G158" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H158" s="51">
         <v>8</v>
@@ -10641,7 +10716,7 @@
         <v>25</v>
       </c>
       <c r="G159" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H159" s="51">
         <v>4</v>
@@ -10656,10 +10731,10 @@
         <v>25</v>
       </c>
       <c r="G160" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H160" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I160" s="51">
         <v>172</v>
@@ -10671,7 +10746,7 @@
         <v>25</v>
       </c>
       <c r="G161" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H161" s="51">
         <v>6</v>
@@ -10686,7 +10761,7 @@
         <v>25</v>
       </c>
       <c r="G162" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H162" s="51">
         <v>3</v>
@@ -10701,7 +10776,7 @@
         <v>25</v>
       </c>
       <c r="G163" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H163" s="51">
         <v>1</v>
@@ -10716,7 +10791,7 @@
         <v>25</v>
       </c>
       <c r="G164" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H164">
         <v>3</v>
@@ -10734,9 +10809,11 @@
         <v>26</v>
       </c>
       <c r="G165" t="s">
-        <v>218</v>
-      </c>
-      <c r="H165" s="51"/>
+        <v>222</v>
+      </c>
+      <c r="H165" s="51">
+        <v>12</v>
+      </c>
       <c r="I165" s="51">
         <v>162</v>
       </c>
@@ -10747,9 +10824,11 @@
         <v>26</v>
       </c>
       <c r="G166" t="s">
-        <v>219</v>
-      </c>
-      <c r="H166" s="51"/>
+        <v>223</v>
+      </c>
+      <c r="H166" s="51">
+        <v>6</v>
+      </c>
       <c r="I166" s="51">
         <v>162</v>
       </c>
@@ -10760,9 +10839,11 @@
         <v>26</v>
       </c>
       <c r="G167" t="s">
-        <v>220</v>
-      </c>
-      <c r="H167" s="51"/>
+        <v>224</v>
+      </c>
+      <c r="H167" s="51">
+        <v>4</v>
+      </c>
       <c r="I167" s="51">
         <v>162</v>
       </c>
@@ -10773,9 +10854,11 @@
         <v>26</v>
       </c>
       <c r="G168" t="s">
-        <v>221</v>
-      </c>
-      <c r="H168" s="51"/>
+        <v>225</v>
+      </c>
+      <c r="H168" s="51">
+        <v>15</v>
+      </c>
       <c r="I168" s="51">
         <v>162</v>
       </c>
@@ -10786,9 +10869,11 @@
         <v>26</v>
       </c>
       <c r="G169" t="s">
-        <v>222</v>
-      </c>
-      <c r="H169" s="51"/>
+        <v>226</v>
+      </c>
+      <c r="H169" s="51">
+        <v>11</v>
+      </c>
       <c r="I169" s="51">
         <v>162</v>
       </c>
@@ -10799,9 +10884,11 @@
         <v>26</v>
       </c>
       <c r="G170" t="s">
-        <v>223</v>
-      </c>
-      <c r="H170" s="51"/>
+        <v>227</v>
+      </c>
+      <c r="H170" s="51">
+        <v>12</v>
+      </c>
       <c r="I170" s="51">
         <v>162</v>
       </c>
@@ -10812,9 +10899,11 @@
         <v>26</v>
       </c>
       <c r="G171" t="s">
-        <v>224</v>
-      </c>
-      <c r="H171" s="51"/>
+        <v>228</v>
+      </c>
+      <c r="H171" s="51">
+        <v>17</v>
+      </c>
       <c r="I171" s="51">
         <v>162</v>
       </c>
@@ -10825,9 +10914,11 @@
         <v>26</v>
       </c>
       <c r="G172" t="s">
-        <v>225</v>
-      </c>
-      <c r="H172" s="51"/>
+        <v>229</v>
+      </c>
+      <c r="H172" s="51">
+        <v>6</v>
+      </c>
       <c r="I172" s="51">
         <v>162</v>
       </c>
@@ -10838,9 +10929,11 @@
         <v>26</v>
       </c>
       <c r="G173" t="s">
-        <v>226</v>
-      </c>
-      <c r="H173" s="51"/>
+        <v>230</v>
+      </c>
+      <c r="H173" s="51">
+        <v>11</v>
+      </c>
       <c r="I173" s="51">
         <v>162</v>
       </c>
@@ -10854,10 +10947,10 @@
         <v>27</v>
       </c>
       <c r="G174" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H174" s="51">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I174" s="51">
         <v>140</v>
@@ -10869,7 +10962,7 @@
         <v>27</v>
       </c>
       <c r="G175" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H175" s="51">
         <v>2</v>
@@ -10884,10 +10977,10 @@
         <v>27</v>
       </c>
       <c r="G176" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H176" s="51">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I176" s="51">
         <v>140</v>
@@ -10899,10 +10992,10 @@
         <v>27</v>
       </c>
       <c r="G177" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H177" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I177" s="51">
         <v>140</v>
@@ -10914,10 +11007,10 @@
         <v>27</v>
       </c>
       <c r="G178" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H178" s="51">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I178" s="51">
         <v>140</v>
@@ -10929,10 +11022,10 @@
         <v>27</v>
       </c>
       <c r="G179" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H179" s="51">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I179" s="51">
         <v>140</v>
@@ -10944,10 +11037,10 @@
         <v>27</v>
       </c>
       <c r="G180" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I180" s="51">
         <v>140</v>
@@ -10959,10 +11052,10 @@
         <v>27</v>
       </c>
       <c r="G181" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H181" s="51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I181" s="51">
         <v>140</v>
@@ -10974,10 +11067,10 @@
         <v>27</v>
       </c>
       <c r="G182" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H182" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I182" s="51">
         <v>140</v>
@@ -10992,10 +11085,10 @@
         <v>28</v>
       </c>
       <c r="G183" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H183" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I183" s="51">
         <v>168</v>
@@ -11007,10 +11100,10 @@
         <v>28</v>
       </c>
       <c r="G184" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H184" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I184" s="51">
         <v>168</v>
@@ -11022,10 +11115,10 @@
         <v>28</v>
       </c>
       <c r="G185" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H185" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I185" s="51">
         <v>168</v>
@@ -11037,10 +11130,10 @@
         <v>28</v>
       </c>
       <c r="G186" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H186">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I186" s="51">
         <v>168</v>
@@ -11052,10 +11145,10 @@
         <v>28</v>
       </c>
       <c r="G187" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H187" s="51">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I187" s="51">
         <v>168</v>
@@ -11067,10 +11160,10 @@
         <v>28</v>
       </c>
       <c r="G188" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H188" s="51">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I188" s="51">
         <v>168</v>
@@ -11082,10 +11175,10 @@
         <v>28</v>
       </c>
       <c r="G189" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H189" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I189" s="51">
         <v>168</v>
@@ -11097,10 +11190,10 @@
         <v>28</v>
       </c>
       <c r="G190" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H190" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I190" s="51">
         <v>168</v>
@@ -11112,9 +11205,11 @@
         <v>28</v>
       </c>
       <c r="G191" t="s">
-        <v>226</v>
-      </c>
-      <c r="H191" s="51"/>
+        <v>230</v>
+      </c>
+      <c r="H191" s="51">
+        <v>2</v>
+      </c>
       <c r="I191" s="51">
         <v>168</v>
       </c>
@@ -11128,10 +11223,10 @@
         <v>3</v>
       </c>
       <c r="G192" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H192" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I192" s="51">
         <v>170</v>
@@ -11143,10 +11238,10 @@
         <v>3</v>
       </c>
       <c r="G193" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H193" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I193" s="51">
         <v>170</v>
@@ -11158,10 +11253,10 @@
         <v>3</v>
       </c>
       <c r="G194" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H194" s="51">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I194" s="51">
         <v>170</v>
@@ -11173,10 +11268,10 @@
         <v>3</v>
       </c>
       <c r="G195" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H195" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I195" s="51">
         <v>170</v>
@@ -11188,10 +11283,10 @@
         <v>3</v>
       </c>
       <c r="G196" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H196">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I196" s="51">
         <v>170</v>
@@ -11203,10 +11298,10 @@
         <v>3</v>
       </c>
       <c r="G197" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H197" s="51">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I197" s="51">
         <v>170</v>
@@ -11218,9 +11313,11 @@
         <v>3</v>
       </c>
       <c r="G198" t="s">
-        <v>224</v>
-      </c>
-      <c r="H198" s="51"/>
+        <v>228</v>
+      </c>
+      <c r="H198" s="51">
+        <v>5</v>
+      </c>
       <c r="I198" s="51">
         <v>170</v>
       </c>
@@ -11231,10 +11328,10 @@
         <v>3</v>
       </c>
       <c r="G199" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H199" s="51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I199" s="51">
         <v>170</v>
@@ -11246,10 +11343,10 @@
         <v>3</v>
       </c>
       <c r="G200" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H200" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I200" s="51">
         <v>170</v>
@@ -11264,9 +11361,11 @@
         <v>30</v>
       </c>
       <c r="G201" t="s">
-        <v>218</v>
-      </c>
-      <c r="H201" s="51"/>
+        <v>222</v>
+      </c>
+      <c r="H201" s="51">
+        <v>2</v>
+      </c>
       <c r="I201" s="51">
         <v>138</v>
       </c>
@@ -11277,7 +11376,7 @@
         <v>30</v>
       </c>
       <c r="G202" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H202" s="51"/>
       <c r="I202" s="51">
@@ -11290,9 +11389,11 @@
         <v>30</v>
       </c>
       <c r="G203" t="s">
-        <v>220</v>
-      </c>
-      <c r="H203" s="51"/>
+        <v>224</v>
+      </c>
+      <c r="H203" s="51">
+        <v>1</v>
+      </c>
       <c r="I203" s="51">
         <v>138</v>
       </c>
@@ -11303,7 +11404,7 @@
         <v>30</v>
       </c>
       <c r="G204" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H204" s="51"/>
       <c r="I204" s="51">
@@ -11316,7 +11417,7 @@
         <v>30</v>
       </c>
       <c r="G205" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H205" s="51"/>
       <c r="I205" s="51">
@@ -11329,7 +11430,7 @@
         <v>30</v>
       </c>
       <c r="G206" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H206" s="51"/>
       <c r="I206" s="51">
@@ -11342,7 +11443,7 @@
         <v>30</v>
       </c>
       <c r="G207" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H207" s="51"/>
       <c r="I207" s="51">
@@ -11355,7 +11456,7 @@
         <v>30</v>
       </c>
       <c r="G208" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H208" s="51"/>
       <c r="I208" s="51">
@@ -11368,7 +11469,7 @@
         <v>30</v>
       </c>
       <c r="G209" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H209" s="51"/>
       <c r="I209" s="51">
@@ -11384,10 +11485,10 @@
         <v>31</v>
       </c>
       <c r="G210" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H210" s="51">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I210" s="51">
         <v>161</v>
@@ -11399,10 +11500,10 @@
         <v>31</v>
       </c>
       <c r="G211" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H211" s="51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I211" s="51">
         <v>161</v>
@@ -11414,10 +11515,10 @@
         <v>31</v>
       </c>
       <c r="G212" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H212">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I212" s="51">
         <v>161</v>
@@ -11429,10 +11530,10 @@
         <v>31</v>
       </c>
       <c r="G213" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H213" s="51">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I213" s="51">
         <v>161</v>
@@ -11444,10 +11545,10 @@
         <v>31</v>
       </c>
       <c r="G214" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H214" s="51">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I214" s="51">
         <v>161</v>
@@ -11459,10 +11560,10 @@
         <v>31</v>
       </c>
       <c r="G215" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H215" s="51">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I215" s="51">
         <v>161</v>
@@ -11474,10 +11575,10 @@
         <v>31</v>
       </c>
       <c r="G216" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H216" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I216" s="51">
         <v>161</v>
@@ -11489,10 +11590,10 @@
         <v>31</v>
       </c>
       <c r="G217" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H217" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I217" s="51">
         <v>161</v>
@@ -11504,10 +11605,10 @@
         <v>31</v>
       </c>
       <c r="G218" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H218" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I218" s="51">
         <v>161</v>
@@ -11522,10 +11623,10 @@
         <v>32</v>
       </c>
       <c r="G219" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H219" s="51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I219" s="51">
         <v>56</v>
@@ -11537,9 +11638,11 @@
         <v>32</v>
       </c>
       <c r="G220" t="s">
-        <v>219</v>
-      </c>
-      <c r="H220" s="51"/>
+        <v>223</v>
+      </c>
+      <c r="H220" s="51">
+        <v>1</v>
+      </c>
       <c r="I220" s="51">
         <v>56</v>
       </c>
@@ -11550,10 +11653,10 @@
         <v>32</v>
       </c>
       <c r="G221" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H221" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I221" s="51">
         <v>56</v>
@@ -11565,10 +11668,10 @@
         <v>32</v>
       </c>
       <c r="G222" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H222" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I222" s="51">
         <v>56</v>
@@ -11580,10 +11683,10 @@
         <v>32</v>
       </c>
       <c r="G223" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H223" s="51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I223" s="51">
         <v>56</v>
@@ -11595,10 +11698,10 @@
         <v>32</v>
       </c>
       <c r="G224" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H224" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I224" s="51">
         <v>56</v>
@@ -11610,10 +11713,10 @@
         <v>32</v>
       </c>
       <c r="G225" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H225" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I225" s="51">
         <v>56</v>
@@ -11625,10 +11728,10 @@
         <v>32</v>
       </c>
       <c r="G226" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H226" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I226" s="51">
         <v>56</v>
@@ -11640,10 +11743,10 @@
         <v>32</v>
       </c>
       <c r="G227" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H227" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I227" s="51">
         <v>56</v>
@@ -11658,10 +11761,10 @@
         <v>33</v>
       </c>
       <c r="G228" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H228" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I228" s="51">
         <v>172</v>
@@ -11673,10 +11776,10 @@
         <v>33</v>
       </c>
       <c r="G229" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H229" s="51">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I229" s="51">
         <v>172</v>
@@ -11688,10 +11791,10 @@
         <v>33</v>
       </c>
       <c r="G230" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H230" s="51">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I230" s="51">
         <v>172</v>
@@ -11703,10 +11806,10 @@
         <v>33</v>
       </c>
       <c r="G231" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H231" s="51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I231" s="51">
         <v>172</v>
@@ -11718,10 +11821,10 @@
         <v>33</v>
       </c>
       <c r="G232" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H232" s="51">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I232" s="51">
         <v>172</v>
@@ -11733,10 +11836,10 @@
         <v>33</v>
       </c>
       <c r="G233" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H233" s="51">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I233" s="51">
         <v>172</v>
@@ -11748,7 +11851,7 @@
         <v>33</v>
       </c>
       <c r="G234" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H234" s="51">
         <v>2</v>
@@ -11763,10 +11866,10 @@
         <v>33</v>
       </c>
       <c r="G235" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H235" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I235" s="51">
         <v>172</v>
@@ -11778,7 +11881,10 @@
         <v>33</v>
       </c>
       <c r="G236" t="s">
-        <v>226</v>
+        <v>230</v>
+      </c>
+      <c r="H236">
+        <v>2</v>
       </c>
       <c r="I236" s="51">
         <v>172</v>
@@ -11793,10 +11899,10 @@
         <v>36</v>
       </c>
       <c r="G237" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H237" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I237" s="51">
         <v>156</v>
@@ -11808,10 +11914,10 @@
         <v>36</v>
       </c>
       <c r="G238" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H238" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I238" s="51">
         <v>156</v>
@@ -11823,10 +11929,10 @@
         <v>36</v>
       </c>
       <c r="G239" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H239" s="51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I239" s="51">
         <v>156</v>
@@ -11838,10 +11944,10 @@
         <v>36</v>
       </c>
       <c r="G240" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H240" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I240" s="51">
         <v>156</v>
@@ -11853,10 +11959,10 @@
         <v>36</v>
       </c>
       <c r="G241" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H241" s="51">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I241" s="51">
         <v>156</v>
@@ -11868,10 +11974,10 @@
         <v>36</v>
       </c>
       <c r="G242" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H242" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I242" s="51">
         <v>156</v>
@@ -11883,10 +11989,10 @@
         <v>36</v>
       </c>
       <c r="G243" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H243" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I243" s="51">
         <v>156</v>
@@ -11898,7 +12004,7 @@
         <v>36</v>
       </c>
       <c r="G244" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H244">
         <v>1</v>
@@ -11913,7 +12019,7 @@
         <v>36</v>
       </c>
       <c r="G245" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H245" s="51"/>
       <c r="I245" s="51">
@@ -11929,10 +12035,10 @@
         <v>37</v>
       </c>
       <c r="G246" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H246" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I246" s="51">
         <v>141</v>
@@ -11944,7 +12050,7 @@
         <v>37</v>
       </c>
       <c r="G247" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H247" s="51"/>
       <c r="I247" s="51">
@@ -11957,9 +12063,11 @@
         <v>37</v>
       </c>
       <c r="G248" t="s">
-        <v>220</v>
-      </c>
-      <c r="H248" s="51"/>
+        <v>224</v>
+      </c>
+      <c r="H248" s="51">
+        <v>2</v>
+      </c>
       <c r="I248" s="51">
         <v>141</v>
       </c>
@@ -11970,7 +12078,7 @@
         <v>37</v>
       </c>
       <c r="G249" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H249" s="51"/>
       <c r="I249" s="51">
@@ -11983,10 +12091,10 @@
         <v>37</v>
       </c>
       <c r="G250" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H250" s="51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I250" s="51">
         <v>141</v>
@@ -11998,10 +12106,10 @@
         <v>37</v>
       </c>
       <c r="G251" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H251" s="51">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I251" s="51">
         <v>141</v>
@@ -12013,10 +12121,10 @@
         <v>37</v>
       </c>
       <c r="G252" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H252">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I252" s="51">
         <v>141</v>
@@ -12028,10 +12136,10 @@
         <v>37</v>
       </c>
       <c r="G253" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H253" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I253" s="51">
         <v>141</v>
@@ -12043,7 +12151,7 @@
         <v>37</v>
       </c>
       <c r="G254" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H254" s="51"/>
       <c r="I254" s="51">
@@ -12059,10 +12167,10 @@
         <v>4</v>
       </c>
       <c r="G255" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H255" s="51">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I255" s="51">
         <v>182</v>
@@ -12074,10 +12182,10 @@
         <v>4</v>
       </c>
       <c r="G256" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H256" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I256" s="51">
         <v>182</v>
@@ -12089,10 +12197,10 @@
         <v>4</v>
       </c>
       <c r="G257" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H257" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I257" s="51">
         <v>182</v>
@@ -12104,10 +12212,10 @@
         <v>4</v>
       </c>
       <c r="G258" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H258">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I258" s="51">
         <v>182</v>
@@ -12119,10 +12227,10 @@
         <v>4</v>
       </c>
       <c r="G259" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H259" s="51">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I259" s="51">
         <v>182</v>
@@ -12134,10 +12242,10 @@
         <v>4</v>
       </c>
       <c r="G260" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H260">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I260" s="51">
         <v>182</v>
@@ -12149,10 +12257,10 @@
         <v>4</v>
       </c>
       <c r="G261" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H261" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I261" s="51">
         <v>182</v>
@@ -12164,10 +12272,10 @@
         <v>4</v>
       </c>
       <c r="G262" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H262" s="51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I262" s="51">
         <v>182</v>
@@ -12179,10 +12287,10 @@
         <v>4</v>
       </c>
       <c r="G263" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H263" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I263" s="51">
         <v>182</v>
@@ -12197,10 +12305,10 @@
         <v>40</v>
       </c>
       <c r="G264" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H264" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I264" s="51">
         <v>249</v>
@@ -12212,7 +12320,7 @@
         <v>40</v>
       </c>
       <c r="G265" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H265">
         <v>1</v>
@@ -12227,10 +12335,10 @@
         <v>40</v>
       </c>
       <c r="G266" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H266" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I266" s="51">
         <v>249</v>
@@ -12242,10 +12350,10 @@
         <v>40</v>
       </c>
       <c r="G267" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H267" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I267" s="51">
         <v>249</v>
@@ -12257,10 +12365,10 @@
         <v>40</v>
       </c>
       <c r="G268" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H268">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I268" s="51">
         <v>249</v>
@@ -12272,10 +12380,10 @@
         <v>40</v>
       </c>
       <c r="G269" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H269" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I269" s="51">
         <v>249</v>
@@ -12287,10 +12395,10 @@
         <v>40</v>
       </c>
       <c r="G270" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H270" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I270" s="51">
         <v>249</v>
@@ -12302,10 +12410,10 @@
         <v>40</v>
       </c>
       <c r="G271" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H271" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I271" s="51">
         <v>249</v>
@@ -12317,10 +12425,10 @@
         <v>40</v>
       </c>
       <c r="G272" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H272" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I272" s="51">
         <v>249</v>
@@ -12335,7 +12443,7 @@
         <v>42</v>
       </c>
       <c r="G273" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H273" s="51"/>
       <c r="I273" s="51">
@@ -12348,7 +12456,7 @@
         <v>42</v>
       </c>
       <c r="G274" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H274" s="51"/>
       <c r="I274" s="51">
@@ -12361,7 +12469,7 @@
         <v>42</v>
       </c>
       <c r="G275" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H275" s="51"/>
       <c r="I275" s="51">
@@ -12374,7 +12482,7 @@
         <v>42</v>
       </c>
       <c r="G276" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I276" s="51">
         <v>52</v>
@@ -12386,7 +12494,7 @@
         <v>42</v>
       </c>
       <c r="G277" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H277" s="51"/>
       <c r="I277" s="51">
@@ -12399,7 +12507,7 @@
         <v>42</v>
       </c>
       <c r="G278" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H278" s="51"/>
       <c r="I278" s="51">
@@ -12412,7 +12520,7 @@
         <v>42</v>
       </c>
       <c r="G279" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H279" s="51"/>
       <c r="I279" s="51">
@@ -12425,7 +12533,7 @@
         <v>42</v>
       </c>
       <c r="G280" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H280" s="51"/>
       <c r="I280" s="51">
@@ -12438,7 +12546,7 @@
         <v>42</v>
       </c>
       <c r="G281" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H281" s="51"/>
       <c r="I281" s="51">
@@ -12454,7 +12562,7 @@
         <v>43</v>
       </c>
       <c r="G282" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H282" s="51"/>
       <c r="I282" s="51">
@@ -12467,7 +12575,7 @@
         <v>43</v>
       </c>
       <c r="G283" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H283" s="51"/>
       <c r="I283" s="51">
@@ -12480,7 +12588,7 @@
         <v>43</v>
       </c>
       <c r="G284" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I284" s="51">
         <v>93</v>
@@ -12492,7 +12600,7 @@
         <v>43</v>
       </c>
       <c r="G285" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I285" s="51">
         <v>93</v>
@@ -12504,7 +12612,7 @@
         <v>43</v>
       </c>
       <c r="G286" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I286" s="51">
         <v>93</v>
@@ -12516,7 +12624,7 @@
         <v>43</v>
       </c>
       <c r="G287" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I287" s="51">
         <v>93</v>
@@ -12528,7 +12636,7 @@
         <v>43</v>
       </c>
       <c r="G288" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I288" s="51">
         <v>93</v>
@@ -12540,7 +12648,7 @@
         <v>43</v>
       </c>
       <c r="G289" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H289" s="51"/>
       <c r="I289" s="51">
@@ -12553,7 +12661,7 @@
         <v>43</v>
       </c>
       <c r="G290" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="I290" s="51">
         <v>93</v>
@@ -12568,10 +12676,10 @@
         <v>44</v>
       </c>
       <c r="G291" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H291">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I291" s="51">
         <v>169</v>
@@ -12583,7 +12691,7 @@
         <v>44</v>
       </c>
       <c r="G292" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H292">
         <v>6</v>
@@ -12598,10 +12706,10 @@
         <v>44</v>
       </c>
       <c r="G293" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H293">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I293" s="51">
         <v>169</v>
@@ -12613,10 +12721,10 @@
         <v>44</v>
       </c>
       <c r="G294" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H294">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I294" s="51">
         <v>169</v>
@@ -12628,10 +12736,10 @@
         <v>44</v>
       </c>
       <c r="G295" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H295">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I295" s="51">
         <v>169</v>
@@ -12643,10 +12751,10 @@
         <v>44</v>
       </c>
       <c r="G296" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H296">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I296" s="51">
         <v>169</v>
@@ -12658,10 +12766,10 @@
         <v>44</v>
       </c>
       <c r="G297" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H297" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I297" s="51">
         <v>169</v>
@@ -12673,10 +12781,10 @@
         <v>44</v>
       </c>
       <c r="G298" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H298">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I298" s="51">
         <v>169</v>
@@ -12688,10 +12796,10 @@
         <v>44</v>
       </c>
       <c r="G299" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H299" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I299" s="51">
         <v>169</v>
@@ -12706,7 +12814,7 @@
         <v>49</v>
       </c>
       <c r="G300" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H300" s="51">
         <v>8</v>
@@ -12721,7 +12829,7 @@
         <v>49</v>
       </c>
       <c r="G301" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H301" s="51">
         <v>8</v>
@@ -12736,7 +12844,7 @@
         <v>49</v>
       </c>
       <c r="G302" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H302" s="51">
         <v>26</v>
@@ -12751,7 +12859,7 @@
         <v>49</v>
       </c>
       <c r="G303" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H303" s="51">
         <v>6</v>
@@ -12766,7 +12874,7 @@
         <v>49</v>
       </c>
       <c r="G304" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H304" s="51">
         <v>20</v>
@@ -12781,7 +12889,7 @@
         <v>49</v>
       </c>
       <c r="G305" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H305" s="51">
         <v>11</v>
@@ -12796,7 +12904,7 @@
         <v>49</v>
       </c>
       <c r="G306" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H306" s="51">
         <v>19</v>
@@ -12811,7 +12919,7 @@
         <v>49</v>
       </c>
       <c r="G307" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H307">
         <v>7</v>
@@ -12826,7 +12934,7 @@
         <v>49</v>
       </c>
       <c r="G308" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H308">
         <v>8</v>
@@ -12844,10 +12952,10 @@
         <v>5</v>
       </c>
       <c r="G309" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H309">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I309" s="51">
         <v>260</v>
@@ -12859,10 +12967,10 @@
         <v>5</v>
       </c>
       <c r="G310" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H310">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I310" s="51">
         <v>260</v>
@@ -12874,10 +12982,10 @@
         <v>5</v>
       </c>
       <c r="G311" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H311">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I311" s="51">
         <v>260</v>
@@ -12889,10 +12997,10 @@
         <v>5</v>
       </c>
       <c r="G312" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H312">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I312" s="51">
         <v>260</v>
@@ -12904,10 +13012,10 @@
         <v>5</v>
       </c>
       <c r="G313" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H313">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I313" s="51">
         <v>260</v>
@@ -12919,10 +13027,10 @@
         <v>5</v>
       </c>
       <c r="G314" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H314">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I314" s="51">
         <v>260</v>
@@ -12934,10 +13042,10 @@
         <v>5</v>
       </c>
       <c r="G315" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H315" s="51">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I315" s="51">
         <v>260</v>
@@ -12949,10 +13057,10 @@
         <v>5</v>
       </c>
       <c r="G316" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H316">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I316" s="51">
         <v>260</v>
@@ -12964,10 +13072,10 @@
         <v>5</v>
       </c>
       <c r="G317" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H317" s="51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I317" s="51">
         <v>260</v>
@@ -12982,7 +13090,7 @@
         <v>52</v>
       </c>
       <c r="G318" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H318" s="51">
         <v>1</v>
@@ -12997,7 +13105,7 @@
         <v>52</v>
       </c>
       <c r="G319" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H319" s="51"/>
       <c r="I319" s="51">
@@ -13010,7 +13118,7 @@
         <v>52</v>
       </c>
       <c r="G320" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H320" s="51"/>
       <c r="I320" s="51">
@@ -13023,7 +13131,7 @@
         <v>52</v>
       </c>
       <c r="G321" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H321" s="51"/>
       <c r="I321" s="51">
@@ -13036,7 +13144,7 @@
         <v>52</v>
       </c>
       <c r="G322" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H322" s="51"/>
       <c r="I322" s="51">
@@ -13049,7 +13157,7 @@
         <v>52</v>
       </c>
       <c r="G323" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I323" s="51">
         <v>101</v>
@@ -13061,10 +13169,10 @@
         <v>52</v>
       </c>
       <c r="G324" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H324" s="51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I324" s="51">
         <v>101</v>
@@ -13076,7 +13184,7 @@
         <v>52</v>
       </c>
       <c r="G325" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H325" s="51"/>
       <c r="I325" s="51">
@@ -13089,7 +13197,7 @@
         <v>52</v>
       </c>
       <c r="G326" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H326" s="51"/>
       <c r="I326" s="51">
@@ -13105,7 +13213,7 @@
         <v>53</v>
       </c>
       <c r="G327" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I327" s="51">
         <v>105</v>
@@ -13117,7 +13225,7 @@
         <v>53</v>
       </c>
       <c r="G328" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I328" s="51">
         <v>105</v>
@@ -13129,7 +13237,7 @@
         <v>53</v>
       </c>
       <c r="G329" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H329" s="51"/>
       <c r="I329" s="51">
@@ -13142,7 +13250,7 @@
         <v>53</v>
       </c>
       <c r="G330" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I330" s="51">
         <v>105</v>
@@ -13154,7 +13262,7 @@
         <v>53</v>
       </c>
       <c r="G331" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H331" s="51"/>
       <c r="I331" s="51">
@@ -13167,7 +13275,7 @@
         <v>53</v>
       </c>
       <c r="G332" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I332" s="51">
         <v>105</v>
@@ -13179,10 +13287,10 @@
         <v>53</v>
       </c>
       <c r="G333" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H333" s="51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I333" s="51">
         <v>105</v>
@@ -13194,7 +13302,7 @@
         <v>53</v>
       </c>
       <c r="G334" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H334" s="51"/>
       <c r="I334" s="51">
@@ -13207,7 +13315,7 @@
         <v>53</v>
       </c>
       <c r="G335" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H335" s="51"/>
       <c r="I335" s="51">
@@ -13223,10 +13331,10 @@
         <v>54</v>
       </c>
       <c r="G336" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H336" s="51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I336" s="51">
         <v>202</v>
@@ -13238,10 +13346,10 @@
         <v>54</v>
       </c>
       <c r="G337" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H337" s="51">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I337" s="51">
         <v>202</v>
@@ -13253,10 +13361,10 @@
         <v>54</v>
       </c>
       <c r="G338" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H338" s="51">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I338" s="51">
         <v>202</v>
@@ -13268,10 +13376,10 @@
         <v>54</v>
       </c>
       <c r="G339" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H339" s="51">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I339" s="51">
         <v>202</v>
@@ -13283,10 +13391,10 @@
         <v>54</v>
       </c>
       <c r="G340" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H340">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I340" s="51">
         <v>202</v>
@@ -13298,10 +13406,10 @@
         <v>54</v>
       </c>
       <c r="G341" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H341" s="51">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I341" s="51">
         <v>202</v>
@@ -13313,10 +13421,10 @@
         <v>54</v>
       </c>
       <c r="G342" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H342" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I342" s="51">
         <v>202</v>
@@ -13328,10 +13436,10 @@
         <v>54</v>
       </c>
       <c r="G343" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H343" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I343" s="51">
         <v>202</v>
@@ -13343,10 +13451,10 @@
         <v>54</v>
       </c>
       <c r="G344" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H344" s="51">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I344" s="51">
         <v>202</v>
@@ -13361,7 +13469,7 @@
         <v>56</v>
       </c>
       <c r="G345" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I345" s="51">
         <v>198</v>
@@ -13373,7 +13481,7 @@
         <v>56</v>
       </c>
       <c r="G346" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H346" s="51"/>
       <c r="I346" s="51">
@@ -13386,7 +13494,7 @@
         <v>56</v>
       </c>
       <c r="G347" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H347" s="51"/>
       <c r="I347" s="51">
@@ -13399,7 +13507,7 @@
         <v>56</v>
       </c>
       <c r="G348" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I348" s="51">
         <v>198</v>
@@ -13411,7 +13519,7 @@
         <v>56</v>
       </c>
       <c r="G349" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H349" s="51"/>
       <c r="I349" s="51">
@@ -13424,7 +13532,7 @@
         <v>56</v>
       </c>
       <c r="G350" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H350" s="51"/>
       <c r="I350" s="51">
@@ -13437,7 +13545,7 @@
         <v>56</v>
       </c>
       <c r="G351" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H351" s="51"/>
       <c r="I351" s="51">
@@ -13450,7 +13558,7 @@
         <v>56</v>
       </c>
       <c r="G352" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="I352" s="51">
         <v>198</v>
@@ -13462,7 +13570,7 @@
         <v>56</v>
       </c>
       <c r="G353" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H353" s="51"/>
       <c r="I353" s="51">
@@ -13478,7 +13586,7 @@
         <v>57</v>
       </c>
       <c r="G354" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H354" s="51"/>
       <c r="I354" s="51">
@@ -13491,7 +13599,7 @@
         <v>57</v>
       </c>
       <c r="G355" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H355" s="51"/>
       <c r="I355" s="51">
@@ -13504,7 +13612,7 @@
         <v>57</v>
       </c>
       <c r="G356" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H356" s="51"/>
       <c r="I356" s="51">
@@ -13517,7 +13625,7 @@
         <v>57</v>
       </c>
       <c r="G357" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H357" s="51"/>
       <c r="I357" s="51">
@@ -13530,7 +13638,7 @@
         <v>57</v>
       </c>
       <c r="G358" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H358" s="51"/>
       <c r="I358" s="51">
@@ -13543,7 +13651,7 @@
         <v>57</v>
       </c>
       <c r="G359" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H359" s="51"/>
       <c r="I359" s="51">
@@ -13556,9 +13664,11 @@
         <v>57</v>
       </c>
       <c r="G360" t="s">
-        <v>224</v>
-      </c>
-      <c r="H360" s="51"/>
+        <v>228</v>
+      </c>
+      <c r="H360" s="51">
+        <v>1</v>
+      </c>
       <c r="I360" s="51">
         <v>103</v>
       </c>
@@ -13569,7 +13679,7 @@
         <v>57</v>
       </c>
       <c r="G361" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H361" s="51"/>
       <c r="I361" s="51">
@@ -13582,7 +13692,7 @@
         <v>57</v>
       </c>
       <c r="G362" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H362" s="51"/>
       <c r="I362" s="51">
@@ -13598,11 +13708,11 @@
         <v>58</v>
       </c>
       <c r="G363" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H363" s="51"/>
       <c r="I363" s="51">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="364" spans="5:9" x14ac:dyDescent="0.25">
@@ -13611,11 +13721,11 @@
         <v>58</v>
       </c>
       <c r="G364" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H364" s="51"/>
       <c r="I364" s="51">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="365" spans="5:9" x14ac:dyDescent="0.25">
@@ -13624,11 +13734,11 @@
         <v>58</v>
       </c>
       <c r="G365" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H365" s="51"/>
       <c r="I365" s="51">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="366" spans="5:9" x14ac:dyDescent="0.25">
@@ -13637,11 +13747,11 @@
         <v>58</v>
       </c>
       <c r="G366" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H366" s="51"/>
       <c r="I366" s="51">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="367" spans="5:9" x14ac:dyDescent="0.25">
@@ -13650,11 +13760,11 @@
         <v>58</v>
       </c>
       <c r="G367" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H367" s="51"/>
       <c r="I367" s="51">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="368" spans="5:9" x14ac:dyDescent="0.25">
@@ -13663,11 +13773,11 @@
         <v>58</v>
       </c>
       <c r="G368" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H368" s="51"/>
       <c r="I368" s="51">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="369" spans="5:9" x14ac:dyDescent="0.25">
@@ -13676,11 +13786,11 @@
         <v>58</v>
       </c>
       <c r="G369" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H369" s="51"/>
       <c r="I369" s="51">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="370" spans="5:9" x14ac:dyDescent="0.25">
@@ -13689,11 +13799,11 @@
         <v>58</v>
       </c>
       <c r="G370" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H370" s="51"/>
       <c r="I370" s="51">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="371" spans="5:9" x14ac:dyDescent="0.25">
@@ -13702,11 +13812,11 @@
         <v>58</v>
       </c>
       <c r="G371" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H371" s="35"/>
       <c r="I371" s="35">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="372" spans="5:9" x14ac:dyDescent="0.25">
@@ -13718,7 +13828,7 @@
         <v>59</v>
       </c>
       <c r="G372" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I372">
         <v>119</v>
@@ -13730,7 +13840,7 @@
         <v>59</v>
       </c>
       <c r="G373" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I373">
         <v>119</v>
@@ -13742,7 +13852,7 @@
         <v>59</v>
       </c>
       <c r="G374" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I374">
         <v>119</v>
@@ -13754,7 +13864,7 @@
         <v>59</v>
       </c>
       <c r="G375" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I375">
         <v>119</v>
@@ -13766,7 +13876,7 @@
         <v>59</v>
       </c>
       <c r="G376" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I376">
         <v>119</v>
@@ -13778,7 +13888,7 @@
         <v>59</v>
       </c>
       <c r="G377" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I377">
         <v>119</v>
@@ -13790,7 +13900,7 @@
         <v>59</v>
       </c>
       <c r="G378" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I378">
         <v>119</v>
@@ -13802,7 +13912,7 @@
         <v>59</v>
       </c>
       <c r="G379" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="I379">
         <v>119</v>
@@ -13814,7 +13924,7 @@
         <v>59</v>
       </c>
       <c r="G380" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="I380">
         <v>119</v>
@@ -13829,7 +13939,10 @@
         <v>7</v>
       </c>
       <c r="G381" t="s">
-        <v>218</v>
+        <v>222</v>
+      </c>
+      <c r="H381">
+        <v>1</v>
       </c>
       <c r="I381">
         <v>113</v>
@@ -13841,7 +13954,7 @@
         <v>7</v>
       </c>
       <c r="G382" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I382">
         <v>113</v>
@@ -13853,7 +13966,10 @@
         <v>7</v>
       </c>
       <c r="G383" t="s">
-        <v>220</v>
+        <v>224</v>
+      </c>
+      <c r="H383">
+        <v>1</v>
       </c>
       <c r="I383">
         <v>113</v>
@@ -13865,7 +13981,7 @@
         <v>7</v>
       </c>
       <c r="G384" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I384">
         <v>113</v>
@@ -13877,7 +13993,10 @@
         <v>7</v>
       </c>
       <c r="G385" t="s">
-        <v>222</v>
+        <v>226</v>
+      </c>
+      <c r="H385">
+        <v>1</v>
       </c>
       <c r="I385">
         <v>113</v>
@@ -13889,7 +14008,7 @@
         <v>7</v>
       </c>
       <c r="G386" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I386">
         <v>113</v>
@@ -13901,7 +14020,10 @@
         <v>7</v>
       </c>
       <c r="G387" t="s">
-        <v>224</v>
+        <v>228</v>
+      </c>
+      <c r="H387">
+        <v>1</v>
       </c>
       <c r="I387">
         <v>113</v>
@@ -13913,7 +14035,7 @@
         <v>7</v>
       </c>
       <c r="G388" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="I388">
         <v>113</v>
@@ -13925,7 +14047,7 @@
         <v>7</v>
       </c>
       <c r="G389" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="I389">
         <v>113</v>
@@ -13940,10 +14062,10 @@
         <v>8</v>
       </c>
       <c r="G390" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H390">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I390">
         <v>194</v>
@@ -13955,7 +14077,7 @@
         <v>8</v>
       </c>
       <c r="G391" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I391">
         <v>194</v>
@@ -13967,10 +14089,10 @@
         <v>8</v>
       </c>
       <c r="G392" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H392">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I392">
         <v>194</v>
@@ -13982,10 +14104,10 @@
         <v>8</v>
       </c>
       <c r="G393" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H393">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I393">
         <v>194</v>
@@ -13997,10 +14119,10 @@
         <v>8</v>
       </c>
       <c r="G394" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H394">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I394">
         <v>194</v>
@@ -14012,10 +14134,10 @@
         <v>8</v>
       </c>
       <c r="G395" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H395">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I395">
         <v>194</v>
@@ -14027,10 +14149,10 @@
         <v>8</v>
       </c>
       <c r="G396" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H396">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I396">
         <v>194</v>
@@ -14042,10 +14164,10 @@
         <v>8</v>
       </c>
       <c r="G397" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H397">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I397">
         <v>194</v>
@@ -14057,10 +14179,10 @@
         <v>8</v>
       </c>
       <c r="G398" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H398">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I398">
         <v>194</v>
@@ -14075,10 +14197,10 @@
         <v>9</v>
       </c>
       <c r="G399" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H399">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I399">
         <v>161</v>
@@ -14090,10 +14212,10 @@
         <v>9</v>
       </c>
       <c r="G400" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H400">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I400">
         <v>161</v>
@@ -14105,10 +14227,10 @@
         <v>9</v>
       </c>
       <c r="G401" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H401">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I401">
         <v>161</v>
@@ -14120,10 +14242,10 @@
         <v>9</v>
       </c>
       <c r="G402" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H402">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I402">
         <v>161</v>
@@ -14135,10 +14257,10 @@
         <v>9</v>
       </c>
       <c r="G403" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H403">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I403">
         <v>161</v>
@@ -14150,10 +14272,10 @@
         <v>9</v>
       </c>
       <c r="G404" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H404">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I404">
         <v>161</v>
@@ -14165,10 +14287,10 @@
         <v>9</v>
       </c>
       <c r="G405" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H405">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I405">
         <v>161</v>
@@ -14180,10 +14302,10 @@
         <v>9</v>
       </c>
       <c r="G406" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H406">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I406">
         <v>161</v>
@@ -14195,10 +14317,10 @@
         <v>9</v>
       </c>
       <c r="G407" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H407">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I407">
         <v>161</v>

--- a/data/historial/2026-06-29.xlsx
+++ b/data/historial/2026-06-29.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE1BB90A-BFEB-48EE-87C3-D034647CF518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{349C1206-A2E4-4AA5-898B-16F0DAD2F070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="233">
   <si>
     <t>GOMEZ MARTÍN</t>
   </si>
@@ -761,6 +761,12 @@
   </si>
   <si>
     <t>145 - PILAS</t>
+  </si>
+  <si>
+    <t>42 - ROMERO ARIEL</t>
+  </si>
+  <si>
+    <t>123 - TORRES ROLANDO</t>
   </si>
 </sst>
 </file>
@@ -944,7 +950,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="41">
@@ -2482,7 +2487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
@@ -2529,22 +2534,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="96">
-        <v>12759.648138517299</v>
+        <v>17146.3661547753</v>
       </c>
       <c r="D2" s="96">
-        <v>61262.625914064098</v>
+        <v>85454.712087362597</v>
       </c>
       <c r="E2" s="96">
-        <v>223094212.44056469</v>
+        <v>298472871.26286787</v>
       </c>
       <c r="F2" s="96">
         <v>0</v>
       </c>
       <c r="G2" s="96">
-        <v>141404.35170655229</v>
+        <v>185038.5097417341</v>
       </c>
       <c r="H2" s="96">
-        <v>141404.38</v>
+        <v>185038.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2555,22 +2560,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="96">
-        <v>168.2765046287</v>
+        <v>250.12620409120001</v>
       </c>
       <c r="D3" s="96">
-        <v>491.7907233853</v>
+        <v>592.11105820729995</v>
       </c>
       <c r="E3" s="96">
-        <v>4713478.3902184051</v>
+        <v>6167950.3247244535</v>
       </c>
       <c r="F3" s="96">
         <v>0</v>
       </c>
       <c r="G3" s="96">
-        <v>141404.35170655229</v>
+        <v>185038.5097417341</v>
       </c>
       <c r="H3" s="96">
-        <v>141404.38</v>
+        <v>185038.5</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2581,13 +2586,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="96">
-        <v>89.716765872799996</v>
+        <v>104.8786706344</v>
       </c>
       <c r="D4" s="96">
-        <v>228.65250000060001</v>
+        <v>236.1575000002</v>
       </c>
       <c r="E4" s="96">
-        <v>3490474.4748070529</v>
+        <v>3831780.4656781647</v>
       </c>
       <c r="F4" s="96">
         <v>0</v>
@@ -2607,13 +2612,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="96">
-        <v>113.08222222160001</v>
+        <v>160.9195238085</v>
       </c>
       <c r="D5" s="96">
-        <v>487.77000000160001</v>
+        <v>612.02249999640003</v>
       </c>
       <c r="E5" s="96">
-        <v>2539362.2668490014</v>
+        <v>3383340.6159000443</v>
       </c>
       <c r="F5" s="96">
         <v>0</v>
@@ -2633,13 +2638,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="96">
-        <v>319.23392857089999</v>
+        <v>361.47559523759998</v>
       </c>
       <c r="D6" s="96">
-        <v>1011.7841785766</v>
+        <v>1048.2891785794</v>
       </c>
       <c r="E6" s="96">
-        <v>5960130.3637676956</v>
+        <v>6899879.8473196756</v>
       </c>
       <c r="F6" s="96">
         <v>0</v>
@@ -2659,13 +2664,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="96">
-        <v>219.94720238030001</v>
+        <v>327.00688491969998</v>
       </c>
       <c r="D7" s="96">
-        <v>984.96450000130005</v>
+        <v>1128.9845000005</v>
       </c>
       <c r="E7" s="96">
-        <v>4232380.5042614806</v>
+        <v>6168952.3513542237</v>
       </c>
       <c r="F7" s="96">
         <v>0</v>
@@ -2685,13 +2690,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="96">
-        <v>1614.9333333334</v>
+        <v>1635.1449074075001</v>
       </c>
       <c r="D8" s="96">
-        <v>1507.4840000014001</v>
+        <v>1871.1244768535</v>
       </c>
       <c r="E8" s="96">
-        <v>16463801.298558187</v>
+        <v>17081843.43377829</v>
       </c>
       <c r="F8" s="96">
         <v>0</v>
@@ -2711,13 +2716,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="96">
-        <v>113.1691071427</v>
+        <v>151.30611111069999</v>
       </c>
       <c r="D9" s="96">
-        <v>643.5574999982</v>
+        <v>844.06249999780005</v>
       </c>
       <c r="E9" s="96">
-        <v>2229458.8498637299</v>
+        <v>2938195.7767915935</v>
       </c>
       <c r="F9" s="96">
         <v>0</v>
@@ -2737,13 +2742,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="96">
-        <v>67.089751984100005</v>
+        <v>97.588759920800001</v>
       </c>
       <c r="D10" s="96">
-        <v>200.80203124760001</v>
+        <v>283.49911458560001</v>
       </c>
       <c r="E10" s="96">
-        <v>2237337.654012111</v>
+        <v>2863924.6281832345</v>
       </c>
       <c r="F10" s="96">
         <v>0</v>
@@ -2763,13 +2768,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="96">
-        <v>69.604761904499995</v>
+        <v>115.3075396819</v>
       </c>
       <c r="D11" s="96">
-        <v>303.04959523730003</v>
+        <v>293.55459523730002</v>
       </c>
       <c r="E11" s="96">
-        <v>1556471.8667402903</v>
+        <v>2292259.0263364343</v>
       </c>
       <c r="F11" s="96">
         <v>0</v>
@@ -2789,13 +2794,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="96">
-        <v>178.19682539589999</v>
+        <v>345.86944444289998</v>
       </c>
       <c r="D12" s="96">
-        <v>527.69845237909999</v>
+        <v>2278.2034523770999</v>
       </c>
       <c r="E12" s="96">
-        <v>3454829.7358999122</v>
+        <v>5810906.7980635744</v>
       </c>
       <c r="F12" s="96">
         <v>0</v>
@@ -2815,13 +2820,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="96">
-        <v>225.7950396821</v>
+        <v>276.10170634870002</v>
       </c>
       <c r="D13" s="96">
-        <v>829.79151190790003</v>
+        <v>940.33651190850003</v>
       </c>
       <c r="E13" s="96">
-        <v>4650179.1579327742</v>
+        <v>5672001.5032034451</v>
       </c>
       <c r="F13" s="96">
         <v>0</v>
@@ -2841,13 +2846,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="96">
-        <v>1444.0819444447</v>
+        <v>1609.1910714287001</v>
       </c>
       <c r="D14" s="96">
-        <v>13580.7225000012</v>
+        <v>14799.4800000014</v>
       </c>
       <c r="E14" s="96">
-        <v>35677866.984969728</v>
+        <v>38609317.055148289</v>
       </c>
       <c r="F14" s="96">
         <v>0</v>
@@ -2867,13 +2872,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="96">
-        <v>203.11855158700001</v>
+        <v>247.15327380900001</v>
       </c>
       <c r="D15" s="96">
-        <v>755.52499999940005</v>
+        <v>974.77749999800005</v>
       </c>
       <c r="E15" s="96">
-        <v>3799689.1529486589</v>
+        <v>4655359.4802594241</v>
       </c>
       <c r="F15" s="96">
         <v>0</v>
@@ -2893,13 +2898,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="96">
-        <v>128.3049206343</v>
+        <v>178.4678174595</v>
       </c>
       <c r="D16" s="96">
-        <v>693.45458333670001</v>
+        <v>966.66851190839998</v>
       </c>
       <c r="E16" s="96">
-        <v>3126324.9965506792</v>
+        <v>4172472.7522102422</v>
       </c>
       <c r="F16" s="96">
         <v>0</v>
@@ -2919,13 +2924,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="96">
-        <v>214.7180555544</v>
+        <v>300.13720237960001</v>
       </c>
       <c r="D17" s="96">
-        <v>616.00885714909998</v>
+        <v>957.02602381810004</v>
       </c>
       <c r="E17" s="96">
-        <v>5092283.3348378455</v>
+        <v>6362623.1530077159</v>
       </c>
       <c r="F17" s="96">
         <v>0</v>
@@ -2945,13 +2950,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="96">
-        <v>339.81365079310001</v>
+        <v>484.40908730130002</v>
       </c>
       <c r="D18" s="96">
-        <v>2209.1249285679</v>
+        <v>2532.7421785693</v>
       </c>
       <c r="E18" s="96">
-        <v>6538018.3834050605</v>
+        <v>10180781.322442733</v>
       </c>
       <c r="F18" s="96">
         <v>0</v>
@@ -2971,13 +2976,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="96">
-        <v>242.1867394173</v>
+        <v>381.46455026360002</v>
       </c>
       <c r="D19" s="96">
-        <v>821.9142142938</v>
+        <v>1583.1667142941999</v>
       </c>
       <c r="E19" s="96">
-        <v>5313079.7996425815</v>
+        <v>8068602.606727235</v>
       </c>
       <c r="F19" s="96">
         <v>0</v>
@@ -2997,13 +3002,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="96">
-        <v>1331.513234127</v>
+        <v>1502.1562896826999</v>
       </c>
       <c r="D20" s="96">
-        <v>7081.0849999985003</v>
+        <v>8207.8199999985009</v>
       </c>
       <c r="E20" s="96">
-        <v>18543635.055367131</v>
+        <v>21714287.032106198</v>
       </c>
       <c r="F20" s="96">
         <v>0</v>
@@ -3023,13 +3028,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="96">
-        <v>174.00490079319999</v>
+        <v>211.5864484121</v>
       </c>
       <c r="D21" s="96">
-        <v>605.7746071478</v>
+        <v>833.7746071478</v>
       </c>
       <c r="E21" s="96">
-        <v>3621062.6775038806</v>
+        <v>4521737.6382463202</v>
       </c>
       <c r="F21" s="96">
         <v>0</v>
@@ -3049,13 +3054,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="96">
-        <v>123.90625</v>
+        <v>165.08382936460001</v>
       </c>
       <c r="D22" s="96">
-        <v>291.22892856869998</v>
+        <v>427.67851190099998</v>
       </c>
       <c r="E22" s="96">
-        <v>1931060.2247250369</v>
+        <v>2633216.6305364068</v>
       </c>
       <c r="F22" s="96">
         <v>0</v>
@@ -3075,13 +3080,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="96">
-        <v>128.10228174549999</v>
+        <v>790.79180555489995</v>
       </c>
       <c r="D23" s="96">
-        <v>339.25166666370001</v>
+        <v>4836.2267976160001</v>
       </c>
       <c r="E23" s="96">
-        <v>1999132.6820728134</v>
+        <v>17286368.69822238</v>
       </c>
       <c r="F23" s="96">
         <v>0</v>
@@ -3101,13 +3106,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="96">
-        <v>748.66458333349999</v>
+        <v>731.66458333349999</v>
       </c>
       <c r="D24" s="96">
-        <v>4813.7219583328997</v>
+        <v>4795.7219583328997</v>
       </c>
       <c r="E24" s="96">
-        <v>13993499.751331689</v>
+        <v>13810777.689331688</v>
       </c>
       <c r="F24" s="96">
         <v>0</v>
@@ -3127,13 +3132,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="96">
-        <v>151.11507936480001</v>
+        <v>266.02386904759999</v>
       </c>
       <c r="D25" s="96">
-        <v>563.25500000219995</v>
+        <v>745.76000000479996</v>
       </c>
       <c r="E25" s="96">
-        <v>3265458.2459612871</v>
+        <v>4425690.3579718489</v>
       </c>
       <c r="F25" s="96">
         <v>0</v>
@@ -3153,13 +3158,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="96">
-        <v>78.740436507300004</v>
+        <v>116.358075396</v>
       </c>
       <c r="D26" s="96">
-        <v>282.00000000040001</v>
+        <v>329.2370833343</v>
       </c>
       <c r="E26" s="96">
-        <v>1905347.2963424551</v>
+        <v>2299134.4748592312</v>
       </c>
       <c r="F26" s="96">
         <v>0</v>
@@ -3179,13 +3184,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="96">
-        <v>1334.5</v>
+        <v>1858.5</v>
       </c>
       <c r="D27" s="96">
-        <v>2577.1799999999998</v>
+        <v>9370.84</v>
       </c>
       <c r="E27" s="96">
-        <v>13136953.343350001</v>
+        <v>22612109.009</v>
       </c>
       <c r="F27" s="96">
         <v>0</v>
@@ -3205,13 +3210,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="96">
-        <v>224.8947354492</v>
+        <v>335.03509589909999</v>
       </c>
       <c r="D28" s="96">
-        <v>1004.4995833371</v>
+        <v>1431.6175520900999</v>
       </c>
       <c r="E28" s="96">
-        <v>4525419.7648018571</v>
+        <v>6604601.1312453747</v>
       </c>
       <c r="F28" s="96">
         <v>0</v>
@@ -3231,13 +3236,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="96">
-        <v>386.73</v>
+        <v>1070.0341666667</v>
       </c>
       <c r="D29" s="96">
-        <v>1523.5400000018999</v>
+        <v>2070.5600000021</v>
       </c>
       <c r="E29" s="96">
-        <v>7197381.3632933144</v>
+        <v>14993819.966923174</v>
       </c>
       <c r="F29" s="96">
         <v>0</v>
@@ -3257,13 +3262,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="96">
-        <v>73.557242063700002</v>
+        <v>94.954265873200001</v>
       </c>
       <c r="D30" s="96">
-        <v>290.52000000279997</v>
+        <v>328.6716666758</v>
       </c>
       <c r="E30" s="96">
-        <v>1342266.2312651528</v>
+        <v>1808557.8257932956</v>
       </c>
       <c r="F30" s="96">
         <v>0</v>
@@ -3283,13 +3288,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="96">
-        <v>90.458531745100004</v>
+        <v>129.67519841169999</v>
       </c>
       <c r="D31" s="96">
-        <v>283.59499999920001</v>
+        <v>329.79500000109999</v>
       </c>
       <c r="E31" s="96">
-        <v>1662817.6962441357</v>
+        <v>2246997.9859188953</v>
       </c>
       <c r="F31" s="96">
         <v>0</v>
@@ -3309,13 +3314,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="96">
-        <v>28.535912698600001</v>
+        <v>35.690277778000002</v>
       </c>
       <c r="D32" s="96">
-        <v>178.64666666860001</v>
+        <v>226.89916666760001</v>
       </c>
       <c r="E32" s="96">
-        <v>920475.59202497394</v>
+        <v>1134886.8601273343</v>
       </c>
       <c r="F32" s="96">
         <v>0</v>
@@ -3335,13 +3340,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="96">
-        <v>215.69446428559999</v>
+        <v>295.61113095220003</v>
       </c>
       <c r="D33" s="96">
-        <v>439.00999999959998</v>
+        <v>667.99600000179998</v>
       </c>
       <c r="E33" s="96">
-        <v>2806120.8392654946</v>
+        <v>4669958.7290065279</v>
       </c>
       <c r="F33" s="96">
         <v>0</v>
@@ -3355,19 +3360,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="96" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="B34" s="96">
         <v>1</v>
       </c>
       <c r="C34" s="96">
-        <v>-25</v>
+        <v>25.288194444399998</v>
       </c>
       <c r="D34" s="96">
-        <v>0</v>
+        <v>354.02</v>
       </c>
       <c r="E34" s="96">
-        <v>-233849</v>
+        <v>715253.15687714703</v>
       </c>
       <c r="F34" s="96">
         <v>0</v>
@@ -3381,19 +3386,19 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="96" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="B35" s="96">
         <v>1</v>
       </c>
       <c r="C35" s="96">
-        <v>186.83611111089999</v>
+        <v>-25</v>
       </c>
       <c r="D35" s="96">
-        <v>804.41601190910001</v>
+        <v>0</v>
       </c>
       <c r="E35" s="96">
-        <v>3880349.2779353959</v>
+        <v>-233849</v>
       </c>
       <c r="F35" s="96">
         <v>0</v>
@@ -3407,19 +3412,19 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="96" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="B36" s="96">
         <v>1</v>
       </c>
       <c r="C36" s="96">
-        <v>414.39123015899997</v>
+        <v>249.8000992058</v>
       </c>
       <c r="D36" s="96">
-        <v>2342.8888214259</v>
+        <v>1087.4160119085</v>
       </c>
       <c r="E36" s="96">
-        <v>7342359.2744361712</v>
+        <v>5027241.122842595</v>
       </c>
       <c r="F36" s="96">
         <v>0</v>
@@ -3433,19 +3438,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="96" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B37" s="96">
         <v>1</v>
       </c>
       <c r="C37" s="96">
-        <v>197.30909090899999</v>
+        <v>414.39123015899997</v>
       </c>
       <c r="D37" s="96">
-        <v>2277.9899999992999</v>
+        <v>2342.8888214259</v>
       </c>
       <c r="E37" s="96">
-        <v>4699575.8856638623</v>
+        <v>7342359.2744361712</v>
       </c>
       <c r="F37" s="96">
         <v>0</v>
@@ -3459,19 +3464,19 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="96" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B38" s="96">
         <v>1</v>
       </c>
       <c r="C38" s="96">
-        <v>283.9166666667</v>
+        <v>259.89242424230002</v>
       </c>
       <c r="D38" s="96">
-        <v>3082.25</v>
+        <v>2636.4299999988998</v>
       </c>
       <c r="E38" s="96">
-        <v>5825319.4707523696</v>
+        <v>5554944.6639294196</v>
       </c>
       <c r="F38" s="96">
         <v>0</v>
@@ -3485,19 +3490,19 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="96" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B39" s="96">
         <v>1</v>
       </c>
       <c r="C39" s="96">
-        <v>131.14181216910001</v>
+        <v>403.9166666667</v>
       </c>
       <c r="D39" s="96">
-        <v>471.4394986822</v>
+        <v>4611.43</v>
       </c>
       <c r="E39" s="96">
-        <v>3150944.560423614</v>
+        <v>8252554.4917521486</v>
       </c>
       <c r="F39" s="96">
         <v>0</v>
@@ -3511,19 +3516,19 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="96" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="B40" s="96">
         <v>1</v>
       </c>
       <c r="C40" s="96">
-        <v>548.43968253950004</v>
+        <v>319.48347883600002</v>
       </c>
       <c r="D40" s="96">
-        <v>4046.0241666669999</v>
+        <v>1582.4444986829001</v>
       </c>
       <c r="E40" s="96">
-        <v>7402539.5016198214</v>
+        <v>4507114.506957056</v>
       </c>
       <c r="F40" s="96">
         <v>0</v>
@@ -3537,19 +3542,19 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="96" t="s">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="B41" s="96">
         <v>1</v>
       </c>
       <c r="C41" s="96">
-        <v>6</v>
+        <v>548.18968253950004</v>
       </c>
       <c r="D41" s="96">
-        <v>81</v>
+        <v>4043.0241666669999</v>
       </c>
       <c r="E41" s="96">
-        <v>149294.68419999999</v>
+        <v>7398936.6723073218</v>
       </c>
       <c r="F41" s="96">
         <v>0</v>
@@ -3563,19 +3568,19 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="96" t="s">
-        <v>145</v>
+        <v>217</v>
       </c>
       <c r="B42" s="96">
         <v>1</v>
       </c>
       <c r="C42" s="96">
-        <v>-6.2142857142999999</v>
+        <v>11</v>
       </c>
       <c r="D42" s="96">
-        <v>-6.2810714286999998</v>
+        <v>126.04</v>
       </c>
       <c r="E42" s="96">
-        <v>-275260.76904147147</v>
+        <v>280769.63740000001</v>
       </c>
       <c r="F42" s="96">
         <v>0</v>
@@ -3589,19 +3594,19 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B43" s="96">
         <v>1</v>
       </c>
       <c r="C43" s="96">
-        <v>-3.2847222223000001</v>
+        <v>-6.2142857142999999</v>
       </c>
       <c r="D43" s="96">
-        <v>-20.505000001599999</v>
+        <v>-6.2810714286999998</v>
       </c>
       <c r="E43" s="96">
-        <v>-402349.89063324447</v>
+        <v>-275260.76904147147</v>
       </c>
       <c r="F43" s="96">
         <v>0</v>
@@ -3615,19 +3620,19 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="96" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B44" s="96">
         <v>1</v>
       </c>
       <c r="C44" s="96">
-        <v>184.42559523840001</v>
+        <v>-3.2847222223000001</v>
       </c>
       <c r="D44" s="96">
-        <v>2016.0000000025</v>
+        <v>-20.505000001599999</v>
       </c>
       <c r="E44" s="96">
-        <v>3629491.4663937623</v>
+        <v>-402349.89063324447</v>
       </c>
       <c r="F44" s="96">
         <v>0</v>
@@ -3636,6 +3641,58 @@
         <v>0</v>
       </c>
       <c r="H44" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="96" t="s">
+        <v>156</v>
+      </c>
+      <c r="B45" s="96">
+        <v>1</v>
+      </c>
+      <c r="C45" s="96">
+        <v>217.31500000029999</v>
+      </c>
+      <c r="D45" s="96">
+        <v>2178.0000000025002</v>
+      </c>
+      <c r="E45" s="96">
+        <v>4246358.1772271991</v>
+      </c>
+      <c r="F45" s="96">
+        <v>0</v>
+      </c>
+      <c r="G45" s="96">
+        <v>0</v>
+      </c>
+      <c r="H45" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="96" t="s">
+        <v>232</v>
+      </c>
+      <c r="B46" s="96">
+        <v>1</v>
+      </c>
+      <c r="C46" s="96">
+        <v>101.875</v>
+      </c>
+      <c r="D46" s="96">
+        <v>-24.9999999996</v>
+      </c>
+      <c r="E46" s="96">
+        <v>136464.048396092</v>
+      </c>
+      <c r="F46" s="96">
+        <v>0</v>
+      </c>
+      <c r="G46" s="96">
+        <v>0</v>
+      </c>
+      <c r="H46" s="96">
         <v>0</v>
       </c>
     </row>
@@ -3716,44 +3773,44 @@
       </c>
       <c r="D2" s="59">
         <f>IFERROR(+VLOOKUP(B2,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10180781.322442733</v>
+      </c>
+      <c r="E2" s="59">
         <v>6538018.3834050605</v>
-      </c>
-      <c r="E2" s="59">
-        <v>4682028.2206923608</v>
       </c>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>1855990.1627126997</v>
+        <v>3642762.9390376722</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G41" si="1">+D2/C2</f>
-        <v>0.20254663591143432</v>
+        <v>0.31539877786895837</v>
       </c>
       <c r="H2" s="59">
         <f>+D2/$N$3*$N$4</f>
-        <v>52304147.067240477</v>
+        <v>61084687.934656397</v>
       </c>
       <c r="I2" s="60">
         <f t="shared" ref="I2:I41" si="2">+H2/C2</f>
-        <v>1.6203730872914743</v>
+        <v>1.8923926672137501</v>
       </c>
       <c r="J2" s="59">
         <f>+D2/$N$3</f>
-        <v>2179339.46113502</v>
+        <v>2545195.3306106832</v>
       </c>
       <c r="K2" s="59">
         <f t="shared" ref="K2:K41" si="3">+(C2-D2)/$N$2</f>
-        <v>1225764.6788021759</v>
+        <v>1104914.765790401</v>
       </c>
       <c r="L2" s="61" cm="1">
         <f t="array" ref="L2">+_xlfn.IFS(I2&gt;114%,H2*0.02,I2&gt;109%,H2*0.015,I2&gt;104%,H2*0.0125,I2&gt;99%,H2*0.01,I2&lt;99%,H2*0)</f>
-        <v>1046082.9413448096</v>
+        <v>1221693.7586931279</v>
       </c>
       <c r="M2" s="53" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3766,45 +3823,45 @@
       </c>
       <c r="D3" s="4">
         <f>IFERROR(+VLOOKUP(B3,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6362623.1530077159</v>
+      </c>
+      <c r="E3" s="4">
         <v>5092283.3348378455</v>
-      </c>
-      <c r="E3" s="4">
-        <v>2774896.9225576972</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="0"/>
-        <v>2317386.4122801484</v>
+        <v>1270339.8181698704</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
-        <v>0.16435877774987445</v>
+        <v>0.20536032580062649</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H41" si="4">+D3/$N$3*$N$4</f>
-        <v>40738266.678702764</v>
+        <v>38175738.918046296</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="2"/>
-        <v>1.3148702219989956</v>
+        <v>1.2321619548037588</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J41" si="5">+D3/$N$3</f>
-        <v>1697427.7782792819</v>
+        <v>1590655.788251929</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="3"/>
-        <v>1232878.3259069242</v>
+        <v>1231005.251293777</v>
       </c>
       <c r="L3" s="63" cm="1">
         <f t="array" ref="L3">+_xlfn.IFS(I3&gt;114%,H3*0.02,I3&gt;109%,H3*0.015,I3&gt;104%,H3*0.0125,I3&gt;99%,H3*0.01,I3&lt;99%,H3*0)</f>
-        <v>814765.33357405534</v>
+        <v>763514.77836092596</v>
       </c>
       <c r="M3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="N3">
         <f>N4-N2</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3817,38 +3874,38 @@
       </c>
       <c r="D4" s="4">
         <f>IFERROR(+VLOOKUP(B4,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4655359.4802594241</v>
+      </c>
+      <c r="E4" s="4">
         <v>3799689.1529486589</v>
-      </c>
-      <c r="E4" s="4">
-        <v>2224929.6365325735</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>1574759.5164160854</v>
+        <v>855670.32731076516</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>0.13383885062086462</v>
+        <v>0.16397866693420166</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="4"/>
-        <v>30397513.223589271</v>
+        <v>27932156.881556544</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>1.070710804966917</v>
+        <v>0.98387200160521004</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="5"/>
-        <v>1266563.0509828862</v>
+        <v>1163839.870064856</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>1170968.6717714092</v>
+        <v>1186733.5889944416</v>
       </c>
       <c r="L4" s="63" cm="1">
         <f t="array" ref="L4">+_xlfn.IFS(I4&gt;114%,H4*0.02,I4&gt;109%,H4*0.015,I4&gt;104%,H4*0.0125,I4&gt;99%,H4*0.01,I4&lt;99%,H4*0)</f>
-        <v>379968.9152948659</v>
+        <v>0</v>
       </c>
       <c r="M4" s="53" t="s">
         <v>47</v>
@@ -3867,38 +3924,38 @@
       </c>
       <c r="D5" s="4">
         <f>IFERROR(+VLOOKUP(B5,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5672001.5032034451</v>
+      </c>
+      <c r="E5" s="4">
         <v>4650179.1579327742</v>
-      </c>
-      <c r="E5" s="4">
-        <v>3752668.2666791501</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>897510.89125362411</v>
+        <v>1021822.345270671</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>0.16379619716940358</v>
+        <v>0.19978849093996473</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="4"/>
-        <v>37201433.263462193</v>
+        <v>34032009.019220673</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>1.3103695773552286</v>
+        <v>1.1987309456397885</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="5"/>
-        <v>1550059.7193109246</v>
+        <v>1418000.3758008613</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>1130469.1477245467</v>
+        <v>1135901.4878472404</v>
       </c>
       <c r="L5" s="63" cm="1">
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
-        <v>744028.66526924388</v>
+        <v>680640.18038441346</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3911,38 +3968,38 @@
       </c>
       <c r="D6" s="4">
         <f>IFERROR(+VLOOKUP(B6,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5810906.7980635744</v>
+      </c>
+      <c r="E6" s="4">
         <v>3454829.7358999122</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1763034.9919922091</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>1691794.7439077031</v>
+        <v>2356077.0621636622</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>0.14683455239533538</v>
+        <v>0.24697075223084025</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="4"/>
-        <v>27638637.887199298</v>
+        <v>34865440.788381442</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>1.1746764191626831</v>
+        <v>1.4818245133850414</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="5"/>
-        <v>1151609.9119666375</v>
+        <v>1452726.6995158936</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>955899.75245810545</v>
+        <v>885890.88697282749</v>
       </c>
       <c r="L6" s="63" cm="1">
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
-        <v>552772.75774398597</v>
+        <v>697308.81576762884</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3955,34 +4012,34 @@
       </c>
       <c r="D7" s="4">
         <f>IFERROR(+VLOOKUP(B7,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2938195.7767915935</v>
+      </c>
+      <c r="E7" s="4">
         <v>2229458.8498637299</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1244100.7657470268</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F8" si="6">+D7-E7</f>
-        <v>985358.08411670313</v>
+        <v>708736.92692786362</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>8.0364441623913901E-2</v>
+        <v>0.10591200774933836</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="4"/>
-        <v>17835670.798909839</v>
+        <v>17629174.660749562</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>0.64291553299131121</v>
+        <v>0.63547204649603017</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="5"/>
-        <v>743152.94995457667</v>
+        <v>734548.94419789838</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>1214876.103838132</v>
+        <v>1240183.0626836454</v>
       </c>
       <c r="L7" s="63" cm="1">
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
@@ -3999,38 +4056,38 @@
       </c>
       <c r="D8" s="4">
         <f>IFERROR(+VLOOKUP(B8,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6168952.3513542237</v>
+      </c>
+      <c r="E8" s="4">
         <v>4232380.5042614806</v>
-      </c>
-      <c r="E8" s="4">
-        <v>2332273.4502824824</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="6"/>
-        <v>1900107.0539789982</v>
+        <v>1936571.847092743</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>0.11812040044839839</v>
+        <v>0.17216767758838331</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="4"/>
-        <v>33859044.034091845</v>
+        <v>37013714.108125344</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>0.94496320358718711</v>
+        <v>1.0330060655302999</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="5"/>
-        <v>1410793.5014204935</v>
+        <v>1542238.0878385559</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="3"/>
-        <v>1504699.5672693441</v>
+        <v>1483105.9532781742</v>
       </c>
       <c r="L8" s="63" cm="1">
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
-        <v>0</v>
+        <v>370137.14108125347</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4043,38 +4100,38 @@
       </c>
       <c r="D9" s="4">
         <f>IFERROR(+VLOOKUP(B9,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6899879.8473196756</v>
+      </c>
+      <c r="E9" s="4">
         <v>5960130.3637676956</v>
-      </c>
-      <c r="E9" s="4">
-        <v>4892925.4103550436</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>1067204.953412652</v>
+        <v>939749.48355198</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>0.16633971935747391</v>
+        <v>0.19256694188781318</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="4"/>
-        <v>47681042.910141565</v>
+        <v>41399279.08391805</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>1.3307177548597913</v>
+        <v>1.155401651326879</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="5"/>
-        <v>1986710.1212558986</v>
+        <v>1724969.9618299189</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>1422425.7644357148</v>
+        <v>1446559.5784799014</v>
       </c>
       <c r="L9" s="63" cm="1">
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
-        <v>953620.85820283135</v>
+        <v>827985.58167836105</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4085,34 +4142,34 @@
       </c>
       <c r="D10" s="64">
         <f>+SUM(D2:D9)</f>
+        <v>48688700.232442394</v>
+      </c>
+      <c r="E10" s="65">
         <v>35956969.48291716</v>
-      </c>
-      <c r="E10" s="65">
-        <v>23666857.664838541</v>
       </c>
       <c r="F10" s="64">
         <f>+SUM(F2:F9)</f>
-        <v>12290111.818078615</v>
+        <v>12731730.749525227</v>
       </c>
       <c r="G10" s="66">
         <f t="shared" si="1"/>
-        <v>0.14798654141378115</v>
+        <v>0.2003859740391824</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="4"/>
-        <v>287655755.86333728</v>
+        <v>292132201.39465439</v>
       </c>
       <c r="I10" s="66">
         <f t="shared" si="2"/>
-        <v>1.1838923313102492</v>
+        <v>1.2023158442350945</v>
       </c>
       <c r="J10" s="64">
         <f t="shared" si="5"/>
-        <v>11985656.494305721</v>
+        <v>12172175.058110598</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
-        <v>9857982.0122063495</v>
+        <v>9714294.5753404051</v>
       </c>
       <c r="L10" s="68"/>
     </row>
@@ -4128,38 +4185,38 @@
       </c>
       <c r="D11" s="59">
         <f>IFERROR(+VLOOKUP(B11,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>21714287.032106198</v>
+      </c>
+      <c r="E11" s="59">
         <v>18543635.055367131</v>
-      </c>
-      <c r="E11" s="59">
-        <v>7023074.0484903501</v>
       </c>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F16" si="7">+D11-E11</f>
-        <v>11520561.006876782</v>
+        <v>3170651.9767390676</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
-        <v>0.19122679647058316</v>
+        <v>0.22392338580835955</v>
       </c>
       <c r="H11" s="59">
         <f t="shared" si="4"/>
-        <v>148349080.44293705</v>
+        <v>130285722.19263719</v>
       </c>
       <c r="I11" s="60">
         <f t="shared" si="2"/>
-        <v>1.5298143717646653</v>
+        <v>1.3435403148501575</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="5"/>
-        <v>6181211.6851223772</v>
+        <v>5428571.7580265496</v>
       </c>
       <c r="K11" s="59">
         <f t="shared" si="3"/>
-        <v>3734681.5916557326</v>
+        <v>3762883.0724015655</v>
       </c>
       <c r="L11" s="61" cm="1">
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
-        <v>1854363.5055367132</v>
+        <v>1628571.5274079649</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4175,11 +4232,11 @@
         <v>7342359.2744361712</v>
       </c>
       <c r="E12" s="4">
-        <v>7395442.6965926401</v>
+        <v>7342359.2744361712</v>
       </c>
       <c r="F12" s="4">
         <f t="shared" si="7"/>
-        <v>-53083.422156468965</v>
+        <v>0</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
@@ -4187,23 +4244,23 @@
       </c>
       <c r="H12" s="4">
         <f t="shared" si="4"/>
-        <v>58738874.195489362</v>
+        <v>44054155.646617025</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>1.8570091183860868</v>
+        <v>1.3927568387895652</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="5"/>
-        <v>2447453.0914787236</v>
+        <v>1835589.8186090428</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>1156597.2921014682</v>
+        <v>1214427.1567065415</v>
       </c>
       <c r="L12" s="63" cm="1">
         <f t="array" ref="L12">+_xlfn.IFS(I12&gt;114%,H12*0.02,I12&gt;109%,H12*0.015,I12&gt;104%,H12*0.0125,I12&gt;99%,H12*0.01,I12&lt;99%,H12*0)</f>
-        <v>1174777.4839097874</v>
+        <v>881083.11293234047</v>
       </c>
       <c r="M12" s="27"/>
     </row>
@@ -4217,38 +4274,38 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>38609317.055148289</v>
+      </c>
+      <c r="E13" s="4">
         <v>35677866.984969728</v>
-      </c>
-      <c r="E13" s="4">
-        <v>27711765.916719597</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="7"/>
-        <v>7966101.0682501309</v>
+        <v>2931450.0701785609</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>0.27794311731832977</v>
+        <v>0.30078014317281015</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>285422935.87975782</v>
+        <v>231655902.33088973</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>2.2235449385466382</v>
+        <v>1.8046808590368608</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>11892622.328323243</v>
+        <v>9652329.2637870722</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>4413621.3852216788</v>
+        <v>4487729.9509738348</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;114%,H13*0.0125,I13&gt;109%,H13*0.01,I13&gt;104%,H13*0.0075,I13&gt;99%,H13*0.005,I13&lt;99%,H13*0)</f>
-        <v>3567786.6984969731</v>
+        <v>2895698.7791361217</v>
       </c>
       <c r="M13" s="53" t="s">
         <v>61</v>
@@ -4267,34 +4324,34 @@
       </c>
       <c r="D14" s="4">
         <f>IFERROR(+VLOOKUP(B14,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5554944.6639294196</v>
+      </c>
+      <c r="E14" s="4">
         <v>4699575.8856638623</v>
-      </c>
-      <c r="E14" s="4">
-        <v>968840.97419863928</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="7"/>
-        <v>3730734.9114652229</v>
+        <v>855368.77826555725</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.11071095977316531</v>
+        <v>0.13086143732809949</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="4"/>
-        <v>37596607.085310899</v>
+        <v>33329667.983576518</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0.88568767818532246</v>
+        <v>0.78516862396859699</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="5"/>
-        <v>1566525.2952212875</v>
+        <v>1388736.1659823549</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>1797594.3575862448</v>
+        <v>1844705.6365522791</v>
       </c>
       <c r="L14" s="63" cm="1">
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
@@ -4312,38 +4369,38 @@
       </c>
       <c r="D15" s="4">
         <f>IFERROR(+VLOOKUP(B15,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8252554.4917521486</v>
+      </c>
+      <c r="E15" s="4">
         <v>5825319.4707523696</v>
-      </c>
-      <c r="E15" s="4">
-        <v>1445131.6450023698</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="7"/>
-        <v>4380187.8257499998</v>
+        <v>2427235.020999779</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.13723083216076207</v>
+        <v>0.1944107831409482</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="4"/>
-        <v>46602555.766018957</v>
+        <v>49515326.950512893</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>1.0978466572860965</v>
+        <v>1.1664646988456893</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="5"/>
-        <v>1941773.1569174565</v>
+        <v>2063138.6229380372</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>1743987.5202010777</v>
+        <v>1709825.1451611426</v>
       </c>
       <c r="L15" s="63" cm="1">
         <f t="array" ref="L15">+_xlfn.IFS(I15&gt;109%,H15*0.015,I15&gt;104%,H15*0.0125,I15&gt;99%,H15*0.01,I15&lt;99%,H15*0)</f>
-        <v>699038.3364902843</v>
+        <v>742729.90425769333</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4354,34 +4411,34 @@
       </c>
       <c r="D16" s="64">
         <f>+SUM(D11:D15)</f>
+        <v>81473462.517372221</v>
+      </c>
+      <c r="E16" s="65">
         <v>72088756.671189263</v>
-      </c>
-      <c r="E16" s="65">
-        <v>44544255.281003602</v>
       </c>
       <c r="F16" s="64">
         <f t="shared" si="7"/>
-        <v>27544501.390185662</v>
+        <v>9384705.8461829573</v>
       </c>
       <c r="G16" s="66">
         <f t="shared" si="1"/>
-        <v>0.21086914894994976</v>
+        <v>0.23832065493106369</v>
       </c>
       <c r="H16" s="64">
         <f t="shared" si="4"/>
-        <v>576710053.36951411</v>
+        <v>488840775.10423332</v>
       </c>
       <c r="I16" s="66">
         <f t="shared" si="2"/>
-        <v>1.6869531915995981</v>
+        <v>1.4299239295863821</v>
       </c>
       <c r="J16" s="64">
         <f t="shared" si="5"/>
-        <v>24029585.557063088</v>
+        <v>20368365.629343055</v>
       </c>
       <c r="K16" s="67">
         <f t="shared" si="3"/>
-        <v>12846482.146766203</v>
+        <v>13019570.961795364</v>
       </c>
       <c r="L16" s="68"/>
     </row>
@@ -4397,34 +4454,34 @@
       </c>
       <c r="D17" s="59">
         <f>IFERROR(+VLOOKUP(B17,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3831780.4656781647</v>
+      </c>
+      <c r="E17" s="59">
         <v>3490474.4748070529</v>
-      </c>
-      <c r="E17" s="59">
-        <v>1647814.3144255385</v>
       </c>
       <c r="F17" s="59">
         <f t="shared" ref="F17:F40" si="8">+D17-E17</f>
-        <v>1842660.1603815143</v>
+        <v>341305.99087111186</v>
       </c>
       <c r="G17" s="60">
         <f t="shared" si="1"/>
-        <v>0.11897444670744077</v>
+        <v>0.13060802022729012</v>
       </c>
       <c r="H17" s="59">
         <f t="shared" si="4"/>
-        <v>27923795.798456423</v>
+        <v>22990682.794068988</v>
       </c>
       <c r="I17" s="60">
         <f t="shared" si="2"/>
-        <v>0.95179557365952616</v>
+        <v>0.78364812136374074</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" si="5"/>
-        <v>1163491.491602351</v>
+        <v>957945.11641954118</v>
       </c>
       <c r="K17" s="59">
         <f t="shared" si="3"/>
-        <v>1230835.4122710929</v>
+        <v>1275311.8833410919</v>
       </c>
       <c r="L17" s="61" cm="1">
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
@@ -4441,34 +4498,34 @@
       </c>
       <c r="D18" s="4">
         <f>IFERROR(+VLOOKUP(B18,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3383340.6159000443</v>
+      </c>
+      <c r="E18" s="4">
         <v>2539362.2668490014</v>
-      </c>
-      <c r="E18" s="4">
-        <v>1318807.9914469167</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="8"/>
-        <v>1220554.2754020847</v>
+        <v>843978.34905104293</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.10173928430406153</v>
+        <v>0.13555318881132356</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="4"/>
-        <v>20314898.134792011</v>
+        <v>20300043.695400268</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0.8139142744324922</v>
+        <v>0.81331913286794133</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="5"/>
-        <v>846454.08894966717</v>
+        <v>845835.15397501108</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>1067625.8872929048</v>
+        <v>1078808.264204998</v>
       </c>
       <c r="L18" s="63" cm="1">
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
@@ -4485,34 +4542,34 @@
       </c>
       <c r="D19" s="4">
         <f>IFERROR(+VLOOKUP(B19,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4172472.7522102422</v>
+      </c>
+      <c r="E19" s="4">
         <v>3126324.9965506792</v>
-      </c>
-      <c r="E19" s="4">
-        <v>1974051.5620993127</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="8"/>
-        <v>1152273.4344513665</v>
+        <v>1046147.755659563</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.12090990041401692</v>
+        <v>0.16136942432618312</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="4"/>
-        <v>25010599.972405434</v>
+        <v>25034836.513261452</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>0.96727920331213535</v>
+        <v>0.96821654595709861</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="5"/>
-        <v>1042108.3321835598</v>
+        <v>1043118.1880525606</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
-        <v>1082396.4366166343</v>
+        <v>1084208.8706644881</v>
       </c>
       <c r="L19" s="63" cm="1">
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
@@ -4529,38 +4586,38 @@
       </c>
       <c r="D20" s="4">
         <f>IFERROR(+VLOOKUP(B20,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8068602.606727235</v>
+      </c>
+      <c r="E20" s="4">
         <v>5313079.7996425815</v>
-      </c>
-      <c r="E20" s="4">
-        <v>3804498.4929125779</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="8"/>
-        <v>1508581.3067300036</v>
+        <v>2755522.8070846535</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.15837186155063132</v>
+        <v>0.24050826698022318</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="4"/>
-        <v>42504638.397140652</v>
+        <v>48411615.64036341</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>1.2669748924050506</v>
+        <v>1.4430496018813392</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="5"/>
-        <v>1771026.5998808604</v>
+        <v>2017150.6516818088</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>1344526.2000170199</v>
+        <v>1273976.3696636383</v>
       </c>
       <c r="L20" s="63" cm="1">
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
-        <v>850092.76794281311</v>
+        <v>968232.31280726823</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4573,38 +4630,38 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4521737.6382463202</v>
+      </c>
+      <c r="E21" s="4">
         <v>3621062.6775038806</v>
-      </c>
-      <c r="E21" s="4">
-        <v>2482567.9113498144</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" ref="F21:F23" si="9">+D21-E21</f>
-        <v>1138494.7661540662</v>
+        <v>900674.96074243961</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.14223388083214142</v>
+        <v>0.17761202985745514</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>28968501.420031041</v>
+        <v>27130425.829477921</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>1.1378710466571311</v>
+        <v>1.0656721791447308</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>1207020.8925012934</v>
+        <v>1130434.40956158</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1039878.4439283867</v>
+        <v>1046838.618087684</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
-        <v>434527.52130046563</v>
+        <v>339130.32286847406</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4617,38 +4674,38 @@
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6604601.1312453747</v>
+      </c>
+      <c r="E22" s="4">
         <v>4525419.7648018571</v>
-      </c>
-      <c r="E22" s="4">
-        <v>3717567.9331198842</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>807851.83168197284</v>
+        <v>2079181.3664435176</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.14256483062156253</v>
+        <v>0.20806552552815036</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>36203358.118414856</v>
+        <v>39627606.787472248</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>1.1405186449725002</v>
+        <v>1.2483931531689021</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>1508473.2549339524</v>
+        <v>1651150.2828113437</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>1296070.0207237212</v>
+        <v>1256914.4534377314</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
-        <v>724067.16236829711</v>
+        <v>792552.13574944495</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4661,38 +4718,38 @@
       </c>
       <c r="D23" s="4">
         <f>IFERROR(+VLOOKUP(B23,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5027241.122842595</v>
+      </c>
+      <c r="E23" s="4">
         <v>3880349.2779353959</v>
-      </c>
-      <c r="E23" s="4">
-        <v>2007902.2622231084</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="9"/>
-        <v>1872447.0157122875</v>
+        <v>1146891.844907199</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.1414330399034098</v>
+        <v>0.18323556551315615</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>31042794.223483168</v>
+        <v>30163446.73705557</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>1.1314643192272784</v>
+        <v>1.0994133930789369</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="5"/>
-        <v>1293449.7593117987</v>
+        <v>1256810.2807106487</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>1121695.0929554575</v>
+        <v>1120435.2553578704</v>
       </c>
       <c r="L23" s="63" cm="1">
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
-        <v>465641.9133522475</v>
+        <v>452451.70105583355</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4705,34 +4762,34 @@
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4507114.506957056</v>
+      </c>
+      <c r="E24" s="4">
         <v>3150944.560423614</v>
-      </c>
-      <c r="E24" s="4">
-        <v>2373341.2642009868</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>777603.29622262716</v>
+        <v>1356169.946533442</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>9.407474133614499E-2</v>
+        <v>0.13456461174847464</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>25207556.483388916</v>
+        <v>27042687.041742336</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>0.75259793068916003</v>
+        <v>0.80738767049084792</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>1050314.8534745381</v>
+        <v>1126778.626739264</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>1444910.020932209</v>
+        <v>1449347.0246521472</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
@@ -4749,38 +4806,38 @@
       </c>
       <c r="D25" s="4">
         <f>IFERROR(+VLOOKUP(B25,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7398936.6723073218</v>
+      </c>
+      <c r="E25" s="4">
         <v>7402539.5016198214</v>
-      </c>
-      <c r="E25" s="4">
-        <v>-2433547.0814999999</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="8"/>
-        <v>9836086.5831198208</v>
+        <v>-3602.8293124996126</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.13691937400008347</v>
+        <v>0.13685273509407175</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>59220316.012958571</v>
+        <v>44393620.033843935</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>1.0953549920006678</v>
+        <v>0.82111641056443052</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="5"/>
-        <v>2467513.1672066073</v>
+        <v>1849734.1680768305</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>2222019.6839704849</v>
+        <v>2333300.8096346343</v>
       </c>
       <c r="L25" s="63" cm="1">
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;109%,H25*0.015,I25&gt;104%,H25*0.0125,I25&gt;99%,H25*0.01,I25&lt;99%,H25*0)</f>
-        <v>888304.74019437854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4791,34 +4848,34 @@
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
+        <v>47515827.512114353</v>
+      </c>
+      <c r="E26" s="65">
         <v>37049557.32013388</v>
-      </c>
-      <c r="E26" s="65">
-        <v>16893004.650278136</v>
       </c>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>20156552.669855744</v>
+        <v>10466270.191980474</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>0.12958982569357178</v>
+        <v>0.16619814784222828</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>296396458.56107104</v>
+        <v>285094965.07268614</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>1.0367186055485742</v>
+        <v>0.99718888705336972</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>12349852.440044627</v>
+        <v>11878956.878028588</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>11849957.198707912</v>
+        <v>11919141.549044285</v>
       </c>
       <c r="L26" s="68"/>
     </row>
@@ -4834,38 +4891,38 @@
       </c>
       <c r="D27" s="59">
         <f>IFERROR(+VLOOKUP(B27,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>14993819.966923174</v>
+      </c>
+      <c r="E27" s="59">
         <v>7197381.3632933144</v>
-      </c>
-      <c r="E27" s="59">
-        <v>5151540.6591492426</v>
       </c>
       <c r="F27" s="59">
         <f t="shared" si="8"/>
-        <v>2045840.7041440718</v>
+        <v>7796438.6036298592</v>
       </c>
       <c r="G27" s="60">
         <f t="shared" si="1"/>
-        <v>8.7796819907039525E-2</v>
+        <v>0.1829012032165232</v>
       </c>
       <c r="H27" s="59">
         <f t="shared" si="4"/>
-        <v>57579050.906346515</v>
+        <v>89962919.801539034</v>
       </c>
       <c r="I27" s="60">
         <f t="shared" si="2"/>
-        <v>0.7023745592563162</v>
+        <v>1.0974072192991391</v>
       </c>
       <c r="J27" s="59">
         <f t="shared" si="5"/>
-        <v>2399127.1210977715</v>
+        <v>3748454.9917307934</v>
       </c>
       <c r="K27" s="59">
         <f t="shared" si="3"/>
-        <v>3560967.5541288895</v>
+        <v>3349194.0016538412</v>
       </c>
       <c r="L27" s="61" cm="1">
         <f t="array" ref="L27">+_xlfn.IFS(I27&gt;114%,H27*0.0125,I27&gt;109%,H27*0.01,I27&gt;104%,H27*0.0075,I27&gt;99%,H27*0.005,I27&lt;99%,H27*0)</f>
-        <v>0</v>
+        <v>899629.19801539031</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4878,34 +4935,34 @@
       </c>
       <c r="D28" s="4">
         <f>IFERROR(+VLOOKUP(B28,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2246997.9859188953</v>
+      </c>
+      <c r="E28" s="4">
         <v>1662817.6962441357</v>
-      </c>
-      <c r="E28" s="4">
-        <v>1127867.2813395613</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>534950.4149045744</v>
+        <v>584180.28967475961</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>7.9181795059244553E-2</v>
+        <v>0.10699990409137597</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
-        <v>13302541.569953088</v>
+        <v>13481987.915513372</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>0.63345436047395653</v>
+        <v>0.64199942454825576</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="5"/>
-        <v>554272.56541471195</v>
+        <v>561749.49647972384</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>920818.2049407555</v>
+        <v>937650.10070405528</v>
       </c>
       <c r="L28" s="63" cm="1">
         <f t="array" ref="L28">+_xlfn.IFS(I28&gt;114%,H28*0.02,I28&gt;109%,H28*0.015,I28&gt;104%,H28*0.0125,I28&gt;99%,H28*0.01,I28&lt;99%,H28*0)</f>
@@ -4922,34 +4979,34 @@
       </c>
       <c r="D29" s="4">
         <f>IFERROR(+VLOOKUP(B29,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2863924.6281832345</v>
+      </c>
+      <c r="E29" s="4">
         <v>2237337.654012111</v>
-      </c>
-      <c r="E29" s="4">
-        <v>3336344.5485263281</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="8"/>
-        <v>-1099006.894514217</v>
+        <v>626586.97417112347</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>8.6921667852077181E-2</v>
+        <v>0.11126487986197331</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
-        <v>17898701.232096888</v>
+        <v>17183547.769099407</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>0.69537334281661745</v>
+        <v>0.66758927917183986</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="5"/>
-        <v>745779.21800403704</v>
+        <v>715981.15704580862</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>1119160.1117137091</v>
+        <v>1143788.7685908382</v>
       </c>
       <c r="L29" s="63" cm="1">
         <f t="array" ref="L29">+_xlfn.IFS(I29&gt;114%,H29*0.02,I29&gt;109%,H29*0.015,I29&gt;104%,H29*0.0125,I29&gt;99%,H29*0.01,I29&lt;99%,H29*0)</f>
@@ -4967,34 +5024,34 @@
       </c>
       <c r="D30" s="4">
         <f>IFERROR(+VLOOKUP(B30,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4669958.7290065279</v>
+      </c>
+      <c r="E30" s="4">
         <v>2806120.8392654946</v>
-      </c>
-      <c r="E30" s="4">
-        <v>1465987.5738126547</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="8"/>
-        <v>1340133.2654528399</v>
+        <v>1863837.8897410333</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>7.3394862686401677E-2</v>
+        <v>0.12214405554833929</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="4"/>
-        <v>22448966.714123957</v>
+        <v>28019752.374039166</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>0.58715890149121341</v>
+        <v>0.73286433329003575</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="5"/>
-        <v>935373.61308849824</v>
+        <v>1167489.682251632</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>1687004.0129933418</v>
+        <v>1678162.3191559571</v>
       </c>
       <c r="L30" s="63" cm="1">
         <f t="array" ref="L30">+_xlfn.IFS(I30&gt;114%,H30*0.02,I30&gt;109%,H30*0.015,I30&gt;104%,H30*0.0125,I30&gt;99%,H30*0.01,I30&lt;99%,H30*0)</f>
@@ -5012,38 +5069,38 @@
       </c>
       <c r="D31" s="4">
         <f>IFERROR(+VLOOKUP(B31,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4425690.3579718489</v>
+      </c>
+      <c r="E31" s="4">
         <v>3265458.2459612871</v>
-      </c>
-      <c r="E31" s="4">
-        <v>2185400.7533588032</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="8"/>
-        <v>1080057.4926024838</v>
+        <v>1160232.1120105619</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>0.12848420715756434</v>
+        <v>0.17413522817882371</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="4"/>
-        <v>26123665.967690296</v>
+        <v>26554142.147831094</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>1.0278736572605147</v>
+        <v>1.0448113690729421</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="5"/>
-        <v>1088486.0819870958</v>
+        <v>1106422.5894929622</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>1054751.9882875578</v>
+        <v>1049477.9821014076</v>
       </c>
       <c r="L31" s="63" cm="1">
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
-        <v>261236.65967690296</v>
+        <v>331926.77684788872</v>
       </c>
       <c r="M31" s="27"/>
     </row>
@@ -5057,34 +5114,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2292259.0263364343</v>
+      </c>
+      <c r="E32" s="4">
         <v>1556471.8667402903</v>
-      </c>
-      <c r="E32" s="4">
-        <v>772280.47046408884</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="8"/>
-        <v>784191.39627620147</v>
+        <v>735787.15959614399</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>6.1764756616678185E-2</v>
+        <v>9.0962659775255333E-2</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>12451774.933922322</v>
+        <v>13753554.158018606</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.49411805293342548</v>
+        <v>0.54577595865153194</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>518823.95558009675</v>
+        <v>573064.75658410857</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1125882.2920599862</v>
+        <v>1145387.0486831781</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -5102,34 +5159,34 @@
       </c>
       <c r="D33" s="4">
         <f>IFERROR(+VLOOKUP(B33,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2299134.4748592312</v>
+      </c>
+      <c r="E33" s="4">
         <v>1905347.2963424551</v>
-      </c>
-      <c r="E33" s="4">
-        <v>1312962.2237802313</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="8"/>
-        <v>592385.07256222377</v>
+        <v>393787.17851677607</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>7.19087169687775E-2</v>
+        <v>8.6770433161019039E-2</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="4"/>
-        <v>15242778.370739641</v>
+        <v>13794806.849155387</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>0.57526973575022</v>
+        <v>0.52062259896611418</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="5"/>
-        <v>635115.76544748503</v>
+        <v>574783.61871480779</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>1171019.1763646449</v>
+        <v>1209880.7762570386</v>
       </c>
       <c r="L33" s="63" cm="1">
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
@@ -5146,34 +5203,34 @@
       </c>
       <c r="D34" s="4">
         <f>IFERROR(+VLOOKUP(B34,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1808557.8257932956</v>
+      </c>
+      <c r="E34" s="4">
         <v>1342266.2312651528</v>
-      </c>
-      <c r="E34" s="4">
-        <v>1012363.4850253685</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="8"/>
-        <v>329902.74623978429</v>
+        <v>466291.59452814283</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>6.3917439584054894E-2</v>
+        <v>8.6121801228252179E-2</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="4"/>
-        <v>10738129.850121222</v>
+        <v>10851346.954759773</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>0.51133951667243915</v>
+        <v>0.51673080736951305</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="5"/>
-        <v>447422.07708838425</v>
+        <v>452139.45644832391</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>936082.56041594502</v>
+        <v>959572.10871033522</v>
       </c>
       <c r="L34" s="63" cm="1">
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
@@ -5190,34 +5247,34 @@
       </c>
       <c r="D35" s="4">
         <f>IFERROR(+VLOOKUP(B35,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1134886.8601273343</v>
+      </c>
+      <c r="E35" s="4">
         <v>920475.59202497394</v>
-      </c>
-      <c r="E35" s="4">
-        <v>474208.7541035653</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="8"/>
-        <v>446266.83792140865</v>
+        <v>214411.26810236031</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>3.7329391116341579E-2</v>
+        <v>4.6024724437604296E-2</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="4"/>
-        <v>7363804.7361997925</v>
+        <v>6809321.160764005</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>0.29863512893073269</v>
+        <v>0.27614834662562576</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="5"/>
-        <v>306825.197341658</v>
+        <v>283721.71503183356</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>1130367.8289511916</v>
+        <v>1176165.6569936334</v>
       </c>
       <c r="L35" s="63" cm="1">
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.02,I35&gt;109%,H35*0.015,I35&gt;104%,H35*0.0125,I35&gt;99%,H35*0.01,I35&lt;99%,H35*0)</f>
@@ -5234,34 +5291,34 @@
       </c>
       <c r="D36" s="4">
         <f>IFERROR(+VLOOKUP(B36,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2633216.6305364068</v>
+      </c>
+      <c r="E36" s="4">
         <v>1931060.2247250369</v>
-      </c>
-      <c r="E36" s="4">
-        <v>1231155.9948169386</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="8"/>
-        <v>699904.22990809823</v>
+        <v>702156.40581136988</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>7.6523091924907347E-2</v>
+        <v>0.1043477959396238</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="4"/>
-        <v>15448481.797800295</v>
+        <v>15799299.78321844</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>0.61218473539925877</v>
+        <v>0.62608677563774284</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="5"/>
-        <v>643686.74157501233</v>
+        <v>658304.15763410169</v>
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>1109711.4178702363</v>
+        <v>1130089.1684731797</v>
       </c>
       <c r="L36" s="63" cm="1">
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;114%,H36*0.02,I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
@@ -5278,38 +5335,38 @@
       </c>
       <c r="D37" s="4">
         <f>IFERROR(+VLOOKUP(B37,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>17081843.43377829</v>
+      </c>
+      <c r="E37" s="4">
         <v>16463801.298558187</v>
-      </c>
-      <c r="E37" s="4">
-        <v>-974804.98299181263</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="8"/>
-        <v>17438606.281549998</v>
+        <v>618042.13522010297</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
-        <v>0.13493619506775525</v>
+        <v>0.14000162634974328</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="4"/>
-        <v>131710410.38846549</v>
+        <v>102491060.60266975</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>1.079489560542042</v>
+        <v>0.84000975809845979</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="5"/>
-        <v>5487933.7661860622</v>
+        <v>4270460.8584445724</v>
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>5026092.7953067524</v>
+        <v>5246495.3283110857</v>
       </c>
       <c r="L37" s="63" cm="1">
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.0125,I37&gt;109%,H37*0.01,I37&gt;104%,H37*0.0075,I37&gt;99%,H37*0.005,I37&lt;99%,H37*0)</f>
-        <v>987828.07791349117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -5322,34 +5379,34 @@
       </c>
       <c r="D38" s="4">
         <f>IFERROR(+VLOOKUP(B38,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>280769.63740000001</v>
+      </c>
+      <c r="E38" s="4">
         <v>149294.68419999999</v>
-      </c>
-      <c r="E38" s="4">
-        <v>0</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" ref="F38" si="10">+D38-E38</f>
-        <v>149294.68419999999</v>
+        <v>131474.95320000002</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="1"/>
-        <v>4.1819239271708684E-3</v>
+        <v>7.8646957254901971E-3</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="4"/>
-        <v>1194357.4735999999</v>
+        <v>1684617.8244</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="2"/>
-        <v>3.3455391417366948E-2</v>
+        <v>4.7188174352941176E-2</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="5"/>
-        <v>49764.894733333327</v>
+        <v>70192.409350000002</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>1692890.7293238097</v>
+        <v>1770961.51813</v>
       </c>
       <c r="L38" s="63" cm="1">
         <f t="array" ref="L38">+_xlfn.IFS(I38&gt;109%,H38*0.015,I38&gt;104%,H38*0.0125,I38&gt;99%,H38*0.01,I38&lt;99%,H38*0)</f>
@@ -5366,38 +5423,38 @@
       </c>
       <c r="D39" s="4">
         <f>IFERROR(+VLOOKUP(B39,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6167950.3247244535</v>
+      </c>
+      <c r="E39" s="4">
         <v>4713478.3902184051</v>
-      </c>
-      <c r="E39" s="4">
-        <v>3667023.6813626946</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="8"/>
-        <v>1046454.7088557105</v>
+        <v>1454471.9345060484</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>0.12962852900198119</v>
+        <v>0.16962893671276072</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="4"/>
-        <v>37707827.12174724</v>
+        <v>37007701.948346719</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>1.0370282320158495</v>
+        <v>1.0177736202765644</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="5"/>
-        <v>1571159.4634061351</v>
+        <v>1541987.5811811134</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>1507045.2070848378</v>
+        <v>1509673.8707137774</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
-        <v>377078.27121747239</v>
+        <v>370077.01948346721</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5408,34 +5465,34 @@
       </c>
       <c r="D40" s="67">
         <f>+SUM(D27:D39)</f>
+        <v>62899009.881559134</v>
+      </c>
+      <c r="E40" s="65">
         <v>46151311.382850848</v>
-      </c>
-      <c r="E40" s="65">
-        <v>20762330.442747667</v>
       </c>
       <c r="F40" s="67">
         <f t="shared" si="8"/>
-        <v>25388980.940103181</v>
+        <v>16747698.498708285</v>
       </c>
       <c r="G40" s="66">
         <f t="shared" si="1"/>
-        <v>9.0665390258040754E-2</v>
+        <v>0.12356665730358822</v>
       </c>
       <c r="H40" s="64">
         <f t="shared" si="4"/>
-        <v>369210491.06280679</v>
+        <v>377394059.2893548</v>
       </c>
       <c r="I40" s="66">
         <f t="shared" si="2"/>
-        <v>0.72532312206432603</v>
+        <v>0.74139994382152929</v>
       </c>
       <c r="J40" s="64">
         <f t="shared" si="5"/>
-        <v>15383770.460950283</v>
+        <v>15724752.470389783</v>
       </c>
       <c r="K40" s="67">
         <f t="shared" si="3"/>
-        <v>22041793.87944166</v>
+        <v>22306498.648478329</v>
       </c>
       <c r="L40" s="68"/>
     </row>
@@ -5449,34 +5506,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
+        <v>240577000.14348808</v>
+      </c>
+      <c r="E41" s="82">
         <v>191246594.85709113</v>
-      </c>
-      <c r="E41" s="82">
-        <v>105866448.03886795</v>
       </c>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>85380146.818223178</v>
+        <v>49330405.28639695</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>0.13860787688705689</v>
+        <v>0.17436058008072636</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1529972758.856729</v>
+        <v>1443462000.8609285</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>1.1088630150964551</v>
+        <v>1.046163480484358</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>63748864.952363707</v>
+        <v>60144250.03587202</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>56596216.773144998</v>
+        <v>56959507.347482398</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -5527,11 +5584,11 @@
         <v>-275260.76904147147</v>
       </c>
       <c r="E43" s="4">
-        <v>0</v>
+        <v>-275260.76904147147</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" ref="F43" si="11">+D43-E43</f>
-        <v>-275260.76904147147</v>
+        <v>0</v>
       </c>
       <c r="G43" s="5">
         <f>+D43/C43</f>
@@ -5539,19 +5596,19 @@
       </c>
       <c r="H43" s="4">
         <f t="shared" ref="H43" si="12">+D43/$N$3*$N$4</f>
-        <v>-2202086.1523317718</v>
+        <v>-1651564.614248829</v>
       </c>
       <c r="I43" s="5">
         <f>+H43/C43</f>
-        <v>-5.5052153808294292E-2</v>
+        <v>-4.1289115356220721E-2</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43" si="13">+D43/$N$3</f>
-        <v>-91753.589680490491</v>
+        <v>-68815.192260367869</v>
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>1917869.5604305463</v>
+        <v>2013763.0384520735</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
@@ -5570,11 +5627,11 @@
         <v>-402349.89063324447</v>
       </c>
       <c r="E44" s="4">
-        <v>-388379.73864699452</v>
+        <v>-402349.89063324447</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" ref="F44" si="14">+D44-E44</f>
-        <v>-13970.151986249955</v>
+        <v>0</v>
       </c>
       <c r="G44" s="5">
         <f>+D44/C44</f>
@@ -5582,19 +5639,19 @@
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>-3218799.1250659563</v>
+        <v>-2414099.3437994667</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>-0.10729330416886521</v>
+        <v>-8.0469978126648897E-2</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>-134116.6302110815</v>
+        <v>-100587.47265831112</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>1447730.9471730117</v>
+        <v>1520117.4945316622</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
@@ -5736,14 +5793,14 @@
       </c>
       <c r="D2" s="22">
         <f>H2/G2</f>
-        <v>0.22222222222222221</v>
+        <v>0.40277777777777779</v>
       </c>
       <c r="E2" s="13">
         <v>33</v>
       </c>
       <c r="F2" s="12">
         <f>+H2-E2</f>
-        <v>-17</v>
+        <v>-4</v>
       </c>
       <c r="G2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5751,11 +5808,11 @@
       </c>
       <c r="H2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I2" s="17">
         <f>(+G2*$M$2)-H2</f>
-        <v>45.199999999999996</v>
+        <v>32.199999999999996</v>
       </c>
       <c r="J2" t="s">
         <v>55</v>
@@ -5801,14 +5858,14 @@
       </c>
       <c r="D3" s="22">
         <f t="shared" ref="D3:D38" si="0">H3/G3</f>
-        <v>0.23012552301255229</v>
+        <v>0.22175732217573221</v>
       </c>
       <c r="E3" s="13">
         <v>1</v>
       </c>
       <c r="F3" s="12">
         <f t="shared" ref="F3:F38" si="1">+H3-E3</f>
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5816,11 +5873,11 @@
       </c>
       <c r="H3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I3" s="17">
         <f t="shared" ref="I3:I38" si="2">(+G3*$M$2)-H3</f>
-        <v>148.15</v>
+        <v>150.15</v>
       </c>
       <c r="J3" t="s">
         <v>56</v>
@@ -5839,14 +5896,14 @@
         <v>145 - ALMACEN</v>
       </c>
       <c r="S3" s="12">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T3" s="12">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U3" s="41">
         <f>+S3/T3</f>
-        <v>7.0422535211267609E-2</v>
+        <v>7.476635514018691E-2</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -5860,14 +5917,14 @@
       </c>
       <c r="D4" s="22">
         <f t="shared" si="0"/>
-        <v>0.25550660792951541</v>
+        <v>0.42290748898678415</v>
       </c>
       <c r="E4" s="13">
         <v>126</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" si="1"/>
-        <v>-68</v>
+        <v>-30</v>
       </c>
       <c r="G4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5875,11 +5932,11 @@
       </c>
       <c r="H4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>134.94999999999999</v>
+        <v>96.949999999999989</v>
       </c>
       <c r="J4" t="s">
         <v>57</v>
@@ -5897,14 +5954,14 @@
         <v>145 - Articulos Sin Asociar Agrupacion</v>
       </c>
       <c r="S4" s="13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T4" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U11" si="3">+S4/T4</f>
-        <v>3.2863849765258218E-2</v>
+        <v>5.6074766355140186E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -5918,14 +5975,14 @@
       </c>
       <c r="D5" s="22">
         <f t="shared" si="0"/>
-        <v>0.18461538461538463</v>
+        <v>0.29230769230769232</v>
       </c>
       <c r="E5" s="13">
         <v>21</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" si="1"/>
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5933,11 +5990,11 @@
       </c>
       <c r="H5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>43.25</v>
+        <v>36.25</v>
       </c>
       <c r="K5" t="s">
         <v>64</v>
@@ -5952,14 +6009,14 @@
         <v>145 - BEBIDAS</v>
       </c>
       <c r="S5" s="13">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T5" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="3"/>
-        <v>5.1643192488262914E-2</v>
+        <v>7.9439252336448593E-2</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -5973,14 +6030,14 @@
       </c>
       <c r="D6" s="22">
         <f t="shared" si="0"/>
-        <v>0.28502415458937197</v>
+        <v>0.42995169082125606</v>
       </c>
       <c r="E6" s="13">
         <v>100</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" si="1"/>
-        <v>-41</v>
+        <v>-11</v>
       </c>
       <c r="G6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5988,11 +6045,11 @@
       </c>
       <c r="H6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>116.94999999999999</v>
+        <v>86.949999999999989</v>
       </c>
       <c r="J6" t="s">
         <v>58</v>
@@ -6010,14 +6067,14 @@
         <v>145 - CHOCOLATE</v>
       </c>
       <c r="S6" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T6" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="3"/>
-        <v>3.2863849765258218E-2</v>
+        <v>5.1401869158878503E-2</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -6031,14 +6088,14 @@
       </c>
       <c r="D7" s="22">
         <f t="shared" si="0"/>
-        <v>0.20202020202020202</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="E7" s="13">
         <v>81</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>-41</v>
+        <v>-26</v>
       </c>
       <c r="G7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6046,11 +6103,11 @@
       </c>
       <c r="H7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>128.29999999999998</v>
+        <v>113.29999999999998</v>
       </c>
       <c r="J7" t="s">
         <v>58</v>
@@ -6068,14 +6125,14 @@
         <v>145 - GALLETITAS</v>
       </c>
       <c r="S7" s="13">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="T7" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="3"/>
-        <v>8.9201877934272297E-2</v>
+        <v>0.13551401869158877</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -6089,26 +6146,26 @@
       </c>
       <c r="D8" s="22">
         <f t="shared" si="0"/>
-        <v>0.22535211267605634</v>
+        <v>0.32242990654205606</v>
       </c>
       <c r="E8" s="13">
         <v>89</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>-41</v>
+        <v>-20</v>
       </c>
       <c r="G8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>133.04999999999998</v>
+        <v>112.9</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
@@ -6127,14 +6184,14 @@
         <v>145 - GOLOSINAS</v>
       </c>
       <c r="S8" s="13">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="T8" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="3"/>
-        <v>8.4507042253521125E-2</v>
+        <v>0.12149532710280374</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -6148,26 +6205,26 @@
       </c>
       <c r="D9" s="22">
         <f>H9/G9</f>
-        <v>0.21818181818181817</v>
+        <v>0.3592814371257485</v>
       </c>
       <c r="E9" s="13">
         <v>92</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>-56</v>
+        <v>-32</v>
       </c>
       <c r="G9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>104.25</v>
+        <v>81.949999999999989</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
@@ -6188,11 +6245,11 @@
         <v>7</v>
       </c>
       <c r="T9" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="3"/>
-        <v>3.2863849765258218E-2</v>
+        <v>3.2710280373831772E-2</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -6206,26 +6263,26 @@
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
-        <v>0.15979381443298968</v>
+        <v>0.28205128205128205</v>
       </c>
       <c r="E10" s="13">
         <v>64</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>-33</v>
+        <v>-9</v>
       </c>
       <c r="G10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>133.9</v>
+        <v>110.75</v>
       </c>
       <c r="J10" t="s">
         <v>58</v>
@@ -6243,14 +6300,14 @@
         <v>145 - NO PERECEDEROS</v>
       </c>
       <c r="S10" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
-        <v>9.3896713615023476E-3</v>
+        <v>1.4018691588785047E-2</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -6264,14 +6321,14 @@
       </c>
       <c r="D11" s="32">
         <f t="shared" si="0"/>
-        <v>7.9207920792079209E-2</v>
+        <v>0.13861386138613863</v>
       </c>
       <c r="E11" s="31">
         <v>19</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
-        <v>-11</v>
+        <v>-5</v>
       </c>
       <c r="G11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6279,11 +6336,11 @@
       </c>
       <c r="H11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I11" s="34">
         <f t="shared" si="2"/>
-        <v>77.849999999999994</v>
+        <v>71.849999999999994</v>
       </c>
       <c r="J11" t="s">
         <v>59</v>
@@ -6298,14 +6355,14 @@
         <v>145 - PILAS</v>
       </c>
       <c r="S11" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T11" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="3"/>
-        <v>1.4084507042253521E-2</v>
+        <v>1.8691588785046728E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -6319,14 +6376,14 @@
       </c>
       <c r="D12" s="32">
         <f t="shared" si="0"/>
-        <v>7.6190476190476197E-2</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="E12" s="31">
         <v>24</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="G12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6334,11 +6391,11 @@
       </c>
       <c r="H12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I12" s="34">
         <f t="shared" si="2"/>
-        <v>81.25</v>
+        <v>75.25</v>
       </c>
       <c r="J12" t="s">
         <v>59</v>
@@ -6355,14 +6412,14 @@
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
-        <v>0.20384615384615384</v>
+        <v>0.35</v>
       </c>
       <c r="E13" s="13">
         <v>144</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>-53</v>
       </c>
       <c r="G13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6370,11 +6427,11 @@
       </c>
       <c r="H13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="J13" t="s">
         <v>57</v>
@@ -6394,14 +6451,14 @@
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
-        <v>0.21978021978021978</v>
+        <v>0.31868131868131866</v>
       </c>
       <c r="E14" s="13">
         <v>85</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" si="1"/>
-        <v>-45</v>
+        <v>-27</v>
       </c>
       <c r="G14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6409,11 +6466,11 @@
       </c>
       <c r="H14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="2"/>
-        <v>114.69999999999999</v>
+        <v>96.699999999999989</v>
       </c>
       <c r="J14" t="s">
         <v>55</v>
@@ -6429,15 +6486,15 @@
       <c r="E15" s="14"/>
       <c r="F15" s="16">
         <f>+SUM(F2:F14)</f>
-        <v>-415</v>
+        <v>-177</v>
       </c>
       <c r="G15" s="8">
         <f>+SUM(G2:G14)</f>
-        <v>2228</v>
+        <v>2232</v>
       </c>
       <c r="H15" s="8">
         <f>+SUM(H2:H14)</f>
-        <v>464</v>
+        <v>702</v>
       </c>
       <c r="I15" s="8"/>
     </row>
@@ -6454,14 +6511,14 @@
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
-        <v>0.29813664596273293</v>
+        <v>0.40993788819875776</v>
       </c>
       <c r="E16" s="13">
         <v>90</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" si="1"/>
-        <v>-42</v>
+        <v>-24</v>
       </c>
       <c r="G16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6469,11 +6526,11 @@
       </c>
       <c r="H16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="2"/>
-        <v>88.85</v>
+        <v>70.849999999999994</v>
       </c>
       <c r="J16" t="s">
         <v>55</v>
@@ -6493,14 +6550,14 @@
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
-        <v>0.22277227722772278</v>
+        <v>0.28712871287128711</v>
       </c>
       <c r="E17" s="13">
         <v>92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="1"/>
-        <v>-47</v>
+        <v>-34</v>
       </c>
       <c r="G17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6508,11 +6565,11 @@
       </c>
       <c r="H17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>126.69999999999999</v>
+        <v>113.69999999999999</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -6532,14 +6589,14 @@
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.44117647058823528</v>
       </c>
       <c r="E18" s="13">
         <v>88</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="1"/>
-        <v>-37</v>
+        <v>-13</v>
       </c>
       <c r="G18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6547,11 +6604,11 @@
       </c>
       <c r="H18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>93.5</v>
+        <v>69.5</v>
       </c>
       <c r="J18" t="s">
         <v>58</v>
@@ -6571,14 +6628,14 @@
       </c>
       <c r="D19" s="22">
         <f t="shared" si="0"/>
-        <v>0.33750000000000002</v>
+        <v>0.51249999999999996</v>
       </c>
       <c r="E19" s="13">
         <v>95</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="1"/>
-        <v>-41</v>
+        <v>-13</v>
       </c>
       <c r="G19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6586,11 +6643,11 @@
       </c>
       <c r="H19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="2"/>
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="J19" t="s">
         <v>58</v>
@@ -6610,14 +6667,14 @@
       </c>
       <c r="D20" s="22">
         <f t="shared" si="0"/>
-        <v>0.2824858757062147</v>
+        <v>0.43502824858757061</v>
       </c>
       <c r="E20" s="13">
         <v>83</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="1"/>
-        <v>-33</v>
+        <v>-6</v>
       </c>
       <c r="G20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6625,11 +6682,11 @@
       </c>
       <c r="H20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>100.44999999999999</v>
+        <v>73.449999999999989</v>
       </c>
       <c r="J20" t="s">
         <v>55</v>
@@ -6649,14 +6706,14 @@
       </c>
       <c r="D21" s="22">
         <f t="shared" si="0"/>
-        <v>0.30769230769230771</v>
+        <v>0.42011834319526625</v>
       </c>
       <c r="E21" s="13">
         <v>64</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" si="1"/>
-        <v>-12</v>
+        <v>7</v>
       </c>
       <c r="G21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6664,11 +6721,11 @@
       </c>
       <c r="H21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="2"/>
-        <v>91.65</v>
+        <v>72.650000000000006</v>
       </c>
       <c r="J21" t="s">
         <v>58</v>
@@ -6688,14 +6745,14 @@
       </c>
       <c r="D22" s="22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.20707070707070707</v>
       </c>
       <c r="E22" s="13">
         <v>66</v>
       </c>
       <c r="F22" s="12">
         <f t="shared" si="1"/>
-        <v>-66</v>
+        <v>-25</v>
       </c>
       <c r="G22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6703,11 +6760,11 @@
       </c>
       <c r="H22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I22" s="17">
         <f t="shared" si="2"/>
-        <v>168.29999999999998</v>
+        <v>127.29999999999998</v>
       </c>
       <c r="J22" t="s">
         <v>58</v>
@@ -6727,14 +6784,14 @@
       </c>
       <c r="D23" s="22">
         <f t="shared" si="0"/>
-        <v>0.20289855072463769</v>
+        <v>0.39130434782608697</v>
       </c>
       <c r="E23" s="13">
         <v>70</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" si="1"/>
-        <v>-42</v>
+        <v>-16</v>
       </c>
       <c r="G23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6742,11 +6799,11 @@
       </c>
       <c r="H23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="I23" s="17">
         <f t="shared" si="2"/>
-        <v>89.3</v>
+        <v>63.3</v>
       </c>
       <c r="J23" t="s">
         <v>58</v>
@@ -6766,14 +6823,14 @@
       </c>
       <c r="D24" s="22">
         <f t="shared" si="0"/>
-        <v>0.22941176470588234</v>
+        <v>0.41764705882352943</v>
       </c>
       <c r="E24" s="13">
         <v>79</v>
       </c>
       <c r="F24" s="12">
         <f t="shared" si="1"/>
-        <v>-40</v>
+        <v>-8</v>
       </c>
       <c r="G24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6781,11 +6838,11 @@
       </c>
       <c r="H24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="I24" s="17">
         <f t="shared" si="2"/>
-        <v>105.5</v>
+        <v>73.5</v>
       </c>
       <c r="J24" t="s">
         <v>60</v>
@@ -6801,7 +6858,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="16">
         <f>+SUM(F16:F24)</f>
-        <v>-360</v>
+        <v>-132</v>
       </c>
       <c r="G25" s="8">
         <f>+SUM(G16:G24)</f>
@@ -6809,7 +6866,7 @@
       </c>
       <c r="H25" s="8">
         <f>+SUM(H16:H24)</f>
-        <v>367</v>
+        <v>595</v>
       </c>
       <c r="I25" s="8"/>
     </row>
@@ -6826,14 +6883,14 @@
       </c>
       <c r="D26" s="22">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.23214285714285715</v>
       </c>
       <c r="E26" s="13">
         <v>20</v>
       </c>
       <c r="F26" s="12">
         <f>+H26-E26</f>
-        <v>-12</v>
+        <v>-7</v>
       </c>
       <c r="G26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6841,11 +6898,11 @@
       </c>
       <c r="H26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I26" s="17">
         <f t="shared" si="2"/>
-        <v>39.6</v>
+        <v>34.6</v>
       </c>
       <c r="J26" t="s">
         <v>55</v>
@@ -6865,14 +6922,14 @@
       </c>
       <c r="D27" s="22">
         <f t="shared" si="0"/>
-        <v>0.21153846153846154</v>
+        <v>0.35256410256410259</v>
       </c>
       <c r="E27" s="13">
         <v>68</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" si="1"/>
-        <v>-35</v>
+        <v>-13</v>
       </c>
       <c r="G27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6880,11 +6937,11 @@
       </c>
       <c r="H27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" si="2"/>
-        <v>99.6</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="J27" t="s">
         <v>58</v>
@@ -6904,14 +6961,14 @@
       </c>
       <c r="D28" s="22">
         <f t="shared" si="0"/>
-        <v>0.21739130434782608</v>
+        <v>0.29813664596273293</v>
       </c>
       <c r="E28" s="13">
         <v>80</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" si="1"/>
-        <v>-45</v>
+        <v>-32</v>
       </c>
       <c r="G28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6919,11 +6976,11 @@
       </c>
       <c r="H28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I28" s="17">
         <f t="shared" si="2"/>
-        <v>101.85</v>
+        <v>88.85</v>
       </c>
       <c r="J28" t="s">
         <v>58</v>
@@ -6943,14 +7000,14 @@
       </c>
       <c r="D29" s="22">
         <f t="shared" si="0"/>
-        <v>0.10441767068273092</v>
+        <v>0.1606425702811245</v>
       </c>
       <c r="E29" s="13">
         <v>68</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" si="1"/>
-        <v>-42</v>
+        <v>-28</v>
       </c>
       <c r="G29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6958,11 +7015,11 @@
       </c>
       <c r="H29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" si="2"/>
-        <v>185.65</v>
+        <v>171.65</v>
       </c>
       <c r="J29" t="s">
         <v>58</v>
@@ -6982,14 +7039,14 @@
       </c>
       <c r="D30" s="22">
         <f t="shared" si="0"/>
-        <v>0.23571428571428571</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="E30" s="13">
         <v>73</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" si="1"/>
-        <v>-40</v>
+        <v>-13</v>
       </c>
       <c r="G30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6997,11 +7054,11 @@
       </c>
       <c r="H30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="2"/>
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="J30" t="s">
         <v>55</v>
@@ -7021,14 +7078,14 @@
       </c>
       <c r="D31" s="22">
         <f t="shared" si="0"/>
-        <v>0.17679558011049723</v>
+        <v>0.25966850828729282</v>
       </c>
       <c r="E31" s="13">
         <v>40</v>
       </c>
       <c r="F31" s="12">
         <f t="shared" si="1"/>
-        <v>-8</v>
+        <v>7</v>
       </c>
       <c r="G31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7036,11 +7093,11 @@
       </c>
       <c r="H31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="I31" s="17">
         <f t="shared" si="2"/>
-        <v>121.85</v>
+        <v>106.85</v>
       </c>
       <c r="J31" t="s">
         <v>58</v>
@@ -7060,14 +7117,14 @@
       </c>
       <c r="D32" s="22">
         <f t="shared" si="0"/>
-        <v>0.21428571428571427</v>
+        <v>0.30357142857142855</v>
       </c>
       <c r="E32" s="13">
         <v>67</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>-31</v>
+        <v>-16</v>
       </c>
       <c r="G32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7075,11 +7132,11 @@
       </c>
       <c r="H32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="2"/>
-        <v>106.79999999999998</v>
+        <v>91.799999999999983</v>
       </c>
       <c r="J32" t="s">
         <v>58</v>
@@ -7099,14 +7156,14 @@
       </c>
       <c r="D33" s="22">
         <f t="shared" si="0"/>
-        <v>0.23837209302325582</v>
+        <v>0.34883720930232559</v>
       </c>
       <c r="E33" s="13">
         <v>66</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>-25</v>
+        <v>-6</v>
       </c>
       <c r="G33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7114,11 +7171,11 @@
       </c>
       <c r="H33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="I33" s="17">
         <f t="shared" si="2"/>
-        <v>105.19999999999999</v>
+        <v>86.199999999999989</v>
       </c>
       <c r="J33" t="s">
         <v>58</v>
@@ -7138,26 +7195,26 @@
       </c>
       <c r="D34" s="22">
         <f t="shared" si="0"/>
-        <v>9.2198581560283682E-2</v>
+        <v>0.14788732394366197</v>
       </c>
       <c r="E34" s="13">
         <v>82</v>
       </c>
       <c r="F34" s="12">
         <f t="shared" si="1"/>
-        <v>-69</v>
+        <v>-61</v>
       </c>
       <c r="G34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I34" s="17">
         <f t="shared" si="2"/>
-        <v>106.85</v>
+        <v>99.7</v>
       </c>
       <c r="J34" t="s">
         <v>55</v>
@@ -7177,14 +7234,14 @@
       </c>
       <c r="D35" s="22">
         <f t="shared" si="0"/>
-        <v>0.17415730337078653</v>
+        <v>0.2808988764044944</v>
       </c>
       <c r="E35" s="13">
         <v>81</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" si="1"/>
-        <v>-50</v>
+        <v>-31</v>
       </c>
       <c r="G35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7192,11 +7249,11 @@
       </c>
       <c r="H35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="I35" s="17">
         <f t="shared" si="2"/>
-        <v>120.29999999999998</v>
+        <v>101.29999999999998</v>
       </c>
       <c r="J35" t="s">
         <v>58</v>
@@ -7252,14 +7309,14 @@
       </c>
       <c r="D37" s="22">
         <f t="shared" si="0"/>
-        <v>9.7087378640776691E-3</v>
+        <v>1.9417475728155338E-2</v>
       </c>
       <c r="E37" s="13">
         <v>17</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" si="1"/>
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="G37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7267,11 +7324,11 @@
       </c>
       <c r="H37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="17">
         <f t="shared" si="2"/>
-        <v>86.55</v>
+        <v>85.55</v>
       </c>
       <c r="J37" t="s">
         <v>59</v>
@@ -7288,14 +7345,14 @@
       </c>
       <c r="D38" s="22">
         <f t="shared" si="0"/>
-        <v>0.29133858267716534</v>
+        <v>0.40157480314960631</v>
       </c>
       <c r="E38" s="13">
         <v>60</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="1"/>
-        <v>-23</v>
+        <v>-9</v>
       </c>
       <c r="G38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7303,11 +7360,11 @@
       </c>
       <c r="H38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="I38" s="17">
         <f t="shared" si="2"/>
-        <v>70.95</v>
+        <v>56.95</v>
       </c>
       <c r="J38" t="s">
         <v>55</v>
@@ -7323,15 +7380,15 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8">
         <f>+SUM(F26:F38)</f>
-        <v>-395</v>
+        <v>-223</v>
       </c>
       <c r="G39" s="8">
         <f>+SUM(G26:G38)</f>
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="H39" s="8">
         <f>+SUM(H26:H38)</f>
-        <v>327</v>
+        <v>499</v>
       </c>
       <c r="I39" s="8"/>
       <c r="L39" t="s">
@@ -7347,20 +7404,20 @@
       <c r="E40" s="6"/>
       <c r="F40" s="8">
         <f>+SUM(F39+F25+F15)</f>
-        <v>-1170</v>
+        <v>-532</v>
       </c>
       <c r="G40" s="8">
         <f>+G15+G25+G39</f>
-        <v>5718</v>
+        <v>5723</v>
       </c>
       <c r="H40" s="8">
         <f>+H15+H25+H39</f>
-        <v>1158</v>
+        <v>1796</v>
       </c>
       <c r="I40" s="8"/>
       <c r="L40" s="1">
         <f>+H40/G40</f>
-        <v>0.20251836306400839</v>
+        <v>0.31382142233094529</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -7405,14 +7462,14 @@
       </c>
       <c r="D42" s="22">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4033613445378148E-3</v>
       </c>
       <c r="E42" s="13">
         <v>60</v>
       </c>
       <c r="F42" s="12">
         <f t="shared" si="5"/>
-        <v>-60</v>
+        <v>-59</v>
       </c>
       <c r="G42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7420,11 +7477,11 @@
       </c>
       <c r="H42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="17">
         <f t="shared" si="6"/>
-        <v>101.14999999999999</v>
+        <v>100.14999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -7998,7 +8055,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="51">
         <v>3408</v>
@@ -8006,7 +8063,9 @@
       <c r="G3" t="s">
         <v>222</v>
       </c>
-      <c r="H3" s="51"/>
+      <c r="H3" s="51">
+        <v>1</v>
+      </c>
       <c r="I3" s="51">
         <v>3408</v>
       </c>
@@ -8016,13 +8075,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="51">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C4" s="51">
         <v>127</v>
       </c>
       <c r="G4" t="s">
         <v>223</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
       </c>
       <c r="I4" s="51">
         <v>3408</v>
@@ -8033,7 +8095,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="51">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C5" s="51">
         <v>181</v>
@@ -8051,7 +8113,7 @@
         <v>100</v>
       </c>
       <c r="B6" s="51">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="51">
         <v>2024</v>
@@ -8069,15 +8131,17 @@
         <v>11</v>
       </c>
       <c r="B7" s="51">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C7" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G7" t="s">
         <v>226</v>
       </c>
-      <c r="H7" s="51"/>
+      <c r="H7" s="51">
+        <v>1</v>
+      </c>
       <c r="I7" s="51">
         <v>3408</v>
       </c>
@@ -8087,10 +8151,10 @@
         <v>12</v>
       </c>
       <c r="B8" s="51">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C8" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G8" t="s">
         <v>227</v>
@@ -8107,7 +8171,7 @@
         <v>123</v>
       </c>
       <c r="B9" s="51">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C9" s="51">
         <v>489</v>
@@ -8115,7 +8179,9 @@
       <c r="G9" t="s">
         <v>228</v>
       </c>
-      <c r="H9" s="51"/>
+      <c r="H9" s="51">
+        <v>1</v>
+      </c>
       <c r="I9" s="51">
         <v>3408</v>
       </c>
@@ -8125,13 +8191,16 @@
         <v>15</v>
       </c>
       <c r="B10" s="51">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C10" s="51">
         <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>229</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
       </c>
       <c r="I10" s="51">
         <v>3408</v>
@@ -8142,7 +8211,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="51">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C11" s="51">
         <v>198</v>
@@ -8160,7 +8229,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="51">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C12" s="51">
         <v>177</v>
@@ -8176,7 +8245,7 @@
         <v>222</v>
       </c>
       <c r="H12">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I12" s="51">
         <v>127</v>
@@ -8187,7 +8256,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="51">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="C13" s="51">
         <v>207</v>
@@ -8200,7 +8269,7 @@
         <v>223</v>
       </c>
       <c r="H13" s="51">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I13" s="51">
         <v>127</v>
@@ -8211,7 +8280,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="51">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C14" s="51">
         <v>138</v>
@@ -8224,7 +8293,7 @@
         <v>224</v>
       </c>
       <c r="H14" s="51">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I14" s="51">
         <v>127</v>
@@ -8235,7 +8304,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="51">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="C15" s="51">
         <v>227</v>
@@ -8248,7 +8317,7 @@
         <v>225</v>
       </c>
       <c r="H15" s="51">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I15" s="51">
         <v>127</v>
@@ -8259,7 +8328,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="51">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="C16" s="51">
         <v>170</v>
@@ -8272,7 +8341,7 @@
         <v>226</v>
       </c>
       <c r="H16" s="51">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I16" s="51">
         <v>127</v>
@@ -8283,7 +8352,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="51">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C17" s="51">
         <v>72</v>
@@ -8296,7 +8365,7 @@
         <v>227</v>
       </c>
       <c r="H17" s="51">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="I17" s="51">
         <v>127</v>
@@ -8307,7 +8376,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="51">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="C18" s="51">
         <v>160</v>
@@ -8320,7 +8389,7 @@
         <v>228</v>
       </c>
       <c r="H18" s="51">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I18" s="51">
         <v>127</v>
@@ -8331,7 +8400,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="51">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C19" s="51">
         <v>178</v>
@@ -8344,7 +8413,7 @@
         <v>229</v>
       </c>
       <c r="H19" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I19" s="51">
         <v>127</v>
@@ -8368,7 +8437,7 @@
         <v>230</v>
       </c>
       <c r="H20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I20" s="51">
         <v>127</v>
@@ -8379,7 +8448,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="51">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="51">
         <v>162</v>
@@ -8395,7 +8464,7 @@
         <v>222</v>
       </c>
       <c r="H21" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" s="51">
         <v>181</v>
@@ -8406,7 +8475,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="51">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C22" s="51">
         <v>140</v>
@@ -8418,9 +8487,7 @@
       <c r="G22" t="s">
         <v>223</v>
       </c>
-      <c r="H22" s="51">
-        <v>1</v>
-      </c>
+      <c r="H22" s="51"/>
       <c r="I22" s="51">
         <v>181</v>
       </c>
@@ -8430,7 +8497,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="51">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C23" s="51">
         <v>168</v>
@@ -8443,7 +8510,7 @@
         <v>224</v>
       </c>
       <c r="H23" s="51">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I23" s="51">
         <v>181</v>
@@ -8454,7 +8521,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="51">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="C24" s="51">
         <v>170</v>
@@ -8467,7 +8534,7 @@
         <v>225</v>
       </c>
       <c r="H24" s="51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I24" s="51">
         <v>181</v>
@@ -8478,7 +8545,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C25" s="51">
         <v>138</v>
@@ -8491,7 +8558,7 @@
         <v>226</v>
       </c>
       <c r="H25" s="51">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I25" s="51">
         <v>181</v>
@@ -8502,7 +8569,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="51">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C26" s="51">
         <v>161</v>
@@ -8515,7 +8582,7 @@
         <v>227</v>
       </c>
       <c r="H26" s="51">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I26" s="51">
         <v>181</v>
@@ -8526,7 +8593,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="51">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C27" s="51">
         <v>56</v>
@@ -8539,7 +8606,7 @@
         <v>228</v>
       </c>
       <c r="H27" s="51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I27" s="51">
         <v>181</v>
@@ -8550,7 +8617,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="51">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C28" s="51">
         <v>172</v>
@@ -8563,7 +8630,7 @@
         <v>229</v>
       </c>
       <c r="H28" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="51">
         <v>181</v>
@@ -8574,7 +8641,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="51">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C29" s="51">
         <v>156</v>
@@ -8586,7 +8653,9 @@
       <c r="G29" t="s">
         <v>230</v>
       </c>
-      <c r="H29" s="51"/>
+      <c r="H29" s="51">
+        <v>3</v>
+      </c>
       <c r="I29" s="51">
         <v>181</v>
       </c>
@@ -8596,10 +8665,10 @@
         <v>37</v>
       </c>
       <c r="B30" s="51">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C30" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E30">
         <f>+$F$30</f>
@@ -8612,7 +8681,7 @@
         <v>222</v>
       </c>
       <c r="H30" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I30" s="51">
         <v>2024</v>
@@ -8623,7 +8692,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="51">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C31" s="51">
         <v>182</v>
@@ -8636,7 +8705,7 @@
         <v>223</v>
       </c>
       <c r="H31" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" s="51">
         <v>2024</v>
@@ -8647,7 +8716,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="51">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C32" s="51">
         <v>249</v>
@@ -8682,7 +8751,7 @@
         <v>225</v>
       </c>
       <c r="H33" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" s="51">
         <v>2024</v>
@@ -8704,7 +8773,7 @@
         <v>226</v>
       </c>
       <c r="H34" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I34" s="51">
         <v>2024</v>
@@ -8715,7 +8784,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="51">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C35" s="51">
         <v>169</v>
@@ -8728,7 +8797,7 @@
         <v>227</v>
       </c>
       <c r="H35" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I35" s="51">
         <v>2024</v>
@@ -8739,7 +8808,7 @@
         <v>49</v>
       </c>
       <c r="B36" s="51">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C36" s="51">
         <v>239</v>
@@ -8752,7 +8821,7 @@
         <v>228</v>
       </c>
       <c r="H36" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I36" s="51">
         <v>2024</v>
@@ -8763,7 +8832,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="51">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="C37" s="51">
         <v>260</v>
@@ -8776,7 +8845,7 @@
         <v>229</v>
       </c>
       <c r="H37" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I37" s="51">
         <v>2024</v>
@@ -8787,7 +8856,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="51">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C38" s="51">
         <v>101</v>
@@ -8809,7 +8878,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="51">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C39" s="51">
         <v>105</v>
@@ -8825,10 +8894,10 @@
         <v>222</v>
       </c>
       <c r="H39" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I39" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -8836,7 +8905,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="51">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C40" s="51">
         <v>202</v>
@@ -8848,15 +8917,20 @@
       <c r="G40" t="s">
         <v>223</v>
       </c>
-      <c r="H40" s="51"/>
+      <c r="H40" s="51">
+        <v>3</v>
+      </c>
       <c r="I40" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>56</v>
       </c>
+      <c r="B41">
+        <v>41</v>
+      </c>
       <c r="C41" s="51">
         <v>198</v>
       </c>
@@ -8868,10 +8942,10 @@
         <v>224</v>
       </c>
       <c r="H41" s="51">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I41" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -8879,7 +8953,7 @@
         <v>57</v>
       </c>
       <c r="B42" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" s="51">
         <v>103</v>
@@ -8892,10 +8966,10 @@
         <v>225</v>
       </c>
       <c r="H42" s="51">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I42" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -8914,17 +8988,19 @@
         <v>226</v>
       </c>
       <c r="H43" s="51">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="I43" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>59</v>
       </c>
-      <c r="B44" s="51"/>
+      <c r="B44" s="51">
+        <v>1</v>
+      </c>
       <c r="C44" s="51">
         <v>119</v>
       </c>
@@ -8936,10 +9012,10 @@
         <v>227</v>
       </c>
       <c r="H44" s="51">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I44" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -8960,10 +9036,10 @@
         <v>228</v>
       </c>
       <c r="H45" s="51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I45" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -8971,10 +9047,10 @@
         <v>8</v>
       </c>
       <c r="B46" s="51">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C46" s="51">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E46">
         <f t="shared" si="3"/>
@@ -8987,7 +9063,7 @@
         <v>6</v>
       </c>
       <c r="I46" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -8995,7 +9071,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="51">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C47" s="51">
         <v>161</v>
@@ -9008,10 +9084,10 @@
         <v>230</v>
       </c>
       <c r="H47" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -9028,10 +9104,10 @@
         <v>222</v>
       </c>
       <c r="H48" s="51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I48" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.25">
@@ -9045,10 +9121,10 @@
         <v>223</v>
       </c>
       <c r="H49" s="51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I49" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.25">
@@ -9060,10 +9136,10 @@
         <v>224</v>
       </c>
       <c r="H50" s="51">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I50" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.25">
@@ -9075,10 +9151,10 @@
         <v>225</v>
       </c>
       <c r="H51" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I51" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
@@ -9090,10 +9166,10 @@
         <v>226</v>
       </c>
       <c r="H52" s="51">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I52" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.25">
@@ -9105,10 +9181,10 @@
         <v>227</v>
       </c>
       <c r="H53" s="51">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I53" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
@@ -9123,7 +9199,7 @@
         <v>7</v>
       </c>
       <c r="I54" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
@@ -9135,10 +9211,10 @@
         <v>229</v>
       </c>
       <c r="H55" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I55" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
@@ -9150,10 +9226,10 @@
         <v>230</v>
       </c>
       <c r="H56" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I56" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
@@ -9168,7 +9244,7 @@
         <v>222</v>
       </c>
       <c r="H57" s="51">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I57" s="51">
         <v>489</v>
@@ -9183,7 +9259,7 @@
         <v>223</v>
       </c>
       <c r="H58" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I58" s="51">
         <v>489</v>
@@ -9198,7 +9274,7 @@
         <v>224</v>
       </c>
       <c r="H59" s="51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I59" s="51">
         <v>489</v>
@@ -9226,7 +9302,7 @@
         <v>226</v>
       </c>
       <c r="H61" s="51">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I61" s="51">
         <v>489</v>
@@ -9254,7 +9330,7 @@
         <v>228</v>
       </c>
       <c r="H63" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I63" s="51">
         <v>489</v>
@@ -9268,7 +9344,9 @@
       <c r="G64" t="s">
         <v>229</v>
       </c>
-      <c r="H64" s="51"/>
+      <c r="H64" s="51">
+        <v>1</v>
+      </c>
       <c r="I64" s="51">
         <v>489</v>
       </c>
@@ -9298,7 +9376,7 @@
         <v>222</v>
       </c>
       <c r="H66" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I66" s="51">
         <v>65</v>
@@ -9313,7 +9391,7 @@
         <v>223</v>
       </c>
       <c r="H67" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I67" s="51">
         <v>65</v>
@@ -9328,7 +9406,7 @@
         <v>224</v>
       </c>
       <c r="H68" s="51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I68" s="51">
         <v>65</v>
@@ -9343,7 +9421,7 @@
         <v>225</v>
       </c>
       <c r="H69" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I69" s="51">
         <v>65</v>
@@ -9358,7 +9436,7 @@
         <v>226</v>
       </c>
       <c r="H70" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I70" s="51">
         <v>65</v>
@@ -9373,7 +9451,7 @@
         <v>227</v>
       </c>
       <c r="H71" s="51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I71" s="51">
         <v>65</v>
@@ -9388,7 +9466,7 @@
         <v>228</v>
       </c>
       <c r="H72" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I72" s="51">
         <v>65</v>
@@ -9403,7 +9481,7 @@
         <v>229</v>
       </c>
       <c r="H73" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I73" s="51">
         <v>65</v>
@@ -9436,7 +9514,7 @@
         <v>222</v>
       </c>
       <c r="H75" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I75" s="51">
         <v>198</v>
@@ -9451,7 +9529,7 @@
         <v>223</v>
       </c>
       <c r="H76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I76" s="51">
         <v>198</v>
@@ -9466,7 +9544,7 @@
         <v>224</v>
       </c>
       <c r="H77" s="51">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I77" s="51">
         <v>198</v>
@@ -9481,7 +9559,7 @@
         <v>225</v>
       </c>
       <c r="H78" s="51">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I78" s="51">
         <v>198</v>
@@ -9496,7 +9574,7 @@
         <v>226</v>
       </c>
       <c r="H79" s="51">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I79" s="51">
         <v>198</v>
@@ -9511,7 +9589,7 @@
         <v>227</v>
       </c>
       <c r="H80" s="51">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I80" s="51">
         <v>198</v>
@@ -9541,7 +9619,7 @@
         <v>229</v>
       </c>
       <c r="H82" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I82" s="51">
         <v>198</v>
@@ -9556,7 +9634,7 @@
         <v>230</v>
       </c>
       <c r="H83" s="51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I83" s="51">
         <v>198</v>
@@ -9574,7 +9652,7 @@
         <v>222</v>
       </c>
       <c r="H84" s="51">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I84" s="51">
         <v>177</v>
@@ -9589,7 +9667,7 @@
         <v>223</v>
       </c>
       <c r="H85" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I85" s="51">
         <v>177</v>
@@ -9604,7 +9682,7 @@
         <v>224</v>
       </c>
       <c r="H86" s="51">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I86" s="51">
         <v>177</v>
@@ -9619,7 +9697,7 @@
         <v>225</v>
       </c>
       <c r="H87" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I87" s="51">
         <v>177</v>
@@ -9634,7 +9712,7 @@
         <v>226</v>
       </c>
       <c r="H88" s="51">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="I88" s="51">
         <v>177</v>
@@ -9649,7 +9727,7 @@
         <v>227</v>
       </c>
       <c r="H89" s="51">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I89" s="51">
         <v>177</v>
@@ -9664,7 +9742,7 @@
         <v>228</v>
       </c>
       <c r="H90" s="51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I90" s="51">
         <v>177</v>
@@ -9679,7 +9757,7 @@
         <v>229</v>
       </c>
       <c r="H91" s="51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I91" s="51">
         <v>177</v>
@@ -9694,7 +9772,7 @@
         <v>230</v>
       </c>
       <c r="H92" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I92" s="51">
         <v>177</v>
@@ -9712,7 +9790,7 @@
         <v>222</v>
       </c>
       <c r="H93" s="51">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I93" s="51">
         <v>207</v>
@@ -9727,7 +9805,7 @@
         <v>223</v>
       </c>
       <c r="H94" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I94" s="51">
         <v>207</v>
@@ -9742,7 +9820,7 @@
         <v>224</v>
       </c>
       <c r="H95" s="51">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I95" s="51">
         <v>207</v>
@@ -9757,7 +9835,7 @@
         <v>225</v>
       </c>
       <c r="H96" s="51">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I96" s="51">
         <v>207</v>
@@ -9772,7 +9850,7 @@
         <v>226</v>
       </c>
       <c r="H97" s="51">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="I97" s="51">
         <v>207</v>
@@ -9787,7 +9865,7 @@
         <v>227</v>
       </c>
       <c r="H98" s="51">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I98" s="51">
         <v>207</v>
@@ -9801,7 +9879,9 @@
       <c r="G99" t="s">
         <v>228</v>
       </c>
-      <c r="H99" s="51"/>
+      <c r="H99" s="51">
+        <v>6</v>
+      </c>
       <c r="I99" s="51">
         <v>207</v>
       </c>
@@ -9815,7 +9895,7 @@
         <v>229</v>
       </c>
       <c r="H100" s="51">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I100" s="51">
         <v>207</v>
@@ -9830,7 +9910,7 @@
         <v>230</v>
       </c>
       <c r="H101" s="51">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I101" s="51">
         <v>207</v>
@@ -9848,7 +9928,7 @@
         <v>222</v>
       </c>
       <c r="H102" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I102" s="51">
         <v>138</v>
@@ -9863,7 +9943,7 @@
         <v>223</v>
       </c>
       <c r="H103" s="51">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I103" s="51">
         <v>138</v>
@@ -9878,7 +9958,7 @@
         <v>224</v>
       </c>
       <c r="H104" s="51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I104" s="51">
         <v>138</v>
@@ -9893,7 +9973,7 @@
         <v>225</v>
       </c>
       <c r="H105" s="51">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I105" s="51">
         <v>138</v>
@@ -9908,7 +9988,7 @@
         <v>226</v>
       </c>
       <c r="H106" s="51">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I106" s="51">
         <v>138</v>
@@ -9923,7 +10003,7 @@
         <v>227</v>
       </c>
       <c r="H107" s="51">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I107" s="51">
         <v>138</v>
@@ -9953,7 +10033,7 @@
         <v>229</v>
       </c>
       <c r="H109" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I109" s="51">
         <v>138</v>
@@ -9968,7 +10048,7 @@
         <v>230</v>
       </c>
       <c r="H110" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I110" s="51">
         <v>138</v>
@@ -9986,7 +10066,7 @@
         <v>222</v>
       </c>
       <c r="H111" s="51">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I111" s="51">
         <v>227</v>
@@ -10001,7 +10081,7 @@
         <v>223</v>
       </c>
       <c r="H112" s="51">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I112" s="51">
         <v>227</v>
@@ -10016,7 +10096,7 @@
         <v>224</v>
       </c>
       <c r="H113" s="51">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I113" s="51">
         <v>227</v>
@@ -10031,7 +10111,7 @@
         <v>225</v>
       </c>
       <c r="H114" s="51">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I114" s="51">
         <v>227</v>
@@ -10046,7 +10126,7 @@
         <v>226</v>
       </c>
       <c r="H115" s="51">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="I115" s="51">
         <v>227</v>
@@ -10061,7 +10141,7 @@
         <v>227</v>
       </c>
       <c r="H116">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I116" s="51">
         <v>227</v>
@@ -10076,7 +10156,7 @@
         <v>228</v>
       </c>
       <c r="H117" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I117" s="51">
         <v>227</v>
@@ -10091,7 +10171,7 @@
         <v>229</v>
       </c>
       <c r="H118" s="51">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I118" s="51">
         <v>227</v>
@@ -10106,7 +10186,7 @@
         <v>230</v>
       </c>
       <c r="H119" s="51">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I119" s="51">
         <v>227</v>
@@ -10124,7 +10204,7 @@
         <v>222</v>
       </c>
       <c r="H120" s="51">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I120" s="51">
         <v>170</v>
@@ -10139,7 +10219,7 @@
         <v>223</v>
       </c>
       <c r="H121" s="51">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I121" s="51">
         <v>170</v>
@@ -10154,7 +10234,7 @@
         <v>224</v>
       </c>
       <c r="H122" s="51">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I122" s="51">
         <v>170</v>
@@ -10169,7 +10249,7 @@
         <v>225</v>
       </c>
       <c r="H123" s="51">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I123" s="51">
         <v>170</v>
@@ -10184,7 +10264,7 @@
         <v>226</v>
       </c>
       <c r="H124">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="I124" s="51">
         <v>170</v>
@@ -10199,7 +10279,7 @@
         <v>227</v>
       </c>
       <c r="H125" s="51">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I125" s="51">
         <v>170</v>
@@ -10214,7 +10294,7 @@
         <v>228</v>
       </c>
       <c r="H126" s="51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I126" s="51">
         <v>170</v>
@@ -10229,7 +10309,7 @@
         <v>229</v>
       </c>
       <c r="H127" s="51">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I127" s="51">
         <v>170</v>
@@ -10244,7 +10324,7 @@
         <v>230</v>
       </c>
       <c r="H128" s="51">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I128" s="51">
         <v>170</v>
@@ -10262,7 +10342,7 @@
         <v>222</v>
       </c>
       <c r="H129" s="51">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I129" s="51">
         <v>72</v>
@@ -10277,7 +10357,7 @@
         <v>223</v>
       </c>
       <c r="H130" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I130" s="51">
         <v>72</v>
@@ -10292,7 +10372,7 @@
         <v>224</v>
       </c>
       <c r="H131" s="51">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I131" s="51">
         <v>72</v>
@@ -10307,7 +10387,7 @@
         <v>225</v>
       </c>
       <c r="H132" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I132" s="51">
         <v>72</v>
@@ -10322,7 +10402,7 @@
         <v>226</v>
       </c>
       <c r="H133" s="51">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I133" s="51">
         <v>72</v>
@@ -10352,7 +10432,7 @@
         <v>228</v>
       </c>
       <c r="H135" s="51">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I135" s="51">
         <v>72</v>
@@ -10367,7 +10447,7 @@
         <v>229</v>
       </c>
       <c r="H136" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I136" s="51">
         <v>72</v>
@@ -10382,7 +10462,7 @@
         <v>230</v>
       </c>
       <c r="H137" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I137" s="51">
         <v>72</v>
@@ -10400,7 +10480,7 @@
         <v>222</v>
       </c>
       <c r="H138" s="51">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I138" s="51">
         <v>160</v>
@@ -10415,7 +10495,7 @@
         <v>223</v>
       </c>
       <c r="H139" s="51">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I139" s="51">
         <v>160</v>
@@ -10430,7 +10510,7 @@
         <v>224</v>
       </c>
       <c r="H140">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I140" s="51">
         <v>160</v>
@@ -10445,7 +10525,7 @@
         <v>225</v>
       </c>
       <c r="H141" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I141" s="51">
         <v>160</v>
@@ -10460,7 +10540,7 @@
         <v>226</v>
       </c>
       <c r="H142" s="51">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="I142" s="51">
         <v>160</v>
@@ -10475,7 +10555,7 @@
         <v>227</v>
       </c>
       <c r="H143" s="51">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="I143" s="51">
         <v>160</v>
@@ -10490,7 +10570,7 @@
         <v>228</v>
       </c>
       <c r="H144" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I144" s="51">
         <v>160</v>
@@ -10505,7 +10585,7 @@
         <v>229</v>
       </c>
       <c r="H145" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I145" s="51">
         <v>160</v>
@@ -10520,7 +10600,7 @@
         <v>230</v>
       </c>
       <c r="H146" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I146" s="51">
         <v>160</v>
@@ -10538,7 +10618,7 @@
         <v>222</v>
       </c>
       <c r="H147" s="51">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I147" s="51">
         <v>178</v>
@@ -10553,7 +10633,7 @@
         <v>223</v>
       </c>
       <c r="H148">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I148" s="51">
         <v>178</v>
@@ -10568,7 +10648,7 @@
         <v>224</v>
       </c>
       <c r="H149" s="51">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I149" s="51">
         <v>178</v>
@@ -10583,7 +10663,7 @@
         <v>225</v>
       </c>
       <c r="H150" s="51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I150" s="51">
         <v>178</v>
@@ -10598,7 +10678,7 @@
         <v>226</v>
       </c>
       <c r="H151" s="51">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I151" s="51">
         <v>178</v>
@@ -10613,7 +10693,7 @@
         <v>227</v>
       </c>
       <c r="H152" s="51">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I152" s="51">
         <v>178</v>
@@ -10628,7 +10708,7 @@
         <v>228</v>
       </c>
       <c r="H153" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I153" s="51">
         <v>178</v>
@@ -10642,7 +10722,9 @@
       <c r="G154" t="s">
         <v>229</v>
       </c>
-      <c r="H154" s="51"/>
+      <c r="H154" s="51">
+        <v>5</v>
+      </c>
       <c r="I154" s="51">
         <v>178</v>
       </c>
@@ -10842,7 +10924,7 @@
         <v>224</v>
       </c>
       <c r="H167" s="51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I167" s="51">
         <v>162</v>
@@ -10902,7 +10984,7 @@
         <v>228</v>
       </c>
       <c r="H171" s="51">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I171" s="51">
         <v>162</v>
@@ -10950,7 +11032,7 @@
         <v>222</v>
       </c>
       <c r="H174" s="51">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I174" s="51">
         <v>140</v>
@@ -10965,7 +11047,7 @@
         <v>223</v>
       </c>
       <c r="H175" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I175" s="51">
         <v>140</v>
@@ -10980,7 +11062,7 @@
         <v>224</v>
       </c>
       <c r="H176" s="51">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I176" s="51">
         <v>140</v>
@@ -10995,7 +11077,7 @@
         <v>225</v>
       </c>
       <c r="H177" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I177" s="51">
         <v>140</v>
@@ -11010,7 +11092,7 @@
         <v>226</v>
       </c>
       <c r="H178" s="51">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="I178" s="51">
         <v>140</v>
@@ -11025,7 +11107,7 @@
         <v>227</v>
       </c>
       <c r="H179" s="51">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I179" s="51">
         <v>140</v>
@@ -11040,7 +11122,7 @@
         <v>228</v>
       </c>
       <c r="H180">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I180" s="51">
         <v>140</v>
@@ -11055,7 +11137,7 @@
         <v>229</v>
       </c>
       <c r="H181" s="51">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I181" s="51">
         <v>140</v>
@@ -11070,7 +11152,7 @@
         <v>230</v>
       </c>
       <c r="H182" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I182" s="51">
         <v>140</v>
@@ -11088,7 +11170,7 @@
         <v>222</v>
       </c>
       <c r="H183" s="51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I183" s="51">
         <v>168</v>
@@ -11103,7 +11185,7 @@
         <v>223</v>
       </c>
       <c r="H184" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I184" s="51">
         <v>168</v>
@@ -11118,7 +11200,7 @@
         <v>224</v>
       </c>
       <c r="H185" s="51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I185" s="51">
         <v>168</v>
@@ -11133,7 +11215,7 @@
         <v>225</v>
       </c>
       <c r="H186">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I186" s="51">
         <v>168</v>
@@ -11148,7 +11230,7 @@
         <v>226</v>
       </c>
       <c r="H187" s="51">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I187" s="51">
         <v>168</v>
@@ -11163,7 +11245,7 @@
         <v>227</v>
       </c>
       <c r="H188" s="51">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I188" s="51">
         <v>168</v>
@@ -11193,7 +11275,7 @@
         <v>229</v>
       </c>
       <c r="H190" s="51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I190" s="51">
         <v>168</v>
@@ -11226,7 +11308,7 @@
         <v>222</v>
       </c>
       <c r="H192" s="51">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I192" s="51">
         <v>170</v>
@@ -11241,7 +11323,7 @@
         <v>223</v>
       </c>
       <c r="H193" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I193" s="51">
         <v>170</v>
@@ -11256,7 +11338,7 @@
         <v>224</v>
       </c>
       <c r="H194" s="51">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I194" s="51">
         <v>170</v>
@@ -11271,7 +11353,7 @@
         <v>225</v>
       </c>
       <c r="H195" s="51">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I195" s="51">
         <v>170</v>
@@ -11286,7 +11368,7 @@
         <v>226</v>
       </c>
       <c r="H196">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="I196" s="51">
         <v>170</v>
@@ -11301,7 +11383,7 @@
         <v>227</v>
       </c>
       <c r="H197" s="51">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="I197" s="51">
         <v>170</v>
@@ -11316,7 +11398,7 @@
         <v>228</v>
       </c>
       <c r="H198" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I198" s="51">
         <v>170</v>
@@ -11346,7 +11428,7 @@
         <v>230</v>
       </c>
       <c r="H200" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I200" s="51">
         <v>170</v>
@@ -11364,7 +11446,7 @@
         <v>222</v>
       </c>
       <c r="H201" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I201" s="51">
         <v>138</v>
@@ -11392,7 +11474,7 @@
         <v>224</v>
       </c>
       <c r="H203" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I203" s="51">
         <v>138</v>
@@ -11419,7 +11501,9 @@
       <c r="G205" t="s">
         <v>226</v>
       </c>
-      <c r="H205" s="51"/>
+      <c r="H205" s="51">
+        <v>3</v>
+      </c>
       <c r="I205" s="51">
         <v>138</v>
       </c>
@@ -11445,7 +11529,9 @@
       <c r="G207" t="s">
         <v>228</v>
       </c>
-      <c r="H207" s="51"/>
+      <c r="H207" s="51">
+        <v>2</v>
+      </c>
       <c r="I207" s="51">
         <v>138</v>
       </c>
@@ -11488,7 +11574,7 @@
         <v>222</v>
       </c>
       <c r="H210" s="51">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I210" s="51">
         <v>161</v>
@@ -11503,7 +11589,7 @@
         <v>223</v>
       </c>
       <c r="H211" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I211" s="51">
         <v>161</v>
@@ -11518,7 +11604,7 @@
         <v>224</v>
       </c>
       <c r="H212">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I212" s="51">
         <v>161</v>
@@ -11533,7 +11619,7 @@
         <v>225</v>
       </c>
       <c r="H213" s="51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I213" s="51">
         <v>161</v>
@@ -11548,7 +11634,7 @@
         <v>226</v>
       </c>
       <c r="H214" s="51">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I214" s="51">
         <v>161</v>
@@ -11563,7 +11649,7 @@
         <v>227</v>
       </c>
       <c r="H215" s="51">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I215" s="51">
         <v>161</v>
@@ -11593,7 +11679,7 @@
         <v>229</v>
       </c>
       <c r="H217" s="51">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I217" s="51">
         <v>161</v>
@@ -11608,7 +11694,7 @@
         <v>230</v>
       </c>
       <c r="H218" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I218" s="51">
         <v>161</v>
@@ -11626,7 +11712,7 @@
         <v>222</v>
       </c>
       <c r="H219" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I219" s="51">
         <v>56</v>
@@ -11656,7 +11742,7 @@
         <v>224</v>
       </c>
       <c r="H221" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I221" s="51">
         <v>56</v>
@@ -11671,7 +11757,7 @@
         <v>225</v>
       </c>
       <c r="H222" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I222" s="51">
         <v>56</v>
@@ -11686,7 +11772,7 @@
         <v>226</v>
       </c>
       <c r="H223" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I223" s="51">
         <v>56</v>
@@ -11701,7 +11787,7 @@
         <v>227</v>
       </c>
       <c r="H224" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I224" s="51">
         <v>56</v>
@@ -11716,7 +11802,7 @@
         <v>228</v>
       </c>
       <c r="H225" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I225" s="51">
         <v>56</v>
@@ -11731,7 +11817,7 @@
         <v>229</v>
       </c>
       <c r="H226" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I226" s="51">
         <v>56</v>
@@ -11746,7 +11832,7 @@
         <v>230</v>
       </c>
       <c r="H227" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I227" s="51">
         <v>56</v>
@@ -11764,7 +11850,7 @@
         <v>222</v>
       </c>
       <c r="H228" s="51">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I228" s="51">
         <v>172</v>
@@ -11779,7 +11865,7 @@
         <v>223</v>
       </c>
       <c r="H229" s="51">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I229" s="51">
         <v>172</v>
@@ -11794,7 +11880,7 @@
         <v>224</v>
       </c>
       <c r="H230" s="51">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I230" s="51">
         <v>172</v>
@@ -11809,7 +11895,7 @@
         <v>225</v>
       </c>
       <c r="H231" s="51">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I231" s="51">
         <v>172</v>
@@ -11824,7 +11910,7 @@
         <v>226</v>
       </c>
       <c r="H232" s="51">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I232" s="51">
         <v>172</v>
@@ -11839,7 +11925,7 @@
         <v>227</v>
       </c>
       <c r="H233" s="51">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I233" s="51">
         <v>172</v>
@@ -11869,7 +11955,7 @@
         <v>229</v>
       </c>
       <c r="H235" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I235" s="51">
         <v>172</v>
@@ -11884,7 +11970,7 @@
         <v>230</v>
       </c>
       <c r="H236">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I236" s="51">
         <v>172</v>
@@ -11902,7 +11988,7 @@
         <v>222</v>
       </c>
       <c r="H237" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I237" s="51">
         <v>156</v>
@@ -11932,7 +12018,7 @@
         <v>224</v>
       </c>
       <c r="H239" s="51">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I239" s="51">
         <v>156</v>
@@ -11947,7 +12033,7 @@
         <v>225</v>
       </c>
       <c r="H240" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I240" s="51">
         <v>156</v>
@@ -11962,7 +12048,7 @@
         <v>226</v>
       </c>
       <c r="H241" s="51">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I241" s="51">
         <v>156</v>
@@ -11977,7 +12063,7 @@
         <v>227</v>
       </c>
       <c r="H242" s="51">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I242" s="51">
         <v>156</v>
@@ -11992,7 +12078,7 @@
         <v>228</v>
       </c>
       <c r="H243" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I243" s="51">
         <v>156</v>
@@ -12007,7 +12093,7 @@
         <v>229</v>
       </c>
       <c r="H244">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I244" s="51">
         <v>156</v>
@@ -12021,7 +12107,9 @@
       <c r="G245" t="s">
         <v>230</v>
       </c>
-      <c r="H245" s="51"/>
+      <c r="H245" s="51">
+        <v>2</v>
+      </c>
       <c r="I245" s="51">
         <v>156</v>
       </c>
@@ -12038,10 +12126,10 @@
         <v>222</v>
       </c>
       <c r="H246" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I246" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="247" spans="5:9" x14ac:dyDescent="0.25">
@@ -12052,9 +12140,11 @@
       <c r="G247" t="s">
         <v>223</v>
       </c>
-      <c r="H247" s="51"/>
+      <c r="H247" s="51">
+        <v>2</v>
+      </c>
       <c r="I247" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="248" spans="5:9" x14ac:dyDescent="0.25">
@@ -12066,10 +12156,10 @@
         <v>224</v>
       </c>
       <c r="H248" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I248" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="249" spans="5:9" x14ac:dyDescent="0.25">
@@ -12080,9 +12170,11 @@
       <c r="G249" t="s">
         <v>225</v>
       </c>
-      <c r="H249" s="51"/>
+      <c r="H249" s="51">
+        <v>4</v>
+      </c>
       <c r="I249" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="250" spans="5:9" x14ac:dyDescent="0.25">
@@ -12094,10 +12186,10 @@
         <v>226</v>
       </c>
       <c r="H250" s="51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I250" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="251" spans="5:9" x14ac:dyDescent="0.25">
@@ -12109,10 +12201,10 @@
         <v>227</v>
       </c>
       <c r="H251" s="51">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I251" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="252" spans="5:9" x14ac:dyDescent="0.25">
@@ -12124,10 +12216,10 @@
         <v>228</v>
       </c>
       <c r="H252">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I252" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="253" spans="5:9" x14ac:dyDescent="0.25">
@@ -12139,10 +12231,10 @@
         <v>229</v>
       </c>
       <c r="H253" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I253" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="254" spans="5:9" x14ac:dyDescent="0.25">
@@ -12153,9 +12245,11 @@
       <c r="G254" t="s">
         <v>230</v>
       </c>
-      <c r="H254" s="51"/>
+      <c r="H254" s="51">
+        <v>3</v>
+      </c>
       <c r="I254" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="255" spans="5:9" x14ac:dyDescent="0.25">
@@ -12170,7 +12264,7 @@
         <v>222</v>
       </c>
       <c r="H255" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I255" s="51">
         <v>182</v>
@@ -12185,7 +12279,7 @@
         <v>223</v>
       </c>
       <c r="H256" s="51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I256" s="51">
         <v>182</v>
@@ -12200,7 +12294,7 @@
         <v>224</v>
       </c>
       <c r="H257" s="51">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I257" s="51">
         <v>182</v>
@@ -12215,7 +12309,7 @@
         <v>225</v>
       </c>
       <c r="H258">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I258" s="51">
         <v>182</v>
@@ -12230,7 +12324,7 @@
         <v>226</v>
       </c>
       <c r="H259" s="51">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I259" s="51">
         <v>182</v>
@@ -12245,7 +12339,7 @@
         <v>227</v>
       </c>
       <c r="H260">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I260" s="51">
         <v>182</v>
@@ -12260,7 +12354,7 @@
         <v>228</v>
       </c>
       <c r="H261" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I261" s="51">
         <v>182</v>
@@ -12275,7 +12369,7 @@
         <v>229</v>
       </c>
       <c r="H262" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I262" s="51">
         <v>182</v>
@@ -12290,7 +12384,7 @@
         <v>230</v>
       </c>
       <c r="H263" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I263" s="51">
         <v>182</v>
@@ -12308,7 +12402,7 @@
         <v>222</v>
       </c>
       <c r="H264" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I264" s="51">
         <v>249</v>
@@ -12338,7 +12432,7 @@
         <v>224</v>
       </c>
       <c r="H266" s="51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I266" s="51">
         <v>249</v>
@@ -12353,7 +12447,7 @@
         <v>225</v>
       </c>
       <c r="H267" s="51">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I267" s="51">
         <v>249</v>
@@ -12368,7 +12462,7 @@
         <v>226</v>
       </c>
       <c r="H268">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I268" s="51">
         <v>249</v>
@@ -12383,7 +12477,7 @@
         <v>227</v>
       </c>
       <c r="H269" s="51">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I269" s="51">
         <v>249</v>
@@ -12413,7 +12507,7 @@
         <v>229</v>
       </c>
       <c r="H271" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I271" s="51">
         <v>249</v>
@@ -12428,7 +12522,7 @@
         <v>230</v>
       </c>
       <c r="H272" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I272" s="51">
         <v>249</v>
@@ -12679,7 +12773,7 @@
         <v>222</v>
       </c>
       <c r="H291">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I291" s="51">
         <v>169</v>
@@ -12694,7 +12788,7 @@
         <v>223</v>
       </c>
       <c r="H292">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I292" s="51">
         <v>169</v>
@@ -12709,7 +12803,7 @@
         <v>224</v>
       </c>
       <c r="H293">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I293" s="51">
         <v>169</v>
@@ -12724,7 +12818,7 @@
         <v>225</v>
       </c>
       <c r="H294">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I294" s="51">
         <v>169</v>
@@ -12739,7 +12833,7 @@
         <v>226</v>
       </c>
       <c r="H295">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="I295" s="51">
         <v>169</v>
@@ -12754,7 +12848,7 @@
         <v>227</v>
       </c>
       <c r="H296">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I296" s="51">
         <v>169</v>
@@ -12769,7 +12863,7 @@
         <v>228</v>
       </c>
       <c r="H297" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I297" s="51">
         <v>169</v>
@@ -12799,7 +12893,7 @@
         <v>230</v>
       </c>
       <c r="H299" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I299" s="51">
         <v>169</v>
@@ -12847,7 +12941,7 @@
         <v>224</v>
       </c>
       <c r="H302" s="51">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I302" s="51">
         <v>239</v>
@@ -12877,7 +12971,7 @@
         <v>226</v>
       </c>
       <c r="H304" s="51">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I304" s="51">
         <v>239</v>
@@ -12955,7 +13049,7 @@
         <v>222</v>
       </c>
       <c r="H309">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I309" s="51">
         <v>260</v>
@@ -12970,7 +13064,7 @@
         <v>223</v>
       </c>
       <c r="H310">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I310" s="51">
         <v>260</v>
@@ -12985,7 +13079,7 @@
         <v>224</v>
       </c>
       <c r="H311">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I311" s="51">
         <v>260</v>
@@ -13000,7 +13094,7 @@
         <v>225</v>
       </c>
       <c r="H312">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I312" s="51">
         <v>260</v>
@@ -13015,7 +13109,7 @@
         <v>226</v>
       </c>
       <c r="H313">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="I313" s="51">
         <v>260</v>
@@ -13030,7 +13124,7 @@
         <v>227</v>
       </c>
       <c r="H314">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I314" s="51">
         <v>260</v>
@@ -13045,7 +13139,7 @@
         <v>228</v>
       </c>
       <c r="H315" s="51">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I315" s="51">
         <v>260</v>
@@ -13060,7 +13154,7 @@
         <v>229</v>
       </c>
       <c r="H316">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I316" s="51">
         <v>260</v>
@@ -13075,7 +13169,7 @@
         <v>230</v>
       </c>
       <c r="H317" s="51">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I317" s="51">
         <v>260</v>
@@ -13107,7 +13201,9 @@
       <c r="G319" t="s">
         <v>223</v>
       </c>
-      <c r="H319" s="51"/>
+      <c r="H319" s="51">
+        <v>1</v>
+      </c>
       <c r="I319" s="51">
         <v>101</v>
       </c>
@@ -13172,7 +13268,7 @@
         <v>228</v>
       </c>
       <c r="H324" s="51">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I324" s="51">
         <v>101</v>
@@ -13290,7 +13386,7 @@
         <v>228</v>
       </c>
       <c r="H333" s="51">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I333" s="51">
         <v>105</v>
@@ -13334,7 +13430,7 @@
         <v>222</v>
       </c>
       <c r="H336" s="51">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I336" s="51">
         <v>202</v>
@@ -13349,7 +13445,7 @@
         <v>223</v>
       </c>
       <c r="H337" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I337" s="51">
         <v>202</v>
@@ -13364,7 +13460,7 @@
         <v>224</v>
       </c>
       <c r="H338" s="51">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I338" s="51">
         <v>202</v>
@@ -13379,7 +13475,7 @@
         <v>225</v>
       </c>
       <c r="H339" s="51">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I339" s="51">
         <v>202</v>
@@ -13394,7 +13490,7 @@
         <v>226</v>
       </c>
       <c r="H340">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I340" s="51">
         <v>202</v>
@@ -13409,7 +13505,7 @@
         <v>227</v>
       </c>
       <c r="H341" s="51">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I341" s="51">
         <v>202</v>
@@ -13424,7 +13520,7 @@
         <v>228</v>
       </c>
       <c r="H342" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I342" s="51">
         <v>202</v>
@@ -13439,7 +13535,7 @@
         <v>229</v>
       </c>
       <c r="H343" s="51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I343" s="51">
         <v>202</v>
@@ -13454,7 +13550,7 @@
         <v>230</v>
       </c>
       <c r="H344" s="51">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I344" s="51">
         <v>202</v>
@@ -13471,6 +13567,9 @@
       <c r="G345" t="s">
         <v>222</v>
       </c>
+      <c r="H345">
+        <v>6</v>
+      </c>
       <c r="I345" s="51">
         <v>198</v>
       </c>
@@ -13483,7 +13582,9 @@
       <c r="G346" t="s">
         <v>223</v>
       </c>
-      <c r="H346" s="51"/>
+      <c r="H346" s="51">
+        <v>8</v>
+      </c>
       <c r="I346" s="51">
         <v>198</v>
       </c>
@@ -13496,7 +13597,9 @@
       <c r="G347" t="s">
         <v>224</v>
       </c>
-      <c r="H347" s="51"/>
+      <c r="H347" s="51">
+        <v>17</v>
+      </c>
       <c r="I347" s="51">
         <v>198</v>
       </c>
@@ -13509,6 +13612,9 @@
       <c r="G348" t="s">
         <v>225</v>
       </c>
+      <c r="H348">
+        <v>6</v>
+      </c>
       <c r="I348" s="51">
         <v>198</v>
       </c>
@@ -13521,7 +13627,9 @@
       <c r="G349" t="s">
         <v>226</v>
       </c>
-      <c r="H349" s="51"/>
+      <c r="H349" s="51">
+        <v>14</v>
+      </c>
       <c r="I349" s="51">
         <v>198</v>
       </c>
@@ -13534,7 +13642,9 @@
       <c r="G350" t="s">
         <v>227</v>
       </c>
-      <c r="H350" s="51"/>
+      <c r="H350" s="51">
+        <v>6</v>
+      </c>
       <c r="I350" s="51">
         <v>198</v>
       </c>
@@ -13547,7 +13657,9 @@
       <c r="G351" t="s">
         <v>228</v>
       </c>
-      <c r="H351" s="51"/>
+      <c r="H351" s="51">
+        <v>18</v>
+      </c>
       <c r="I351" s="51">
         <v>198</v>
       </c>
@@ -13560,6 +13672,9 @@
       <c r="G352" t="s">
         <v>229</v>
       </c>
+      <c r="H352">
+        <v>4</v>
+      </c>
       <c r="I352" s="51">
         <v>198</v>
       </c>
@@ -13572,7 +13687,9 @@
       <c r="G353" t="s">
         <v>230</v>
       </c>
-      <c r="H353" s="51"/>
+      <c r="H353" s="51">
+        <v>2</v>
+      </c>
       <c r="I353" s="51">
         <v>198</v>
       </c>
@@ -13667,7 +13784,7 @@
         <v>228</v>
       </c>
       <c r="H360" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I360" s="51">
         <v>103</v>
@@ -13842,6 +13959,9 @@
       <c r="G373" t="s">
         <v>223</v>
       </c>
+      <c r="H373">
+        <v>1</v>
+      </c>
       <c r="I373">
         <v>119</v>
       </c>
@@ -14065,10 +14185,10 @@
         <v>222</v>
       </c>
       <c r="H390">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I390">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="391" spans="5:9" x14ac:dyDescent="0.25">
@@ -14079,8 +14199,11 @@
       <c r="G391" t="s">
         <v>223</v>
       </c>
+      <c r="H391">
+        <v>3</v>
+      </c>
       <c r="I391">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="392" spans="5:9" x14ac:dyDescent="0.25">
@@ -14092,10 +14215,10 @@
         <v>224</v>
       </c>
       <c r="H392">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I392">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="393" spans="5:9" x14ac:dyDescent="0.25">
@@ -14107,10 +14230,10 @@
         <v>225</v>
       </c>
       <c r="H393">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I393">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="394" spans="5:9" x14ac:dyDescent="0.25">
@@ -14122,10 +14245,10 @@
         <v>226</v>
       </c>
       <c r="H394">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="I394">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="395" spans="5:9" x14ac:dyDescent="0.25">
@@ -14137,10 +14260,10 @@
         <v>227</v>
       </c>
       <c r="H395">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I395">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="396" spans="5:9" x14ac:dyDescent="0.25">
@@ -14152,10 +14275,10 @@
         <v>228</v>
       </c>
       <c r="H396">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I396">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="397" spans="5:9" x14ac:dyDescent="0.25">
@@ -14167,10 +14290,10 @@
         <v>229</v>
       </c>
       <c r="H397">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I397">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="398" spans="5:9" x14ac:dyDescent="0.25">
@@ -14182,10 +14305,10 @@
         <v>230</v>
       </c>
       <c r="H398">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I398">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="399" spans="5:9" x14ac:dyDescent="0.25">
@@ -14200,7 +14323,7 @@
         <v>222</v>
       </c>
       <c r="H399">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I399">
         <v>161</v>
@@ -14215,7 +14338,7 @@
         <v>223</v>
       </c>
       <c r="H400">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I400">
         <v>161</v>
@@ -14230,7 +14353,7 @@
         <v>224</v>
       </c>
       <c r="H401">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I401">
         <v>161</v>
@@ -14245,7 +14368,7 @@
         <v>225</v>
       </c>
       <c r="H402">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I402">
         <v>161</v>
@@ -14260,7 +14383,7 @@
         <v>226</v>
       </c>
       <c r="H403">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I403">
         <v>161</v>
@@ -14275,7 +14398,7 @@
         <v>227</v>
       </c>
       <c r="H404">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I404">
         <v>161</v>
@@ -14305,7 +14428,7 @@
         <v>229</v>
       </c>
       <c r="H406">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I406">
         <v>161</v>
@@ -14320,7 +14443,7 @@
         <v>230</v>
       </c>
       <c r="H407">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I407">
         <v>161</v>
